--- a/docs/Today_PoohPoints_SEC_ByOwner_2026-03-07.xlsx
+++ b/docs/Today_PoohPoints_SEC_ByOwner_2026-03-07.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V37"/>
+  <dimension ref="A1:V53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -428,8 +428,8 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
     <col width="6" customWidth="1" min="8" max="8"/>
     <col width="5" customWidth="1" min="9" max="9"/>
     <col width="5" customWidth="1" min="10" max="10"/>
@@ -592,11 +592,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>4:46 - 2nd Half</t>
+          <t>1:31 - OT</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I2" t="n">
         <v>10</v>
@@ -617,22 +617,22 @@
         <v>2</v>
       </c>
       <c r="O2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P2" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="Q2" t="n">
         <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
         <v>2</v>
@@ -674,41 +674,41 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>10:49 - 2nd Half</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N3" t="n">
         <v>3</v>
       </c>
-      <c r="J3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>2</v>
-      </c>
-      <c r="N3" t="n">
-        <v>1</v>
-      </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -741,32 +741,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Jacob Crews</t>
+          <t>Devin McGlockton</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>4:46 - 2nd Half</t>
+          <t>10:27 - 1st Half</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -781,13 +781,13 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
@@ -796,7 +796,7 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -813,22 +813,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Backslashers</t>
+          <t>Boozers Losers</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Trevon Brazile</t>
+          <t>Jacob Crews</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ARK</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -838,53 +838,53 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4:46 - 2nd Half</t>
+          <t>1:31 - OT</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="Q5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -905,68 +905,68 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Meechie Johnson</t>
+          <t>Trevon Brazile</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ARK</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>1:31 - OT</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>7</v>
+      </c>
+      <c r="R6" t="n">
+        <v>13</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
         <v>3</v>
       </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>5</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2</v>
-      </c>
       <c r="U6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -982,73 +982,73 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Meleek Thomas</t>
+          <t>Meechie Johnson</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ARK</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4:46 - 2nd Half</t>
+          <t>10:49 - 2nd Half</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="I7" t="n">
+        <v>9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" t="n">
         <v>25</v>
       </c>
-      <c r="J7" t="n">
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
         <v>7</v>
       </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
         <v>3</v>
       </c>
-      <c r="P7" t="n">
-        <v>35</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>8</v>
-      </c>
-      <c r="R7" t="n">
-        <v>19</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>5</v>
-      </c>
       <c r="U7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -1064,73 +1064,73 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Malik Dia</t>
+          <t>Ja'Kobi Gillespie</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>10:27 - 1st Half</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>11</v>
+        <v>-4</v>
       </c>
       <c r="I8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1141,22 +1141,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hilton Heads</t>
+          <t>The Backslashers</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mark Mitchell</t>
+          <t>Meleek Thomas</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>ARK</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1166,50 +1166,50 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4:46 - 2nd Half</t>
+          <t>1:31 - OT</t>
         </is>
       </c>
       <c r="H9" t="n">
+        <v>23</v>
+      </c>
+      <c r="I9" t="n">
+        <v>28</v>
+      </c>
+      <c r="J9" t="n">
+        <v>7</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3</v>
+      </c>
+      <c r="P9" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>9</v>
+      </c>
+      <c r="R9" t="n">
         <v>22</v>
       </c>
-      <c r="I9" t="n">
-        <v>25</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>2</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>33</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>10</v>
-      </c>
-      <c r="R9" t="n">
-        <v>16</v>
-      </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V9" t="n">
         <v>6</v>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Hilton Heads</t>
+          <t>The Backslashers</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Ilias Kamardine</t>
+          <t>Malik Dia</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1248,41 +1248,41 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>10:49 - 2nd Half</t>
         </is>
       </c>
       <c r="H10" t="n">
+        <v>13</v>
+      </c>
+      <c r="I10" t="n">
+        <v>14</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
         <v>3</v>
       </c>
-      <c r="I10" t="n">
-        <v>2</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>2</v>
-      </c>
       <c r="P10" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1291,10 +1291,10 @@
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -1305,78 +1305,78 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Three Dawg Nite</t>
+          <t>The Backslashers</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Jayden Stone</t>
+          <t>Felix Okpara</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4:46 - 2nd Half</t>
+          <t>10:27 - 1st Half</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" t="n">
         <v>6</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>3</v>
-      </c>
-      <c r="O11" t="n">
-        <v>2</v>
-      </c>
-      <c r="P11" t="n">
-        <v>25</v>
-      </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Three Dawg Nite</t>
+          <t>Hilton Heads</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1397,68 +1397,68 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>AJ Storr</t>
+          <t>Mark Mitchell</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>1:31 - OT</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="I12" t="n">
+        <v>32</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>11</v>
+      </c>
+      <c r="R12" t="n">
+        <v>20</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
         <v>9</v>
       </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>4</v>
-      </c>
-      <c r="R12" t="n">
-        <v>7</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1</v>
-      </c>
       <c r="V12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
@@ -1469,78 +1469,78 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Three Dawg Nite</t>
+          <t>Hilton Heads</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Anthony Robinson II</t>
+          <t>Tyler Nickel</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4:46 - 2nd Half</t>
+          <t>10:27 - 1st Half</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>10</v>
+        <v>-2</v>
       </c>
       <c r="I13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Three Dawg Nite</t>
+          <t>Hilton Heads</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Myles Stute</t>
+          <t>Ilias Kamardine</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1576,47 +1576,47 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>10:49 - 2nd Half</t>
         </is>
       </c>
       <c r="H14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
         <v>3</v>
       </c>
-      <c r="I14" t="n">
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
         <v>3</v>
       </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2</v>
-      </c>
       <c r="P14" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -1638,17 +1638,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Nick Pringle</t>
+          <t>Jayden Stone</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ARK</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1658,53 +1658,53 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4:46 - 2nd Half</t>
+          <t>1:31 - OT</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P15" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1715,22 +1715,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>G-Flop</t>
+          <t>Three Dawg Nite</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Kobe Knox</t>
+          <t>AJ Storr</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1740,17 +1740,17 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>10:49 - 2nd Half</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I16" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1768,25 +1768,25 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="Q16" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V16" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1797,45 +1797,45 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The Oddities</t>
+          <t>Three Dawg Nite</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Mike Sharavjamts</t>
+          <t>Anthony Robinson II</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>1:31 - OT</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J17" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L17" t="n">
         <v>1</v>
@@ -1844,16 +1844,16 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P17" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="Q17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
         <v>4</v>
@@ -1862,13 +1862,13 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Undrafted</t>
+          <t>Three Dawg Nite</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1889,32 +1889,32 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Shawn Phillips Jr.</t>
+          <t>Myles Stute</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4:46 - 2nd Half</t>
+          <t>10:49 - 2nd Half</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I18" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J18" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1923,34 +1923,34 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
+        <v>2</v>
+      </c>
+      <c r="P18" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2</v>
+      </c>
+      <c r="R18" t="n">
         <v>3</v>
       </c>
-      <c r="P18" t="n">
-        <v>28</v>
-      </c>
-      <c r="Q18" t="n">
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
         <v>3</v>
       </c>
-      <c r="R18" t="n">
-        <v>6</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
       <c r="U18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Undrafted</t>
+          <t>Three Dawg Nite</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1971,62 +1971,62 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Nordin Kapic</t>
+          <t>Nick Pringle</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ARK</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>1:31 - OT</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="I19" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Undrafted</t>
+          <t>Three Dawg Nite</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2053,62 +2053,62 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>D.J. Wagner</t>
+          <t>Jaylen Carey</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ARK</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>4:46 - 2nd Half</t>
+          <t>10:27 - 1st Half</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -2125,48 +2125,48 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Undrafted</t>
+          <t>Bend Rimmers</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Trent Pierce</t>
+          <t>Duke Miles</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>4:46 - 2nd Half</t>
+          <t>10:27 - 1st Half</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I21" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2175,25 +2175,25 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="Q21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="S21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" t="n">
         <v>1</v>
@@ -2207,78 +2207,78 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Undrafted</t>
+          <t>Bend Rimmers</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Travis Perry</t>
+          <t>J.P. Estrella</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>10:27 - 1st Half</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>1</v>
       </c>
       <c r="P22" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Undrafted</t>
+          <t>G-Flop</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Eduardo Klafke</t>
+          <t>Kobe Knox</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2314,53 +2314,53 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>10:49 - 2nd Half</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P23" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
@@ -2371,17 +2371,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Undrafted</t>
+          <t>The Oddities</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Eli Ellis</t>
+          <t>Mike Sharavjamts</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2396,23 +2396,23 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>10:49 - 2nd Half</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J24" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K24" t="n">
         <v>2</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -2421,16 +2421,16 @@
         <v>1</v>
       </c>
       <c r="O24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P24" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -2453,48 +2453,48 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Undrafted</t>
+          <t>The Oddities</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Elijah Strong</t>
+          <t>Tyler Tanner</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>10:27 - 1st Half</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I25" t="n">
         <v>2</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -2506,13 +2506,13 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q25" t="n">
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2535,7 +2535,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Undrafted</t>
+          <t>The Oddities</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2545,68 +2545,68 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>T.O. Barrett</t>
+          <t>Jalen Washington</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>4:46 - 2nd Half</t>
+          <t>10:27 - 1st Half</t>
         </is>
       </c>
       <c r="H26" t="n">
         <v>2</v>
       </c>
       <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
         <v>6</v>
       </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>1</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1</v>
-      </c>
-      <c r="P26" t="n">
-        <v>21</v>
-      </c>
       <c r="Q26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2627,32 +2627,32 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Corey Chest</t>
+          <t>Shawn Phillips Jr.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>1:31 - OT</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -2661,22 +2661,22 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P27" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -2685,10 +2685,10 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2709,68 +2709,68 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>EJ Walker</t>
+          <t>Malique Ewin</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ARK</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>1:31 - OT</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J28" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P28" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2791,68 +2791,68 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Grant Polk</t>
+          <t>Trent Pierce</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>1:31 - OT</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I29" t="n">
+        <v>13</v>
+      </c>
+      <c r="J29" t="n">
+        <v>5</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2</v>
+      </c>
+      <c r="P29" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>5</v>
+      </c>
+      <c r="R29" t="n">
+        <v>11</v>
+      </c>
+      <c r="S29" t="n">
         <v>3</v>
       </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1</v>
-      </c>
-      <c r="P29" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>1</v>
-      </c>
-      <c r="R29" t="n">
-        <v>3</v>
-      </c>
-      <c r="S29" t="n">
-        <v>1</v>
-      </c>
       <c r="T29" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2873,68 +2873,68 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Kezza Giffa</t>
+          <t>D.J. Wagner</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>ARK</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>1:31 - OT</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P30" t="n">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R30" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2955,32 +2955,32 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Isaiah Sealy</t>
+          <t>Nordin Kapic</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ARK</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>4:46 - 2nd Half</t>
+          <t>10:49 - 2nd Half</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
         <v>1</v>
@@ -2989,28 +2989,28 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N31" t="n">
         <v>1</v>
       </c>
       <c r="O31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P31" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>4</v>
+      </c>
+      <c r="R31" t="n">
+        <v>5</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2</v>
+      </c>
+      <c r="T31" t="n">
         <v>3</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
@@ -3037,12 +3037,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Jordan Butler</t>
+          <t>Eduardo Klafke</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3052,47 +3052,47 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>10:49 - 2nd Half</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P32" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -3119,68 +3119,68 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Trent Burns</t>
+          <t>Travis Perry</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>4:46 - 2nd Half</t>
+          <t>10:49 - 2nd Half</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P33" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -3201,35 +3201,35 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Zach Day</t>
+          <t>AK Okereke</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>10:27 - 1st Half</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -3238,19 +3238,19 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P34" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -3259,10 +3259,10 @@
         <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -3283,57 +3283,57 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Malique Ewin</t>
+          <t>Amari Evans</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ARK</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>4:46 - 2nd Half</t>
+          <t>10:27 - 1st Half</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="I35" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2</v>
+      </c>
+      <c r="R35" t="n">
         <v>3</v>
       </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>1</v>
-      </c>
-      <c r="M35" t="n">
-        <v>2</v>
-      </c>
-      <c r="N35" t="n">
-        <v>3</v>
-      </c>
-      <c r="O35" t="n">
-        <v>3</v>
-      </c>
-      <c r="P35" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>2</v>
-      </c>
-      <c r="R35" t="n">
-        <v>8</v>
-      </c>
       <c r="S35" t="n">
         <v>0</v>
       </c>
@@ -3341,7 +3341,7 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V35" t="n">
         <v>2</v>
@@ -3365,7 +3365,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Max Smith</t>
+          <t>Kezza Giffa</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3380,20 +3380,20 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>10:49 - 2nd Half</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -3402,19 +3402,19 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P36" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -3423,10 +3423,10 @@
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -3447,67 +3447,1379 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t>Eli Ellis</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>SC@MISS</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>10:49 - 2nd Half</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>3</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1</v>
+      </c>
+      <c r="P37" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>2</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>T.O. Barrett</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>MIZ</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>ARK@MIZ</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1:31 - OT</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>3</v>
+      </c>
+      <c r="I38" t="n">
+        <v>8</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1</v>
+      </c>
+      <c r="P38" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>3</v>
+      </c>
+      <c r="R38" t="n">
+        <v>10</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
+      </c>
+      <c r="V38" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Chandler Bing</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>VAN</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>VAN@TENN</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>10:27 - 1st Half</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>2</v>
+      </c>
+      <c r="I39" t="n">
+        <v>2</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1</v>
+      </c>
+      <c r="P39" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>EJ Walker</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>SC@MISS</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>10:49 - 2nd Half</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>2</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>4</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>2</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1</v>
+      </c>
+      <c r="P40" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Zach Day</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>MISS</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>SC@MISS</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>10:49 - 2nd Half</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Corey Chest</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>MISS</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>SC@MISS</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>10:49 - 2nd Half</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>DeWayne Brown II</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>TENN</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>VAN@TENN</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>10:27 - 1st Half</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Elijah Strong</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>SC@MISS</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>10:49 - 2nd Half</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" t="n">
+        <v>2</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1</v>
+      </c>
+      <c r="P44" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>1</v>
+      </c>
+      <c r="R44" t="n">
+        <v>3</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Grant Polk</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>SC@MISS</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>10:49 - 2nd Half</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" t="n">
+        <v>3</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>1</v>
+      </c>
+      <c r="P45" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>1</v>
+      </c>
+      <c r="R45" t="n">
+        <v>3</v>
+      </c>
+      <c r="S45" t="n">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Amaree Abram</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>TENN</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>VAN@TENN</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>10:27 - 1st Half</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Bishop Boswell</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>TENN</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>VAN@TENN</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>10:27 - 1st Half</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>2</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>1</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1</v>
+      </c>
+      <c r="P47" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1</v>
+      </c>
+      <c r="R47" t="n">
+        <v>2</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Isaiah Sealy</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>ARK</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>ARK@MIZ</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1:31 - OT</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>1</v>
+      </c>
+      <c r="O48" t="n">
+        <v>1</v>
+      </c>
+      <c r="P48" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Jordan Butler</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>SC@MISS</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>10:49 - 2nd Half</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Trent Burns</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>MIZ</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>ARK@MIZ</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>1:31 - OT</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Ethan Burg</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>TENN</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>VAN@TENN</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>10:27 - 1st Half</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>1</v>
+      </c>
+      <c r="P51" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Max Smith</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>MISS</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>SC@MISS</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>10:49 - 2nd Half</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
           <t>Patton Pinkins</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>MISS</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>SC@MISS</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Halftime</t>
-        </is>
-      </c>
-      <c r="H37" t="n">
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>10:49 - 2nd Half</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
         <v>-2</v>
       </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="n">
-        <v>1</v>
-      </c>
-      <c r="K37" t="n">
-        <v>1</v>
-      </c>
-      <c r="L37" t="n">
-        <v>1</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
-        <v>1</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="n">
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>1</v>
+      </c>
+      <c r="K53" t="n">
+        <v>1</v>
+      </c>
+      <c r="L53" t="n">
+        <v>1</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>1</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
         <v>4</v>
       </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>2</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" t="n">
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3522,7 +4834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3554,10 +4866,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -3567,61 +4879,74 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Boozers Losers</t>
+          <t>Three Dawg Nite</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Three Dawg Nite</t>
+          <t>Boozers Losers</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>18</v>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>The Oddities</t>
+          <t>Bend Rimmers</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>The Oddities</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>12</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>G-Flop</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" t="n">
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
         <v>0</v>
       </c>
     </row>

--- a/docs/Today_PoohPoints_SEC_ByOwner_2026-03-07.xlsx
+++ b/docs/Today_PoohPoints_SEC_ByOwner_2026-03-07.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V53"/>
+  <dimension ref="A1:V56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -429,7 +429,7 @@
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
     <col width="6" customWidth="1" min="8" max="8"/>
     <col width="5" customWidth="1" min="9" max="9"/>
     <col width="5" customWidth="1" min="10" max="10"/>
@@ -592,7 +592,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1:31 - OT</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -674,14 +674,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10:49 - 2nd Half</t>
+          <t>3:10 - 2nd Half</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J3" t="n">
         <v>4</v>
@@ -702,13 +702,13 @@
         <v>2</v>
       </c>
       <c r="P3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -756,20 +756,20 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>10:27 - 1st Half</t>
+          <t>3:35 - 1st Half</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -778,31 +778,31 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -838,7 +838,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1:31 - OT</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -920,14 +920,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1:31 - OT</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I6" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J6" t="n">
         <v>9</v>
@@ -936,7 +936,7 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M6" t="n">
         <v>1</v>
@@ -948,19 +948,19 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U6" t="n">
         <v>1</v>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>10:49 - 2nd Half</t>
+          <t>3:10 - 2nd Half</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I7" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K7" t="n">
         <v>4</v>
@@ -1030,25 +1030,25 @@
         <v>1</v>
       </c>
       <c r="P7" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -1084,14 +1084,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>10:27 - 1st Half</t>
+          <t>3:35 - 1st Half</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1106,25 +1106,25 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
         <v>6</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1166,11 +1166,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1:31 - OT</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I9" t="n">
         <v>28</v>
@@ -1182,7 +1182,7 @@
         <v>2</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
         <v>1</v>
@@ -1194,7 +1194,7 @@
         <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="Q9" t="n">
         <v>9</v>
@@ -1248,17 +1248,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>10:49 - 2nd Half</t>
+          <t>3:10 - 2nd Half</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I10" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1273,16 +1273,16 @@
         <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R10" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>10:27 - 1st Half</t>
+          <t>3:35 - 1st Half</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1349,16 +1349,16 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
       </c>
       <c r="P11" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1:31 - OT</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -1440,7 +1440,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q12" t="n">
         <v>11</v>
@@ -1494,23 +1494,23 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>10:27 - 1st Half</t>
+          <t>3:35 - 1st Half</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>10:49 - 2nd Half</t>
+          <t>3:10 - 2nd Half</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1589,7 +1589,7 @@
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L14" t="n">
         <v>1</v>
@@ -1601,22 +1601,22 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P14" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="Q14" t="n">
         <v>2</v>
       </c>
       <c r="R14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1:31 - OT</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1686,7 +1686,7 @@
         <v>2</v>
       </c>
       <c r="P15" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Q15" t="n">
         <v>4</v>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>10:49 - 2nd Half</t>
+          <t>3:10 - 2nd Half</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1750,10 +1750,10 @@
         <v>13</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L16" t="n">
         <v>1</v>
@@ -1768,19 +1768,19 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="Q16" t="n">
         <v>6</v>
       </c>
       <c r="R16" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
         <v>1</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1:31 - OT</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -1847,7 +1847,7 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P17" t="n">
         <v>33</v>
@@ -1904,11 +1904,11 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>10:49 - 2nd Half</t>
+          <t>3:10 - 2nd Half</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I18" t="n">
         <v>6</v>
@@ -1923,7 +1923,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
         <v>2</v>
       </c>
       <c r="P18" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="Q18" t="n">
         <v>2</v>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1:31 - OT</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -2011,10 +2011,10 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q19" t="n">
         <v>2</v>
@@ -2068,17 +2068,17 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>10:27 - 1st Half</t>
+          <t>3:35 - 1st Half</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -2150,11 +2150,11 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>10:27 - 1st Half</t>
+          <t>3:35 - 1st Half</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I21" t="n">
         <v>7</v>
@@ -2166,25 +2166,25 @@
         <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Q21" t="n">
         <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -2232,17 +2232,17 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>10:27 - 1st Half</t>
+          <t>3:35 - 1st Half</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -2257,10 +2257,10 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>10:49 - 2nd Half</t>
+          <t>3:10 - 2nd Half</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -2324,7 +2324,7 @@
         <v>12</v>
       </c>
       <c r="J23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2342,13 +2342,13 @@
         <v>1</v>
       </c>
       <c r="P23" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="Q23" t="n">
         <v>4</v>
       </c>
       <c r="R23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -2396,18 +2396,18 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>10:49 - 2nd Half</t>
+          <t>3:10 - 2nd Half</t>
         </is>
       </c>
       <c r="H24" t="n">
+        <v>13</v>
+      </c>
+      <c r="I24" t="n">
+        <v>6</v>
+      </c>
+      <c r="J24" t="n">
         <v>9</v>
       </c>
-      <c r="I24" t="n">
-        <v>4</v>
-      </c>
-      <c r="J24" t="n">
-        <v>7</v>
-      </c>
       <c r="K24" t="n">
         <v>2</v>
       </c>
@@ -2415,7 +2415,7 @@
         <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" t="n">
         <v>1</v>
@@ -2424,19 +2424,19 @@
         <v>2</v>
       </c>
       <c r="P24" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="Q24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -2478,17 +2478,17 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>10:27 - 1st Half</t>
+          <t>3:35 - 1st Half</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -2500,13 +2500,13 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="Q25" t="n">
         <v>1</v>
@@ -2521,10 +2521,10 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -2560,17 +2560,17 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>10:27 - 1st Half</t>
+          <t>3:35 - 1st Half</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -2585,16 +2585,16 @@
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P26" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -2642,14 +2642,14 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1:31 - OT</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H27" t="n">
         <v>19</v>
       </c>
       <c r="I27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J27" t="n">
         <v>10</v>
@@ -2670,7 +2670,7 @@
         <v>4</v>
       </c>
       <c r="P27" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q27" t="n">
         <v>5</v>
@@ -2685,10 +2685,10 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1:31 - OT</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I28" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J28" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -2752,7 +2752,7 @@
         <v>3</v>
       </c>
       <c r="P28" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Q28" t="n">
         <v>6</v>
@@ -2767,10 +2767,10 @@
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V28" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
@@ -2791,68 +2791,68 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Trent Pierce</t>
+          <t>Nordin Kapic</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1:31 - OT</t>
+          <t>3:10 - 2nd Half</t>
         </is>
       </c>
       <c r="H29" t="n">
+        <v>13</v>
+      </c>
+      <c r="I29" t="n">
         <v>12</v>
       </c>
-      <c r="I29" t="n">
-        <v>13</v>
-      </c>
       <c r="J29" t="n">
+        <v>4</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2</v>
+      </c>
+      <c r="P29" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>4</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T29" t="n">
         <v>5</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>1</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>2</v>
-      </c>
-      <c r="P29" t="n">
-        <v>37</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>5</v>
-      </c>
-      <c r="R29" t="n">
-        <v>11</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3</v>
-      </c>
-      <c r="T29" t="n">
-        <v>7</v>
-      </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>D.J. Wagner</t>
+          <t>Trent Pierce</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ARK</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2888,20 +2888,20 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1:31 - OT</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I30" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J30" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
         <v>1</v>
@@ -2910,31 +2910,31 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O30" t="n">
         <v>3</v>
       </c>
       <c r="P30" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="Q30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R30" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T30" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2955,68 +2955,68 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Nordin Kapic</t>
+          <t>D.J. Wagner</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ARK</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>10:49 - 2nd Half</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I31" t="n">
         <v>10</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K31" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P31" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="Q31" t="n">
         <v>4</v>
       </c>
       <c r="R31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="S31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -3052,17 +3052,17 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>10:49 - 2nd Half</t>
+          <t>3:10 - 2nd Half</t>
         </is>
       </c>
       <c r="H32" t="n">
+        <v>7</v>
+      </c>
+      <c r="I32" t="n">
         <v>5</v>
       </c>
-      <c r="I32" t="n">
-        <v>3</v>
-      </c>
       <c r="J32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K32" t="n">
         <v>1</v>
@@ -3080,13 +3080,13 @@
         <v>2</v>
       </c>
       <c r="P32" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="Q32" t="n">
         <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3095,10 +3095,10 @@
         <v>2</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -3119,38 +3119,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Travis Perry</t>
+          <t>Amari Evans</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>10:49 - 2nd Half</t>
+          <t>3:35 - 1st Half</t>
         </is>
       </c>
       <c r="H33" t="n">
         <v>5</v>
       </c>
       <c r="I33" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -3159,16 +3159,16 @@
         <v>1</v>
       </c>
       <c r="O33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R33" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -3180,7 +3180,7 @@
         <v>2</v>
       </c>
       <c r="V33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -3201,38 +3201,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>AK Okereke</t>
+          <t>Eli Ellis</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>10:27 - 1st Half</t>
+          <t>3:10 - 2nd Half</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2</v>
+      </c>
+      <c r="K34" t="n">
         <v>5</v>
       </c>
-      <c r="J34" t="n">
-        <v>1</v>
-      </c>
-      <c r="K34" t="n">
-        <v>1</v>
-      </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -3244,25 +3244,25 @@
         <v>2</v>
       </c>
       <c r="P34" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="Q34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -3283,68 +3283,68 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Amari Evans</t>
+          <t>Elijah Strong</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>10:27 - 1st Half</t>
+          <t>3:10 - 2nd Half</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I35" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P35" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Q35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R35" t="n">
+        <v>7</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
         <v>3</v>
       </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
       <c r="U35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Kezza Giffa</t>
+          <t>Travis Perry</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3380,23 +3380,23 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>10:49 - 2nd Half</t>
+          <t>3:10 - 2nd Half</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I36" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K36" t="n">
         <v>2</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -3408,10 +3408,10 @@
         <v>1</v>
       </c>
       <c r="P36" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>3</v>
@@ -3420,7 +3420,7 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U36" t="n">
         <v>2</v>
@@ -3447,68 +3447,68 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Eli Ellis</t>
+          <t>AK Okereke</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>10:49 - 2nd Half</t>
+          <t>3:35 - 1st Half</t>
         </is>
       </c>
       <c r="H37" t="n">
+        <v>4</v>
+      </c>
+      <c r="I37" t="n">
+        <v>5</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1</v>
+      </c>
+      <c r="O37" t="n">
+        <v>2</v>
+      </c>
+      <c r="P37" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2</v>
+      </c>
+      <c r="R37" t="n">
         <v>3</v>
       </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="n">
-        <v>2</v>
-      </c>
-      <c r="K37" t="n">
-        <v>3</v>
-      </c>
-      <c r="L37" t="n">
-        <v>1</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
-        <v>1</v>
-      </c>
-      <c r="O37" t="n">
-        <v>1</v>
-      </c>
-      <c r="P37" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="n">
-        <v>2</v>
-      </c>
       <c r="S37" t="n">
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -3529,41 +3529,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>T.O. Barrett</t>
+          <t>DeWayne Brown II</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1:31 - OT</t>
+          <t>3:35 - 1st Half</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I38" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K38" t="n">
         <v>2</v>
       </c>
       <c r="L38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N38" t="n">
         <v>1</v>
@@ -3572,25 +3572,25 @@
         <v>1</v>
       </c>
       <c r="P38" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="Q38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -3611,35 +3611,35 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Chandler Bing</t>
+          <t>Kezza Giffa</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>10:27 - 1st Half</t>
+          <t>3:10 - 2nd Half</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -3648,31 +3648,31 @@
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O39" t="n">
         <v>1</v>
       </c>
       <c r="P39" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="Q39" t="n">
         <v>1</v>
       </c>
       <c r="R39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -3693,68 +3693,68 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>EJ Walker</t>
+          <t>T.O. Barrett</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>10:49 - 2nd Half</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J40" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>2</v>
+      </c>
+      <c r="O40" t="n">
+        <v>2</v>
+      </c>
+      <c r="P40" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q40" t="n">
         <v>4</v>
       </c>
-      <c r="K40" t="n">
-        <v>1</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="n">
-        <v>2</v>
-      </c>
-      <c r="O40" t="n">
-        <v>1</v>
-      </c>
-      <c r="P40" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -3775,32 +3775,32 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Zach Day</t>
+          <t>Troy Henderson</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>10:49 - 2nd Half</t>
+          <t>3:35 - 1st Half</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -3809,7 +3809,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -3818,19 +3818,19 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -3857,32 +3857,32 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Corey Chest</t>
+          <t>Chandler Bing</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>10:49 - 2nd Half</t>
+          <t>3:35 - 1st Half</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -3897,16 +3897,16 @@
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P42" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -3939,35 +3939,35 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>DeWayne Brown II</t>
+          <t>EJ Walker</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>10:27 - 1st Half</t>
+          <t>3:10 - 2nd Half</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -3976,25 +3976,25 @@
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P43" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
@@ -4021,12 +4021,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Elijah Strong</t>
+          <t>Zach Day</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -4036,41 +4036,41 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>10:49 - 2nd Half</t>
+          <t>3:10 - 2nd Half</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -4103,12 +4103,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Grant Polk</t>
+          <t>Corey Chest</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -4118,17 +4118,17 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>10:49 - 2nd Half</t>
+          <t>3:10 - 2nd Half</t>
         </is>
       </c>
       <c r="H45" t="n">
         <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -4143,22 +4143,22 @@
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
@@ -4185,32 +4185,32 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Amaree Abram</t>
+          <t>Grant Polk</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>10:27 - 1st Half</t>
+          <t>3:10 - 2nd Half</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -4225,22 +4225,22 @@
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P46" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Bishop Boswell</t>
+          <t>Amaree Abram</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4282,17 +4282,17 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>10:27 - 1st Half</t>
+          <t>3:35 - 1st Half</t>
         </is>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -4304,19 +4304,19 @@
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Q47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -4349,56 +4349,56 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Isaiah Sealy</t>
+          <t>Bishop Boswell</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ARK</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1:31 - OT</t>
+          <t>3:35 - 1st Half</t>
         </is>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O48" t="n">
         <v>1</v>
       </c>
       <c r="P48" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -4431,22 +4431,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Jordan Butler</t>
+          <t>Ethan Burg</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>10:49 - 2nd Half</t>
+          <t>3:35 - 1st Half</t>
         </is>
       </c>
       <c r="H49" t="n">
@@ -4459,7 +4459,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -4471,22 +4471,22 @@
         <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P49" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U49" t="n">
         <v>0</v>
@@ -4513,12 +4513,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Trent Burns</t>
+          <t>Isaiah Sealy</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>ARK</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -4528,7 +4528,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>1:31 - OT</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H50" t="n">
@@ -4541,7 +4541,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -4550,13 +4550,13 @@
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -4595,12 +4595,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Ethan Burg</t>
+          <t>Jayden Leverett</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -4610,17 +4610,17 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>10:27 - 1st Half</t>
+          <t>3:35 - 1st Half</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -4635,22 +4635,22 @@
         <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P51" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U51" t="n">
         <v>0</v>
@@ -4677,12 +4677,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Max Smith</t>
+          <t>Jordan Butler</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -4692,11 +4692,11 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>10:49 - 2nd Half</t>
+          <t>3:10 - 2nd Half</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
@@ -4726,13 +4726,13 @@
         <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U52" t="n">
         <v>0</v>
@@ -4759,67 +4759,313 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
+          <t>Trent Burns</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>MIZ</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>ARK@MIZ</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Final/OT</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Tyler Harris</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>VAN</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>VAN@TENN</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>3:35 - 1st Half</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Max Smith</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>MISS</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>SC@MISS</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>3:10 - 2nd Half</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
           <t>Patton Pinkins</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>MISS</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>SC@MISS</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>10:49 - 2nd Half</t>
-        </is>
-      </c>
-      <c r="H53" t="n">
-        <v>-2</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" t="n">
-        <v>1</v>
-      </c>
-      <c r="K53" t="n">
-        <v>1</v>
-      </c>
-      <c r="L53" t="n">
-        <v>1</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="n">
-        <v>1</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" t="n">
-        <v>4</v>
-      </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="n">
-        <v>2</v>
-      </c>
-      <c r="U53" t="n">
-        <v>0</v>
-      </c>
-      <c r="V53" t="n">
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>3:10 - 2nd Half</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I56" t="n">
+        <v>2</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" t="n">
+        <v>1</v>
+      </c>
+      <c r="L56" t="n">
+        <v>2</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>1</v>
+      </c>
+      <c r="O56" t="n">
+        <v>1</v>
+      </c>
+      <c r="P56" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>1</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4866,7 +5112,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C2" t="n">
         <v>3</v>
@@ -4879,7 +5125,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C3" t="n">
         <v>2</v>
@@ -4914,11 +5160,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bend Rimmers</t>
+          <t>The Oddities</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C6" t="n">
         <v>2</v>
@@ -4927,7 +5173,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>The Oddities</t>
+          <t>Bend Rimmers</t>
         </is>
       </c>
       <c r="B7" t="n">

--- a/docs/Today_PoohPoints_SEC_ByOwner_2026-03-07.xlsx
+++ b/docs/Today_PoohPoints_SEC_ByOwner_2026-03-07.xlsx
@@ -674,7 +674,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3:10 - 2nd Half</t>
+          <t>0:05 - 2nd Half</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -756,11 +756,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3:35 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
         <v>6</v>
@@ -778,13 +778,13 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q4" t="n">
         <v>2</v>
@@ -1002,14 +1002,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3:10 - 2nd Half</t>
+          <t>0:05 - 2nd Half</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I7" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J7" t="n">
         <v>4</v>
@@ -1030,19 +1030,19 @@
         <v>1</v>
       </c>
       <c r="P7" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U7" t="n">
         <v>4</v>
@@ -1084,11 +1084,11 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3:35 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="I8" t="n">
         <v>3</v>
@@ -1112,13 +1112,13 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1248,17 +1248,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3:10 - 2nd Half</t>
+          <t>0:05 - 2nd Half</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I10" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1276,13 +1276,13 @@
         <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Q10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3:35 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1358,19 +1358,19 @@
         <v>1</v>
       </c>
       <c r="P11" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -1494,20 +1494,20 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>3:35 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>1</v>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1576,17 +1576,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>3:10 - 2nd Half</t>
+          <t>0:05 - 2nd Half</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I14" t="n">
         <v>4</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K14" t="n">
         <v>4</v>
@@ -1604,13 +1604,13 @@
         <v>4</v>
       </c>
       <c r="P14" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="Q14" t="n">
         <v>2</v>
       </c>
       <c r="R14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -1740,11 +1740,11 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>3:10 - 2nd Half</t>
+          <t>0:05 - 2nd Half</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I16" t="n">
         <v>13</v>
@@ -1786,7 +1786,7 @@
         <v>1</v>
       </c>
       <c r="V16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>3:10 - 2nd Half</t>
+          <t>0:05 - 2nd Half</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>3:35 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -2096,7 +2096,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>3:35 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -2160,10 +2160,10 @@
         <v>7</v>
       </c>
       <c r="J21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L21" t="n">
         <v>3</v>
@@ -2178,19 +2178,19 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q21" t="n">
         <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
         <v>1</v>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>3:35 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -2314,17 +2314,17 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>3:10 - 2nd Half</t>
+          <t>0:05 - 2nd Half</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I23" t="n">
         <v>12</v>
       </c>
       <c r="J23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
         <v>2</v>
       </c>
       <c r="O23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P23" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="Q23" t="n">
         <v>4</v>
@@ -2396,14 +2396,14 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>3:10 - 2nd Half</t>
+          <t>0:05 - 2nd Half</t>
         </is>
       </c>
       <c r="H24" t="n">
         <v>13</v>
       </c>
       <c r="I24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J24" t="n">
         <v>9</v>
@@ -2424,7 +2424,7 @@
         <v>2</v>
       </c>
       <c r="P24" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="Q24" t="n">
         <v>3</v>
@@ -2439,10 +2439,10 @@
         <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -2478,41 +2478,41 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>3:35 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I25" t="n">
+        <v>6</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>2</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2</v>
+      </c>
+      <c r="R25" t="n">
         <v>4</v>
-      </c>
-      <c r="J25" t="n">
-        <v>2</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>2</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>1</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1</v>
-      </c>
-      <c r="R25" t="n">
-        <v>3</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2560,41 +2560,41 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>3:35 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H26" t="n">
+        <v>11</v>
+      </c>
+      <c r="I26" t="n">
+        <v>6</v>
+      </c>
+      <c r="J26" t="n">
         <v>5</v>
       </c>
-      <c r="I26" t="n">
-        <v>2</v>
-      </c>
-      <c r="J26" t="n">
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>2</v>
+      </c>
+      <c r="P26" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q26" t="n">
         <v>3</v>
       </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1</v>
-      </c>
-      <c r="P26" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1</v>
-      </c>
       <c r="R26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>3:10 - 2nd Half</t>
+          <t>0:05 - 2nd Half</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -3052,17 +3052,17 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>3:10 - 2nd Half</t>
+          <t>0:05 - 2nd Half</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I32" t="n">
         <v>5</v>
       </c>
       <c r="J32" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K32" t="n">
         <v>1</v>
@@ -3080,7 +3080,7 @@
         <v>2</v>
       </c>
       <c r="P32" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Q32" t="n">
         <v>1</v>
@@ -3119,38 +3119,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Amari Evans</t>
+          <t>Travis Perry</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>3:35 - 1st Half</t>
+          <t>0:05 - 2nd Half</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I33" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -3159,16 +3159,16 @@
         <v>1</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P33" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -3180,7 +3180,7 @@
         <v>2</v>
       </c>
       <c r="V33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -3201,68 +3201,68 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Eli Ellis</t>
+          <t>Amari Evans</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>3:10 - 2nd Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H34" t="n">
         <v>5</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q34" t="n">
         <v>5</v>
       </c>
-      <c r="L34" t="n">
-        <v>1</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>1</v>
-      </c>
-      <c r="O34" t="n">
-        <v>2</v>
-      </c>
-      <c r="P34" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
@@ -3283,68 +3283,68 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Elijah Strong</t>
+          <t>AK Okereke</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>3:10 - 2nd Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H35" t="n">
+        <v>4</v>
+      </c>
+      <c r="I35" t="n">
         <v>5</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" t="n">
+        <v>2</v>
+      </c>
+      <c r="P35" t="n">
         <v>7</v>
       </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>1</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>1</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>2</v>
-      </c>
-      <c r="P35" t="n">
-        <v>12</v>
-      </c>
       <c r="Q35" t="n">
+        <v>2</v>
+      </c>
+      <c r="R35" t="n">
         <v>3</v>
       </c>
-      <c r="R35" t="n">
-        <v>7</v>
-      </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -3365,41 +3365,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Travis Perry</t>
+          <t>DeWayne Brown II</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>3:10 - 2nd Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K36" t="n">
         <v>2</v>
       </c>
       <c r="L36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N36" t="n">
         <v>1</v>
@@ -3408,25 +3408,25 @@
         <v>1</v>
       </c>
       <c r="P36" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -3447,38 +3447,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>AK Okereke</t>
+          <t>Eli Ellis</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>3:35 - 1st Half</t>
+          <t>0:05 - 2nd Half</t>
         </is>
       </c>
       <c r="H37" t="n">
         <v>4</v>
       </c>
       <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2</v>
+      </c>
+      <c r="K37" t="n">
         <v>5</v>
       </c>
-      <c r="J37" t="n">
-        <v>1</v>
-      </c>
-      <c r="K37" t="n">
-        <v>1</v>
-      </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -3490,10 +3490,10 @@
         <v>2</v>
       </c>
       <c r="P37" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="Q37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
         <v>3</v>
@@ -3502,13 +3502,13 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -3529,35 +3529,35 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>DeWayne Brown II</t>
+          <t>Elijah Strong</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>3:35 - 1st Half</t>
+          <t>0:05 - 2nd Half</t>
         </is>
       </c>
       <c r="H38" t="n">
         <v>4</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -3566,25 +3566,25 @@
         <v>1</v>
       </c>
       <c r="N38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P38" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
@@ -3611,62 +3611,62 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Kezza Giffa</t>
+          <t>T.O. Barrett</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>3:10 - 2nd Half</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H39" t="n">
         <v>4</v>
       </c>
       <c r="I39" t="n">
+        <v>10</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>2</v>
+      </c>
+      <c r="O39" t="n">
+        <v>2</v>
+      </c>
+      <c r="P39" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q39" t="n">
         <v>4</v>
       </c>
-      <c r="J39" t="n">
-        <v>1</v>
-      </c>
-      <c r="K39" t="n">
-        <v>2</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
-        <v>1</v>
-      </c>
-      <c r="O39" t="n">
-        <v>1</v>
-      </c>
-      <c r="P39" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>1</v>
-      </c>
       <c r="R39" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U39" t="n">
         <v>2</v>
@@ -3693,38 +3693,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>T.O. Barrett</t>
+          <t>Kezza Giffa</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>0:05 - 2nd Half</t>
         </is>
       </c>
       <c r="H40" t="n">
+        <v>3</v>
+      </c>
+      <c r="I40" t="n">
         <v>4</v>
       </c>
-      <c r="I40" t="n">
-        <v>10</v>
-      </c>
       <c r="J40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K40" t="n">
         <v>2</v>
       </c>
       <c r="L40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -3733,22 +3733,22 @@
         <v>2</v>
       </c>
       <c r="O40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P40" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="Q40" t="n">
+        <v>1</v>
+      </c>
+      <c r="R40" t="n">
         <v>4</v>
       </c>
-      <c r="R40" t="n">
-        <v>12</v>
-      </c>
       <c r="S40" t="n">
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U40" t="n">
         <v>2</v>
@@ -3790,7 +3790,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>3:35 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -3803,7 +3803,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -3818,13 +3818,13 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q41" t="n">
         <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -3872,7 +3872,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>3:35 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>EJ Walker</t>
+          <t>Zach Day</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>3:10 - 2nd Half</t>
+          <t>0:05 - 2nd Half</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -3964,37 +3964,37 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Zach Day</t>
+          <t>Corey Chest</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4036,11 +4036,11 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>3:10 - 2nd Half</t>
+          <t>0:05 - 2nd Half</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4055,7 +4055,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
@@ -4064,7 +4064,7 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -4103,12 +4103,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Corey Chest</t>
+          <t>EJ Walker</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>3:10 - 2nd Half</t>
+          <t>0:05 - 2nd Half</t>
         </is>
       </c>
       <c r="H45" t="n">
@@ -4128,10 +4128,10 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -4140,25 +4140,25 @@
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P45" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
@@ -4200,7 +4200,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>3:10 - 2nd Half</t>
+          <t>0:05 - 2nd Half</t>
         </is>
       </c>
       <c r="H46" t="n">
@@ -4267,62 +4267,62 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Amaree Abram</t>
+          <t>Patton Pinkins</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>3:35 - 1st Half</t>
+          <t>0:05 - 2nd Half</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J47" t="n">
         <v>1</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P47" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R47" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Bishop Boswell</t>
+          <t>Amaree Abram</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4364,41 +4364,41 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>3:35 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Q48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>3:35 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H49" t="n">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>3:35 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>3:10 - 2nd Half</t>
+          <t>0:05 - 2nd Half</t>
         </is>
       </c>
       <c r="H52" t="n">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>3:35 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H54" t="n">
@@ -4923,29 +4923,29 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Max Smith</t>
+          <t>Bishop Boswell</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>3:10 - 2nd Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H55" t="n">
         <v>-1</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4954,31 +4954,31 @@
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P55" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U55" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Patton Pinkins</t>
+          <t>Max Smith</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5020,47 +5020,47 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>3:10 - 2nd Half</t>
+          <t>0:05 - 2nd Half</t>
         </is>
       </c>
       <c r="H56" t="n">
         <v>-1</v>
       </c>
       <c r="I56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U56" t="n">
         <v>0</v>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C2" t="n">
         <v>3</v>
@@ -5125,7 +5125,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C3" t="n">
         <v>2</v>
@@ -5138,7 +5138,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C4" t="n">
         <v>2</v>
@@ -5147,27 +5147,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Boozers Losers</t>
+          <t>The Oddities</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>The Oddities</t>
+          <t>Boozers Losers</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>18</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">

--- a/docs/Today_PoohPoints_SEC_ByOwner_2026-03-07.xlsx
+++ b/docs/Today_PoohPoints_SEC_ByOwner_2026-03-07.xlsx
@@ -429,7 +429,7 @@
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
     <col width="6" customWidth="1" min="8" max="8"/>
     <col width="5" customWidth="1" min="9" max="9"/>
     <col width="5" customWidth="1" min="10" max="10"/>
@@ -674,7 +674,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0:05 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0:05 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0:05 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0:05 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0:05 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0:05 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0:05 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0:05 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0:05 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0:05 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0:05 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0:05 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0:05 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0:05 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0:05 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0:05 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0:05 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H45" t="n">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>0:05 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H46" t="n">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>0:05 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H47" t="n">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>0:05 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H52" t="n">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>0:05 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H56" t="n">

--- a/docs/Today_PoohPoints_SEC_ByOwner_2026-03-07.xlsx
+++ b/docs/Today_PoohPoints_SEC_ByOwner_2026-03-07.xlsx
@@ -420,16 +420,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V56"/>
+  <dimension ref="A1:V70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
     <col width="6" customWidth="1" min="8" max="8"/>
     <col width="5" customWidth="1" min="9" max="9"/>
     <col width="5" customWidth="1" min="10" max="10"/>
@@ -756,14 +756,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>10:03 - 2nd Half</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J4" t="n">
         <v>3</v>
@@ -775,22 +775,22 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4" t="n">
         <v>2</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -823,32 +823,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Jacob Crews</t>
+          <t>Jeremiah Wilkinson</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>15:56 - 1st Half</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -863,19 +863,19 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
@@ -895,22 +895,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Backslashers</t>
+          <t>Boozers Losers</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Trevon Brazile</t>
+          <t>Jacob Crews</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ARK</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -924,49 +924,49 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="Q6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -987,68 +987,68 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Meechie Johnson</t>
+          <t>Trevon Brazile</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ARK</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="I7" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J7" t="n">
+        <v>9</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>8</v>
+      </c>
+      <c r="R7" t="n">
+        <v>14</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
         <v>4</v>
       </c>
-      <c r="K7" t="n">
-        <v>4</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
+      <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" t="n">
         <v>3</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1</v>
-      </c>
-      <c r="P7" t="n">
-        <v>33</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>5</v>
-      </c>
-      <c r="R7" t="n">
-        <v>11</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>7</v>
-      </c>
-      <c r="U7" t="n">
-        <v>4</v>
-      </c>
-      <c r="V7" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -1069,68 +1069,68 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ja'Kobi Gillespie</t>
+          <t>Meechie Johnson</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>-7</v>
+        <v>16</v>
       </c>
       <c r="I8" t="n">
+        <v>17</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
         <v>3</v>
       </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>5</v>
+      </c>
+      <c r="R8" t="n">
+        <v>11</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>7</v>
+      </c>
+      <c r="U8" t="n">
         <v>4</v>
       </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>8</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1</v>
-      </c>
-      <c r="T8" t="n">
-        <v>6</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -1146,73 +1146,73 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Meleek Thomas</t>
+          <t>Ja'Kobi Gillespie</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ARK</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>10:03 - 2nd Half</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>24</v>
+        <v>-4</v>
       </c>
       <c r="I9" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>5</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3</v>
+      </c>
+      <c r="R9" t="n">
+        <v>13</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
         <v>7</v>
       </c>
-      <c r="K9" t="n">
-        <v>2</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1</v>
-      </c>
-      <c r="O9" t="n">
-        <v>3</v>
-      </c>
-      <c r="P9" t="n">
-        <v>45</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>9</v>
-      </c>
-      <c r="R9" t="n">
-        <v>22</v>
-      </c>
-      <c r="S9" t="n">
-        <v>5</v>
-      </c>
-      <c r="T9" t="n">
-        <v>6</v>
-      </c>
       <c r="U9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="V9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -1233,65 +1233,65 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Malik Dia</t>
+          <t>Meleek Thomas</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>ARK</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H10" t="n">
+        <v>24</v>
+      </c>
+      <c r="I10" t="n">
+        <v>28</v>
+      </c>
+      <c r="J10" t="n">
+        <v>7</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3</v>
+      </c>
+      <c r="P10" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>9</v>
+      </c>
+      <c r="R10" t="n">
         <v>22</v>
       </c>
-      <c r="I10" t="n">
-        <v>22</v>
-      </c>
-      <c r="J10" t="n">
-        <v>4</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>4</v>
-      </c>
-      <c r="P10" t="n">
-        <v>21</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>8</v>
-      </c>
-      <c r="R10" t="n">
-        <v>13</v>
-      </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V10" t="n">
         <v>6</v>
@@ -1315,38 +1315,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Felix Okpara</t>
+          <t>Malik Dia</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="J11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
         <v>1</v>
@@ -1355,16 +1355,16 @@
         <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -1373,10 +1373,10 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -1387,78 +1387,78 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Hilton Heads</t>
+          <t>The Backslashers</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Mark Mitchell</t>
+          <t>Felix Okpara</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>10:03 - 2nd Half</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="I12" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N12" t="n">
         <v>2</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="Q12" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="V12" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1469,36 +1469,36 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Hilton Heads</t>
+          <t>The Backslashers</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Tyler Nickel</t>
+          <t>Jayden Epps</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>15:56 - 1st Half</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1507,10 +1507,10 @@
         <v>2</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1522,13 +1522,13 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1556,37 +1556,37 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Ilias Kamardine</t>
+          <t>Mark Mitchell</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="I14" t="n">
+        <v>32</v>
+      </c>
+      <c r="J14" t="n">
         <v>4</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3</v>
       </c>
       <c r="K14" t="n">
         <v>4</v>
@@ -1598,31 +1598,31 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="R14" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Three Dawg Nite</t>
+          <t>Hilton Heads</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1643,35 +1643,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Jayden Stone</t>
+          <t>Tyler Nickel</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>10:03 - 2nd Half</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I15" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>2</v>
@@ -1680,31 +1680,31 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="S15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1715,17 +1715,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Three Dawg Nite</t>
+          <t>Hilton Heads</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>AJ Storr</t>
+          <t>Ilias Kamardine</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1744,16 +1744,16 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I16" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L16" t="n">
         <v>1</v>
@@ -1762,19 +1762,19 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P16" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="Q16" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1783,10 +1783,10 @@
         <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Three Dawg Nite</t>
+          <t>Hilton Heads</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1807,68 +1807,68 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Anthony Robinson II</t>
+          <t>Quincy Ballard</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>15:56 - 1st Half</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1884,73 +1884,73 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Myles Stute</t>
+          <t>Jayden Stone</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I18" t="n">
+        <v>11</v>
+      </c>
+      <c r="J18" t="n">
         <v>6</v>
       </c>
-      <c r="J18" t="n">
-        <v>2</v>
-      </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O18" t="n">
         <v>2</v>
       </c>
       <c r="P18" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="Q18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="S18" t="n">
         <v>2</v>
       </c>
       <c r="T18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1966,73 +1966,73 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Nick Pringle</t>
+          <t>AJ Storr</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ARK</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I19" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="Q19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R19" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -2053,38 +2053,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Jaylen Carey</t>
+          <t>Anthony Robinson II</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J20" t="n">
         <v>3</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2093,28 +2093,28 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P20" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -2125,78 +2125,78 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bend Rimmers</t>
+          <t>Three Dawg Nite</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Duke Miles</t>
+          <t>Myles Stute</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2</v>
+      </c>
+      <c r="P21" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2</v>
+      </c>
+      <c r="R21" t="n">
         <v>3</v>
       </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>1</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q21" t="n">
+      <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="n">
         <v>3</v>
       </c>
-      <c r="R21" t="n">
-        <v>9</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1</v>
-      </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2207,17 +2207,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bend Rimmers</t>
+          <t>Three Dawg Nite</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>J.P. Estrella</t>
+          <t>Jaylen Carey</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2232,35 +2232,35 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>10:03 - 2nd Half</t>
         </is>
       </c>
       <c r="H22" t="n">
+        <v>5</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>5</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
         <v>3</v>
       </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>3</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>2</v>
-      </c>
       <c r="P22" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>G-Flop</t>
+          <t>Three Dawg Nite</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2299,68 +2299,68 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Kobe Knox</t>
+          <t>Nick Pringle</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ARK</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I23" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J23" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P23" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="Q23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R23" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>The Oddities</t>
+          <t>Bend Rimmers</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2381,68 +2381,68 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Mike Sharavjamts</t>
+          <t>J.P. Estrella</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>10:03 - 2nd Half</t>
         </is>
       </c>
       <c r="H24" t="n">
         <v>13</v>
       </c>
       <c r="I24" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J24" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>1</v>
       </c>
       <c r="N24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P24" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="Q24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R24" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
         <v>1</v>
       </c>
       <c r="V24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>The Oddities</t>
+          <t>Bend Rimmers</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Tyler Tanner</t>
+          <t>Duke Miles</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2478,53 +2478,53 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>10:03 - 2nd Half</t>
         </is>
       </c>
       <c r="H25" t="n">
+        <v>9</v>
+      </c>
+      <c r="I25" t="n">
         <v>7</v>
       </c>
-      <c r="I25" t="n">
-        <v>6</v>
-      </c>
       <c r="J25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P25" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="Q25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R25" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -2535,66 +2535,66 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>The Oddities</t>
+          <t>Bend Rimmers</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Jalen Washington</t>
+          <t>Somtochukwu Cyril</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>15:56 - 1st Half</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I26" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="Q26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -2617,78 +2617,78 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Undrafted</t>
+          <t>G-Flop</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Shawn Phillips Jr.</t>
+          <t>Blue Cain</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>15:56 - 1st Half</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="I27" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="J27" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
         <v>4</v>
       </c>
-      <c r="N27" t="n">
-        <v>4</v>
-      </c>
-      <c r="O27" t="n">
-        <v>4</v>
-      </c>
-      <c r="P27" t="n">
-        <v>36</v>
-      </c>
       <c r="Q27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2699,78 +2699,78 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Undrafted</t>
+          <t>G-Flop</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Malique Ewin</t>
+          <t>Josh Hubbard</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ARK</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>15:56 - 1st Half</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="J28" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
         <v>3</v>
       </c>
-      <c r="O28" t="n">
-        <v>3</v>
-      </c>
-      <c r="P28" t="n">
-        <v>31</v>
-      </c>
       <c r="Q28" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Undrafted</t>
+          <t>G-Flop</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Nordin Kapic</t>
+          <t>Kobe Knox</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2810,22 +2810,22 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I29" t="n">
         <v>12</v>
       </c>
       <c r="J29" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>2</v>
@@ -2834,25 +2834,25 @@
         <v>2</v>
       </c>
       <c r="P29" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="Q29" t="n">
         <v>4</v>
       </c>
       <c r="R29" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="S29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V29" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Undrafted</t>
+          <t>G-Flop</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2873,68 +2873,68 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Trent Pierce</t>
+          <t>Marcus Millender</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>15:56 - 1st Half</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2945,78 +2945,78 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Undrafted</t>
+          <t>The Oddities</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>D.J. Wagner</t>
+          <t>Tyler Tanner</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ARK</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>10:03 - 2nd Half</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="I31" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K31" t="n">
+        <v>2</v>
+      </c>
+      <c r="L31" t="n">
+        <v>2</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1</v>
+      </c>
+      <c r="P31" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>6</v>
+      </c>
+      <c r="R31" t="n">
+        <v>8</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
         <v>5</v>
       </c>
-      <c r="L31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>3</v>
-      </c>
-      <c r="O31" t="n">
-        <v>3</v>
-      </c>
-      <c r="P31" t="n">
-        <v>45</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>4</v>
-      </c>
-      <c r="R31" t="n">
-        <v>10</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>4</v>
-      </c>
-      <c r="U31" t="n">
-        <v>2</v>
-      </c>
       <c r="V31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32">
@@ -3027,22 +3027,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Undrafted</t>
+          <t>The Oddities</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Eduardo Klafke</t>
+          <t>Mike Sharavjamts</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3056,22 +3056,22 @@
         </is>
       </c>
       <c r="H32" t="n">
+        <v>13</v>
+      </c>
+      <c r="I32" t="n">
+        <v>7</v>
+      </c>
+      <c r="J32" t="n">
         <v>9</v>
       </c>
-      <c r="I32" t="n">
-        <v>5</v>
-      </c>
-      <c r="J32" t="n">
-        <v>6</v>
-      </c>
       <c r="K32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N32" t="n">
         <v>1</v>
@@ -3080,22 +3080,22 @@
         <v>2</v>
       </c>
       <c r="P32" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R32" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
         <v>2</v>
       </c>
       <c r="U32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V32" t="n">
         <v>2</v>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Undrafted</t>
+          <t>The Oddities</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3119,65 +3119,65 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Travis Perry</t>
+          <t>Jalen Washington</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>10:03 - 2nd Half</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I33" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J33" t="n">
+        <v>8</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1</v>
+      </c>
+      <c r="O33" t="n">
+        <v>2</v>
+      </c>
+      <c r="P33" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q33" t="n">
         <v>3</v>
       </c>
-      <c r="K33" t="n">
-        <v>3</v>
-      </c>
-      <c r="L33" t="n">
-        <v>2</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>1</v>
-      </c>
-      <c r="O33" t="n">
-        <v>1</v>
-      </c>
-      <c r="P33" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V33" t="n">
         <v>2</v>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Undrafted</t>
+          <t>The Oddities</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3201,32 +3201,32 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Amari Evans</t>
+          <t>Shawn Jones Jr.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>15:56 - 1st Half</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I34" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -3238,31 +3238,31 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="Q34" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R34" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -3283,68 +3283,68 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>AK Okereke</t>
+          <t>Shawn Phillips Jr.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H35" t="n">
+        <v>19</v>
+      </c>
+      <c r="I35" t="n">
+        <v>13</v>
+      </c>
+      <c r="J35" t="n">
+        <v>10</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
         <v>4</v>
       </c>
-      <c r="I35" t="n">
+      <c r="N35" t="n">
+        <v>4</v>
+      </c>
+      <c r="O35" t="n">
+        <v>4</v>
+      </c>
+      <c r="P35" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q35" t="n">
         <v>5</v>
       </c>
-      <c r="J35" t="n">
-        <v>1</v>
-      </c>
-      <c r="K35" t="n">
-        <v>1</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>1</v>
-      </c>
-      <c r="O35" t="n">
-        <v>2</v>
-      </c>
-      <c r="P35" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>2</v>
-      </c>
       <c r="R35" t="n">
+        <v>8</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
         <v>3</v>
       </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1</v>
-      </c>
       <c r="V35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
@@ -3365,68 +3365,68 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>DeWayne Brown II</t>
+          <t>Malique Ewin</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>ARK</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H36" t="n">
+        <v>17</v>
+      </c>
+      <c r="I36" t="n">
+        <v>17</v>
+      </c>
+      <c r="J36" t="n">
+        <v>9</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1</v>
+      </c>
+      <c r="M36" t="n">
+        <v>2</v>
+      </c>
+      <c r="N36" t="n">
+        <v>3</v>
+      </c>
+      <c r="O36" t="n">
+        <v>3</v>
+      </c>
+      <c r="P36" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>6</v>
+      </c>
+      <c r="R36" t="n">
+        <v>12</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
         <v>4</v>
       </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="n">
-        <v>2</v>
-      </c>
-      <c r="K36" t="n">
-        <v>2</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>1</v>
-      </c>
-      <c r="N36" t="n">
-        <v>1</v>
-      </c>
-      <c r="O36" t="n">
-        <v>1</v>
-      </c>
-      <c r="P36" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37">
@@ -3447,68 +3447,68 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Eli Ellis</t>
+          <t>AK Okereke</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>10:03 - 2nd Half</t>
         </is>
       </c>
       <c r="H37" t="n">
+        <v>14</v>
+      </c>
+      <c r="I37" t="n">
+        <v>13</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1</v>
+      </c>
+      <c r="O37" t="n">
+        <v>3</v>
+      </c>
+      <c r="P37" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q37" t="n">
         <v>4</v>
       </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="n">
-        <v>2</v>
-      </c>
-      <c r="K37" t="n">
+      <c r="R37" t="n">
         <v>5</v>
       </c>
-      <c r="L37" t="n">
-        <v>1</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
-        <v>1</v>
-      </c>
-      <c r="O37" t="n">
-        <v>2</v>
-      </c>
-      <c r="P37" t="n">
-        <v>28</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="n">
-        <v>3</v>
-      </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Elijah Strong</t>
+          <t>Nordin Kapic</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3548,49 +3548,49 @@
         </is>
       </c>
       <c r="H38" t="n">
+        <v>13</v>
+      </c>
+      <c r="I38" t="n">
+        <v>12</v>
+      </c>
+      <c r="J38" t="n">
         <v>4</v>
       </c>
-      <c r="I38" t="n">
+      <c r="K38" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2</v>
+      </c>
+      <c r="O38" t="n">
+        <v>2</v>
+      </c>
+      <c r="P38" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>4</v>
+      </c>
+      <c r="R38" t="n">
         <v>7</v>
       </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="n">
-        <v>1</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" t="n">
-        <v>1</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>2</v>
-      </c>
-      <c r="P38" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>3</v>
-      </c>
-      <c r="R38" t="n">
-        <v>8</v>
-      </c>
       <c r="S38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T38" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>T.O. Barrett</t>
+          <t>Trent Pierce</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3630,16 +3630,16 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I39" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J39" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
         <v>1</v>
@@ -3648,31 +3648,31 @@
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P39" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="Q39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R39" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T39" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -3693,68 +3693,68 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Kezza Giffa</t>
+          <t>Amari Evans</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>10:03 - 2nd Half</t>
         </is>
       </c>
       <c r="H40" t="n">
+        <v>10</v>
+      </c>
+      <c r="I40" t="n">
+        <v>16</v>
+      </c>
+      <c r="J40" t="n">
         <v>3</v>
       </c>
-      <c r="I40" t="n">
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>2</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>1</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>7</v>
+      </c>
+      <c r="R40" t="n">
+        <v>15</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
+      </c>
+      <c r="V40" t="n">
         <v>4</v>
-      </c>
-      <c r="J40" t="n">
-        <v>2</v>
-      </c>
-      <c r="K40" t="n">
-        <v>2</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="n">
-        <v>2</v>
-      </c>
-      <c r="O40" t="n">
-        <v>1</v>
-      </c>
-      <c r="P40" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>1</v>
-      </c>
-      <c r="R40" t="n">
-        <v>4</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" t="n">
-        <v>1</v>
-      </c>
-      <c r="U40" t="n">
-        <v>2</v>
-      </c>
-      <c r="V40" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -3775,68 +3775,68 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Troy Henderson</t>
+          <t>D.J. Wagner</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>ARK</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H41" t="n">
+        <v>9</v>
+      </c>
+      <c r="I41" t="n">
+        <v>10</v>
+      </c>
+      <c r="J41" t="n">
+        <v>4</v>
+      </c>
+      <c r="K41" t="n">
+        <v>5</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
         <v>3</v>
       </c>
-      <c r="I41" t="n">
+      <c r="O41" t="n">
         <v>3</v>
       </c>
-      <c r="J41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" t="n">
-        <v>1</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
       <c r="P41" t="n">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="Q41" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R41" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="S41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
@@ -3857,68 +3857,68 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Chandler Bing</t>
+          <t>Eduardo Klafke</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P42" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="Q42" t="n">
         <v>1</v>
       </c>
       <c r="R42" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Zach Day</t>
+          <t>Travis Perry</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3958,49 +3958,49 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P43" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -4021,56 +4021,56 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Corey Chest</t>
+          <t>DeWayne Brown II</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>10:03 - 2nd Half</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P44" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>EJ Walker</t>
+          <t>Eli Ellis</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4122,37 +4122,37 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
       <c r="J45" t="n">
+        <v>2</v>
+      </c>
+      <c r="K45" t="n">
         <v>5</v>
       </c>
-      <c r="K45" t="n">
-        <v>1</v>
-      </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
       </c>
       <c r="N45" t="n">
+        <v>1</v>
+      </c>
+      <c r="O45" t="n">
+        <v>2</v>
+      </c>
+      <c r="P45" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
         <v>3</v>
-      </c>
-      <c r="O45" t="n">
-        <v>2</v>
-      </c>
-      <c r="P45" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" t="n">
-        <v>2</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -4185,7 +4185,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Grant Polk</t>
+          <t>Elijah Strong</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4204,37 +4204,37 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I46" t="n">
+        <v>7</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>2</v>
+      </c>
+      <c r="P46" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q46" t="n">
         <v>3</v>
       </c>
-      <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="n">
-        <v>1</v>
-      </c>
-      <c r="P46" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>1</v>
-      </c>
       <c r="R46" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="S46" t="n">
         <v>1</v>
@@ -4267,68 +4267,68 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Patton Pinkins</t>
+          <t>Ethan Burg</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>10:03 - 2nd Half</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I47" t="n">
         <v>4</v>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P47" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="Q47" t="n">
         <v>2</v>
       </c>
       <c r="R47" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -4349,68 +4349,68 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Amaree Abram</t>
+          <t>T.O. Barrett</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J48" t="n">
         <v>1</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P48" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R48" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -4431,35 +4431,35 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Ethan Burg</t>
+          <t>Kezza Giffa</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -4468,19 +4468,19 @@
         <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O49" t="n">
         <v>1</v>
       </c>
       <c r="P49" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R49" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -4489,10 +4489,10 @@
         <v>1</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -4513,29 +4513,29 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Isaiah Sealy</t>
+          <t>Troy Henderson</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ARK</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>10:03 - 2nd Half</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4550,25 +4550,25 @@
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U50" t="n">
         <v>0</v>
@@ -4595,26 +4595,26 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Jayden Leverett</t>
+          <t>Achor Achor</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>15:56 - 1st Half</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
@@ -4635,7 +4635,7 @@
         <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
         <v>3</v>
@@ -4644,7 +4644,7 @@
         <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -4677,29 +4677,29 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Jordan Butler</t>
+          <t>Chandler Bing</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>10:03 - 2nd Half</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -4717,16 +4717,16 @@
         <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P52" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -4759,29 +4759,29 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Trent Burns</t>
+          <t>Sergej Macura</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>15:56 - 1st Half</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4802,13 +4802,13 @@
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -4841,32 +4841,32 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Tyler Harris</t>
+          <t>Zach Day</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -4875,7 +4875,7 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N54" t="n">
         <v>0</v>
@@ -4884,7 +4884,7 @@
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -4938,20 +4938,20 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>10:03 - 2nd Half</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="I55" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" t="n">
         <v>1</v>
@@ -4963,22 +4963,22 @@
         <v>2</v>
       </c>
       <c r="O55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P55" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="Q55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R55" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U55" t="n">
         <v>0</v>
@@ -5005,67 +5005,1215 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
+          <t>Corey Chest</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>MISS</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>SC@MISS</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>1</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>EJ Walker</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>SC@MISS</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>5</v>
+      </c>
+      <c r="K57" t="n">
+        <v>1</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>3</v>
+      </c>
+      <c r="O57" t="n">
+        <v>2</v>
+      </c>
+      <c r="P57" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>2</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Grant Polk</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>SC@MISS</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" t="n">
+        <v>3</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>1</v>
+      </c>
+      <c r="P58" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>1</v>
+      </c>
+      <c r="R58" t="n">
+        <v>3</v>
+      </c>
+      <c r="S58" t="n">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Jamarion Davis-Fleming</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>MSST</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>UGA@MSST</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>15:56 - 1st Half</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>1</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>1</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Patton Pinkins</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>MISS</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>SC@MISS</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>1</v>
+      </c>
+      <c r="I60" t="n">
+        <v>4</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1</v>
+      </c>
+      <c r="K60" t="n">
+        <v>1</v>
+      </c>
+      <c r="L60" t="n">
+        <v>2</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
+        <v>1</v>
+      </c>
+      <c r="O60" t="n">
+        <v>1</v>
+      </c>
+      <c r="P60" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>2</v>
+      </c>
+      <c r="R60" t="n">
+        <v>8</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Amaree Abram</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>TENN</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>VAN@TENN</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>10:03 - 2nd Half</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" t="n">
+        <v>1</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Isaiah Sealy</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>ARK</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>ARK@MIZ</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Final/OT</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>1</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
+        <v>1</v>
+      </c>
+      <c r="O62" t="n">
+        <v>1</v>
+      </c>
+      <c r="P62" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Jayden Leverett</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>VAN</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>VAN@TENN</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>10:03 - 2nd Half</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>2</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
+        <v>2</v>
+      </c>
+      <c r="P63" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" t="n">
+        <v>2</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Jordan Butler</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>SC@MISS</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Trent Burns</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>MIZ</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>ARK@MIZ</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Final/OT</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Tyler Harris</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>VAN</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>VAN@TENN</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>10:03 - 2nd Half</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
+      </c>
+      <c r="V66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Kanon Catchings</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>UGA</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>UGA@MSST</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>15:56 - 1st Half</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
+        <v>1</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" t="n">
+        <v>2</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
+      </c>
+      <c r="V67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Kareem Stagg</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>UGA</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>UGA@MSST</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>15:56 - 1st Half</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" t="n">
+        <v>1</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
+      </c>
+      <c r="V68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
           <t>Max Smith</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>MISS</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>SC@MISS</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>Final</t>
         </is>
       </c>
-      <c r="H56" t="n">
+      <c r="H69" t="n">
         <v>-1</v>
       </c>
-      <c r="I56" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" t="n">
-        <v>1</v>
-      </c>
-      <c r="S56" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" t="n">
-        <v>1</v>
-      </c>
-      <c r="U56" t="n">
-        <v>0</v>
-      </c>
-      <c r="V56" t="n">
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="n">
+        <v>1</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
+      </c>
+      <c r="V69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Jordan Ross</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>UGA</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>UGA@MSST</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>15:56 - 1st Half</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="n">
+        <v>2</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="n">
+        <v>1</v>
+      </c>
+      <c r="S70" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
+      </c>
+      <c r="V70" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5112,7 +6260,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C2" t="n">
         <v>3</v>
@@ -5125,7 +6273,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C3" t="n">
         <v>2</v>
@@ -5134,11 +6282,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Three Dawg Nite</t>
+          <t>The Oddities</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C4" t="n">
         <v>2</v>
@@ -5147,40 +6295,40 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>The Oddities</t>
+          <t>Bend Rimmers</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Boozers Losers</t>
+          <t>Three Dawg Nite</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bend Rimmers</t>
+          <t>Boozers Losers</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -5190,10 +6338,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Today_PoohPoints_SEC_ByOwner_2026-03-07.xlsx
+++ b/docs/Today_PoohPoints_SEC_ByOwner_2026-03-07.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V70"/>
+  <dimension ref="A1:V74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -429,7 +429,7 @@
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
     <col width="6" customWidth="1" min="8" max="8"/>
     <col width="5" customWidth="1" min="9" max="9"/>
     <col width="5" customWidth="1" min="10" max="10"/>
@@ -756,7 +756,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>10:03 - 2nd Half</t>
+          <t>3:42 - 2nd Half</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -784,7 +784,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
@@ -838,23 +838,23 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>15:56 - 1st Half</t>
+          <t>8:35 - 1st Half</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -866,25 +866,25 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -1166,14 +1166,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>10:03 - 2nd Half</t>
+          <t>3:42 - 2nd Half</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="I9" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1194,25 +1194,25 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R9" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -1412,27 +1412,27 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>10:03 - 2nd Half</t>
+          <t>3:42 - 2nd Half</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I12" t="n">
+        <v>6</v>
+      </c>
+      <c r="J12" t="n">
+        <v>10</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>4</v>
       </c>
-      <c r="J12" t="n">
-        <v>9</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>2</v>
-      </c>
       <c r="N12" t="n">
         <v>2</v>
       </c>
@@ -1440,13 +1440,13 @@
         <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -1494,11 +1494,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>15:56 - 1st Half</t>
+          <t>8:35 - 1st Half</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1522,19 +1522,19 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -1658,17 +1658,17 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>10:03 - 2nd Half</t>
+          <t>3:42 - 2nd Half</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1680,19 +1680,19 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>15:56 - 1st Half</t>
+          <t>8:35 - 1st Half</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -1838,19 +1838,19 @@
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>10:03 - 2nd Half</t>
+          <t>3:42 - 2nd Half</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -2396,20 +2396,20 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>10:03 - 2nd Half</t>
+          <t>3:42 - 2nd Half</t>
         </is>
       </c>
       <c r="H24" t="n">
+        <v>22</v>
+      </c>
+      <c r="I24" t="n">
         <v>13</v>
       </c>
-      <c r="I24" t="n">
-        <v>9</v>
-      </c>
       <c r="J24" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -2424,13 +2424,13 @@
         <v>3</v>
       </c>
       <c r="P24" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -2478,14 +2478,14 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>10:03 - 2nd Half</t>
+          <t>3:42 - 2nd Half</t>
         </is>
       </c>
       <c r="H25" t="n">
+        <v>10</v>
+      </c>
+      <c r="I25" t="n">
         <v>9</v>
-      </c>
-      <c r="I25" t="n">
-        <v>7</v>
       </c>
       <c r="J25" t="n">
         <v>4</v>
@@ -2503,16 +2503,16 @@
         <v>2</v>
       </c>
       <c r="O25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P25" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="Q25" t="n">
         <v>3</v>
       </c>
       <c r="R25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2521,10 +2521,10 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>15:56 - 1st Half</t>
+          <t>8:35 - 1st Half</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -2588,7 +2588,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -2642,17 +2642,17 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>15:56 - 1st Half</t>
+          <t>8:35 - 1st Half</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I27" t="n">
         <v>3</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -2670,7 +2670,7 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Q27" t="n">
         <v>1</v>
@@ -2724,20 +2724,20 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>15:56 - 1st Half</t>
+          <t>8:35 - 1st Half</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -2746,25 +2746,25 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R28" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -2888,14 +2888,14 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>15:56 - 1st Half</t>
+          <t>8:35 - 1st Half</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2910,25 +2910,25 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -2970,20 +2970,20 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>10:03 - 2nd Half</t>
+          <t>3:42 - 2nd Half</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="I31" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L31" t="n">
         <v>2</v>
@@ -2998,25 +2998,25 @@
         <v>1</v>
       </c>
       <c r="P31" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="Q31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R31" t="n">
+        <v>9</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>7</v>
+      </c>
+      <c r="V31" t="n">
         <v>8</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2</v>
-      </c>
-      <c r="U31" t="n">
-        <v>5</v>
-      </c>
-      <c r="V31" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="32">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>10:03 - 2nd Half</t>
+          <t>3:42 - 2nd Half</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -3162,7 +3162,7 @@
         <v>2</v>
       </c>
       <c r="P33" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="Q33" t="n">
         <v>3</v>
@@ -3216,11 +3216,11 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>15:56 - 1st Half</t>
+          <t>8:35 - 1st Half</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I34" t="n">
         <v>2</v>
@@ -3229,10 +3229,10 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -3244,7 +3244,7 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Q34" t="n">
         <v>1</v>
@@ -3283,68 +3283,68 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Shawn Phillips Jr.</t>
+          <t>Amari Evans</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>3:42 - 2nd Half</t>
         </is>
       </c>
       <c r="H35" t="n">
         <v>19</v>
       </c>
       <c r="I35" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>9</v>
+      </c>
+      <c r="R35" t="n">
+        <v>18</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2</v>
+      </c>
+      <c r="T35" t="n">
+        <v>6</v>
+      </c>
+      <c r="U35" t="n">
         <v>4</v>
       </c>
-      <c r="N35" t="n">
-        <v>4</v>
-      </c>
-      <c r="O35" t="n">
-        <v>4</v>
-      </c>
-      <c r="P35" t="n">
-        <v>36</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>5</v>
-      </c>
-      <c r="R35" t="n">
-        <v>8</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
-        <v>3</v>
-      </c>
       <c r="V35" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36">
@@ -3365,12 +3365,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Malique Ewin</t>
+          <t>Shawn Phillips Jr.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ARK</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3384,49 +3384,49 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I36" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J36" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P36" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="Q36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R36" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
+        <v>3</v>
+      </c>
+      <c r="V36" t="n">
         <v>4</v>
-      </c>
-      <c r="V36" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="37">
@@ -3447,56 +3447,56 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>AK Okereke</t>
+          <t>Malique Ewin</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>ARK</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>10:03 - 2nd Half</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I37" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O37" t="n">
         <v>3</v>
       </c>
       <c r="P37" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="Q37" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R37" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -3508,7 +3508,7 @@
         <v>4</v>
       </c>
       <c r="V37" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38">
@@ -3529,68 +3529,68 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Nordin Kapic</t>
+          <t>AK Okereke</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>3:42 - 2nd Half</t>
         </is>
       </c>
       <c r="H38" t="n">
+        <v>15</v>
+      </c>
+      <c r="I38" t="n">
         <v>13</v>
       </c>
-      <c r="I38" t="n">
-        <v>12</v>
-      </c>
       <c r="J38" t="n">
+        <v>3</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" t="n">
         <v>4</v>
       </c>
-      <c r="K38" t="n">
-        <v>1</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" t="n">
-        <v>1</v>
-      </c>
-      <c r="N38" t="n">
-        <v>2</v>
-      </c>
-      <c r="O38" t="n">
-        <v>2</v>
-      </c>
       <c r="P38" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q38" t="n">
         <v>4</v>
       </c>
       <c r="R38" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>4</v>
+      </c>
+      <c r="V38" t="n">
         <v>5</v>
-      </c>
-      <c r="U38" t="n">
-        <v>2</v>
-      </c>
-      <c r="V38" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -3611,68 +3611,68 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Trent Pierce</t>
+          <t>Nordin Kapic</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H39" t="n">
+        <v>13</v>
+      </c>
+      <c r="I39" t="n">
         <v>12</v>
       </c>
-      <c r="I39" t="n">
-        <v>13</v>
-      </c>
       <c r="J39" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P39" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="Q39" t="n">
+        <v>4</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2</v>
+      </c>
+      <c r="T39" t="n">
         <v>5</v>
       </c>
-      <c r="R39" t="n">
-        <v>11</v>
-      </c>
-      <c r="S39" t="n">
-        <v>3</v>
-      </c>
-      <c r="T39" t="n">
-        <v>7</v>
-      </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -3693,38 +3693,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Amari Evans</t>
+          <t>Trent Pierce</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>10:03 - 2nd Half</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I40" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J40" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -3733,28 +3733,28 @@
         <v>1</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P40" t="n">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="Q40" t="n">
+        <v>5</v>
+      </c>
+      <c r="R40" t="n">
+        <v>11</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3</v>
+      </c>
+      <c r="T40" t="n">
         <v>7</v>
       </c>
-      <c r="R40" t="n">
-        <v>15</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" t="n">
-        <v>3</v>
-      </c>
       <c r="U40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -3939,68 +3939,68 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Travis Perry</t>
+          <t>Chandler Bing</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>3:42 - 2nd Half</t>
         </is>
       </c>
       <c r="H43" t="n">
+        <v>8</v>
+      </c>
+      <c r="I43" t="n">
+        <v>9</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>2</v>
+      </c>
+      <c r="P43" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>4</v>
+      </c>
+      <c r="R43" t="n">
         <v>6</v>
       </c>
-      <c r="I43" t="n">
-        <v>2</v>
-      </c>
-      <c r="J43" t="n">
-        <v>3</v>
-      </c>
-      <c r="K43" t="n">
-        <v>3</v>
-      </c>
-      <c r="L43" t="n">
-        <v>2</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" t="n">
-        <v>1</v>
-      </c>
-      <c r="O43" t="n">
-        <v>1</v>
-      </c>
-      <c r="P43" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" t="n">
-        <v>3</v>
-      </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -4021,41 +4021,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>DeWayne Brown II</t>
+          <t>Travis Perry</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>10:03 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
         <v>1</v>
@@ -4070,19 +4070,19 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -4103,62 +4103,62 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Eli Ellis</t>
+          <t>Achor Achor</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>8:35 - 1st Half</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K45" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
@@ -4185,62 +4185,62 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Elijah Strong</t>
+          <t>Bishop Boswell</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>3:42 - 2nd Half</t>
         </is>
       </c>
       <c r="H46" t="n">
+        <v>5</v>
+      </c>
+      <c r="I46" t="n">
+        <v>5</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
         <v>4</v>
       </c>
-      <c r="I46" t="n">
-        <v>7</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="n">
-        <v>1</v>
-      </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O46" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P46" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="Q46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R46" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="S46" t="n">
         <v>1</v>
       </c>
       <c r="T46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Ethan Burg</t>
+          <t>DeWayne Brown II</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4282,18 +4282,18 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>10:03 - 2nd Half</t>
+          <t>3:42 - 2nd Half</t>
         </is>
       </c>
       <c r="H47" t="n">
+        <v>5</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
         <v>4</v>
       </c>
-      <c r="I47" t="n">
-        <v>4</v>
-      </c>
-      <c r="J47" t="n">
-        <v>0</v>
-      </c>
       <c r="K47" t="n">
         <v>2</v>
       </c>
@@ -4301,34 +4301,34 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P47" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -4349,62 +4349,62 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>T.O. Barrett</t>
+          <t>Jamarion Davis-Fleming</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>8:35 - 1st Half</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I48" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P48" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="Q48" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
         <v>2</v>
@@ -4431,35 +4431,35 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Kezza Giffa</t>
+          <t>Kanon Catchings</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>8:35 - 1st Half</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -4468,31 +4468,31 @@
         <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P49" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="Q49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R49" t="n">
         <v>4</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T49" t="n">
         <v>1</v>
       </c>
       <c r="U49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -4513,62 +4513,62 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Troy Henderson</t>
+          <t>Eli Ellis</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>10:03 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I50" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K50" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P50" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="Q50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U50" t="n">
         <v>0</v>
@@ -4595,62 +4595,62 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Achor Achor</t>
+          <t>Elijah Strong</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>MSST</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>15:56 - 1st Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N51" t="n">
         <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P51" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U51" t="n">
         <v>0</v>
@@ -4677,12 +4677,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Chandler Bing</t>
+          <t>Ethan Burg</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -4692,20 +4692,20 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>10:03 - 2nd Half</t>
+          <t>3:42 - 2nd Half</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I52" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -4717,28 +4717,28 @@
         <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P52" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U52" t="n">
         <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Sergej Macura</t>
+          <t>Ja'Borri McGhee</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -4774,14 +4774,14 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>15:56 - 1st Half</t>
+          <t>8:35 - 1st Half</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I53" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -4790,31 +4790,31 @@
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U53" t="n">
         <v>0</v>
@@ -4841,29 +4841,29 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Zach Day</t>
+          <t>Sergej Macura</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>8:35 - 1st Half</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J54" t="n">
         <v>1</v>
@@ -4872,10 +4872,10 @@
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
         <v>0</v>
@@ -4884,13 +4884,13 @@
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -4923,35 +4923,35 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Bishop Boswell</t>
+          <t>T.O. Barrett</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>10:03 - 2nd Half</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L55" t="n">
         <v>1</v>
@@ -4963,28 +4963,28 @@
         <v>2</v>
       </c>
       <c r="O55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P55" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="Q55" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R55" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="S55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Corey Chest</t>
+          <t>Kezza Giffa</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5024,16 +5024,16 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -5042,31 +5042,31 @@
         <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P56" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>1</v>
+      </c>
+      <c r="R56" t="n">
         <v>4</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" t="n">
-        <v>0</v>
-      </c>
       <c r="S56" t="n">
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -5087,32 +5087,32 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>EJ Walker</t>
+          <t>Troy Henderson</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>3:42 - 2nd Half</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J57" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
         <v>1</v>
@@ -5124,25 +5124,25 @@
         <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R57" t="n">
         <v>2</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U57" t="n">
         <v>0</v>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Grant Polk</t>
+          <t>Zach Day</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -5188,13 +5188,13 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I58" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -5203,28 +5203,28 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N58" t="n">
         <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U58" t="n">
         <v>0</v>
@@ -5251,22 +5251,22 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Jamarion Davis-Fleming</t>
+          <t>Corey Chest</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>MSST</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>15:56 - 1st Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H59" t="n">
@@ -5276,10 +5276,10 @@
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -5333,12 +5333,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Patton Pinkins</t>
+          <t>EJ Walker</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -5355,34 +5355,34 @@
         <v>1</v>
       </c>
       <c r="I60" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K60" t="n">
         <v>1</v>
       </c>
       <c r="L60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
         <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P60" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="Q60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -5415,32 +5415,32 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Amaree Abram</t>
+          <t>Grant Polk</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>10:03 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -5455,22 +5455,22 @@
         <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P61" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T61" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U61" t="n">
         <v>0</v>
@@ -5497,38 +5497,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Isaiah Sealy</t>
+          <t>Patton Pinkins</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ARK</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K62" t="n">
         <v>1</v>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
@@ -5540,19 +5540,19 @@
         <v>1</v>
       </c>
       <c r="P62" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U62" t="n">
         <v>0</v>
@@ -5579,12 +5579,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Jayden Leverett</t>
+          <t>Amaree Abram</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>10:03 - 2nd Half</t>
+          <t>3:42 - 2nd Half</t>
         </is>
       </c>
       <c r="H63" t="n">
@@ -5604,7 +5604,7 @@
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -5619,16 +5619,16 @@
         <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -5661,22 +5661,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Jordan Butler</t>
+          <t>Isaiah Sealy</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ARK</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H64" t="n">
@@ -5689,7 +5689,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
@@ -5698,13 +5698,13 @@
         <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P64" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -5743,22 +5743,22 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Trent Burns</t>
+          <t>Jayden Leverett</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>3:42 - 2nd Half</t>
         </is>
       </c>
       <c r="H65" t="n">
@@ -5768,7 +5768,7 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -5783,16 +5783,16 @@
         <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P65" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Tyler Harris</t>
+          <t>Jordan Butler</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>10:03 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H66" t="n">
@@ -5868,7 +5868,7 @@
         <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Kanon Catchings</t>
+          <t>Justin Abson</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -5922,17 +5922,17 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>15:56 - 1st Half</t>
+          <t>8:35 - 1st Half</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -5950,13 +5950,13 @@
         <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -5989,7 +5989,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Kareem Stagg</t>
+          <t>Justin Bailey</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6004,11 +6004,11 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>15:56 - 1st Half</t>
+          <t>8:35 - 1st Half</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I68" t="n">
         <v>0</v>
@@ -6020,16 +6020,16 @@
         <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M68" t="n">
         <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P68" t="n">
         <v>2</v>
@@ -6038,13 +6038,13 @@
         <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U68" t="n">
         <v>0</v>
@@ -6071,26 +6071,26 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Max Smith</t>
+          <t>Trent Burns</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I69" t="n">
         <v>0</v>
@@ -6114,19 +6114,19 @@
         <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
       </c>
       <c r="T69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U69" t="n">
         <v>0</v>
@@ -6153,67 +6153,395 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
+          <t>Tyler Harris</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>VAN</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>VAN@TENN</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>3:42 - 2nd Half</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
+      </c>
+      <c r="V70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Dylan James</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>UGA</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>UGA@MSST</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>8:35 - 1st Half</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="n">
+        <v>1</v>
+      </c>
+      <c r="S71" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
           <t>Jordan Ross</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>UGA</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>UGA@MSST</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>15:56 - 1st Half</t>
-        </is>
-      </c>
-      <c r="H70" t="n">
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>8:35 - 1st Half</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I72" t="n">
+        <v>3</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" t="n">
+        <v>2</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>1</v>
+      </c>
+      <c r="R72" t="n">
+        <v>3</v>
+      </c>
+      <c r="S72" t="n">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
+      </c>
+      <c r="V72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Max Smith</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>MISS</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>SC@MISS</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>1</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>1</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
+      </c>
+      <c r="V73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Kareem Stagg</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>UGA</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>UGA@MSST</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>8:35 - 1st Half</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
         <v>-3</v>
       </c>
-      <c r="I70" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" t="n">
-        <v>0</v>
-      </c>
-      <c r="M70" t="n">
-        <v>0</v>
-      </c>
-      <c r="N70" t="n">
-        <v>2</v>
-      </c>
-      <c r="O70" t="n">
-        <v>0</v>
-      </c>
-      <c r="P70" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
-      <c r="R70" t="n">
-        <v>1</v>
-      </c>
-      <c r="S70" t="n">
-        <v>0</v>
-      </c>
-      <c r="T70" t="n">
-        <v>0</v>
-      </c>
-      <c r="U70" t="n">
-        <v>0</v>
-      </c>
-      <c r="V70" t="n">
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" t="n">
+        <v>1</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="n">
+        <v>2</v>
+      </c>
+      <c r="S74" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
+      </c>
+      <c r="V74" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6256,14 +6584,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>The Backslashers</t>
+          <t>The Oddities</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -6273,7 +6601,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C3" t="n">
         <v>2</v>
@@ -6282,24 +6610,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>The Oddities</t>
+          <t>Bend Rimmers</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bend Rimmers</t>
+          <t>The Backslashers</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="C5" t="n">
         <v>3</v>
@@ -6338,7 +6666,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C8" t="n">
         <v>2</v>

--- a/docs/Today_PoohPoints_SEC_ByOwner_2026-03-07.xlsx
+++ b/docs/Today_PoohPoints_SEC_ByOwner_2026-03-07.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V74"/>
+  <dimension ref="A1:V89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -429,7 +429,7 @@
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
     <col width="6" customWidth="1" min="8" max="8"/>
     <col width="5" customWidth="1" min="9" max="9"/>
     <col width="5" customWidth="1" min="10" max="10"/>
@@ -741,68 +741,68 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Devin McGlockton</t>
+          <t>Jeremiah Wilkinson</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3:42 - 2nd Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H4" t="n">
+        <v>11</v>
+      </c>
+      <c r="I4" t="n">
+        <v>12</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R4" t="n">
         <v>8</v>
       </c>
-      <c r="I4" t="n">
-        <v>8</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P4" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3</v>
-      </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="n">
         <v>6</v>
       </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1</v>
-      </c>
       <c r="U4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -823,65 +823,65 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Jeremiah Wilkinson</t>
+          <t>Devin McGlockton</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>8:35 - 1st Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J5" t="n">
         <v>4</v>
       </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
       <c r="K5" t="n">
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3</v>
+      </c>
+      <c r="R5" t="n">
         <v>6</v>
       </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2</v>
-      </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V5" t="n">
         <v>2</v>
@@ -1151,68 +1151,68 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ja'Kobi Gillespie</t>
+          <t>Thomas Haugh</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>3:42 - 2nd Half</t>
+          <t>11:43 - 1st Half</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>-7</v>
+        <v>5</v>
       </c>
       <c r="I9" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P9" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1228,73 +1228,73 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Meleek Thomas</t>
+          <t>Ja'Kobi Gillespie</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ARK</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="J10" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
         <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P10" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="Q10" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="R10" t="n">
         <v>22</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T10" t="n">
+        <v>11</v>
+      </c>
+      <c r="U10" t="n">
         <v>6</v>
       </c>
-      <c r="U10" t="n">
-        <v>5</v>
-      </c>
       <c r="V10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -1315,65 +1315,65 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Malik Dia</t>
+          <t>Meleek Thomas</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>ARK</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H11" t="n">
+        <v>24</v>
+      </c>
+      <c r="I11" t="n">
+        <v>28</v>
+      </c>
+      <c r="J11" t="n">
+        <v>7</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3</v>
+      </c>
+      <c r="P11" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>9</v>
+      </c>
+      <c r="R11" t="n">
         <v>22</v>
       </c>
-      <c r="I11" t="n">
-        <v>22</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="n">
-        <v>4</v>
-      </c>
-      <c r="P11" t="n">
-        <v>21</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>8</v>
-      </c>
-      <c r="R11" t="n">
-        <v>13</v>
-      </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V11" t="n">
         <v>6</v>
@@ -1397,68 +1397,68 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Felix Okpara</t>
+          <t>Malik Dia</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>3:42 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I12" t="n">
+        <v>22</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>4</v>
+      </c>
+      <c r="P12" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>8</v>
+      </c>
+      <c r="R12" t="n">
+        <v>13</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
         <v>6</v>
       </c>
-      <c r="J12" t="n">
-        <v>10</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>4</v>
-      </c>
-      <c r="N12" t="n">
-        <v>2</v>
-      </c>
-      <c r="O12" t="n">
-        <v>2</v>
-      </c>
-      <c r="P12" t="n">
-        <v>29</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2</v>
-      </c>
-      <c r="R12" t="n">
-        <v>3</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2</v>
-      </c>
       <c r="V12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -1479,32 +1479,32 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Jayden Epps</t>
+          <t>Felix Okpara</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MSST</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>8:35 - 1st Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>-2</v>
+        <v>19</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1513,34 +1513,34 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P13" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1551,66 +1551,66 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hilton Heads</t>
+          <t>The Backslashers</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Mark Mitchell</t>
+          <t>Jayden Epps</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="I14" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="J14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P14" t="n">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="Q14" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1619,10 +1619,10 @@
         <v>3</v>
       </c>
       <c r="U14" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1633,72 +1633,72 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hilton Heads</t>
+          <t>The Backslashers</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Tyler Nickel</t>
+          <t>Denzel Aberdeen</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>3:42 - 2nd Half</t>
+          <t>11:43 - 1st Half</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="Q15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Hilton Heads</t>
+          <t>The Backslashers</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1725,38 +1725,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Ilias Kamardine</t>
+          <t>Micah Handlogten</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>11:43 - 1st Half</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -1765,22 +1765,22 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -1802,73 +1802,73 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Quincy Ballard</t>
+          <t>Mark Mitchell</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MSST</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>8:35 - 1st Half</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L17" t="n">
         <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Three Dawg Nite</t>
+          <t>Hilton Heads</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1889,35 +1889,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Jayden Stone</t>
+          <t>Tyler Nickel</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I18" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
         <v>2</v>
@@ -1926,28 +1926,28 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="S18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V18" t="n">
         <v>2</v>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Three Dawg Nite</t>
+          <t>Hilton Heads</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1971,68 +1971,68 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>AJ Storr</t>
+          <t>Collin Chandler</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>11:43 - 1st Half</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>8</v>
+        <v>-2</v>
       </c>
       <c r="I19" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="Q19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Three Dawg Nite</t>
+          <t>Hilton Heads</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2053,68 +2053,68 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Anthony Robinson II</t>
+          <t>Quincy Ballard</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Three Dawg Nite</t>
+          <t>Hilton Heads</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Myles Stute</t>
+          <t>Ilias Kamardine</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2154,43 +2154,43 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I21" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P21" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="Q21" t="n">
         <v>2</v>
       </c>
       <c r="R21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -2212,73 +2212,73 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Jaylen Carey</t>
+          <t>Jayden Stone</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>3:42 - 2nd Half</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H22" t="n">
+        <v>12</v>
+      </c>
+      <c r="I22" t="n">
+        <v>11</v>
+      </c>
+      <c r="J22" t="n">
+        <v>6</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2</v>
+      </c>
+      <c r="P22" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>4</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
         <v>5</v>
       </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>5</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>3</v>
-      </c>
-      <c r="P22" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -2294,73 +2294,73 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Nick Pringle</t>
+          <t>AJ Storr</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ARK</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I23" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="Q23" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R23" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bend Rimmers</t>
+          <t>Three Dawg Nite</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2381,56 +2381,56 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>J.P. Estrella</t>
+          <t>Alex Condon</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>3:42 - 2nd Half</t>
+          <t>11:43 - 1st Half</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="I24" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="J24" t="n">
+        <v>2</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2</v>
+      </c>
+      <c r="P24" t="n">
         <v>8</v>
       </c>
-      <c r="K24" t="n">
-        <v>2</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>3</v>
-      </c>
-      <c r="P24" t="n">
-        <v>20</v>
-      </c>
       <c r="Q24" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -2442,7 +2442,7 @@
         <v>1</v>
       </c>
       <c r="V24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bend Rimmers</t>
+          <t>Three Dawg Nite</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2463,56 +2463,56 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Duke Miles</t>
+          <t>Otega Oweh</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>3:42 - 2nd Half</t>
+          <t>11:43 - 1st Half</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P25" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="Q25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2521,10 +2521,10 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -2535,48 +2535,48 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Bend Rimmers</t>
+          <t>Three Dawg Nite</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Somtochukwu Cyril</t>
+          <t>Anthony Robinson II</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>8:35 - 1st Half</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -2585,28 +2585,28 @@
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P26" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -2617,72 +2617,72 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>G-Flop</t>
+          <t>Three Dawg Nite</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Blue Cain</t>
+          <t>Myles Stute</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>8:35 - 1st Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H27" t="n">
+        <v>8</v>
+      </c>
+      <c r="I27" t="n">
         <v>6</v>
       </c>
-      <c r="I27" t="n">
-        <v>3</v>
-      </c>
       <c r="J27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P27" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -2699,45 +2699,45 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>G-Flop</t>
+          <t>Three Dawg Nite</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Josh Hubbard</t>
+          <t>Jaylen Carey</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>MSST</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>8:35 - 1st Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H28" t="n">
         <v>5</v>
       </c>
       <c r="I28" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -2746,25 +2746,25 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P28" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>G-Flop</t>
+          <t>Three Dawg Nite</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2791,68 +2791,68 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Kobe Knox</t>
+          <t>Nick Pringle</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ARK</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I29" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J29" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P29" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="Q29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R29" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>G-Flop</t>
+          <t>Three Dawg Nite</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2873,22 +2873,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Marcus Millender</t>
+          <t>Boogie Fland</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>8:35 - 1st Half</t>
+          <t>11:43 - 1st Half</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -2910,19 +2910,19 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q30" t="n">
         <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>The Oddities</t>
+          <t>Bend Rimmers</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Tyler Tanner</t>
+          <t>J.P. Estrella</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2970,53 +2970,53 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>3:42 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I31" t="n">
+        <v>20</v>
+      </c>
+      <c r="J31" t="n">
+        <v>10</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>3</v>
+      </c>
+      <c r="P31" t="n">
         <v>23</v>
       </c>
-      <c r="J31" t="n">
-        <v>3</v>
-      </c>
-      <c r="K31" t="n">
-        <v>3</v>
-      </c>
-      <c r="L31" t="n">
-        <v>2</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>1</v>
-      </c>
-      <c r="O31" t="n">
-        <v>1</v>
-      </c>
-      <c r="P31" t="n">
-        <v>32</v>
-      </c>
       <c r="Q31" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R31" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="S31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T31" t="n">
         <v>2</v>
       </c>
       <c r="U31" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="V31" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>The Oddities</t>
+          <t>Bend Rimmers</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3037,17 +3037,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Mike Sharavjamts</t>
+          <t>Duke Miles</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3056,28 +3056,28 @@
         </is>
       </c>
       <c r="H32" t="n">
+        <v>14</v>
+      </c>
+      <c r="I32" t="n">
         <v>13</v>
       </c>
-      <c r="I32" t="n">
-        <v>7</v>
-      </c>
       <c r="J32" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K32" t="n">
         <v>2</v>
       </c>
       <c r="L32" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O32" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P32" t="n">
         <v>30</v>
@@ -3086,19 +3086,19 @@
         <v>3</v>
       </c>
       <c r="R32" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="V32" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33">
@@ -3109,66 +3109,66 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>The Oddities</t>
+          <t>Bend Rimmers</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Jalen Washington</t>
+          <t>Somtochukwu Cyril</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>3:42 - 2nd Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H33" t="n">
         <v>10</v>
       </c>
       <c r="I33" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J33" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="Q33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R33" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -3180,7 +3180,7 @@
         <v>1</v>
       </c>
       <c r="V33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>The Oddities</t>
+          <t>Bend Rimmers</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3201,51 +3201,51 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Shawn Jones Jr.</t>
+          <t>Xaivian Lee</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>MSST</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>8:35 - 1st Half</t>
+          <t>11:43 - 1st Half</t>
         </is>
       </c>
       <c r="H34" t="n">
+        <v>4</v>
+      </c>
+      <c r="I34" t="n">
+        <v>3</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
         <v>5</v>
       </c>
-      <c r="I34" t="n">
-        <v>2</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>1</v>
-      </c>
-      <c r="L34" t="n">
-        <v>2</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>8</v>
-      </c>
       <c r="Q34" t="n">
         <v>1</v>
       </c>
@@ -3253,10 +3253,10 @@
         <v>1</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
@@ -3273,7 +3273,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Undrafted</t>
+          <t>Bend Rimmers</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3283,68 +3283,68 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Amari Evans</t>
+          <t>Malachi Moreno</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>3:42 - 2nd Half</t>
+          <t>11:43 - 1st Half</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="Q35" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -3355,78 +3355,78 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Undrafted</t>
+          <t>G-Flop</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Shawn Phillips Jr.</t>
+          <t>Josh Hubbard</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I36" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J36" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" t="n">
+        <v>4</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>3</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>7</v>
+      </c>
+      <c r="R36" t="n">
         <v>10</v>
       </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>4</v>
-      </c>
-      <c r="N36" t="n">
-        <v>4</v>
-      </c>
-      <c r="O36" t="n">
-        <v>4</v>
-      </c>
-      <c r="P36" t="n">
-        <v>36</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>5</v>
-      </c>
-      <c r="R36" t="n">
-        <v>8</v>
-      </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -3437,66 +3437,66 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Undrafted</t>
+          <t>G-Flop</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Malique Ewin</t>
+          <t>Blue Cain</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ARK</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="I37" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="J37" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L37" t="n">
         <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P37" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="Q37" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R37" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -3505,10 +3505,10 @@
         <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -3519,45 +3519,45 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Undrafted</t>
+          <t>G-Flop</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>AK Okereke</t>
+          <t>Rueben Chinyelu</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>3:42 - 2nd Half</t>
+          <t>11:43 - 1st Half</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I38" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -3566,31 +3566,31 @@
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="Q38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R38" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Undrafted</t>
+          <t>G-Flop</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Nordin Kapic</t>
+          <t>Kobe Knox</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3630,22 +3630,22 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I39" t="n">
         <v>12</v>
       </c>
       <c r="J39" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
         <v>2</v>
@@ -3654,25 +3654,25 @@
         <v>2</v>
       </c>
       <c r="P39" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="Q39" t="n">
         <v>4</v>
       </c>
       <c r="R39" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="S39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V39" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Undrafted</t>
+          <t>G-Flop</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3693,68 +3693,68 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Trent Pierce</t>
+          <t>Marcus Millender</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I40" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J40" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="Q40" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R40" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T40" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Undrafted</t>
+          <t>G-Flop</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3775,68 +3775,68 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>D.J. Wagner</t>
+          <t>Mouhamed Dioubate</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ARK</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>11:43 - 1st Half</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I41" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J41" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>1</v>
+      </c>
+      <c r="O41" t="n">
+        <v>2</v>
+      </c>
+      <c r="P41" t="n">
         <v>4</v>
       </c>
-      <c r="K41" t="n">
-        <v>5</v>
-      </c>
-      <c r="L41" t="n">
-        <v>1</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" t="n">
-        <v>3</v>
-      </c>
-      <c r="O41" t="n">
-        <v>3</v>
-      </c>
-      <c r="P41" t="n">
-        <v>45</v>
-      </c>
       <c r="Q41" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T41" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -3847,27 +3847,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Undrafted</t>
+          <t>The Oddities</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Eduardo Klafke</t>
+          <t>Tyler Tanner</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3876,49 +3876,49 @@
         </is>
       </c>
       <c r="H42" t="n">
+        <v>27</v>
+      </c>
+      <c r="I42" t="n">
+        <v>25</v>
+      </c>
+      <c r="J42" t="n">
+        <v>3</v>
+      </c>
+      <c r="K42" t="n">
+        <v>3</v>
+      </c>
+      <c r="L42" t="n">
+        <v>2</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>3</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1</v>
+      </c>
+      <c r="P42" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>7</v>
+      </c>
+      <c r="R42" t="n">
         <v>9</v>
       </c>
-      <c r="I42" t="n">
-        <v>5</v>
-      </c>
-      <c r="J42" t="n">
-        <v>6</v>
-      </c>
-      <c r="K42" t="n">
-        <v>1</v>
-      </c>
-      <c r="L42" t="n">
-        <v>2</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" t="n">
-        <v>1</v>
-      </c>
-      <c r="O42" t="n">
-        <v>2</v>
-      </c>
-      <c r="P42" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>1</v>
-      </c>
-      <c r="R42" t="n">
-        <v>5</v>
-      </c>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T42" t="n">
         <v>2</v>
       </c>
       <c r="U42" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="V42" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43">
@@ -3929,78 +3929,78 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Undrafted</t>
+          <t>The Oddities</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Chandler Bing</t>
+          <t>Mike Sharavjamts</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>3:42 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H43" t="n">
+        <v>13</v>
+      </c>
+      <c r="I43" t="n">
+        <v>7</v>
+      </c>
+      <c r="J43" t="n">
+        <v>9</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1</v>
+      </c>
+      <c r="N43" t="n">
+        <v>1</v>
+      </c>
+      <c r="O43" t="n">
+        <v>2</v>
+      </c>
+      <c r="P43" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>3</v>
+      </c>
+      <c r="R43" t="n">
         <v>8</v>
       </c>
-      <c r="I43" t="n">
-        <v>9</v>
-      </c>
-      <c r="J43" t="n">
-        <v>1</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" t="n">
-        <v>2</v>
-      </c>
-      <c r="P43" t="n">
-        <v>21</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>4</v>
-      </c>
-      <c r="R43" t="n">
-        <v>6</v>
-      </c>
       <c r="S43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
         <v>2</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Undrafted</t>
+          <t>The Oddities</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4021,17 +4021,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Travis Perry</t>
+          <t>Jalen Washington</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -4040,46 +4040,46 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I44" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J44" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N44" t="n">
         <v>1</v>
       </c>
       <c r="O44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P44" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R44" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V44" t="n">
         <v>2</v>
@@ -4093,7 +4093,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Undrafted</t>
+          <t>The Oddities</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Achor Achor</t>
+          <t>Shawn Jones Jr.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4118,23 +4118,23 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>8:35 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I45" t="n">
         <v>2</v>
       </c>
       <c r="J45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -4146,7 +4146,7 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="Q45" t="n">
         <v>1</v>
@@ -4185,7 +4185,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Bishop Boswell</t>
+          <t>Amari Evans</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4200,53 +4200,53 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>3:42 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="I46" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>3</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>1</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>9</v>
+      </c>
+      <c r="R46" t="n">
+        <v>18</v>
+      </c>
+      <c r="S46" t="n">
+        <v>2</v>
+      </c>
+      <c r="T46" t="n">
+        <v>6</v>
+      </c>
+      <c r="U46" t="n">
         <v>4</v>
       </c>
-      <c r="L46" t="n">
-        <v>2</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
-        <v>2</v>
-      </c>
-      <c r="O46" t="n">
-        <v>4</v>
-      </c>
-      <c r="P46" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>2</v>
-      </c>
-      <c r="R46" t="n">
-        <v>6</v>
-      </c>
-      <c r="S46" t="n">
-        <v>1</v>
-      </c>
-      <c r="T46" t="n">
-        <v>1</v>
-      </c>
-      <c r="U46" t="n">
-        <v>0</v>
-      </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47">
@@ -4267,68 +4267,68 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>DeWayne Brown II</t>
+          <t>Shawn Phillips Jr.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>3:42 - 2nd Half</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H47" t="n">
+        <v>19</v>
+      </c>
+      <c r="I47" t="n">
+        <v>13</v>
+      </c>
+      <c r="J47" t="n">
+        <v>10</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>4</v>
+      </c>
+      <c r="N47" t="n">
+        <v>4</v>
+      </c>
+      <c r="O47" t="n">
+        <v>4</v>
+      </c>
+      <c r="P47" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q47" t="n">
         <v>5</v>
       </c>
-      <c r="I47" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" t="n">
+      <c r="R47" t="n">
+        <v>8</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>3</v>
+      </c>
+      <c r="V47" t="n">
         <v>4</v>
-      </c>
-      <c r="K47" t="n">
-        <v>2</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" t="n">
-        <v>1</v>
-      </c>
-      <c r="N47" t="n">
-        <v>1</v>
-      </c>
-      <c r="O47" t="n">
-        <v>1</v>
-      </c>
-      <c r="P47" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
-      <c r="R47" t="n">
-        <v>1</v>
-      </c>
-      <c r="S47" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" t="n">
-        <v>0</v>
-      </c>
-      <c r="U47" t="n">
-        <v>0</v>
-      </c>
-      <c r="V47" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -4349,68 +4349,68 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Jamarion Davis-Fleming</t>
+          <t>AK Okereke</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>MSST</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>8:35 - 1st Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H48" t="n">
+        <v>17</v>
+      </c>
+      <c r="I48" t="n">
+        <v>17</v>
+      </c>
+      <c r="J48" t="n">
+        <v>4</v>
+      </c>
+      <c r="K48" t="n">
+        <v>3</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>1</v>
+      </c>
+      <c r="O48" t="n">
         <v>5</v>
       </c>
-      <c r="I48" t="n">
-        <v>2</v>
-      </c>
-      <c r="J48" t="n">
-        <v>2</v>
-      </c>
-      <c r="K48" t="n">
-        <v>1</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" t="n">
-        <v>1</v>
-      </c>
       <c r="P48" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>5</v>
+      </c>
+      <c r="R48" t="n">
+        <v>8</v>
+      </c>
+      <c r="S48" t="n">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
         <v>6</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" t="n">
-        <v>0</v>
-      </c>
-      <c r="U48" t="n">
-        <v>2</v>
-      </c>
       <c r="V48" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49">
@@ -4431,68 +4431,68 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Kanon Catchings</t>
+          <t>Malique Ewin</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>ARK</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>8:35 - 1st Half</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="I49" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="J49" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P49" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="Q49" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R49" t="n">
+        <v>12</v>
+      </c>
+      <c r="S49" t="n">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
         <v>4</v>
       </c>
-      <c r="S49" t="n">
-        <v>1</v>
-      </c>
-      <c r="T49" t="n">
-        <v>1</v>
-      </c>
-      <c r="U49" t="n">
-        <v>0</v>
-      </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50">
@@ -4513,7 +4513,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Eli Ellis</t>
+          <t>Nordin Kapic</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4532,49 +4532,49 @@
         </is>
       </c>
       <c r="H50" t="n">
+        <v>13</v>
+      </c>
+      <c r="I50" t="n">
+        <v>12</v>
+      </c>
+      <c r="J50" t="n">
         <v>4</v>
       </c>
-      <c r="I50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" t="n">
-        <v>2</v>
-      </c>
       <c r="K50" t="n">
+        <v>1</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1</v>
+      </c>
+      <c r="N50" t="n">
+        <v>2</v>
+      </c>
+      <c r="O50" t="n">
+        <v>2</v>
+      </c>
+      <c r="P50" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>4</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7</v>
+      </c>
+      <c r="S50" t="n">
+        <v>2</v>
+      </c>
+      <c r="T50" t="n">
         <v>5</v>
       </c>
-      <c r="L50" t="n">
-        <v>1</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" t="n">
-        <v>1</v>
-      </c>
-      <c r="O50" t="n">
-        <v>2</v>
-      </c>
-      <c r="P50" t="n">
-        <v>28</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" t="n">
-        <v>3</v>
-      </c>
-      <c r="S50" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" t="n">
-        <v>2</v>
-      </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -4595,68 +4595,68 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Elijah Strong</t>
+          <t>Trent Pierce</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I51" t="n">
+        <v>13</v>
+      </c>
+      <c r="J51" t="n">
+        <v>6</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>1</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>1</v>
+      </c>
+      <c r="O51" t="n">
+        <v>3</v>
+      </c>
+      <c r="P51" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>5</v>
+      </c>
+      <c r="R51" t="n">
+        <v>11</v>
+      </c>
+      <c r="S51" t="n">
+        <v>3</v>
+      </c>
+      <c r="T51" t="n">
         <v>7</v>
       </c>
-      <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="n">
-        <v>1</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>1</v>
-      </c>
-      <c r="N51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" t="n">
-        <v>2</v>
-      </c>
-      <c r="P51" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>3</v>
-      </c>
-      <c r="R51" t="n">
-        <v>8</v>
-      </c>
-      <c r="S51" t="n">
-        <v>1</v>
-      </c>
-      <c r="T51" t="n">
-        <v>3</v>
-      </c>
       <c r="U51" t="n">
         <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -4677,68 +4677,68 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Ethan Burg</t>
+          <t>D.J. Wagner</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>ARK</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>3:42 - 2nd Half</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H52" t="n">
+        <v>9</v>
+      </c>
+      <c r="I52" t="n">
+        <v>10</v>
+      </c>
+      <c r="J52" t="n">
         <v>4</v>
       </c>
-      <c r="I52" t="n">
+      <c r="K52" t="n">
+        <v>5</v>
+      </c>
+      <c r="L52" t="n">
+        <v>1</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>3</v>
+      </c>
+      <c r="O52" t="n">
+        <v>3</v>
+      </c>
+      <c r="P52" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q52" t="n">
         <v>4</v>
       </c>
-      <c r="J52" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" t="n">
-        <v>2</v>
-      </c>
-      <c r="L52" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" t="n">
-        <v>2</v>
-      </c>
-      <c r="P52" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>2</v>
-      </c>
       <c r="R52" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V52" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
@@ -4759,38 +4759,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Ja'Borri McGhee</t>
+          <t>Eduardo Klafke</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>MSST</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>8:35 - 1st Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I53" t="n">
         <v>5</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
@@ -4799,16 +4799,16 @@
         <v>1</v>
       </c>
       <c r="O53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P53" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="Q53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R53" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S53" t="n">
         <v>1</v>
@@ -4817,10 +4817,10 @@
         <v>2</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -4841,62 +4841,62 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Sergej Macura</t>
+          <t>Chandler Bing</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>MSST</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>8:35 - 1st Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H54" t="n">
+        <v>8</v>
+      </c>
+      <c r="I54" t="n">
+        <v>9</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>3</v>
+      </c>
+      <c r="P54" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q54" t="n">
         <v>4</v>
       </c>
-      <c r="I54" t="n">
-        <v>2</v>
-      </c>
-      <c r="J54" t="n">
-        <v>1</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" t="n">
-        <v>1</v>
-      </c>
-      <c r="M54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>1</v>
-      </c>
       <c r="R54" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U54" t="n">
         <v>0</v>
@@ -4923,35 +4923,35 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>T.O. Barrett</t>
+          <t>Ja'Borri McGhee</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I55" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L55" t="n">
         <v>1</v>
@@ -4960,31 +4960,31 @@
         <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P55" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="Q55" t="n">
         <v>4</v>
       </c>
       <c r="R55" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T55" t="n">
         <v>2</v>
       </c>
       <c r="U55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -5005,35 +5005,35 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Kezza Giffa</t>
+          <t>Achor Achor</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I56" t="n">
         <v>4</v>
       </c>
       <c r="J56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -5042,31 +5042,31 @@
         <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="Q56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R56" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -5087,68 +5087,68 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Troy Henderson</t>
+          <t>Travis Perry</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>3:42 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P57" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="Q57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -5169,17 +5169,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Zach Day</t>
+          <t>DeWayne Brown II</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5188,16 +5188,16 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -5206,19 +5206,19 @@
         <v>1</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P58" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -5251,35 +5251,35 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Corey Chest</t>
+          <t>Jamarion Davis-Fleming</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -5291,10 +5291,10 @@
         <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P59" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -5309,10 +5309,10 @@
         <v>0</v>
       </c>
       <c r="U59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -5333,32 +5333,32 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>EJ Walker</t>
+          <t>Kanon Catchings</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J60" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K60" t="n">
         <v>1</v>
@@ -5370,25 +5370,25 @@
         <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>2</v>
       </c>
       <c r="P60" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R60" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U60" t="n">
         <v>0</v>
@@ -5415,17 +5415,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Grant Polk</t>
+          <t>Bishop Boswell</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -5434,43 +5434,43 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I61" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M61" t="n">
         <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O61" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P61" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>2</v>
+      </c>
+      <c r="R61" t="n">
         <v>7</v>
       </c>
-      <c r="Q61" t="n">
-        <v>1</v>
-      </c>
-      <c r="R61" t="n">
-        <v>3</v>
-      </c>
       <c r="S61" t="n">
         <v>1</v>
       </c>
       <c r="T61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U61" t="n">
         <v>0</v>
@@ -5497,12 +5497,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Patton Pinkins</t>
+          <t>Eli Ellis</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -5516,19 +5516,19 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I62" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K62" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
@@ -5537,16 +5537,16 @@
         <v>1</v>
       </c>
       <c r="O62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P62" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -5579,62 +5579,62 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Amaree Abram</t>
+          <t>Elijah Strong</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>3:42 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N63" t="n">
         <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P63" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R63" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T63" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U63" t="n">
         <v>0</v>
@@ -5661,35 +5661,35 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Isaiah Sealy</t>
+          <t>Ethan Burg</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ARK</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
@@ -5698,31 +5698,31 @@
         <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
       </c>
       <c r="T64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U64" t="n">
         <v>0</v>
       </c>
       <c r="V64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -5743,35 +5743,35 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Jayden Leverett</t>
+          <t>Justin Abson</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>3:42 - 2nd Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -5783,16 +5783,16 @@
         <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -5825,38 +5825,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Jordan Butler</t>
+          <t>Sergej Macura</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
@@ -5865,16 +5865,16 @@
         <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P66" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -5883,10 +5883,10 @@
         <v>0</v>
       </c>
       <c r="U66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -5907,68 +5907,68 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Justin Abson</t>
+          <t>T.O. Barrett</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>8:35 - 1st Half</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M67" t="n">
         <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P67" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
       </c>
       <c r="T67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -5989,7 +5989,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Justin Bailey</t>
+          <t>Jordan Ross</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6004,47 +6004,47 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>8:35 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
         <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O68" t="n">
         <v>1</v>
       </c>
       <c r="P68" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U68" t="n">
         <v>0</v>
@@ -6071,35 +6071,35 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Trent Burns</t>
+          <t>Kezza Giffa</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
@@ -6108,31 +6108,31 @@
         <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P69" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
       </c>
       <c r="T69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -6153,12 +6153,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Tyler Harris</t>
+          <t>Troy Henderson</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -6168,20 +6168,20 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>3:42 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I70" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
@@ -6196,19 +6196,19 @@
         <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U70" t="n">
         <v>0</v>
@@ -6235,32 +6235,32 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Dylan James</t>
+          <t>Zach Day</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>8:35 - 1st Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N71" t="n">
         <v>0</v>
@@ -6278,13 +6278,13 @@
         <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -6317,68 +6317,68 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Jordan Ross</t>
+          <t>Amaree Abram</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>8:35 - 1st Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="I72" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K72" t="n">
         <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M72" t="n">
         <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -6399,7 +6399,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Max Smith</t>
+          <t>Corey Chest</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -6418,13 +6418,13 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -6442,19 +6442,19 @@
         <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
       </c>
       <c r="T73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U73" t="n">
         <v>0</v>
@@ -6481,67 +6481,1297 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
+          <t>Dylan James</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>UGA</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>UGA@MSST</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Halftime</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>1</v>
+      </c>
+      <c r="I74" t="n">
+        <v>2</v>
+      </c>
+      <c r="J74" t="n">
+        <v>1</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>1</v>
+      </c>
+      <c r="R74" t="n">
+        <v>3</v>
+      </c>
+      <c r="S74" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
+      </c>
+      <c r="V74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>EJ Walker</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>SC@MISS</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>1</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>5</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" t="n">
+        <v>3</v>
+      </c>
+      <c r="O75" t="n">
+        <v>2</v>
+      </c>
+      <c r="P75" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>2</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Grant Polk</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>SC@MISS</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>1</v>
+      </c>
+      <c r="I76" t="n">
+        <v>3</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" t="n">
+        <v>1</v>
+      </c>
+      <c r="P76" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>1</v>
+      </c>
+      <c r="R76" t="n">
+        <v>3</v>
+      </c>
+      <c r="S76" t="n">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>3</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
+      </c>
+      <c r="V76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Jake Wilkins</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>UGA</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>UGA@MSST</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Halftime</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>1</v>
+      </c>
+      <c r="I77" t="n">
+        <v>2</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>1</v>
+      </c>
+      <c r="R77" t="n">
+        <v>2</v>
+      </c>
+      <c r="S77" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>1</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0</v>
+      </c>
+      <c r="V77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Patton Pinkins</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>MISS</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>SC@MISS</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>1</v>
+      </c>
+      <c r="I78" t="n">
+        <v>4</v>
+      </c>
+      <c r="J78" t="n">
+        <v>1</v>
+      </c>
+      <c r="K78" t="n">
+        <v>1</v>
+      </c>
+      <c r="L78" t="n">
+        <v>2</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" t="n">
+        <v>1</v>
+      </c>
+      <c r="O78" t="n">
+        <v>1</v>
+      </c>
+      <c r="P78" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>2</v>
+      </c>
+      <c r="R78" t="n">
+        <v>8</v>
+      </c>
+      <c r="S78" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>2</v>
+      </c>
+      <c r="U78" t="n">
+        <v>0</v>
+      </c>
+      <c r="V78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Andrija Jelavic</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>FLA@UK</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>11:43 - 1st Half</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" t="n">
+        <v>2</v>
+      </c>
+      <c r="J79" t="n">
+        <v>1</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" t="n">
+        <v>1</v>
+      </c>
+      <c r="P79" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>1</v>
+      </c>
+      <c r="R79" t="n">
+        <v>4</v>
+      </c>
+      <c r="S79" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" t="n">
+        <v>1</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0</v>
+      </c>
+      <c r="V79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Brandon Garrison</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>FLA@UK</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>11:43 - 1st Half</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
+        <v>0</v>
+      </c>
+      <c r="U80" t="n">
+        <v>0</v>
+      </c>
+      <c r="V80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Isaiah Sealy</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>ARK</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>ARK@MIZ</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Final/OT</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" t="n">
+        <v>1</v>
+      </c>
+      <c r="O81" t="n">
+        <v>1</v>
+      </c>
+      <c r="P81" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" t="n">
+        <v>0</v>
+      </c>
+      <c r="U81" t="n">
+        <v>0</v>
+      </c>
+      <c r="V81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Jayden Leverett</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>VAN</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>VAN@TENN</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="n">
+        <v>2</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" t="n">
+        <v>2</v>
+      </c>
+      <c r="P82" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" t="n">
+        <v>2</v>
+      </c>
+      <c r="S82" t="n">
+        <v>0</v>
+      </c>
+      <c r="T82" t="n">
+        <v>0</v>
+      </c>
+      <c r="U82" t="n">
+        <v>0</v>
+      </c>
+      <c r="V82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Jordan Butler</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>SC@MISS</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" t="n">
+        <v>0</v>
+      </c>
+      <c r="T83" t="n">
+        <v>0</v>
+      </c>
+      <c r="U83" t="n">
+        <v>0</v>
+      </c>
+      <c r="V83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Justin Bailey</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>UGA</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>UGA@MSST</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Halftime</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" t="n">
+        <v>1</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" t="n">
+        <v>1</v>
+      </c>
+      <c r="O84" t="n">
+        <v>1</v>
+      </c>
+      <c r="P84" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>0</v>
+      </c>
+      <c r="R84" t="n">
+        <v>0</v>
+      </c>
+      <c r="S84" t="n">
+        <v>0</v>
+      </c>
+      <c r="T84" t="n">
+        <v>0</v>
+      </c>
+      <c r="U84" t="n">
+        <v>0</v>
+      </c>
+      <c r="V84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Trent Burns</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>MIZ</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>ARK@MIZ</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Final/OT</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" t="n">
+        <v>0</v>
+      </c>
+      <c r="T85" t="n">
+        <v>0</v>
+      </c>
+      <c r="U85" t="n">
+        <v>0</v>
+      </c>
+      <c r="V85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Tyler Harris</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>VAN</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>VAN@TENN</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>0</v>
+      </c>
+      <c r="R86" t="n">
+        <v>0</v>
+      </c>
+      <c r="S86" t="n">
+        <v>0</v>
+      </c>
+      <c r="T86" t="n">
+        <v>0</v>
+      </c>
+      <c r="U86" t="n">
+        <v>0</v>
+      </c>
+      <c r="V86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Urban Klavzar</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>FLA</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>FLA@UK</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>11:43 - 1st Half</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" t="n">
+        <v>0</v>
+      </c>
+      <c r="T87" t="n">
+        <v>0</v>
+      </c>
+      <c r="U87" t="n">
+        <v>0</v>
+      </c>
+      <c r="V87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
           <t>Kareem Stagg</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>UGA</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>UGA@MSST</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>8:35 - 1st Half</t>
-        </is>
-      </c>
-      <c r="H74" t="n">
-        <v>-3</v>
-      </c>
-      <c r="I74" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" t="n">
-        <v>0</v>
-      </c>
-      <c r="K74" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" t="n">
-        <v>0</v>
-      </c>
-      <c r="M74" t="n">
-        <v>0</v>
-      </c>
-      <c r="N74" t="n">
-        <v>1</v>
-      </c>
-      <c r="O74" t="n">
-        <v>0</v>
-      </c>
-      <c r="P74" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
-      <c r="R74" t="n">
-        <v>2</v>
-      </c>
-      <c r="S74" t="n">
-        <v>0</v>
-      </c>
-      <c r="T74" t="n">
-        <v>2</v>
-      </c>
-      <c r="U74" t="n">
-        <v>0</v>
-      </c>
-      <c r="V74" t="n">
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Halftime</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I88" t="n">
+        <v>3</v>
+      </c>
+      <c r="J88" t="n">
+        <v>1</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="n">
+        <v>2</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>1</v>
+      </c>
+      <c r="R88" t="n">
+        <v>4</v>
+      </c>
+      <c r="S88" t="n">
+        <v>1</v>
+      </c>
+      <c r="T88" t="n">
+        <v>4</v>
+      </c>
+      <c r="U88" t="n">
+        <v>0</v>
+      </c>
+      <c r="V88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Max Smith</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>MISS</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>SC@MISS</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" t="n">
+        <v>1</v>
+      </c>
+      <c r="S89" t="n">
+        <v>0</v>
+      </c>
+      <c r="T89" t="n">
+        <v>1</v>
+      </c>
+      <c r="U89" t="n">
+        <v>0</v>
+      </c>
+      <c r="V89" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6584,50 +7814,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>The Oddities</t>
+          <t>Bend Rimmers</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hilton Heads</t>
+          <t>The Backslashers</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bend Rimmers</t>
+          <t>The Oddities</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>The Backslashers</t>
+          <t>Hilton Heads</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C5" t="n">
         <v>3</v>
@@ -6636,40 +7866,40 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Three Dawg Nite</t>
+          <t>G-Flop</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Boozers Losers</t>
+          <t>Three Dawg Nite</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G-Flop</t>
+          <t>Boozers Losers</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Today_PoohPoints_SEC_ByOwner_2026-03-07.xlsx
+++ b/docs/Today_PoohPoints_SEC_ByOwner_2026-03-07.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V89"/>
+  <dimension ref="A1:V91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -756,11 +756,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>13:19 - 2nd Half</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I4" t="n">
         <v>12</v>
@@ -784,19 +784,19 @@
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S4" t="n">
         <v>3</v>
       </c>
       <c r="T4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U4" t="n">
         <v>3</v>
@@ -1069,68 +1069,68 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Meechie Johnson</t>
+          <t>Thomas Haugh</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>3:47 - 1st Half</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I8" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="Q8" t="n">
         <v>5</v>
       </c>
       <c r="R8" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="U8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -1151,68 +1151,68 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Thomas Haugh</t>
+          <t>Meechie Johnson</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FLA</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>11:43 - 1st Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H9" t="n">
+        <v>16</v>
+      </c>
+      <c r="I9" t="n">
+        <v>17</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q9" t="n">
         <v>5</v>
       </c>
-      <c r="I9" t="n">
-        <v>3</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1</v>
-      </c>
-      <c r="P9" t="n">
+      <c r="R9" t="n">
+        <v>11</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="n">
         <v>7</v>
       </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1</v>
-      </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -1576,20 +1576,20 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>13:19 - 2nd Half</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1604,19 +1604,19 @@
         <v>1</v>
       </c>
       <c r="P14" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -1643,12 +1643,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Denzel Aberdeen</t>
+          <t>Micah Handlogten</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1658,32 +1658,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>11:43 - 1st Half</t>
+          <t>3:47 - 1st Half</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P15" t="n">
         <v>8</v>
@@ -1692,7 +1692,7 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -1725,12 +1725,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Micah Handlogten</t>
+          <t>Denzel Aberdeen</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FLA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1740,20 +1740,20 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>11:43 - 1st Half</t>
+          <t>3:47 - 1st Half</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1762,25 +1762,25 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -1986,11 +1986,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>11:43 - 1st Half</t>
+          <t>3:47 - 1st Half</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -1999,7 +1999,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2014,7 +2014,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -2068,17 +2068,17 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>13:19 - 2nd Half</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I20" t="n">
         <v>6</v>
       </c>
       <c r="J20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K20" t="n">
         <v>2</v>
@@ -2096,7 +2096,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q20" t="n">
         <v>2</v>
@@ -2299,38 +2299,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>AJ Storr</t>
+          <t>Otega Oweh</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>3:47 - 1st Half</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -2339,28 +2339,28 @@
         <v>1</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P23" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="Q23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R23" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U23" t="n">
         <v>1</v>
       </c>
       <c r="V23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -2396,20 +2396,20 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>11:43 - 1st Half</t>
+          <t>3:47 - 1st Half</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J24" t="n">
         <v>2</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L24" t="n">
         <v>1</v>
@@ -2424,13 +2424,13 @@
         <v>2</v>
       </c>
       <c r="P24" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -2463,38 +2463,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Otega Oweh</t>
+          <t>AJ Storr</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>11:43 - 1st Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -2503,28 +2503,28 @@
         <v>1</v>
       </c>
       <c r="O25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R25" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
         <v>1</v>
       </c>
       <c r="V25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -2709,62 +2709,62 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Jaylen Carey</t>
+          <t>Boogie Fland</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>3:47 - 1st Half</t>
         </is>
       </c>
       <c r="H28" t="n">
+        <v>7</v>
+      </c>
+      <c r="I28" t="n">
         <v>5</v>
       </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
       <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2</v>
+      </c>
+      <c r="R28" t="n">
         <v>5</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>3</v>
-      </c>
-      <c r="P28" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -2791,32 +2791,32 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Nick Pringle</t>
+          <t>Jaylen Carey</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ARK</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P29" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Q29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -2873,35 +2873,35 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Boogie Fland</t>
+          <t>Nick Pringle</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>FLA</t>
+          <t>ARK</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>11:43 - 1st Half</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P30" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -3134,20 +3134,20 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>13:19 - 2nd Half</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L33" t="n">
         <v>1</v>
@@ -3156,13 +3156,13 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="Q33" t="n">
         <v>2</v>
@@ -3177,10 +3177,10 @@
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -3216,21 +3216,21 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>11:43 - 1st Half</t>
+          <t>3:47 - 1st Half</t>
         </is>
       </c>
       <c r="H34" t="n">
+        <v>12</v>
+      </c>
+      <c r="I34" t="n">
+        <v>7</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="n">
         <v>4</v>
       </c>
-      <c r="I34" t="n">
-        <v>3</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>1</v>
-      </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
@@ -3244,13 +3244,13 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="Q34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -3298,41 +3298,41 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>11:43 - 1st Half</t>
+          <t>3:47 - 1st Half</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P35" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -3380,14 +3380,14 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>13:19 - 2nd Half</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I36" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J36" t="n">
         <v>1</v>
@@ -3408,13 +3408,13 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Q36" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R36" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="S36" t="n">
         <v>2</v>
@@ -3462,23 +3462,23 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>13:19 - 2nd Half</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I37" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J37" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K37" t="n">
         <v>2</v>
       </c>
       <c r="L37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -3490,7 +3490,7 @@
         <v>2</v>
       </c>
       <c r="P37" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="Q37" t="n">
         <v>1</v>
@@ -3505,10 +3505,10 @@
         <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -3544,17 +3544,17 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>11:43 - 1st Half</t>
+          <t>3:47 - 1st Half</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I38" t="n">
         <v>4</v>
       </c>
       <c r="J38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -3572,7 +3572,7 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q38" t="n">
         <v>2</v>
@@ -3708,47 +3708,47 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>13:19 - 2nd Half</t>
         </is>
       </c>
       <c r="H40" t="n">
+        <v>6</v>
+      </c>
+      <c r="I40" t="n">
+        <v>7</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>3</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>2</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2</v>
+      </c>
+      <c r="R40" t="n">
         <v>4</v>
       </c>
-      <c r="I40" t="n">
-        <v>5</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" t="n">
-        <v>2</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="n">
-        <v>2</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>1</v>
-      </c>
-      <c r="R40" t="n">
-        <v>2</v>
-      </c>
       <c r="S40" t="n">
         <v>1</v>
       </c>
       <c r="T40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U40" t="n">
         <v>2</v>
@@ -3790,53 +3790,53 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>11:43 - 1st Half</t>
+          <t>3:47 - 1st Half</t>
         </is>
       </c>
       <c r="H41" t="n">
         <v>3</v>
       </c>
       <c r="I41" t="n">
+        <v>5</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>1</v>
+      </c>
+      <c r="O41" t="n">
+        <v>2</v>
+      </c>
+      <c r="P41" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1</v>
+      </c>
+      <c r="R41" t="n">
+        <v>2</v>
+      </c>
+      <c r="S41" t="n">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
+      </c>
+      <c r="V41" t="n">
         <v>4</v>
-      </c>
-      <c r="J41" t="n">
-        <v>1</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" t="n">
-        <v>1</v>
-      </c>
-      <c r="O41" t="n">
-        <v>2</v>
-      </c>
-      <c r="P41" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>1</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1</v>
-      </c>
-      <c r="S41" t="n">
-        <v>1</v>
-      </c>
-      <c r="T41" t="n">
-        <v>1</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1</v>
-      </c>
-      <c r="V41" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -4118,11 +4118,11 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>13:19 - 2nd Half</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I45" t="n">
         <v>2</v>
@@ -4131,7 +4131,7 @@
         <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L45" t="n">
         <v>2</v>
@@ -4140,19 +4140,19 @@
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Q45" t="n">
         <v>1</v>
       </c>
       <c r="R45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -4392,7 +4392,7 @@
         <v>5</v>
       </c>
       <c r="P48" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q48" t="n">
         <v>5</v>
@@ -4513,68 +4513,68 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Nordin Kapic</t>
+          <t>Kanon Catchings</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>13:19 - 2nd Half</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I50" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J50" t="n">
+        <v>2</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1</v>
+      </c>
+      <c r="L50" t="n">
+        <v>1</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
+        <v>2</v>
+      </c>
+      <c r="P50" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>6</v>
+      </c>
+      <c r="R50" t="n">
+        <v>10</v>
+      </c>
+      <c r="S50" t="n">
         <v>4</v>
-      </c>
-      <c r="K50" t="n">
-        <v>1</v>
-      </c>
-      <c r="L50" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" t="n">
-        <v>1</v>
-      </c>
-      <c r="N50" t="n">
-        <v>2</v>
-      </c>
-      <c r="O50" t="n">
-        <v>2</v>
-      </c>
-      <c r="P50" t="n">
-        <v>21</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>4</v>
-      </c>
-      <c r="R50" t="n">
-        <v>7</v>
-      </c>
-      <c r="S50" t="n">
-        <v>2</v>
       </c>
       <c r="T50" t="n">
         <v>5</v>
       </c>
       <c r="U50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -4595,68 +4595,68 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Trent Pierce</t>
+          <t>Nordin Kapic</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H51" t="n">
+        <v>13</v>
+      </c>
+      <c r="I51" t="n">
         <v>12</v>
       </c>
-      <c r="I51" t="n">
-        <v>13</v>
-      </c>
       <c r="J51" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P51" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="Q51" t="n">
+        <v>4</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7</v>
+      </c>
+      <c r="S51" t="n">
+        <v>2</v>
+      </c>
+      <c r="T51" t="n">
         <v>5</v>
       </c>
-      <c r="R51" t="n">
-        <v>11</v>
-      </c>
-      <c r="S51" t="n">
-        <v>3</v>
-      </c>
-      <c r="T51" t="n">
-        <v>7</v>
-      </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>D.J. Wagner</t>
+          <t>Trent Pierce</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ARK</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -4696,49 +4696,49 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I52" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J52" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>1</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>1</v>
+      </c>
+      <c r="O52" t="n">
+        <v>3</v>
+      </c>
+      <c r="P52" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q52" t="n">
         <v>5</v>
       </c>
-      <c r="L52" t="n">
-        <v>1</v>
-      </c>
-      <c r="M52" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" t="n">
-        <v>3</v>
-      </c>
-      <c r="O52" t="n">
-        <v>3</v>
-      </c>
-      <c r="P52" t="n">
-        <v>45</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>4</v>
-      </c>
       <c r="R52" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T52" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -4759,68 +4759,68 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Eduardo Klafke</t>
+          <t>D.J. Wagner</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>ARK</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H53" t="n">
         <v>9</v>
       </c>
       <c r="I53" t="n">
+        <v>10</v>
+      </c>
+      <c r="J53" t="n">
+        <v>4</v>
+      </c>
+      <c r="K53" t="n">
         <v>5</v>
       </c>
-      <c r="J53" t="n">
-        <v>6</v>
-      </c>
-      <c r="K53" t="n">
-        <v>1</v>
-      </c>
       <c r="L53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P53" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="Q53" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="S53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U53" t="n">
         <v>2</v>
       </c>
       <c r="V53" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54">
@@ -4841,17 +4841,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Chandler Bing</t>
+          <t>Eduardo Klafke</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -4860,37 +4860,37 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I54" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J54" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P54" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Q54" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R54" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S54" t="n">
         <v>1</v>
@@ -4899,10 +4899,10 @@
         <v>2</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -4938,14 +4938,14 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>13:19 - 2nd Half</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I55" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -4963,16 +4963,16 @@
         <v>1</v>
       </c>
       <c r="O55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P55" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R55" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S55" t="n">
         <v>1</v>
@@ -5005,62 +5005,62 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Achor Achor</t>
+          <t>Chandler Bing</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>MSST</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I56" t="n">
+        <v>9</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>3</v>
+      </c>
+      <c r="P56" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q56" t="n">
         <v>4</v>
       </c>
-      <c r="J56" t="n">
-        <v>3</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>2</v>
-      </c>
       <c r="R56" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U56" t="n">
         <v>0</v>
@@ -5087,38 +5087,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Travis Perry</t>
+          <t>Achor Achor</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>13:19 - 2nd Half</t>
         </is>
       </c>
       <c r="H57" t="n">
         <v>6</v>
       </c>
       <c r="I57" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J57" t="n">
         <v>3</v>
       </c>
       <c r="K57" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
@@ -5133,7 +5133,7 @@
         <v>13</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R57" t="n">
         <v>3</v>
@@ -5142,13 +5142,13 @@
         <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -5169,17 +5169,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>DeWayne Brown II</t>
+          <t>Travis Perry</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5188,22 +5188,22 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
         <v>1</v>
@@ -5218,19 +5218,19 @@
         <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -5251,35 +5251,35 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Jamarion Davis-Fleming</t>
+          <t>Brandon Garrison</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>MSST</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>3:47 - 1st Half</t>
         </is>
       </c>
       <c r="H59" t="n">
         <v>5</v>
       </c>
       <c r="I59" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J59" t="n">
         <v>2</v>
       </c>
       <c r="K59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -5288,19 +5288,19 @@
         <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P59" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -5309,10 +5309,10 @@
         <v>0</v>
       </c>
       <c r="U59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -5333,62 +5333,62 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Kanon Catchings</t>
+          <t>DeWayne Brown II</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H60" t="n">
         <v>5</v>
       </c>
       <c r="I60" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P60" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Q60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U60" t="n">
         <v>0</v>
@@ -5415,68 +5415,68 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Bishop Boswell</t>
+          <t>Jamarion Davis-Fleming</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>13:19 - 2nd Half</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I61" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K61" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
         <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P61" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="Q61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -5497,17 +5497,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Eli Ellis</t>
+          <t>Bishop Boswell</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -5519,37 +5519,37 @@
         <v>4</v>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K62" t="n">
+        <v>4</v>
+      </c>
+      <c r="L62" t="n">
+        <v>2</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
+        <v>2</v>
+      </c>
+      <c r="O62" t="n">
         <v>5</v>
       </c>
-      <c r="L62" t="n">
-        <v>1</v>
-      </c>
-      <c r="M62" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" t="n">
-        <v>1</v>
-      </c>
-      <c r="O62" t="n">
-        <v>2</v>
-      </c>
       <c r="P62" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R62" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T62" t="n">
         <v>2</v>
@@ -5579,62 +5579,62 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Elijah Strong</t>
+          <t>Dylan James</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>13:19 - 2nd Half</t>
         </is>
       </c>
       <c r="H63" t="n">
         <v>4</v>
       </c>
       <c r="I63" t="n">
+        <v>4</v>
+      </c>
+      <c r="J63" t="n">
+        <v>2</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
         <v>7</v>
       </c>
-      <c r="J63" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" t="n">
-        <v>1</v>
-      </c>
-      <c r="L63" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" t="n">
-        <v>1</v>
-      </c>
-      <c r="N63" t="n">
-        <v>0</v>
-      </c>
-      <c r="O63" t="n">
-        <v>2</v>
-      </c>
-      <c r="P63" t="n">
-        <v>15</v>
-      </c>
       <c r="Q63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R63" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="S63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U63" t="n">
         <v>0</v>
@@ -5661,17 +5661,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Ethan Burg</t>
+          <t>Eli Ellis</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5683,31 +5683,31 @@
         <v>4</v>
       </c>
       <c r="I64" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K64" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M64" t="n">
         <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O64" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P64" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="Q64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
         <v>3</v>
@@ -5716,13 +5716,13 @@
         <v>0</v>
       </c>
       <c r="T64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U64" t="n">
         <v>0</v>
       </c>
       <c r="V64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -5743,32 +5743,32 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Justin Abson</t>
+          <t>Elijah Strong</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H65" t="n">
         <v>4</v>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J65" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K65" t="n">
         <v>1</v>
@@ -5777,28 +5777,28 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N65" t="n">
         <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P65" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T65" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U65" t="n">
         <v>0</v>
@@ -5825,38 +5825,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Sergej Macura</t>
+          <t>Ethan Burg</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>MSST</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H66" t="n">
         <v>4</v>
       </c>
       <c r="I66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
@@ -5865,28 +5865,28 @@
         <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P66" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="Q66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
       </c>
       <c r="T66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -5907,35 +5907,35 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>T.O. Barrett</t>
+          <t>Isaiah Brown</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>3:47 - 1st Half</t>
         </is>
       </c>
       <c r="H67" t="n">
         <v>4</v>
       </c>
       <c r="I67" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L67" t="n">
         <v>1</v>
@@ -5944,31 +5944,31 @@
         <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P67" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="Q67" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R67" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
       </c>
       <c r="T67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U67" t="n">
         <v>2</v>
       </c>
       <c r="V67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68">
@@ -5989,7 +5989,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Jordan Ross</t>
+          <t>Justin Abson</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6004,47 +6004,47 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>13:19 - 2nd Half</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>3</v>
+      </c>
+      <c r="K68" t="n">
+        <v>1</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" t="n">
         <v>5</v>
       </c>
-      <c r="J68" t="n">
-        <v>0</v>
-      </c>
-      <c r="K68" t="n">
-        <v>2</v>
-      </c>
-      <c r="L68" t="n">
-        <v>0</v>
-      </c>
-      <c r="M68" t="n">
-        <v>0</v>
-      </c>
-      <c r="N68" t="n">
-        <v>2</v>
-      </c>
-      <c r="O68" t="n">
-        <v>1</v>
-      </c>
-      <c r="P68" t="n">
-        <v>12</v>
-      </c>
       <c r="Q68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U68" t="n">
         <v>0</v>
@@ -6071,38 +6071,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Kezza Giffa</t>
+          <t>Sergej Macura</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>13:19 - 2nd Half</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I69" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
@@ -6114,22 +6114,22 @@
         <v>1</v>
       </c>
       <c r="P69" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="Q69" t="n">
         <v>1</v>
       </c>
       <c r="R69" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
       </c>
       <c r="T69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V69" t="n">
         <v>2</v>
@@ -6153,68 +6153,68 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Troy Henderson</t>
+          <t>T.O. Barrett</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I70" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M70" t="n">
         <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P70" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="Q70" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R70" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="S70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -6235,7 +6235,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Zach Day</t>
+          <t>Kezza Giffa</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -6254,49 +6254,49 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P71" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
       </c>
       <c r="T71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Amaree Abram</t>
+          <t>Troy Henderson</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -6336,19 +6336,19 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
         <v>0</v>
@@ -6363,22 +6363,22 @@
         <v>3</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -6399,35 +6399,35 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Corey Chest</t>
+          <t>Jordan Ross</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>13:19 - 2nd Half</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
@@ -6436,25 +6436,25 @@
         <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P73" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U73" t="n">
         <v>0</v>
@@ -6481,29 +6481,29 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Dylan James</t>
+          <t>Zach Day</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J74" t="n">
         <v>1</v>
@@ -6515,7 +6515,7 @@
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N74" t="n">
         <v>0</v>
@@ -6524,13 +6524,13 @@
         <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Q74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -6563,17 +6563,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>EJ Walker</t>
+          <t>Amaree Abram</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -6585,46 +6585,46 @@
         <v>1</v>
       </c>
       <c r="I75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J75" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
       </c>
       <c r="T75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -6645,35 +6645,35 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Grant Polk</t>
+          <t>Andrija Jelavic</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>3:47 - 1st Half</t>
         </is>
       </c>
       <c r="H76" t="n">
         <v>1</v>
       </c>
       <c r="I76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
@@ -6688,19 +6688,19 @@
         <v>1</v>
       </c>
       <c r="P76" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q76" t="n">
         <v>1</v>
       </c>
       <c r="R76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T76" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U76" t="n">
         <v>0</v>
@@ -6727,32 +6727,32 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Jake Wilkins</t>
+          <t>Corey Chest</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H77" t="n">
         <v>1</v>
       </c>
       <c r="I77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
@@ -6770,19 +6770,19 @@
         <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
       </c>
       <c r="T77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U77" t="n">
         <v>0</v>
@@ -6809,12 +6809,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Patton Pinkins</t>
+          <t>EJ Walker</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -6831,34 +6831,34 @@
         <v>1</v>
       </c>
       <c r="I78" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K78" t="n">
         <v>1</v>
       </c>
       <c r="L78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
         <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P78" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="Q78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -6891,32 +6891,32 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Andrija Jelavic</t>
+          <t>Grant Polk</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>11:43 - 1st Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
@@ -6934,19 +6934,19 @@
         <v>1</v>
       </c>
       <c r="P79" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q79" t="n">
         <v>1</v>
       </c>
       <c r="R79" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U79" t="n">
         <v>0</v>
@@ -6973,29 +6973,29 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Brandon Garrison</t>
+          <t>Jake Wilkins</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>11:43 - 1st Half</t>
+          <t>13:19 - 2nd Half</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7016,19 +7016,19 @@
         <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
       </c>
       <c r="T80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U80" t="n">
         <v>0</v>
@@ -7055,38 +7055,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Isaiah Sealy</t>
+          <t>Patton Pinkins</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>ARK</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I81" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K81" t="n">
         <v>1</v>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M81" t="n">
         <v>0</v>
@@ -7098,19 +7098,19 @@
         <v>1</v>
       </c>
       <c r="P81" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
       </c>
       <c r="T81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U81" t="n">
         <v>0</v>
@@ -7137,22 +7137,22 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Jayden Leverett</t>
+          <t>Isaiah Sealy</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>ARK</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H82" t="n">
@@ -7162,10 +7162,10 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
@@ -7174,19 +7174,19 @@
         <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q82" t="n">
         <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -7219,17 +7219,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Jordan Butler</t>
+          <t>Jayden Leverett</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -7244,7 +7244,7 @@
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
@@ -7259,16 +7259,16 @@
         <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P83" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -7301,22 +7301,22 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Justin Bailey</t>
+          <t>Jordan Butler</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H84" t="n">
@@ -7332,19 +7332,19 @@
         <v>0</v>
       </c>
       <c r="L84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
         <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
@@ -7383,22 +7383,22 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Trent Burns</t>
+          <t>Justin Bailey</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>13:19 - 2nd Half</t>
         </is>
       </c>
       <c r="H85" t="n">
@@ -7414,19 +7414,19 @@
         <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P85" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
@@ -7465,62 +7465,62 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Tyler Harris</t>
+          <t>Kareem Stagg</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>13:19 - 2nd Half</t>
         </is>
       </c>
       <c r="H86" t="n">
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T86" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U86" t="n">
         <v>0</v>
@@ -7547,22 +7547,22 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Urban Klavzar</t>
+          <t>Trent Burns</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>FLA</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>11:43 - 1st Half</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H87" t="n">
@@ -7590,7 +7590,7 @@
         <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q87" t="n">
         <v>0</v>
@@ -7629,32 +7629,32 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Kareem Stagg</t>
+          <t>Tyler Harris</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -7666,25 +7666,25 @@
         <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Q88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T88" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U88" t="n">
         <v>0</v>
@@ -7711,67 +7711,231 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
+          <t>Urban Klavzar</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>FLA</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>FLA@UK</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>3:47 - 1st Half</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" t="n">
+        <v>0</v>
+      </c>
+      <c r="T89" t="n">
+        <v>0</v>
+      </c>
+      <c r="U89" t="n">
+        <v>0</v>
+      </c>
+      <c r="V89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Jasper Johnson</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>FLA@UK</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>3:47 - 1st Half</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="n">
+        <v>1</v>
+      </c>
+      <c r="O90" t="n">
+        <v>2</v>
+      </c>
+      <c r="P90" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" t="n">
+        <v>0</v>
+      </c>
+      <c r="T90" t="n">
+        <v>0</v>
+      </c>
+      <c r="U90" t="n">
+        <v>0</v>
+      </c>
+      <c r="V90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
           <t>Max Smith</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="E91" t="inlineStr">
         <is>
           <t>MISS</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t>SC@MISS</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t>Final</t>
         </is>
       </c>
-      <c r="H89" t="n">
+      <c r="H91" t="n">
         <v>-1</v>
       </c>
-      <c r="I89" t="n">
-        <v>0</v>
-      </c>
-      <c r="J89" t="n">
-        <v>0</v>
-      </c>
-      <c r="K89" t="n">
-        <v>0</v>
-      </c>
-      <c r="L89" t="n">
-        <v>0</v>
-      </c>
-      <c r="M89" t="n">
-        <v>0</v>
-      </c>
-      <c r="N89" t="n">
-        <v>0</v>
-      </c>
-      <c r="O89" t="n">
-        <v>0</v>
-      </c>
-      <c r="P89" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
-      <c r="R89" t="n">
-        <v>1</v>
-      </c>
-      <c r="S89" t="n">
-        <v>0</v>
-      </c>
-      <c r="T89" t="n">
-        <v>1</v>
-      </c>
-      <c r="U89" t="n">
-        <v>0</v>
-      </c>
-      <c r="V89" t="n">
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>0</v>
+      </c>
+      <c r="R91" t="n">
+        <v>1</v>
+      </c>
+      <c r="S91" t="n">
+        <v>0</v>
+      </c>
+      <c r="T91" t="n">
+        <v>1</v>
+      </c>
+      <c r="U91" t="n">
+        <v>0</v>
+      </c>
+      <c r="V91" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7814,27 +7978,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bend Rimmers</t>
+          <t>The Backslashers</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>The Backslashers</t>
+          <t>Bend Rimmers</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -7853,14 +8017,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Hilton Heads</t>
+          <t>Three Dawg Nite</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -7870,7 +8034,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="C6" t="n">
         <v>3</v>
@@ -7879,14 +8043,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Three Dawg Nite</t>
+          <t>Hilton Heads</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">

--- a/docs/Today_PoohPoints_SEC_ByOwner_2026-03-07.xlsx
+++ b/docs/Today_PoohPoints_SEC_ByOwner_2026-03-07.xlsx
@@ -429,7 +429,7 @@
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
     <col width="6" customWidth="1" min="8" max="8"/>
     <col width="5" customWidth="1" min="9" max="9"/>
     <col width="5" customWidth="1" min="10" max="10"/>
@@ -741,68 +741,68 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Jeremiah Wilkinson</t>
+          <t>Devin McGlockton</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>13:19 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -823,68 +823,68 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Devin McGlockton</t>
+          <t>Jeremiah Wilkinson</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>8:45 - 2nd Half</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="Q5" t="n">
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="U5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -1084,23 +1084,23 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3:47 - 1st Half</t>
+          <t>0:16 - 1st Half</t>
         </is>
       </c>
       <c r="H8" t="n">
+        <v>21</v>
+      </c>
+      <c r="I8" t="n">
         <v>17</v>
       </c>
-      <c r="I8" t="n">
-        <v>14</v>
-      </c>
       <c r="J8" t="n">
         <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="Q8" t="n">
+        <v>6</v>
+      </c>
+      <c r="R8" t="n">
+        <v>9</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="n">
         <v>5</v>
-      </c>
-      <c r="R8" t="n">
-        <v>7</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3</v>
       </c>
       <c r="U8" t="n">
         <v>2</v>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>13:19 - 2nd Half</t>
+          <t>8:45 - 2nd Half</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1589,7 +1589,7 @@
         <v>6</v>
       </c>
       <c r="K14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1604,13 +1604,13 @@
         <v>1</v>
       </c>
       <c r="P14" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q14" t="n">
         <v>3</v>
       </c>
       <c r="R14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1643,12 +1643,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Micah Handlogten</t>
+          <t>Denzel Aberdeen</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FLA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1658,53 +1658,53 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>3:47 - 1st Half</t>
+          <t>0:16 - 1st Half</t>
         </is>
       </c>
       <c r="H15" t="n">
         <v>2</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Denzel Aberdeen</t>
+          <t>Micah Handlogten</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1740,47 +1740,47 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>3:47 - 1st Half</t>
+          <t>0:16 - 1st Half</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>3:47 - 1st Half</t>
+          <t>0:16 - 1st Half</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -2014,7 +2014,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -2068,17 +2068,17 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>13:19 - 2nd Half</t>
+          <t>8:45 - 2nd Half</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K20" t="n">
         <v>2</v>
@@ -2087,22 +2087,22 @@
         <v>2</v>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P20" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="Q20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -2314,14 +2314,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>3:47 - 1st Half</t>
+          <t>0:16 - 1st Half</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I23" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -2342,19 +2342,19 @@
         <v>1</v>
       </c>
       <c r="P23" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Q23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R23" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U23" t="n">
         <v>1</v>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>3:47 - 1st Half</t>
+          <t>0:16 - 1st Half</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -2627,62 +2627,62 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Myles Stute</t>
+          <t>Boogie Fland</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>0:16 - 1st Half</t>
         </is>
       </c>
       <c r="H27" t="n">
         <v>8</v>
       </c>
       <c r="I27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q27" t="n">
         <v>2</v>
       </c>
       <c r="R27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -2709,62 +2709,62 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Boogie Fland</t>
+          <t>Myles Stute</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FLA</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>3:47 - 1st Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P28" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="Q28" t="n">
         <v>2</v>
       </c>
       <c r="R28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>13:19 - 2nd Half</t>
+          <t>8:45 - 2nd Half</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>3:47 - 1st Half</t>
+          <t>0:16 - 1st Half</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -3298,20 +3298,20 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>3:47 - 1st Half</t>
+          <t>0:16 - 1st Half</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -3320,13 +3320,13 @@
         <v>1</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P35" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -3380,17 +3380,17 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>13:19 - 2nd Half</t>
+          <t>8:45 - 2nd Half</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I36" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K36" t="n">
         <v>4</v>
@@ -3408,19 +3408,19 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="Q36" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="R36" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="S36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T36" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>13:19 - 2nd Half</t>
+          <t>8:45 - 2nd Half</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -3544,17 +3544,17 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>3:47 - 1st Half</t>
+          <t>0:16 - 1st Half</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I38" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J38" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -3563,7 +3563,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -3572,7 +3572,7 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Q38" t="n">
         <v>2</v>
@@ -3587,10 +3587,10 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
@@ -3611,38 +3611,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Kobe Knox</t>
+          <t>Marcus Millender</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>8:45 - 2nd Half</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I39" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J39" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -3651,28 +3651,28 @@
         <v>2</v>
       </c>
       <c r="O39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="Q39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R39" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U39" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V39" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -3693,38 +3693,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Marcus Millender</t>
+          <t>Kobe Knox</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>13:19 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H40" t="n">
         <v>6</v>
       </c>
       <c r="I40" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -3733,28 +3733,28 @@
         <v>2</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P40" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="Q40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R40" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="S40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
         <v>2</v>
       </c>
       <c r="U40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V40" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41">
@@ -3790,11 +3790,11 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>3:47 - 1st Half</t>
+          <t>0:16 - 1st Half</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I41" t="n">
         <v>5</v>
@@ -3815,7 +3815,7 @@
         <v>1</v>
       </c>
       <c r="O41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P41" t="n">
         <v>8</v>
@@ -3824,7 +3824,7 @@
         <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4118,17 +4118,17 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>13:19 - 2nd Half</t>
+          <t>8:45 - 2nd Half</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I45" t="n">
         <v>2</v>
       </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K45" t="n">
         <v>2</v>
@@ -4146,7 +4146,7 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="Q45" t="n">
         <v>1</v>
@@ -4267,68 +4267,68 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Shawn Phillips Jr.</t>
+          <t>Kanon Catchings</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>8:45 - 2nd Half</t>
         </is>
       </c>
       <c r="H47" t="n">
+        <v>20</v>
+      </c>
+      <c r="I47" t="n">
         <v>19</v>
       </c>
-      <c r="I47" t="n">
-        <v>13</v>
-      </c>
       <c r="J47" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M47" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P47" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="Q47" t="n">
+        <v>7</v>
+      </c>
+      <c r="R47" t="n">
+        <v>12</v>
+      </c>
+      <c r="S47" t="n">
         <v>5</v>
       </c>
-      <c r="R47" t="n">
-        <v>8</v>
-      </c>
-      <c r="S47" t="n">
-        <v>0</v>
-      </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -4349,50 +4349,50 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>AK Okereke</t>
+          <t>Shawn Phillips Jr.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I48" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J48" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N48" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O48" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P48" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="Q48" t="n">
         <v>5</v>
@@ -4401,16 +4401,16 @@
         <v>8</v>
       </c>
       <c r="S48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="V48" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
@@ -4431,22 +4431,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Malique Ewin</t>
+          <t>AK Okereke</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ARK</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H49" t="n">
@@ -4456,43 +4456,43 @@
         <v>17</v>
       </c>
       <c r="J49" t="n">
+        <v>4</v>
+      </c>
+      <c r="K49" t="n">
+        <v>3</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>1</v>
+      </c>
+      <c r="O49" t="n">
+        <v>5</v>
+      </c>
+      <c r="P49" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>5</v>
+      </c>
+      <c r="R49" t="n">
+        <v>8</v>
+      </c>
+      <c r="S49" t="n">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>6</v>
+      </c>
+      <c r="V49" t="n">
         <v>9</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="n">
-        <v>1</v>
-      </c>
-      <c r="M49" t="n">
-        <v>2</v>
-      </c>
-      <c r="N49" t="n">
-        <v>3</v>
-      </c>
-      <c r="O49" t="n">
-        <v>3</v>
-      </c>
-      <c r="P49" t="n">
-        <v>31</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>6</v>
-      </c>
-      <c r="R49" t="n">
-        <v>12</v>
-      </c>
-      <c r="S49" t="n">
-        <v>1</v>
-      </c>
-      <c r="T49" t="n">
-        <v>1</v>
-      </c>
-      <c r="U49" t="n">
-        <v>4</v>
-      </c>
-      <c r="V49" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="50">
@@ -4513,68 +4513,68 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Kanon Catchings</t>
+          <t>Malique Ewin</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>ARK</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>13:19 - 2nd Half</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I50" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J50" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L50" t="n">
         <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P50" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="Q50" t="n">
         <v>6</v>
       </c>
       <c r="R50" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="S50" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T50" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51">
@@ -4759,68 +4759,68 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>D.J. Wagner</t>
+          <t>Ja'Borri McGhee</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ARK</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>8:45 - 2nd Half</t>
         </is>
       </c>
       <c r="H53" t="n">
+        <v>10</v>
+      </c>
+      <c r="I53" t="n">
+        <v>13</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>1</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>1</v>
+      </c>
+      <c r="O53" t="n">
+        <v>3</v>
+      </c>
+      <c r="P53" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>6</v>
+      </c>
+      <c r="R53" t="n">
         <v>9</v>
       </c>
-      <c r="I53" t="n">
-        <v>10</v>
-      </c>
-      <c r="J53" t="n">
-        <v>4</v>
-      </c>
-      <c r="K53" t="n">
-        <v>5</v>
-      </c>
-      <c r="L53" t="n">
-        <v>1</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="n">
-        <v>3</v>
-      </c>
-      <c r="O53" t="n">
-        <v>3</v>
-      </c>
-      <c r="P53" t="n">
-        <v>45</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>4</v>
-      </c>
-      <c r="R53" t="n">
-        <v>10</v>
-      </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -4841,68 +4841,68 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Eduardo Klafke</t>
+          <t>D.J. Wagner</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>ARK</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H54" t="n">
         <v>9</v>
       </c>
       <c r="I54" t="n">
+        <v>10</v>
+      </c>
+      <c r="J54" t="n">
+        <v>4</v>
+      </c>
+      <c r="K54" t="n">
         <v>5</v>
       </c>
-      <c r="J54" t="n">
-        <v>6</v>
-      </c>
-      <c r="K54" t="n">
-        <v>1</v>
-      </c>
       <c r="L54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P54" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="Q54" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R54" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="S54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U54" t="n">
         <v>2</v>
       </c>
       <c r="V54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
@@ -4923,38 +4923,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Ja'Borri McGhee</t>
+          <t>Eduardo Klafke</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MSST</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>13:19 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H55" t="n">
         <v>9</v>
       </c>
       <c r="I55" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
@@ -4966,14 +4966,14 @@
         <v>2</v>
       </c>
       <c r="P55" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="Q55" t="n">
+        <v>1</v>
+      </c>
+      <c r="R55" t="n">
         <v>5</v>
       </c>
-      <c r="R55" t="n">
-        <v>7</v>
-      </c>
       <c r="S55" t="n">
         <v>1</v>
       </c>
@@ -4981,10 +4981,10 @@
         <v>2</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -5005,68 +5005,68 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Chandler Bing</t>
+          <t>Jamarion Davis-Fleming</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>8:45 - 2nd Half</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I56" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J56" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N56" t="n">
         <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P56" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="Q56" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -5087,62 +5087,62 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Achor Achor</t>
+          <t>Chandler Bing</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>MSST</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>13:19 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H57" t="n">
+        <v>8</v>
+      </c>
+      <c r="I57" t="n">
+        <v>9</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>3</v>
+      </c>
+      <c r="P57" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>4</v>
+      </c>
+      <c r="R57" t="n">
         <v>6</v>
       </c>
-      <c r="I57" t="n">
-        <v>4</v>
-      </c>
-      <c r="J57" t="n">
-        <v>3</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" t="n">
-        <v>1</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" t="n">
-        <v>1</v>
-      </c>
-      <c r="O57" t="n">
-        <v>1</v>
-      </c>
-      <c r="P57" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>2</v>
-      </c>
-      <c r="R57" t="n">
-        <v>3</v>
-      </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U57" t="n">
         <v>0</v>
@@ -5169,62 +5169,62 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Travis Perry</t>
+          <t>Justin Abson</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>8:45 - 2nd Half</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I58" t="n">
         <v>2</v>
       </c>
       <c r="J58" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U58" t="n">
         <v>2</v>
@@ -5251,38 +5251,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Brandon Garrison</t>
+          <t>Achor Achor</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>3:47 - 1st Half</t>
+          <t>8:45 - 2nd Half</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I59" t="n">
         <v>4</v>
       </c>
       <c r="J59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
@@ -5294,13 +5294,13 @@
         <v>1</v>
       </c>
       <c r="P59" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="Q59" t="n">
         <v>2</v>
       </c>
       <c r="R59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -5333,53 +5333,53 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>DeWayne Brown II</t>
+          <t>Isaiah Brown</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>0:16 - 1st Half</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J60" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M60" t="n">
         <v>1</v>
       </c>
       <c r="N60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>1</v>
       </c>
       <c r="P60" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R60" t="n">
         <v>1</v>
@@ -5391,10 +5391,10 @@
         <v>0</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V60" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
@@ -5415,62 +5415,62 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Jamarion Davis-Fleming</t>
+          <t>Travis Perry</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>MSST</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>13:19 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I61" t="n">
         <v>2</v>
       </c>
       <c r="J61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M61" t="n">
         <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P61" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U61" t="n">
         <v>2</v>
@@ -5497,62 +5497,62 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Bishop Boswell</t>
+          <t>Brandon Garrison</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>0:16 - 1st Half</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I62" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K62" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O62" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P62" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="Q62" t="n">
         <v>2</v>
       </c>
       <c r="R62" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="S62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U62" t="n">
         <v>0</v>
@@ -5579,56 +5579,56 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Dylan James</t>
+          <t>DeWayne Brown II</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>13:19 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I63" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P63" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="Q63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -5661,17 +5661,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Eli Ellis</t>
+          <t>Bishop Boswell</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5683,37 +5683,37 @@
         <v>4</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K64" t="n">
+        <v>4</v>
+      </c>
+      <c r="L64" t="n">
+        <v>2</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="n">
+        <v>2</v>
+      </c>
+      <c r="O64" t="n">
         <v>5</v>
       </c>
-      <c r="L64" t="n">
-        <v>1</v>
-      </c>
-      <c r="M64" t="n">
-        <v>0</v>
-      </c>
-      <c r="N64" t="n">
-        <v>1</v>
-      </c>
-      <c r="O64" t="n">
-        <v>2</v>
-      </c>
       <c r="P64" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R64" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T64" t="n">
         <v>2</v>
@@ -5743,62 +5743,62 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Elijah Strong</t>
+          <t>Dylan James</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>8:45 - 2nd Half</t>
         </is>
       </c>
       <c r="H65" t="n">
         <v>4</v>
       </c>
       <c r="I65" t="n">
+        <v>4</v>
+      </c>
+      <c r="J65" t="n">
+        <v>2</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="n">
         <v>7</v>
       </c>
-      <c r="J65" t="n">
-        <v>0</v>
-      </c>
-      <c r="K65" t="n">
-        <v>1</v>
-      </c>
-      <c r="L65" t="n">
-        <v>0</v>
-      </c>
-      <c r="M65" t="n">
-        <v>1</v>
-      </c>
-      <c r="N65" t="n">
-        <v>0</v>
-      </c>
-      <c r="O65" t="n">
-        <v>2</v>
-      </c>
-      <c r="P65" t="n">
-        <v>15</v>
-      </c>
       <c r="Q65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R65" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="S65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U65" t="n">
         <v>0</v>
@@ -5825,17 +5825,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Ethan Burg</t>
+          <t>Eli Ellis</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5847,31 +5847,31 @@
         <v>4</v>
       </c>
       <c r="I66" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K66" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O66" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P66" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="Q66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
         <v>3</v>
@@ -5880,13 +5880,13 @@
         <v>0</v>
       </c>
       <c r="T66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U66" t="n">
         <v>0</v>
       </c>
       <c r="V66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -5907,68 +5907,68 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Isaiah Brown</t>
+          <t>Elijah Strong</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>FLA</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>3:47 - 1st Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H67" t="n">
         <v>4</v>
       </c>
       <c r="I67" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N67" t="n">
         <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P67" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="Q67" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R67" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="S67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T67" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V67" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -5989,35 +5989,35 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Justin Abson</t>
+          <t>Ethan Burg</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>13:19 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H68" t="n">
         <v>4</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J68" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -6029,28 +6029,28 @@
         <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P68" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U68" t="n">
         <v>0</v>
       </c>
       <c r="V68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>13:19 - 2nd Half</t>
+          <t>8:45 - 2nd Half</t>
         </is>
       </c>
       <c r="H69" t="n">
@@ -6235,35 +6235,35 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Kezza Giffa</t>
+          <t>Jordan Ross</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>8:45 - 2nd Half</t>
         </is>
       </c>
       <c r="H71" t="n">
         <v>3</v>
       </c>
       <c r="I71" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
@@ -6278,25 +6278,25 @@
         <v>1</v>
       </c>
       <c r="P71" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="Q71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R71" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T71" t="n">
         <v>1</v>
       </c>
       <c r="U71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -6317,17 +6317,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Troy Henderson</t>
+          <t>Kezza Giffa</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -6339,13 +6339,13 @@
         <v>3</v>
       </c>
       <c r="I72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
@@ -6354,31 +6354,31 @@
         <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P72" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="Q72" t="n">
         <v>1</v>
       </c>
       <c r="R72" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T72" t="n">
         <v>1</v>
       </c>
       <c r="U72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -6399,35 +6399,35 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Jordan Ross</t>
+          <t>Troy Henderson</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>13:19 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I73" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
@@ -6436,19 +6436,19 @@
         <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="Q73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R73" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S73" t="n">
         <v>1</v>
@@ -6481,62 +6481,62 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Zach Day</t>
+          <t>Kareem Stagg</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>8:45 - 2nd Half</t>
         </is>
       </c>
       <c r="H74" t="n">
         <v>2</v>
       </c>
       <c r="I74" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T74" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U74" t="n">
         <v>0</v>
@@ -6563,38 +6563,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Amaree Abram</t>
+          <t>Urban Klavzar</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>0:16 - 1st Half</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
@@ -6603,28 +6603,28 @@
         <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P75" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -6645,62 +6645,62 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Andrija Jelavic</t>
+          <t>Zach Day</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>3:47 - 1st Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J76" t="n">
         <v>1</v>
       </c>
       <c r="K76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N76" t="n">
         <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
       </c>
       <c r="T76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U76" t="n">
         <v>0</v>
@@ -6727,17 +6727,17 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Corey Chest</t>
+          <t>Amaree Abram</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -6749,7 +6749,7 @@
         <v>1</v>
       </c>
       <c r="I77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J77" t="n">
         <v>1</v>
@@ -6758,7 +6758,7 @@
         <v>0</v>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M77" t="n">
         <v>0</v>
@@ -6770,13 +6770,13 @@
         <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -6785,10 +6785,10 @@
         <v>0</v>
       </c>
       <c r="U77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
@@ -6809,32 +6809,32 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>EJ Walker</t>
+          <t>Andrija Jelavic</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>0:16 - 1st Half</t>
         </is>
       </c>
       <c r="H78" t="n">
         <v>1</v>
       </c>
       <c r="I78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J78" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K78" t="n">
         <v>1</v>
@@ -6846,25 +6846,25 @@
         <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P78" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R78" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
       </c>
       <c r="T78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U78" t="n">
         <v>0</v>
@@ -6891,12 +6891,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Grant Polk</t>
+          <t>Corey Chest</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -6913,10 +6913,10 @@
         <v>1</v>
       </c>
       <c r="I79" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
@@ -6931,22 +6931,22 @@
         <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Q79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T79" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U79" t="n">
         <v>0</v>
@@ -6973,35 +6973,35 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Jake Wilkins</t>
+          <t>EJ Walker</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>13:19 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H80" t="n">
         <v>1</v>
       </c>
       <c r="I80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
@@ -7010,16 +7010,16 @@
         <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P80" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="Q80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
         <v>2</v>
@@ -7028,7 +7028,7 @@
         <v>0</v>
       </c>
       <c r="T80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U80" t="n">
         <v>0</v>
@@ -7055,12 +7055,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Patton Pinkins</t>
+          <t>Grant Polk</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -7077,40 +7077,40 @@
         <v>1</v>
       </c>
       <c r="I81" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
         <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>1</v>
       </c>
       <c r="P81" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="Q81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R81" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="S81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U81" t="n">
         <v>0</v>
@@ -7137,35 +7137,35 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Isaiah Sealy</t>
+          <t>Jake Wilkins</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>ARK</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>8:45 - 2nd Half</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
@@ -7174,25 +7174,25 @@
         <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
       </c>
       <c r="T82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U82" t="n">
         <v>0</v>
@@ -7219,17 +7219,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Jayden Leverett</t>
+          <t>Patton Pinkins</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -7238,43 +7238,43 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I83" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M83" t="n">
         <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P83" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R83" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
       </c>
       <c r="T83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U83" t="n">
         <v>0</v>
@@ -7301,22 +7301,22 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Jordan Butler</t>
+          <t>Isaiah Sealy</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ARK</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H84" t="n">
@@ -7329,7 +7329,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" t="n">
         <v>0</v>
@@ -7338,13 +7338,13 @@
         <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P84" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
@@ -7383,22 +7383,22 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Justin Bailey</t>
+          <t>Jayden Leverett</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>13:19 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H85" t="n">
@@ -7408,31 +7408,31 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P85" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -7465,62 +7465,62 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Kareem Stagg</t>
+          <t>Jordan Butler</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>13:19 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H86" t="n">
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="Q86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T86" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U86" t="n">
         <v>0</v>
@@ -7547,22 +7547,22 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Trent Burns</t>
+          <t>Justin Bailey</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>8:45 - 2nd Half</t>
         </is>
       </c>
       <c r="H87" t="n">
@@ -7578,19 +7578,19 @@
         <v>0</v>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M87" t="n">
         <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P87" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q87" t="n">
         <v>0</v>
@@ -7629,22 +7629,22 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Tyler Harris</t>
+          <t>Trent Burns</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H88" t="n">
@@ -7672,7 +7672,7 @@
         <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q88" t="n">
         <v>0</v>
@@ -7711,22 +7711,22 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Urban Klavzar</t>
+          <t>Tyler Harris</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>FLA</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>3:47 - 1st Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H89" t="n">
@@ -7754,7 +7754,7 @@
         <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
@@ -7808,7 +7808,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>3:47 - 1st Half</t>
+          <t>0:16 - 1st Half</t>
         </is>
       </c>
       <c r="H90" t="n">
@@ -7982,7 +7982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C2" t="n">
         <v>4</v>
@@ -8004,14 +8004,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>The Oddities</t>
+          <t>G-Flop</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -8021,7 +8021,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C5" t="n">
         <v>4</v>
@@ -8030,14 +8030,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G-Flop</t>
+          <t>The Oddities</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">

--- a/docs/Today_PoohPoints_SEC_ByOwner_2026-03-07.xlsx
+++ b/docs/Today_PoohPoints_SEC_ByOwner_2026-03-07.xlsx
@@ -429,7 +429,7 @@
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
     <col width="6" customWidth="1" min="8" max="8"/>
     <col width="5" customWidth="1" min="9" max="9"/>
     <col width="5" customWidth="1" min="10" max="10"/>
@@ -741,68 +741,68 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Devin McGlockton</t>
+          <t>Jeremiah Wilkinson</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>1:01 - 2nd Half</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R4" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="U4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -823,68 +823,68 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Jeremiah Wilkinson</t>
+          <t>Devin McGlockton</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>8:45 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H5" t="n">
+        <v>9</v>
+      </c>
+      <c r="I5" t="n">
         <v>8</v>
       </c>
-      <c r="I5" t="n">
-        <v>12</v>
-      </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="Q5" t="n">
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0:16 - 1st Half</t>
+          <t>15:47 - 2nd Half</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1094,13 +1094,13 @@
         <v>17</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K8" t="n">
         <v>2</v>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="Q8" t="n">
         <v>6</v>
       </c>
       <c r="R8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
       </c>
       <c r="T8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U8" t="n">
         <v>2</v>
@@ -1576,41 +1576,41 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>8:45 - 2nd Half</t>
+          <t>1:01 - 2nd Half</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I14" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J14" t="n">
         <v>6</v>
       </c>
       <c r="K14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O14" t="n">
         <v>1</v>
       </c>
       <c r="P14" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R14" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0:16 - 1st Half</t>
+          <t>15:47 - 2nd Half</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1686,7 +1686,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="Q15" t="n">
         <v>1</v>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0:16 - 1st Half</t>
+          <t>15:47 - 2nd Half</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1750,7 +1750,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1768,13 +1768,13 @@
         <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1986,11 +1986,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0:16 - 1st Half</t>
+          <t>15:47 - 2nd Half</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -2011,22 +2011,22 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P19" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>8:45 - 2nd Half</t>
+          <t>1:01 - 2nd Half</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -2217,41 +2217,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Jayden Stone</t>
+          <t>Alex Condon</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>15:47 - 2nd Half</t>
         </is>
       </c>
       <c r="H22" t="n">
         <v>12</v>
       </c>
       <c r="I22" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J22" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22" t="n">
         <v>3</v>
@@ -2260,19 +2260,19 @@
         <v>2</v>
       </c>
       <c r="P22" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="Q22" t="n">
         <v>4</v>
       </c>
       <c r="R22" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
         <v>1</v>
@@ -2299,68 +2299,68 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Otega Oweh</t>
+          <t>Jayden Stone</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0:16 - 1st Half</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H23" t="n">
+        <v>12</v>
+      </c>
+      <c r="I23" t="n">
         <v>11</v>
       </c>
-      <c r="I23" t="n">
-        <v>17</v>
-      </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P23" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="Q23" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R23" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U23" t="n">
         <v>1</v>
       </c>
       <c r="V23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -2381,12 +2381,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Alex Condon</t>
+          <t>Otega Oweh</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FLA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2396,20 +2396,20 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0:16 - 1st Half</t>
+          <t>15:47 - 2nd Half</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I24" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="J24" t="n">
         <v>2</v>
       </c>
       <c r="K24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
         <v>1</v>
@@ -2418,31 +2418,31 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P24" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="Q24" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R24" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U24" t="n">
         <v>1</v>
       </c>
       <c r="V24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -2627,62 +2627,62 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Boogie Fland</t>
+          <t>Myles Stute</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FLA</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0:16 - 1st Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H27" t="n">
         <v>8</v>
       </c>
       <c r="I27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q27" t="n">
         <v>2</v>
       </c>
       <c r="R27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -2709,62 +2709,62 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Myles Stute</t>
+          <t>Boogie Fland</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>15:47 - 2nd Half</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I28" t="n">
+        <v>5</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
         <v>6</v>
       </c>
-      <c r="J28" t="n">
-        <v>2</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Q28" t="n">
         <v>2</v>
       </c>
       <c r="R28" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -3037,68 +3037,68 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Duke Miles</t>
+          <t>Somtochukwu Cyril</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>1:01 - 2nd Half</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I32" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K32" t="n">
         <v>2</v>
       </c>
       <c r="L32" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N32" t="n">
         <v>2</v>
       </c>
       <c r="O32" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P32" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="Q32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R32" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="V32" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -3119,29 +3119,29 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Somtochukwu Cyril</t>
+          <t>Duke Miles</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>8:45 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I33" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="J33" t="n">
         <v>4</v>
@@ -3150,37 +3150,37 @@
         <v>2</v>
       </c>
       <c r="L33" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P33" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="Q33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R33" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="V33" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0:16 - 1st Half</t>
+          <t>15:47 - 2nd Half</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -3226,7 +3226,7 @@
         <v>7</v>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K34" t="n">
         <v>4</v>
@@ -3244,19 +3244,19 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Q34" t="n">
         <v>3</v>
       </c>
       <c r="R34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
       </c>
       <c r="T34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
@@ -3298,20 +3298,20 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0:16 - 1st Half</t>
+          <t>15:47 - 2nd Half</t>
         </is>
       </c>
       <c r="H35" t="n">
+        <v>9</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2</v>
+      </c>
+      <c r="J35" t="n">
         <v>6</v>
       </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="n">
-        <v>4</v>
-      </c>
       <c r="K35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -3320,19 +3320,19 @@
         <v>1</v>
       </c>
       <c r="N35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P35" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -3380,53 +3380,53 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>8:45 - 2nd Half</t>
+          <t>1:01 - 2nd Half</t>
         </is>
       </c>
       <c r="H36" t="n">
+        <v>36</v>
+      </c>
+      <c r="I36" t="n">
+        <v>39</v>
+      </c>
+      <c r="J36" t="n">
+        <v>5</v>
+      </c>
+      <c r="K36" t="n">
+        <v>4</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>3</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1</v>
+      </c>
+      <c r="P36" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>15</v>
+      </c>
+      <c r="R36" t="n">
         <v>24</v>
       </c>
-      <c r="I36" t="n">
-        <v>25</v>
-      </c>
-      <c r="J36" t="n">
-        <v>4</v>
-      </c>
-      <c r="K36" t="n">
-        <v>4</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>3</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>11</v>
-      </c>
-      <c r="R36" t="n">
-        <v>17</v>
-      </c>
       <c r="S36" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T36" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -3462,21 +3462,21 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>8:45 - 2nd Half</t>
+          <t>1:01 - 2nd Half</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="I37" t="n">
+        <v>15</v>
+      </c>
+      <c r="J37" t="n">
+        <v>6</v>
+      </c>
+      <c r="K37" t="n">
         <v>5</v>
       </c>
-      <c r="J37" t="n">
-        <v>5</v>
-      </c>
-      <c r="K37" t="n">
-        <v>2</v>
-      </c>
       <c r="L37" t="n">
         <v>2</v>
       </c>
@@ -3484,31 +3484,31 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P37" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="Q37" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R37" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U37" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V37" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
@@ -3544,17 +3544,17 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0:16 - 1st Half</t>
+          <t>15:47 - 2nd Half</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I38" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J38" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -3566,19 +3566,19 @@
         <v>1</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P38" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -3626,20 +3626,20 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>8:45 - 2nd Half</t>
+          <t>1:01 - 2nd Half</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -3651,22 +3651,22 @@
         <v>2</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P39" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="Q39" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R39" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="S39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U39" t="n">
         <v>2</v>
@@ -3790,7 +3790,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0:16 - 1st Half</t>
+          <t>15:47 - 2nd Half</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -4118,11 +4118,11 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>8:45 - 2nd Half</t>
+          <t>1:01 - 2nd Half</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I45" t="n">
         <v>2</v>
@@ -4140,13 +4140,13 @@
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P45" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="Q45" t="n">
         <v>1</v>
@@ -4185,68 +4185,68 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Amari Evans</t>
+          <t>Kanon Catchings</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>1:01 - 2nd Half</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I46" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P46" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="Q46" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="R46" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="S46" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T46" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U46" t="n">
         <v>4</v>
       </c>
       <c r="V46" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47">
@@ -4267,68 +4267,68 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Kanon Catchings</t>
+          <t>Amari Evans</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>8:45 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H47" t="n">
         <v>20</v>
       </c>
       <c r="I47" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J47" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="Q47" t="n">
+        <v>9</v>
+      </c>
+      <c r="R47" t="n">
+        <v>18</v>
+      </c>
+      <c r="S47" t="n">
+        <v>2</v>
+      </c>
+      <c r="T47" t="n">
+        <v>6</v>
+      </c>
+      <c r="U47" t="n">
+        <v>4</v>
+      </c>
+      <c r="V47" t="n">
         <v>7</v>
-      </c>
-      <c r="R47" t="n">
-        <v>12</v>
-      </c>
-      <c r="S47" t="n">
-        <v>5</v>
-      </c>
-      <c r="T47" t="n">
-        <v>7</v>
-      </c>
-      <c r="U47" t="n">
-        <v>0</v>
-      </c>
-      <c r="V47" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -4595,68 +4595,68 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Nordin Kapic</t>
+          <t>Ja'Borri McGhee</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>1:01 - 2nd Half</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I51" t="n">
+        <v>20</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>1</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>1</v>
+      </c>
+      <c r="O51" t="n">
+        <v>4</v>
+      </c>
+      <c r="P51" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>8</v>
+      </c>
+      <c r="R51" t="n">
         <v>12</v>
       </c>
-      <c r="J51" t="n">
-        <v>4</v>
-      </c>
-      <c r="K51" t="n">
-        <v>1</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>1</v>
-      </c>
-      <c r="N51" t="n">
-        <v>2</v>
-      </c>
-      <c r="O51" t="n">
-        <v>2</v>
-      </c>
-      <c r="P51" t="n">
-        <v>21</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>4</v>
-      </c>
-      <c r="R51" t="n">
-        <v>7</v>
-      </c>
       <c r="S51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T51" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V51" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
@@ -4677,68 +4677,68 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Trent Pierce</t>
+          <t>Nordin Kapic</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H52" t="n">
+        <v>13</v>
+      </c>
+      <c r="I52" t="n">
         <v>12</v>
       </c>
-      <c r="I52" t="n">
-        <v>13</v>
-      </c>
       <c r="J52" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P52" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="Q52" t="n">
+        <v>4</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7</v>
+      </c>
+      <c r="S52" t="n">
+        <v>2</v>
+      </c>
+      <c r="T52" t="n">
         <v>5</v>
       </c>
-      <c r="R52" t="n">
-        <v>11</v>
-      </c>
-      <c r="S52" t="n">
-        <v>3</v>
-      </c>
-      <c r="T52" t="n">
-        <v>7</v>
-      </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -4759,32 +4759,32 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Ja'Borri McGhee</t>
+          <t>Trent Pierce</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>MSST</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>8:45 - 2nd Half</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I53" t="n">
         <v>13</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -4802,25 +4802,25 @@
         <v>3</v>
       </c>
       <c r="P53" t="n">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="Q53" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R53" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="S53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T53" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U53" t="n">
         <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -4841,68 +4841,68 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>D.J. Wagner</t>
+          <t>Jamarion Davis-Fleming</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ARK</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>1:01 - 2nd Half</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I54" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J54" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K54" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N54" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>3</v>
       </c>
       <c r="P54" t="n">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="Q54" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U54" t="n">
         <v>2</v>
       </c>
       <c r="V54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -4923,68 +4923,68 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Eduardo Klafke</t>
+          <t>D.J. Wagner</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>ARK</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H55" t="n">
         <v>9</v>
       </c>
       <c r="I55" t="n">
+        <v>10</v>
+      </c>
+      <c r="J55" t="n">
+        <v>4</v>
+      </c>
+      <c r="K55" t="n">
         <v>5</v>
       </c>
-      <c r="J55" t="n">
-        <v>6</v>
-      </c>
-      <c r="K55" t="n">
-        <v>1</v>
-      </c>
       <c r="L55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P55" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="Q55" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="S55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U55" t="n">
         <v>2</v>
       </c>
       <c r="V55" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56">
@@ -5005,62 +5005,62 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Jamarion Davis-Fleming</t>
+          <t>Eduardo Klafke</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>MSST</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>8:45 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H56" t="n">
         <v>9</v>
       </c>
       <c r="I56" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J56" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O56" t="n">
         <v>2</v>
       </c>
       <c r="P56" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U56" t="n">
         <v>2</v>
@@ -5087,62 +5087,62 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Chandler Bing</t>
+          <t>Achor Achor</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>1:01 - 2nd Half</t>
         </is>
       </c>
       <c r="H57" t="n">
         <v>8</v>
       </c>
       <c r="I57" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J57" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P57" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="Q57" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R57" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U57" t="n">
         <v>0</v>
@@ -5169,35 +5169,35 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Justin Abson</t>
+          <t>Chandler Bing</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>8:45 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H58" t="n">
         <v>8</v>
       </c>
       <c r="I58" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J58" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -5209,28 +5209,28 @@
         <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P58" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Achor Achor</t>
+          <t>Justin Abson</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>MSST</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -5266,41 +5266,41 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>8:45 - 2nd Half</t>
+          <t>1:01 - 2nd Half</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I59" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J59" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Q59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -5309,10 +5309,10 @@
         <v>0</v>
       </c>
       <c r="U59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Isaiah Brown</t>
+          <t>Brandon Garrison</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>FLA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>0:16 - 1st Half</t>
+          <t>15:47 - 2nd Half</t>
         </is>
       </c>
       <c r="H60" t="n">
@@ -5358,7 +5358,7 @@
         <v>4</v>
       </c>
       <c r="J60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -5367,22 +5367,22 @@
         <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O60" t="n">
         <v>1</v>
       </c>
       <c r="P60" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -5391,10 +5391,10 @@
         <v>0</v>
       </c>
       <c r="U60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V60" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -5415,68 +5415,68 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Travis Perry</t>
+          <t>Isaiah Brown</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>15:47 - 2nd Half</t>
         </is>
       </c>
       <c r="H61" t="n">
         <v>6</v>
       </c>
       <c r="I61" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J61" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K61" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>1</v>
       </c>
       <c r="P61" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R61" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U61" t="n">
         <v>2</v>
       </c>
       <c r="V61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
@@ -5497,38 +5497,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Brandon Garrison</t>
+          <t>Travis Perry</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>0:16 - 1st Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I62" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K62" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
@@ -5540,25 +5540,25 @@
         <v>1</v>
       </c>
       <c r="P62" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Q62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -5661,62 +5661,62 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Bishop Boswell</t>
+          <t>Kareem Stagg</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>1:01 - 2nd Half</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I64" t="n">
+        <v>6</v>
+      </c>
+      <c r="J64" t="n">
+        <v>3</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>1</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="n">
+        <v>2</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>2</v>
+      </c>
+      <c r="R64" t="n">
         <v>5</v>
       </c>
-      <c r="J64" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" t="n">
-        <v>4</v>
-      </c>
-      <c r="L64" t="n">
-        <v>2</v>
-      </c>
-      <c r="M64" t="n">
-        <v>0</v>
-      </c>
-      <c r="N64" t="n">
-        <v>2</v>
-      </c>
-      <c r="O64" t="n">
+      <c r="S64" t="n">
+        <v>2</v>
+      </c>
+      <c r="T64" t="n">
         <v>5</v>
-      </c>
-      <c r="P64" t="n">
-        <v>29</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>2</v>
-      </c>
-      <c r="R64" t="n">
-        <v>7</v>
-      </c>
-      <c r="S64" t="n">
-        <v>1</v>
-      </c>
-      <c r="T64" t="n">
-        <v>2</v>
       </c>
       <c r="U64" t="n">
         <v>0</v>
@@ -5743,22 +5743,22 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Dylan James</t>
+          <t>Andrija Jelavic</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>8:45 - 2nd Half</t>
+          <t>15:47 - 2nd Half</t>
         </is>
       </c>
       <c r="H65" t="n">
@@ -5771,10 +5771,10 @@
         <v>2</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M65" t="n">
         <v>0</v>
@@ -5783,22 +5783,22 @@
         <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P65" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="Q65" t="n">
         <v>2</v>
       </c>
       <c r="R65" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U65" t="n">
         <v>0</v>
@@ -5825,17 +5825,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Eli Ellis</t>
+          <t>Bishop Boswell</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5847,37 +5847,37 @@
         <v>4</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K66" t="n">
+        <v>4</v>
+      </c>
+      <c r="L66" t="n">
+        <v>2</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="n">
+        <v>2</v>
+      </c>
+      <c r="O66" t="n">
         <v>5</v>
       </c>
-      <c r="L66" t="n">
-        <v>1</v>
-      </c>
-      <c r="M66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N66" t="n">
-        <v>1</v>
-      </c>
-      <c r="O66" t="n">
-        <v>2</v>
-      </c>
       <c r="P66" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R66" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="S66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T66" t="n">
         <v>2</v>
@@ -5907,62 +5907,62 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Elijah Strong</t>
+          <t>Dylan James</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>1:01 - 2nd Half</t>
         </is>
       </c>
       <c r="H67" t="n">
         <v>4</v>
       </c>
       <c r="I67" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
         <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="Q67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R67" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="S67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T67" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U67" t="n">
         <v>0</v>
@@ -5989,17 +5989,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Ethan Burg</t>
+          <t>Eli Ellis</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -6011,31 +6011,31 @@
         <v>4</v>
       </c>
       <c r="I68" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K68" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M68" t="n">
         <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O68" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P68" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="Q68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
         <v>3</v>
@@ -6044,13 +6044,13 @@
         <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U68" t="n">
         <v>0</v>
       </c>
       <c r="V68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -6071,68 +6071,68 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Sergej Macura</t>
+          <t>Elijah Strong</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>MSST</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>8:45 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H69" t="n">
         <v>4</v>
       </c>
       <c r="I69" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J69" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P69" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R69" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="S69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T69" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -6153,68 +6153,68 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>T.O. Barrett</t>
+          <t>Ethan Burg</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H70" t="n">
         <v>4</v>
       </c>
       <c r="I70" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K70" t="n">
         <v>2</v>
       </c>
       <c r="L70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
         <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P70" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="Q70" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R70" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
       </c>
       <c r="T70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -6250,14 +6250,14 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>8:45 - 2nd Half</t>
+          <t>1:01 - 2nd Half</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I71" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6272,13 +6272,13 @@
         <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P71" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="Q71" t="n">
         <v>2</v>
@@ -6293,10 +6293,10 @@
         <v>1</v>
       </c>
       <c r="U71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -6317,38 +6317,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Kezza Giffa</t>
+          <t>Sergej Macura</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>1:01 - 2nd Half</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I72" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M72" t="n">
         <v>0</v>
@@ -6360,22 +6360,22 @@
         <v>1</v>
       </c>
       <c r="P72" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="Q72" t="n">
         <v>1</v>
       </c>
       <c r="R72" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
       </c>
       <c r="T72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V72" t="n">
         <v>2</v>
@@ -6399,68 +6399,68 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Troy Henderson</t>
+          <t>T.O. Barrett</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I73" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M73" t="n">
         <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P73" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="Q73" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R73" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="S73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -6481,38 +6481,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Kareem Stagg</t>
+          <t>Kezza Giffa</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>8:45 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J74" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
@@ -6521,10 +6521,10 @@
         <v>2</v>
       </c>
       <c r="O74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P74" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="Q74" t="n">
         <v>1</v>
@@ -6533,16 +6533,16 @@
         <v>4</v>
       </c>
       <c r="S74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T74" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -6563,26 +6563,26 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Urban Klavzar</t>
+          <t>Troy Henderson</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>FLA</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>0:16 - 1st Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I75" t="n">
         <v>3</v>
@@ -6591,7 +6591,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
@@ -6603,10 +6603,10 @@
         <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Q75" t="n">
         <v>1</v>
@@ -6618,7 +6618,7 @@
         <v>1</v>
       </c>
       <c r="T75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U75" t="n">
         <v>0</v>
@@ -6645,32 +6645,32 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Zach Day</t>
+          <t>Urban Klavzar</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>15:47 - 2nd Half</t>
         </is>
       </c>
       <c r="H76" t="n">
         <v>2</v>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
@@ -6679,28 +6679,28 @@
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
         <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P76" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U76" t="n">
         <v>0</v>
@@ -6727,17 +6727,17 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Amaree Abram</t>
+          <t>Zach Day</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -6746,10 +6746,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J77" t="n">
         <v>1</v>
@@ -6758,10 +6758,10 @@
         <v>0</v>
       </c>
       <c r="L77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N77" t="n">
         <v>0</v>
@@ -6770,13 +6770,13 @@
         <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -6785,10 +6785,10 @@
         <v>0</v>
       </c>
       <c r="U77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -6809,38 +6809,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Andrija Jelavic</t>
+          <t>Amaree Abram</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>0:16 - 1st Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H78" t="n">
         <v>1</v>
       </c>
       <c r="I78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J78" t="n">
         <v>1</v>
       </c>
       <c r="K78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M78" t="n">
         <v>0</v>
@@ -6849,28 +6849,28 @@
         <v>0</v>
       </c>
       <c r="O78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Q78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
       </c>
       <c r="T78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -7152,7 +7152,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>8:45 - 2nd Half</t>
+          <t>1:01 - 2nd Half</t>
         </is>
       </c>
       <c r="H82" t="n">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>8:45 - 2nd Half</t>
+          <t>1:01 - 2nd Half</t>
         </is>
       </c>
       <c r="H87" t="n">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>0:16 - 1st Half</t>
+          <t>15:47 - 2nd Half</t>
         </is>
       </c>
       <c r="H90" t="n">
@@ -7833,7 +7833,7 @@
         <v>1</v>
       </c>
       <c r="O90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P90" t="n">
         <v>5</v>
@@ -7978,37 +7978,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>The Backslashers</t>
+          <t>G-Flop</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bend Rimmers</t>
+          <t>The Backslashers</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G-Flop</t>
+          <t>Bend Rimmers</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="C4" t="n">
         <v>3</v>
@@ -8021,7 +8021,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C5" t="n">
         <v>4</v>
@@ -8047,7 +8047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C7" t="n">
         <v>3</v>

--- a/docs/Today_PoohPoints_SEC_ByOwner_2026-03-07.xlsx
+++ b/docs/Today_PoohPoints_SEC_ByOwner_2026-03-07.xlsx
@@ -756,7 +756,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1:01 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -784,7 +784,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q4" t="n">
         <v>4</v>
@@ -987,22 +987,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Trevon Brazile</t>
+          <t>Thomas Haugh</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ARK</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>10:03 - 2nd Half</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1012,43 +1012,43 @@
         <v>19</v>
       </c>
       <c r="J7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
         <v>3</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="Q7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -1069,68 +1069,68 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Thomas Haugh</t>
+          <t>Trevon Brazile</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FLA</t>
+          <t>ARK</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>15:47 - 2nd Half</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
         <v>3</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="Q8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R8" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1:01 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1604,7 +1604,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q14" t="n">
         <v>6</v>
@@ -1658,23 +1658,23 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>15:47 - 2nd Half</t>
+          <t>10:03 - 2nd Half</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -1683,28 +1683,28 @@
         <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R15" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -1740,11 +1740,11 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>15:47 - 2nd Half</t>
+          <t>10:03 - 2nd Half</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -1759,7 +1759,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1768,7 +1768,7 @@
         <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -1986,20 +1986,20 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>15:47 - 2nd Half</t>
+          <t>10:03 - 2nd Half</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2014,13 +2014,13 @@
         <v>1</v>
       </c>
       <c r="P19" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1:01 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -2232,17 +2232,17 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>15:47 - 2nd Half</t>
+          <t>10:03 - 2nd Half</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I22" t="n">
         <v>9</v>
       </c>
       <c r="J22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K22" t="n">
         <v>3</v>
@@ -2251,7 +2251,7 @@
         <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N22" t="n">
         <v>3</v>
@@ -2260,7 +2260,7 @@
         <v>2</v>
       </c>
       <c r="P22" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="Q22" t="n">
         <v>4</v>
@@ -2396,11 +2396,11 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>15:47 - 2nd Half</t>
+          <t>10:03 - 2nd Half</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I24" t="n">
         <v>17</v>
@@ -2409,7 +2409,7 @@
         <v>2</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L24" t="n">
         <v>1</v>
@@ -2421,16 +2421,16 @@
         <v>1</v>
       </c>
       <c r="O24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P24" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="Q24" t="n">
         <v>6</v>
       </c>
       <c r="R24" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -2545,35 +2545,35 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Anthony Robinson II</t>
+          <t>Boogie Fland</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>10:03 - 2nd Half</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I26" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L26" t="n">
         <v>1</v>
@@ -2582,31 +2582,31 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R26" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -2627,68 +2627,68 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Myles Stute</t>
+          <t>Anthony Robinson II</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P27" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="Q27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -2709,62 +2709,62 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Boogie Fland</t>
+          <t>Myles Stute</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FLA</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>15:47 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K28" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P28" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="Q28" t="n">
         <v>2</v>
       </c>
       <c r="R28" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1:01 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -3216,20 +3216,20 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>15:47 - 2nd Half</t>
+          <t>10:03 - 2nd Half</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I34" t="n">
         <v>7</v>
       </c>
       <c r="J34" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -3244,13 +3244,13 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Q34" t="n">
         <v>3</v>
       </c>
       <c r="R34" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -3298,11 +3298,11 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>15:47 - 2nd Half</t>
+          <t>10:03 - 2nd Half</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I35" t="n">
         <v>2</v>
@@ -3317,7 +3317,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N35" t="n">
         <v>3</v>
@@ -3326,7 +3326,7 @@
         <v>3</v>
       </c>
       <c r="P35" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Q35" t="n">
         <v>1</v>
@@ -3380,14 +3380,14 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1:01 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I36" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J36" t="n">
         <v>5</v>
@@ -3405,22 +3405,22 @@
         <v>3</v>
       </c>
       <c r="O36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P36" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q36" t="n">
+        <v>16</v>
+      </c>
+      <c r="R36" t="n">
+        <v>27</v>
+      </c>
+      <c r="S36" t="n">
+        <v>7</v>
+      </c>
+      <c r="T36" t="n">
         <v>15</v>
-      </c>
-      <c r="R36" t="n">
-        <v>24</v>
-      </c>
-      <c r="S36" t="n">
-        <v>6</v>
-      </c>
-      <c r="T36" t="n">
-        <v>12</v>
       </c>
       <c r="U36" t="n">
         <v>3</v>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1:01 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -3490,7 +3490,7 @@
         <v>3</v>
       </c>
       <c r="P37" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q37" t="n">
         <v>4</v>
@@ -3544,14 +3544,14 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>15:47 - 2nd Half</t>
+          <t>10:03 - 2nd Half</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I38" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J38" t="n">
         <v>7</v>
@@ -3569,16 +3569,16 @@
         <v>1</v>
       </c>
       <c r="O38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P38" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R38" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -3626,17 +3626,17 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1:01 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I39" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
         <v>5</v>
@@ -3654,7 +3654,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Q39" t="n">
         <v>5</v>
@@ -3669,10 +3669,10 @@
         <v>5</v>
       </c>
       <c r="U39" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="V39" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40">
@@ -3790,26 +3790,26 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>15:47 - 2nd Half</t>
+          <t>10:03 - 2nd Half</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I41" t="n">
         <v>5</v>
       </c>
       <c r="J41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" t="n">
         <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N41" t="n">
         <v>1</v>
@@ -3818,13 +3818,13 @@
         <v>3</v>
       </c>
       <c r="P41" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Q41" t="n">
         <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4118,11 +4118,11 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1:01 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I45" t="n">
         <v>2</v>
@@ -4131,10 +4131,10 @@
         <v>2</v>
       </c>
       <c r="K45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -4143,7 +4143,7 @@
         <v>2</v>
       </c>
       <c r="O45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P45" t="n">
         <v>28</v>
@@ -4200,17 +4200,17 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1:01 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I46" t="n">
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K46" t="n">
         <v>1</v>
@@ -4228,7 +4228,7 @@
         <v>3</v>
       </c>
       <c r="P46" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q46" t="n">
         <v>7</v>
@@ -4610,7 +4610,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>1:01 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -4620,7 +4620,7 @@
         <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -4638,13 +4638,13 @@
         <v>4</v>
       </c>
       <c r="P51" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q51" t="n">
         <v>8</v>
       </c>
       <c r="R51" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="S51" t="n">
         <v>1</v>
@@ -4677,17 +4677,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Nordin Kapic</t>
+          <t>Jamarion Davis-Fleming</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -4699,13 +4699,13 @@
         <v>13</v>
       </c>
       <c r="I52" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J52" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -4714,25 +4714,25 @@
         <v>1</v>
       </c>
       <c r="N52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P52" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q52" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R52" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="S52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U52" t="n">
         <v>2</v>
@@ -4759,68 +4759,68 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Trent Pierce</t>
+          <t>Nordin Kapic</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H53" t="n">
+        <v>13</v>
+      </c>
+      <c r="I53" t="n">
         <v>12</v>
       </c>
-      <c r="I53" t="n">
-        <v>13</v>
-      </c>
       <c r="J53" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P53" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="Q53" t="n">
+        <v>4</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7</v>
+      </c>
+      <c r="S53" t="n">
+        <v>2</v>
+      </c>
+      <c r="T53" t="n">
         <v>5</v>
       </c>
-      <c r="R53" t="n">
-        <v>11</v>
-      </c>
-      <c r="S53" t="n">
-        <v>3</v>
-      </c>
-      <c r="T53" t="n">
-        <v>7</v>
-      </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -4841,68 +4841,68 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Jamarion Davis-Fleming</t>
+          <t>Trent Pierce</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>MSST</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>1:01 - 2nd Half</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I54" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J54" t="n">
+        <v>6</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>1</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>1</v>
+      </c>
+      <c r="O54" t="n">
+        <v>3</v>
+      </c>
+      <c r="P54" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q54" t="n">
         <v>5</v>
       </c>
-      <c r="K54" t="n">
-        <v>2</v>
-      </c>
-      <c r="L54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" t="n">
-        <v>1</v>
-      </c>
-      <c r="N54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" t="n">
-        <v>3</v>
-      </c>
-      <c r="P54" t="n">
-        <v>21</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -4923,35 +4923,35 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>D.J. Wagner</t>
+          <t>Brandon Garrison</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ARK</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>10:03 - 2nd Half</t>
         </is>
       </c>
       <c r="H55" t="n">
         <v>9</v>
       </c>
       <c r="I55" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J55" t="n">
         <v>4</v>
       </c>
       <c r="K55" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L55" t="n">
         <v>1</v>
@@ -4960,31 +4960,31 @@
         <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P55" t="n">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="Q55" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R55" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V55" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -5005,68 +5005,68 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Eduardo Klafke</t>
+          <t>D.J. Wagner</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>ARK</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H56" t="n">
         <v>9</v>
       </c>
       <c r="I56" t="n">
+        <v>10</v>
+      </c>
+      <c r="J56" t="n">
+        <v>4</v>
+      </c>
+      <c r="K56" t="n">
         <v>5</v>
       </c>
-      <c r="J56" t="n">
-        <v>6</v>
-      </c>
-      <c r="K56" t="n">
-        <v>1</v>
-      </c>
       <c r="L56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P56" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="Q56" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="S56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U56" t="n">
         <v>2</v>
       </c>
       <c r="V56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
@@ -5087,38 +5087,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Achor Achor</t>
+          <t>Eduardo Klafke</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>MSST</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>1:01 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J57" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K57" t="n">
         <v>1</v>
       </c>
       <c r="L57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
@@ -5127,28 +5127,28 @@
         <v>1</v>
       </c>
       <c r="O57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P57" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="Q57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R57" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -5169,68 +5169,68 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Chandler Bing</t>
+          <t>Isaiah Brown</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>10:03 - 2nd Half</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I58" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N58" t="n">
         <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P58" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="Q58" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R58" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S58" t="n">
         <v>1</v>
       </c>
       <c r="T58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V58" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Justin Abson</t>
+          <t>Achor Achor</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -5266,41 +5266,41 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>1:01 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H59" t="n">
         <v>8</v>
       </c>
       <c r="I59" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J59" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K59" t="n">
         <v>1</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P59" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -5309,10 +5309,10 @@
         <v>0</v>
       </c>
       <c r="U59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -5333,62 +5333,62 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Brandon Garrison</t>
+          <t>Chandler Bing</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>15:47 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H60" t="n">
+        <v>8</v>
+      </c>
+      <c r="I60" t="n">
+        <v>9</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
+        <v>3</v>
+      </c>
+      <c r="P60" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>4</v>
+      </c>
+      <c r="R60" t="n">
         <v>6</v>
       </c>
-      <c r="I60" t="n">
-        <v>4</v>
-      </c>
-      <c r="J60" t="n">
-        <v>2</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" t="n">
-        <v>1</v>
-      </c>
-      <c r="M60" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" t="n">
-        <v>1</v>
-      </c>
-      <c r="O60" t="n">
-        <v>1</v>
-      </c>
-      <c r="P60" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>2</v>
-      </c>
-      <c r="R60" t="n">
-        <v>2</v>
-      </c>
       <c r="S60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U60" t="n">
         <v>0</v>
@@ -5415,56 +5415,56 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Isaiah Brown</t>
+          <t>Justin Abson</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>FLA</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>15:47 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I61" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J61" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
         <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P61" t="n">
         <v>9</v>
       </c>
       <c r="Q61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -5476,7 +5476,7 @@
         <v>2</v>
       </c>
       <c r="V61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -5579,62 +5579,62 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>DeWayne Brown II</t>
+          <t>Andrija Jelavic</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>10:03 - 2nd Half</t>
         </is>
       </c>
       <c r="H63" t="n">
         <v>5</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>1</v>
       </c>
       <c r="P63" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R63" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U63" t="n">
         <v>0</v>
@@ -5661,62 +5661,62 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Kareem Stagg</t>
+          <t>DeWayne Brown II</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>1:01 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H64" t="n">
         <v>5</v>
       </c>
       <c r="I64" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P64" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="Q64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T64" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U64" t="n">
         <v>0</v>
@@ -5743,35 +5743,35 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Andrija Jelavic</t>
+          <t>Kareem Stagg</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>15:47 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I65" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L65" t="n">
         <v>1</v>
@@ -5780,25 +5780,25 @@
         <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="Q65" t="n">
         <v>2</v>
       </c>
       <c r="R65" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T65" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U65" t="n">
         <v>0</v>
@@ -5907,62 +5907,62 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Dylan James</t>
+          <t>Eli Ellis</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>1:01 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H67" t="n">
         <v>4</v>
       </c>
       <c r="I67" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
         <v>2</v>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M67" t="n">
         <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P67" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="Q67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
       </c>
       <c r="T67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U67" t="n">
         <v>0</v>
@@ -5989,7 +5989,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Eli Ellis</t>
+          <t>Elijah Strong</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6011,40 +6011,40 @@
         <v>4</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>2</v>
       </c>
       <c r="P68" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R68" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="S68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U68" t="n">
         <v>0</v>
@@ -6071,17 +6071,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Elijah Strong</t>
+          <t>Ethan Burg</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -6093,46 +6093,46 @@
         <v>4</v>
       </c>
       <c r="I69" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
         <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P69" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R69" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="S69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T69" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U69" t="n">
         <v>0</v>
       </c>
       <c r="V69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Ethan Burg</t>
+          <t>Jordan Ross</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -6175,13 +6175,13 @@
         <v>4</v>
       </c>
       <c r="I70" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
@@ -6190,31 +6190,31 @@
         <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O70" t="n">
+        <v>2</v>
+      </c>
+      <c r="P70" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>2</v>
+      </c>
+      <c r="R70" t="n">
         <v>5</v>
       </c>
-      <c r="P70" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>2</v>
-      </c>
-      <c r="R70" t="n">
-        <v>3</v>
-      </c>
       <c r="S70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T70" t="n">
         <v>1</v>
       </c>
       <c r="U70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -6235,12 +6235,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Jordan Ross</t>
+          <t>Sergej Macura</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -6250,50 +6250,50 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>1:01 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H71" t="n">
         <v>4</v>
       </c>
       <c r="I71" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K71" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M71" t="n">
         <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P71" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="Q71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R71" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V71" t="n">
         <v>2</v>
@@ -6317,35 +6317,35 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Sergej Macura</t>
+          <t>T.O. Barrett</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>MSST</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>1:01 - 2nd Half</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H72" t="n">
         <v>4</v>
       </c>
       <c r="I72" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J72" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L72" t="n">
         <v>1</v>
@@ -6357,25 +6357,25 @@
         <v>2</v>
       </c>
       <c r="O72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P72" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="Q72" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R72" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
       </c>
       <c r="T72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V72" t="n">
         <v>2</v>
@@ -6399,68 +6399,68 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>T.O. Barrett</t>
+          <t>Dylan James</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I73" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
         <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="Q73" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R73" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
       </c>
       <c r="T73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -6645,12 +6645,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Urban Klavzar</t>
+          <t>Jasper Johnson</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>FLA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>15:47 - 2nd Half</t>
+          <t>10:03 - 2nd Half</t>
         </is>
       </c>
       <c r="H76" t="n">
@@ -6670,7 +6670,7 @@
         <v>3</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
@@ -6682,13 +6682,13 @@
         <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O76" t="n">
         <v>1</v>
       </c>
       <c r="P76" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q76" t="n">
         <v>1</v>
@@ -7152,7 +7152,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>1:01 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H82" t="n">
@@ -7301,35 +7301,35 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Isaiah Sealy</t>
+          <t>Urban Klavzar</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>ARK</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>10:03 - 2nd Half</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I84" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L84" t="n">
         <v>0</v>
@@ -7338,25 +7338,25 @@
         <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P84" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U84" t="n">
         <v>0</v>
@@ -7383,22 +7383,22 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Jayden Leverett</t>
+          <t>Isaiah Sealy</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>ARK</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H85" t="n">
@@ -7408,10 +7408,10 @@
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
@@ -7420,19 +7420,19 @@
         <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P85" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -7465,17 +7465,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Jordan Butler</t>
+          <t>Jayden Leverett</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -7490,7 +7490,7 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -7505,16 +7505,16 @@
         <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P86" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -7547,22 +7547,22 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Justin Bailey</t>
+          <t>Jordan Butler</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>1:01 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H87" t="n">
@@ -7578,19 +7578,19 @@
         <v>0</v>
       </c>
       <c r="L87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
         <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q87" t="n">
         <v>0</v>
@@ -7629,22 +7629,22 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Trent Burns</t>
+          <t>Justin Bailey</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H88" t="n">
@@ -7660,19 +7660,19 @@
         <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M88" t="n">
         <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P88" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q88" t="n">
         <v>0</v>
@@ -7711,22 +7711,22 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Tyler Harris</t>
+          <t>Trent Burns</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H89" t="n">
@@ -7754,7 +7754,7 @@
         <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
@@ -7793,26 +7793,26 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Jasper Johnson</t>
+          <t>Tyler Harris</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>15:47 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I90" t="n">
         <v>0</v>
@@ -7830,13 +7830,13 @@
         <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
@@ -7982,7 +7982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C2" t="n">
         <v>3</v>
@@ -7995,7 +7995,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C3" t="n">
         <v>4</v>
@@ -8021,7 +8021,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C5" t="n">
         <v>4</v>
@@ -8047,7 +8047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C7" t="n">
         <v>3</v>

--- a/docs/Today_PoohPoints_SEC_ByOwner_2026-03-07.xlsx
+++ b/docs/Today_PoohPoints_SEC_ByOwner_2026-03-07.xlsx
@@ -429,7 +429,7 @@
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
     <col width="6" customWidth="1" min="8" max="8"/>
     <col width="5" customWidth="1" min="9" max="9"/>
     <col width="5" customWidth="1" min="10" max="10"/>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>10:03 - 2nd Half</t>
+          <t>7:30 - 2nd Half</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1030,7 +1030,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Q7" t="n">
         <v>7</v>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>10:03 - 2nd Half</t>
+          <t>7:30 - 2nd Half</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1686,7 +1686,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q15" t="n">
         <v>2</v>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>10:03 - 2nd Half</t>
+          <t>7:30 - 2nd Half</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -1986,17 +1986,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>10:03 - 2nd Half</t>
+          <t>7:30 - 2nd Half</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
         <v>2</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>2</v>
@@ -2011,10 +2011,10 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P19" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="Q19" t="n">
         <v>1</v>
@@ -2232,23 +2232,23 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>10:03 - 2nd Half</t>
+          <t>7:30 - 2nd Half</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I22" t="n">
         <v>9</v>
       </c>
       <c r="J22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M22" t="n">
         <v>2</v>
@@ -2260,13 +2260,13 @@
         <v>2</v>
       </c>
       <c r="P22" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Q22" t="n">
         <v>4</v>
       </c>
       <c r="R22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>10:03 - 2nd Half</t>
+          <t>7:30 - 2nd Half</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -2421,10 +2421,10 @@
         <v>1</v>
       </c>
       <c r="O24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P24" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="Q24" t="n">
         <v>6</v>
@@ -2560,14 +2560,14 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>10:03 - 2nd Half</t>
+          <t>7:30 - 2nd Half</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J26" t="n">
         <v>2</v>
@@ -2585,10 +2585,10 @@
         <v>3</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P26" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Q26" t="n">
         <v>4</v>
@@ -2603,10 +2603,10 @@
         <v>3</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -3216,14 +3216,14 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>10:03 - 2nd Half</t>
+          <t>7:30 - 2nd Half</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I34" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J34" t="n">
         <v>6</v>
@@ -3244,13 +3244,13 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R34" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -3298,14 +3298,14 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>10:03 - 2nd Half</t>
+          <t>7:30 - 2nd Half</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J35" t="n">
         <v>6</v>
@@ -3320,19 +3320,19 @@
         <v>2</v>
       </c>
       <c r="N35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O35" t="n">
         <v>3</v>
       </c>
       <c r="P35" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -3544,14 +3544,14 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>10:03 - 2nd Half</t>
+          <t>7:30 - 2nd Half</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I38" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J38" t="n">
         <v>7</v>
@@ -3572,7 +3572,7 @@
         <v>2</v>
       </c>
       <c r="P38" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="Q38" t="n">
         <v>4</v>
@@ -3587,10 +3587,10 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V38" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>10:03 - 2nd Half</t>
+          <t>7:30 - 2nd Half</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Brandon Garrison</t>
+          <t>Andrija Jelavic</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -4938,47 +4938,47 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>10:03 - 2nd Half</t>
+          <t>7:30 - 2nd Half</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I55" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J55" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L55" t="n">
         <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>2</v>
       </c>
       <c r="P55" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="Q55" t="n">
         <v>3</v>
       </c>
       <c r="R55" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U55" t="n">
         <v>0</v>
@@ -5005,35 +5005,35 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>D.J. Wagner</t>
+          <t>Brandon Garrison</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ARK</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>7:30 - 2nd Half</t>
         </is>
       </c>
       <c r="H56" t="n">
         <v>9</v>
       </c>
       <c r="I56" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J56" t="n">
         <v>4</v>
       </c>
       <c r="K56" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
         <v>1</v>
@@ -5042,31 +5042,31 @@
         <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P56" t="n">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="Q56" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R56" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V56" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -5087,68 +5087,68 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Eduardo Klafke</t>
+          <t>D.J. Wagner</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>ARK</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H57" t="n">
         <v>9</v>
       </c>
       <c r="I57" t="n">
+        <v>10</v>
+      </c>
+      <c r="J57" t="n">
+        <v>4</v>
+      </c>
+      <c r="K57" t="n">
         <v>5</v>
       </c>
-      <c r="J57" t="n">
-        <v>6</v>
-      </c>
-      <c r="K57" t="n">
-        <v>1</v>
-      </c>
       <c r="L57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P57" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="Q57" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R57" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="S57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U57" t="n">
         <v>2</v>
       </c>
       <c r="V57" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58">
@@ -5169,53 +5169,53 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Isaiah Brown</t>
+          <t>Eduardo Klafke</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>FLA</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>10:03 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H58" t="n">
         <v>9</v>
       </c>
       <c r="I58" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J58" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P58" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="Q58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R58" t="n">
         <v>5</v>
@@ -5224,13 +5224,13 @@
         <v>1</v>
       </c>
       <c r="T58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U58" t="n">
         <v>2</v>
       </c>
       <c r="V58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -5415,68 +5415,68 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Justin Abson</t>
+          <t>Isaiah Brown</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>7:30 - 2nd Half</t>
         </is>
       </c>
       <c r="H61" t="n">
         <v>8</v>
       </c>
       <c r="I61" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J61" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N61" t="n">
         <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P61" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T61" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U61" t="n">
         <v>2</v>
       </c>
       <c r="V61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
@@ -5497,17 +5497,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Travis Perry</t>
+          <t>Justin Abson</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -5516,43 +5516,43 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I62" t="n">
         <v>2</v>
       </c>
       <c r="J62" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K62" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U62" t="n">
         <v>2</v>
@@ -5579,68 +5579,68 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Andrija Jelavic</t>
+          <t>Travis Perry</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>10:03 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I63" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J63" t="n">
         <v>3</v>
       </c>
       <c r="K63" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M63" t="n">
         <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O63" t="n">
         <v>1</v>
       </c>
       <c r="P63" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="Q63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>10:03 - 2nd Half</t>
+          <t>7:30 - 2nd Half</t>
         </is>
       </c>
       <c r="H76" t="n">
@@ -6673,7 +6673,7 @@
         <v>1</v>
       </c>
       <c r="K76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
@@ -6688,13 +6688,13 @@
         <v>1</v>
       </c>
       <c r="P76" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q76" t="n">
         <v>1</v>
       </c>
       <c r="R76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S76" t="n">
         <v>1</v>
@@ -7316,7 +7316,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>10:03 - 2nd Half</t>
+          <t>7:30 - 2nd Half</t>
         </is>
       </c>
       <c r="H84" t="n">
@@ -7344,7 +7344,7 @@
         <v>2</v>
       </c>
       <c r="P84" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q84" t="n">
         <v>1</v>
@@ -7982,7 +7982,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C2" t="n">
         <v>3</v>
@@ -8021,7 +8021,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C5" t="n">
         <v>4</v>
@@ -8047,7 +8047,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C7" t="n">
         <v>3</v>

--- a/docs/Today_PoohPoints_SEC_ByOwner_2026-03-07.xlsx
+++ b/docs/Today_PoohPoints_SEC_ByOwner_2026-03-07.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V91"/>
+  <dimension ref="A1:V109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -654,61 +654,61 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>James Scott</t>
+          <t>Pablo Tamba</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>LSU</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>TA&amp;M@LSU</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>6:26 - 1st Half</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
         <v>2</v>
       </c>
       <c r="P3" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -717,10 +717,10 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -741,17 +741,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Jeremiah Wilkinson</t>
+          <t>James Scott</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -763,46 +763,46 @@
         <v>11</v>
       </c>
       <c r="I4" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -823,17 +823,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Devin McGlockton</t>
+          <t>Jeremiah Wilkinson</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -842,49 +842,49 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I5" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="U5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -905,56 +905,56 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Jacob Crews</t>
+          <t>Devin McGlockton</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -963,10 +963,10 @@
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -977,48 +977,48 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Backslashers</t>
+          <t>Boozers Losers</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Thomas Haugh</t>
+          <t>Jacob Crews</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FLA</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>7:30 - 2nd Half</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1027,28 +1027,28 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="Q7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1059,78 +1059,78 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Backslashers</t>
+          <t>Boozers Losers</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Trevon Brazile</t>
+          <t>Marcus Hill</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ARK</t>
+          <t>TA&amp;M</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>TA&amp;M@LSU</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>6:26 - 1st Half</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>25</v>
+        <v>-1</v>
       </c>
       <c r="I8" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="Q8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1151,65 +1151,65 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Meechie Johnson</t>
+          <t>Thomas Haugh</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>0:17 - 2nd Half</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="I9" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J9" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="Q9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R9" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V9" t="n">
         <v>4</v>
@@ -1233,68 +1233,68 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Ja'Kobi Gillespie</t>
+          <t>Trevon Brazile</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>ARK</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="I10" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="Q10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="R10" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T10" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="U10" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="V10" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1310,73 +1310,73 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Meleek Thomas</t>
+          <t>Meechie Johnson</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ARK</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="I11" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="J11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>11</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
         <v>7</v>
       </c>
-      <c r="K11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="n">
-        <v>3</v>
-      </c>
-      <c r="P11" t="n">
-        <v>45</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>9</v>
-      </c>
-      <c r="R11" t="n">
-        <v>22</v>
-      </c>
-      <c r="S11" t="n">
-        <v>5</v>
-      </c>
-      <c r="T11" t="n">
-        <v>6</v>
-      </c>
       <c r="U11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -1392,22 +1392,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Malik Dia</t>
+          <t>Ja'Kobi Gillespie</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1416,49 +1416,49 @@
         </is>
       </c>
       <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>17</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>5</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>5</v>
+      </c>
+      <c r="R12" t="n">
         <v>22</v>
       </c>
-      <c r="I12" t="n">
-        <v>22</v>
-      </c>
-      <c r="J12" t="n">
-        <v>4</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" t="n">
-        <v>4</v>
-      </c>
-      <c r="P12" t="n">
-        <v>21</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>8</v>
-      </c>
-      <c r="R12" t="n">
-        <v>13</v>
-      </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="U12" t="n">
         <v>6</v>
       </c>
       <c r="V12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -1479,68 +1479,68 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Felix Okpara</t>
+          <t>Meleek Thomas</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>ARK</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I13" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="J13" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O13" t="n">
         <v>3</v>
       </c>
       <c r="P13" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="Q13" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="R13" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="V13" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
@@ -1561,17 +1561,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Jayden Epps</t>
+          <t>Malik Dia</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MSST</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1580,49 +1580,49 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="I14" t="n">
+        <v>22</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>4</v>
+      </c>
+      <c r="P14" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>8</v>
+      </c>
+      <c r="R14" t="n">
         <v>13</v>
       </c>
-      <c r="J14" t="n">
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
         <v>6</v>
       </c>
-      <c r="K14" t="n">
-        <v>4</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>4</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1</v>
-      </c>
-      <c r="P14" t="n">
-        <v>34</v>
-      </c>
-      <c r="Q14" t="n">
+      <c r="V14" t="n">
         <v>6</v>
-      </c>
-      <c r="R14" t="n">
-        <v>14</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1</v>
-      </c>
-      <c r="T14" t="n">
-        <v>6</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1643,68 +1643,68 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Denzel Aberdeen</t>
+          <t>Felix Okpara</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>7:30 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="I15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="Q15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Micah Handlogten</t>
+          <t>Denzel Aberdeen</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FLA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1740,53 +1740,53 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>7:30 - 2nd Half</t>
+          <t>0:17 - 2nd Half</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16" t="n">
         <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -1797,78 +1797,78 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hilton Heads</t>
+          <t>The Backslashers</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Mark Mitchell</t>
+          <t>Jayden Epps</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="I17" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="J17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K17" t="n">
         <v>4</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P17" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="Q17" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="R17" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1879,78 +1879,78 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Hilton Heads</t>
+          <t>The Backslashers</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Tyler Nickel</t>
+          <t>Micah Handlogten</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>0:17 - 2nd Half</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I18" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>5</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P18" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="Q18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>3</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1971,68 +1971,68 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Collin Chandler</t>
+          <t>Mark Mitchell</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>7:30 - 2nd Half</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="R19" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20">
@@ -2048,22 +2048,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Quincy Ballard</t>
+          <t>Tyler Nickel</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MSST</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2072,43 +2072,43 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
         <v>2</v>
       </c>
       <c r="M20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="Q20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
         <v>2</v>
@@ -2130,40 +2130,40 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Ilias Kamardine</t>
+          <t>Collin Chandler</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>0:17 - 2nd Half</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L21" t="n">
         <v>1</v>
@@ -2175,22 +2175,22 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P21" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="Q21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -2207,45 +2207,45 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Three Dawg Nite</t>
+          <t>Hilton Heads</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Alex Condon</t>
+          <t>Quincy Ballard</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FLA</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>7:30 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L22" t="n">
         <v>2</v>
@@ -2254,19 +2254,19 @@
         <v>2</v>
       </c>
       <c r="N22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P22" t="n">
         <v>21</v>
       </c>
       <c r="Q22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -2275,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V22" t="n">
         <v>2</v>
@@ -2289,78 +2289,78 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Three Dawg Nite</t>
+          <t>Hilton Heads</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Jayden Stone</t>
+          <t>Ilias Kamardine</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I23" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J23" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P23" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="Q23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2396,17 +2396,17 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>7:30 - 2nd Half</t>
+          <t>0:17 - 2nd Half</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="I24" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="J24" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K24" t="n">
         <v>2</v>
@@ -2421,28 +2421,28 @@
         <v>1</v>
       </c>
       <c r="O24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P24" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="Q24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R24" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
       </c>
       <c r="T24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="V24" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25">
@@ -2463,68 +2463,68 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>AJ Storr</t>
+          <t>Alex Condon</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>0:17 - 2nd Half</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="I25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P25" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="Q25" t="n">
         <v>6</v>
       </c>
       <c r="R25" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -2540,43 +2540,43 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Boogie Fland</t>
+          <t>Jayden Stone</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FLA</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>7:30 - 2nd Half</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H26" t="n">
         <v>12</v>
       </c>
       <c r="I26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J26" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K26" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -2585,28 +2585,28 @@
         <v>3</v>
       </c>
       <c r="O26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P26" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="Q26" t="n">
         <v>4</v>
       </c>
       <c r="R26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S26" t="n">
         <v>2</v>
       </c>
       <c r="T26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -2622,40 +2622,40 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Anthony Robinson II</t>
+          <t>Marquel Sutton</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>LSU</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>TA&amp;M@LSU</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>6:26 - 1st Half</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I27" t="n">
         <v>5</v>
       </c>
       <c r="J27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
         <v>1</v>
@@ -2667,28 +2667,28 @@
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2704,17 +2704,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Myles Stute</t>
+          <t>AJ Storr</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2731,46 +2731,46 @@
         <v>8</v>
       </c>
       <c r="I28" t="n">
+        <v>13</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q28" t="n">
         <v>6</v>
       </c>
-      <c r="J28" t="n">
-        <v>2</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>2</v>
-      </c>
-      <c r="P28" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>2</v>
-      </c>
       <c r="R28" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="S28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -2791,68 +2791,68 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Jaylen Carey</t>
+          <t>Boogie Fland</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>0:17 - 2nd Half</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P29" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Nick Pringle</t>
+          <t>Anthony Robinson II</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ARK</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2892,19 +2892,19 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -2916,25 +2916,25 @@
         <v>5</v>
       </c>
       <c r="P30" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="Q30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -2945,27 +2945,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Bend Rimmers</t>
+          <t>Three Dawg Nite</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>J.P. Estrella</t>
+          <t>Myles Stute</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2974,16 +2974,16 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="I31" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="J31" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -2995,28 +2995,28 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P31" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="Q31" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="R31" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="S31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -3027,27 +3027,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Bend Rimmers</t>
+          <t>Three Dawg Nite</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Somtochukwu Cyril</t>
+          <t>Jaylen Carey</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3056,37 +3056,37 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="I32" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>5</v>
       </c>
       <c r="K32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P32" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -3095,10 +3095,10 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -3109,78 +3109,78 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Bend Rimmers</t>
+          <t>Three Dawg Nite</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Duke Miles</t>
+          <t>Nick Pringle</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>ARK</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="I33" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>5</v>
       </c>
       <c r="P33" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="Q33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R33" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -3196,61 +3196,61 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Xaivian Lee</t>
+          <t>J.P. Estrella</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>FLA</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>7:30 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="I34" t="n">
+        <v>20</v>
+      </c>
+      <c r="J34" t="n">
+        <v>10</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>3</v>
+      </c>
+      <c r="P34" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q34" t="n">
         <v>9</v>
       </c>
-      <c r="J34" t="n">
-        <v>6</v>
-      </c>
-      <c r="K34" t="n">
-        <v>5</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>4</v>
-      </c>
       <c r="R34" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -3259,10 +3259,10 @@
         <v>2</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -3278,61 +3278,61 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Malachi Moreno</t>
+          <t>Somtochukwu Cyril</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>7:30 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="I35" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M35" t="n">
         <v>2</v>
       </c>
       <c r="N35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P35" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -3341,10 +3341,10 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>G-Flop</t>
+          <t>Bend Rimmers</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3365,17 +3365,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Josh Hubbard</t>
+          <t>Duke Miles</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>MSST</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3384,49 +3384,49 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="I36" t="n">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="J36" t="n">
+        <v>4</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2</v>
+      </c>
+      <c r="L36" t="n">
+        <v>4</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>2</v>
+      </c>
+      <c r="O36" t="n">
         <v>5</v>
       </c>
-      <c r="K36" t="n">
-        <v>4</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>3</v>
-      </c>
-      <c r="O36" t="n">
-        <v>2</v>
-      </c>
       <c r="P36" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="Q36" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="R36" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
         <v>7</v>
       </c>
-      <c r="T36" t="n">
-        <v>15</v>
-      </c>
-      <c r="U36" t="n">
-        <v>3</v>
-      </c>
       <c r="V36" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37">
@@ -3437,78 +3437,78 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>G-Flop</t>
+          <t>Bend Rimmers</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Blue Cain</t>
+          <t>Malachi Moreno</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>0:17 - 2nd Half</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="I37" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="J37" t="n">
         <v>6</v>
       </c>
       <c r="K37" t="n">
+        <v>4</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1</v>
+      </c>
+      <c r="M37" t="n">
+        <v>2</v>
+      </c>
+      <c r="N37" t="n">
+        <v>4</v>
+      </c>
+      <c r="O37" t="n">
+        <v>4</v>
+      </c>
+      <c r="P37" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>3</v>
+      </c>
+      <c r="R37" t="n">
         <v>5</v>
       </c>
-      <c r="L37" t="n">
-        <v>2</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
-        <v>1</v>
-      </c>
-      <c r="O37" t="n">
-        <v>3</v>
-      </c>
-      <c r="P37" t="n">
-        <v>29</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>4</v>
-      </c>
-      <c r="R37" t="n">
-        <v>6</v>
-      </c>
       <c r="S37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -3519,17 +3519,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>G-Flop</t>
+          <t>Bend Rimmers</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Rueben Chinyelu</t>
+          <t>Xaivian Lee</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3544,53 +3544,53 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>7:30 - 2nd Half</t>
+          <t>0:17 - 2nd Half</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I38" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J38" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
         <v>1</v>
       </c>
       <c r="O38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P38" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="Q38" t="n">
         <v>4</v>
       </c>
       <c r="R38" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U38" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V38" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>G-Flop</t>
+          <t>Bend Rimmers</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3611,68 +3611,68 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Marcus Millender</t>
+          <t>Mike Nwoko</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>LSU</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>TA&amp;M@LSU</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>6:26 - 1st Half</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I39" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="J39" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K39" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>1</v>
       </c>
       <c r="P39" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="Q39" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R39" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="S39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V39" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
@@ -3688,22 +3688,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Kobe Knox</t>
+          <t>Josh Hubbard</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -3712,49 +3712,49 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="I40" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="J40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O40" t="n">
         <v>2</v>
       </c>
       <c r="P40" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>16</v>
+      </c>
+      <c r="R40" t="n">
         <v>27</v>
       </c>
-      <c r="Q40" t="n">
-        <v>4</v>
-      </c>
-      <c r="R40" t="n">
-        <v>9</v>
-      </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T40" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="U40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V40" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -3770,46 +3770,46 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Mouhamed Dioubate</t>
+          <t>Blue Cain</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>7:30 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="I41" t="n">
+        <v>15</v>
+      </c>
+      <c r="J41" t="n">
+        <v>6</v>
+      </c>
+      <c r="K41" t="n">
         <v>5</v>
       </c>
-      <c r="J41" t="n">
-        <v>3</v>
-      </c>
-      <c r="K41" t="n">
-        <v>1</v>
-      </c>
       <c r="L41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
         <v>1</v>
@@ -3818,22 +3818,22 @@
         <v>3</v>
       </c>
       <c r="P41" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="Q41" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U41" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V41" t="n">
         <v>4</v>
@@ -3847,7 +3847,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>The Oddities</t>
+          <t>G-Flop</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3857,68 +3857,68 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Tyler Tanner</t>
+          <t>Rueben Chinyelu</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>0:17 - 2nd Half</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="I42" t="n">
+        <v>13</v>
+      </c>
+      <c r="J42" t="n">
+        <v>8</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1</v>
+      </c>
+      <c r="N42" t="n">
+        <v>1</v>
+      </c>
+      <c r="O42" t="n">
+        <v>2</v>
+      </c>
+      <c r="P42" t="n">
         <v>25</v>
       </c>
-      <c r="J42" t="n">
-        <v>3</v>
-      </c>
-      <c r="K42" t="n">
-        <v>3</v>
-      </c>
-      <c r="L42" t="n">
-        <v>2</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" t="n">
-        <v>3</v>
-      </c>
-      <c r="O42" t="n">
-        <v>1</v>
-      </c>
-      <c r="P42" t="n">
-        <v>35</v>
-      </c>
       <c r="Q42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R42" t="n">
+        <v>8</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>5</v>
+      </c>
+      <c r="V42" t="n">
         <v>9</v>
-      </c>
-      <c r="S42" t="n">
-        <v>2</v>
-      </c>
-      <c r="T42" t="n">
-        <v>2</v>
-      </c>
-      <c r="U42" t="n">
-        <v>9</v>
-      </c>
-      <c r="V42" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="43">
@@ -3929,27 +3929,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>The Oddities</t>
+          <t>G-Flop</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Mike Sharavjamts</t>
+          <t>Marcus Millender</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3958,49 +3958,49 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I43" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="J43" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P43" t="n">
         <v>30</v>
       </c>
       <c r="Q43" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R43" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T43" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U43" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="V43" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>The Oddities</t>
+          <t>G-Flop</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4021,38 +4021,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Jalen Washington</t>
+          <t>Mouhamed Dioubate</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>0:17 - 2nd Half</t>
         </is>
       </c>
       <c r="H44" t="n">
         <v>10</v>
       </c>
       <c r="I44" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J44" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" t="n">
         <v>1</v>
@@ -4061,10 +4061,10 @@
         <v>1</v>
       </c>
       <c r="O44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P44" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="Q44" t="n">
         <v>3</v>
@@ -4073,16 +4073,16 @@
         <v>7</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V44" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45">
@@ -4093,7 +4093,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>The Oddities</t>
+          <t>G-Flop</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4103,38 +4103,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Shawn Jones Jr.</t>
+          <t>Rylan Griffen</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>MSST</t>
+          <t>TA&amp;M</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>TA&amp;M@LSU</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>6:26 - 1st Half</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J45" t="n">
         <v>2</v>
       </c>
       <c r="K45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -4143,28 +4143,28 @@
         <v>2</v>
       </c>
       <c r="O45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="Q45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46">
@@ -4175,7 +4175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Undrafted</t>
+          <t>G-Flop</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4185,17 +4185,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Kanon Catchings</t>
+          <t>Kobe Knox</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -4204,49 +4204,49 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="I46" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="J46" t="n">
         <v>6</v>
       </c>
       <c r="K46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P46" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="Q46" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R46" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="U46" t="n">
         <v>4</v>
       </c>
       <c r="V46" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47">
@@ -4257,22 +4257,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Undrafted</t>
+          <t>The Oddities</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Amari Evans</t>
+          <t>Tyler Tanner</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -4286,49 +4286,49 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I47" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P47" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="Q47" t="n">
+        <v>7</v>
+      </c>
+      <c r="R47" t="n">
         <v>9</v>
       </c>
-      <c r="R47" t="n">
-        <v>18</v>
-      </c>
       <c r="S47" t="n">
         <v>2</v>
       </c>
       <c r="T47" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="U47" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="V47" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="48">
@@ -4339,63 +4339,63 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Undrafted</t>
+          <t>The Oddities</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Shawn Phillips Jr.</t>
+          <t>Mike Sharavjamts</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="I48" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J48" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N48" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O48" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P48" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="Q48" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R48" t="n">
         <v>8</v>
@@ -4404,13 +4404,13 @@
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V48" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -4421,45 +4421,45 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Undrafted</t>
+          <t>The Oddities</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>AK Okereke</t>
+          <t>Rashaun Agee</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>TA&amp;M</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>TA&amp;M@LSU</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>6:26 - 1st Half</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>17</v>
+        <v>-1</v>
       </c>
       <c r="I49" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K49" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -4471,28 +4471,28 @@
         <v>1</v>
       </c>
       <c r="O49" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P49" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="Q49" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="S49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U49" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="V49" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Undrafted</t>
+          <t>The Oddities</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4513,68 +4513,68 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Malique Ewin</t>
+          <t>Jalen Washington</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ARK</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I50" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="J50" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P50" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="Q50" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R50" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="S50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V50" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -4585,7 +4585,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Undrafted</t>
+          <t>The Oddities</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4595,68 +4595,68 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Ja'Borri McGhee</t>
+          <t>Max Mackinnon</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>MSST</t>
+          <t>LSU</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>TA&amp;M@LSU</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>6:26 - 1st Half</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I51" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="J51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O51" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P51" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="Q51" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="R51" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="S51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Undrafted</t>
+          <t>The Oddities</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Jamarion Davis-Fleming</t>
+          <t>Shawn Jones Jr.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4696,37 +4696,37 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I52" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J52" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P52" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="Q52" t="n">
         <v>1</v>
       </c>
       <c r="R52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -4735,10 +4735,10 @@
         <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Undrafted</t>
+          <t>The Oddities</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4759,68 +4759,68 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Nordin Kapic</t>
+          <t>Rubén Dominguez</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>TA&amp;M</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>TA&amp;M@LSU</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>6:26 - 1st Half</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>13</v>
+        <v>-2</v>
       </c>
       <c r="I53" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P53" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="Q53" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="S53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -4841,68 +4841,68 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Trent Pierce</t>
+          <t>Kanon Catchings</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="I54" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="J54" t="n">
         <v>6</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>3</v>
       </c>
       <c r="P54" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="Q54" t="n">
+        <v>7</v>
+      </c>
+      <c r="R54" t="n">
+        <v>12</v>
+      </c>
+      <c r="S54" t="n">
         <v>5</v>
-      </c>
-      <c r="R54" t="n">
-        <v>11</v>
-      </c>
-      <c r="S54" t="n">
-        <v>3</v>
       </c>
       <c r="T54" t="n">
         <v>7</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V54" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
@@ -4923,68 +4923,68 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Andrija Jelavic</t>
+          <t>Amari Evans</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>7:30 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I55" t="n">
+        <v>24</v>
+      </c>
+      <c r="J55" t="n">
+        <v>6</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>3</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>1</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>9</v>
+      </c>
+      <c r="R55" t="n">
+        <v>18</v>
+      </c>
+      <c r="S55" t="n">
+        <v>2</v>
+      </c>
+      <c r="T55" t="n">
+        <v>6</v>
+      </c>
+      <c r="U55" t="n">
+        <v>4</v>
+      </c>
+      <c r="V55" t="n">
         <v>7</v>
-      </c>
-      <c r="J55" t="n">
-        <v>3</v>
-      </c>
-      <c r="K55" t="n">
-        <v>2</v>
-      </c>
-      <c r="L55" t="n">
-        <v>1</v>
-      </c>
-      <c r="M55" t="n">
-        <v>1</v>
-      </c>
-      <c r="N55" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" t="n">
-        <v>2</v>
-      </c>
-      <c r="P55" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>3</v>
-      </c>
-      <c r="R55" t="n">
-        <v>7</v>
-      </c>
-      <c r="S55" t="n">
-        <v>1</v>
-      </c>
-      <c r="T55" t="n">
-        <v>3</v>
-      </c>
-      <c r="U55" t="n">
-        <v>0</v>
-      </c>
-      <c r="V55" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -5005,56 +5005,56 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Brandon Garrison</t>
+          <t>Shawn Phillips Jr.</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>7:30 - 2nd Half</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="I56" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="J56" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N56" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P56" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="Q56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R56" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -5063,10 +5063,10 @@
         <v>0</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
@@ -5087,68 +5087,68 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>D.J. Wagner</t>
+          <t>AK Okereke</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ARK</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H57" t="n">
+        <v>17</v>
+      </c>
+      <c r="I57" t="n">
+        <v>17</v>
+      </c>
+      <c r="J57" t="n">
+        <v>4</v>
+      </c>
+      <c r="K57" t="n">
+        <v>3</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>1</v>
+      </c>
+      <c r="O57" t="n">
+        <v>5</v>
+      </c>
+      <c r="P57" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>5</v>
+      </c>
+      <c r="R57" t="n">
+        <v>8</v>
+      </c>
+      <c r="S57" t="n">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>6</v>
+      </c>
+      <c r="V57" t="n">
         <v>9</v>
-      </c>
-      <c r="I57" t="n">
-        <v>10</v>
-      </c>
-      <c r="J57" t="n">
-        <v>4</v>
-      </c>
-      <c r="K57" t="n">
-        <v>5</v>
-      </c>
-      <c r="L57" t="n">
-        <v>1</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" t="n">
-        <v>3</v>
-      </c>
-      <c r="O57" t="n">
-        <v>3</v>
-      </c>
-      <c r="P57" t="n">
-        <v>45</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>4</v>
-      </c>
-      <c r="R57" t="n">
-        <v>10</v>
-      </c>
-      <c r="S57" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" t="n">
-        <v>4</v>
-      </c>
-      <c r="U57" t="n">
-        <v>2</v>
-      </c>
-      <c r="V57" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="58">
@@ -5169,68 +5169,68 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Eduardo Klafke</t>
+          <t>Malique Ewin</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>ARK</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H58" t="n">
+        <v>17</v>
+      </c>
+      <c r="I58" t="n">
+        <v>17</v>
+      </c>
+      <c r="J58" t="n">
         <v>9</v>
       </c>
-      <c r="I58" t="n">
-        <v>5</v>
-      </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>1</v>
+      </c>
+      <c r="M58" t="n">
+        <v>2</v>
+      </c>
+      <c r="N58" t="n">
+        <v>3</v>
+      </c>
+      <c r="O58" t="n">
+        <v>3</v>
+      </c>
+      <c r="P58" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q58" t="n">
         <v>6</v>
       </c>
-      <c r="K58" t="n">
-        <v>1</v>
-      </c>
-      <c r="L58" t="n">
-        <v>2</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" t="n">
-        <v>1</v>
-      </c>
-      <c r="O58" t="n">
-        <v>2</v>
-      </c>
-      <c r="P58" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>1</v>
-      </c>
       <c r="R58" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="S58" t="n">
         <v>1</v>
       </c>
       <c r="T58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U58" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V58" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Achor Achor</t>
+          <t>Ja'Borri McGhee</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5270,49 +5270,49 @@
         </is>
       </c>
       <c r="H59" t="n">
+        <v>15</v>
+      </c>
+      <c r="I59" t="n">
+        <v>20</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>1</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>1</v>
+      </c>
+      <c r="O59" t="n">
+        <v>4</v>
+      </c>
+      <c r="P59" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q59" t="n">
         <v>8</v>
       </c>
-      <c r="I59" t="n">
-        <v>4</v>
-      </c>
-      <c r="J59" t="n">
-        <v>4</v>
-      </c>
-      <c r="K59" t="n">
-        <v>1</v>
-      </c>
-      <c r="L59" t="n">
-        <v>1</v>
-      </c>
-      <c r="M59" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" t="n">
-        <v>1</v>
-      </c>
-      <c r="O59" t="n">
-        <v>1</v>
-      </c>
-      <c r="P59" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>2</v>
-      </c>
       <c r="R59" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="S59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U59" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V59" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60">
@@ -5333,17 +5333,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Chandler Bing</t>
+          <t>Jamarion Davis-Fleming</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -5352,22 +5352,22 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I60" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J60" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N60" t="n">
         <v>0</v>
@@ -5376,25 +5376,25 @@
         <v>3</v>
       </c>
       <c r="P60" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q60" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R60" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="S60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -5415,68 +5415,68 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Isaiah Brown</t>
+          <t>Nordin Kapic</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>FLA</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>7:30 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I61" t="n">
+        <v>12</v>
+      </c>
+      <c r="J61" t="n">
+        <v>4</v>
+      </c>
+      <c r="K61" t="n">
+        <v>1</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>1</v>
+      </c>
+      <c r="N61" t="n">
+        <v>2</v>
+      </c>
+      <c r="O61" t="n">
+        <v>2</v>
+      </c>
+      <c r="P61" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>4</v>
+      </c>
+      <c r="R61" t="n">
         <v>7</v>
       </c>
-      <c r="J61" t="n">
-        <v>2</v>
-      </c>
-      <c r="K61" t="n">
-        <v>2</v>
-      </c>
-      <c r="L61" t="n">
-        <v>1</v>
-      </c>
-      <c r="M61" t="n">
-        <v>1</v>
-      </c>
-      <c r="N61" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" t="n">
-        <v>1</v>
-      </c>
-      <c r="P61" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>2</v>
-      </c>
-      <c r="R61" t="n">
-        <v>6</v>
-      </c>
       <c r="S61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U61" t="n">
         <v>2</v>
       </c>
       <c r="V61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -5497,68 +5497,68 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Justin Abson</t>
+          <t>Trent Pierce</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I62" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J62" t="n">
+        <v>6</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>1</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
+        <v>1</v>
+      </c>
+      <c r="O62" t="n">
+        <v>3</v>
+      </c>
+      <c r="P62" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q62" t="n">
         <v>5</v>
       </c>
-      <c r="K62" t="n">
-        <v>1</v>
-      </c>
-      <c r="L62" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T62" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -5579,68 +5579,68 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Travis Perry</t>
+          <t>Andrija Jelavic</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>0:17 - 2nd Half</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I63" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J63" t="n">
         <v>3</v>
       </c>
       <c r="K63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P63" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R63" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T63" t="n">
         <v>3</v>
       </c>
       <c r="U63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -5661,41 +5661,41 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>DeWayne Brown II</t>
+          <t>Jalen Reece</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>LSU</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>TA&amp;M@LSU</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>6:26 - 1st Half</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J64" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
         <v>1</v>
@@ -5704,25 +5704,25 @@
         <v>1</v>
       </c>
       <c r="P64" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -5743,32 +5743,32 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Kareem Stagg</t>
+          <t>Brandon Garrison</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>0:17 - 2nd Half</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I65" t="n">
         <v>6</v>
       </c>
       <c r="J65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -5780,25 +5780,25 @@
         <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P65" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="Q65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R65" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U65" t="n">
         <v>0</v>
@@ -5825,68 +5825,68 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Bishop Boswell</t>
+          <t>D.J. Wagner</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>ARK</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I66" t="n">
+        <v>10</v>
+      </c>
+      <c r="J66" t="n">
+        <v>4</v>
+      </c>
+      <c r="K66" t="n">
         <v>5</v>
       </c>
-      <c r="J66" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" t="n">
-        <v>4</v>
-      </c>
       <c r="L66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O66" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P66" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="Q66" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R66" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="S66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T66" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V66" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67">
@@ -5907,12 +5907,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Eli Ellis</t>
+          <t>Eduardo Klafke</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -5926,49 +5926,49 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J67" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K67" t="n">
+        <v>1</v>
+      </c>
+      <c r="L67" t="n">
+        <v>2</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="n">
+        <v>1</v>
+      </c>
+      <c r="O67" t="n">
+        <v>2</v>
+      </c>
+      <c r="P67" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>1</v>
+      </c>
+      <c r="R67" t="n">
         <v>5</v>
       </c>
-      <c r="L67" t="n">
-        <v>1</v>
-      </c>
-      <c r="M67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N67" t="n">
-        <v>1</v>
-      </c>
-      <c r="O67" t="n">
-        <v>2</v>
-      </c>
-      <c r="P67" t="n">
-        <v>28</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
-      <c r="R67" t="n">
-        <v>3</v>
-      </c>
       <c r="S67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T67" t="n">
         <v>2</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -5989,17 +5989,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Elijah Strong</t>
+          <t>Achor Achor</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -6008,43 +6008,43 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I68" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K68" t="n">
         <v>1</v>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P68" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Q68" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R68" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="S68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U68" t="n">
         <v>0</v>
@@ -6071,12 +6071,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Ethan Burg</t>
+          <t>Chandler Bing</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -6090,16 +6090,16 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I69" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
@@ -6111,28 +6111,28 @@
         <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P69" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="Q69" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R69" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U69" t="n">
         <v>0</v>
       </c>
       <c r="V69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -6153,68 +6153,68 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Jordan Ross</t>
+          <t>Isaiah Brown</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>0:17 - 2nd Half</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I70" t="n">
         <v>7</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N70" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P70" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="Q70" t="n">
         <v>2</v>
       </c>
       <c r="R70" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S70" t="n">
         <v>1</v>
       </c>
       <c r="T70" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U70" t="n">
         <v>2</v>
       </c>
       <c r="V70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
@@ -6235,12 +6235,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Sergej Macura</t>
+          <t>Justin Abson</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>MSST</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -6254,37 +6254,37 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J71" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
         <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="Q71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -6293,7 +6293,7 @@
         <v>0</v>
       </c>
       <c r="U71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V71" t="n">
         <v>2</v>
@@ -6317,62 +6317,62 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>T.O. Barrett</t>
+          <t>Travis Perry</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I72" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J72" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M72" t="n">
         <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P72" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="Q72" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
       </c>
       <c r="T72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U72" t="n">
         <v>2</v>
@@ -6399,17 +6399,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Dylan James</t>
+          <t>DeWayne Brown II</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -6418,37 +6418,37 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I73" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N73" t="n">
         <v>1</v>
       </c>
       <c r="O73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P73" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Q73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -6481,17 +6481,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Kezza Giffa</t>
+          <t>Kareem Stagg</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -6500,19 +6500,19 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I74" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
@@ -6521,28 +6521,28 @@
         <v>2</v>
       </c>
       <c r="O74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="Q74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R74" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T74" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -6563,38 +6563,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Troy Henderson</t>
+          <t>Pop Isaacs</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>TA&amp;M</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>TA&amp;M@LSU</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>6:26 - 1st Half</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K75" t="n">
         <v>1</v>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
@@ -6603,10 +6603,10 @@
         <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P75" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Q75" t="n">
         <v>1</v>
@@ -6615,7 +6615,7 @@
         <v>2</v>
       </c>
       <c r="S75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T75" t="n">
         <v>1</v>
@@ -6645,56 +6645,56 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Jasper Johnson</t>
+          <t>Bishop Boswell</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>7:30 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I76" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O76" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P76" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="Q76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R76" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="S76" t="n">
         <v>1</v>
@@ -6727,12 +6727,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Zach Day</t>
+          <t>Eli Ellis</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -6746,43 +6746,43 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K77" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P77" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
       </c>
       <c r="T77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U77" t="n">
         <v>0</v>
@@ -6809,17 +6809,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Amaree Abram</t>
+          <t>Elijah Strong</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -6828,49 +6828,49 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N78" t="n">
         <v>0</v>
       </c>
       <c r="O78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P78" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R78" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="S78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T78" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -6891,17 +6891,17 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Corey Chest</t>
+          <t>Ethan Burg</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -6910,16 +6910,16 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I79" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
@@ -6931,28 +6931,28 @@
         <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P79" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
       </c>
       <c r="T79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U79" t="n">
         <v>0</v>
       </c>
       <c r="V79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -6973,17 +6973,17 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>EJ Walker</t>
+          <t>Jordan Ross</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -6992,49 +6992,49 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
+        <v>3</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="n">
+        <v>3</v>
+      </c>
+      <c r="O80" t="n">
+        <v>2</v>
+      </c>
+      <c r="P80" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>2</v>
+      </c>
+      <c r="R80" t="n">
         <v>5</v>
       </c>
-      <c r="K80" t="n">
-        <v>1</v>
-      </c>
-      <c r="L80" t="n">
-        <v>0</v>
-      </c>
-      <c r="M80" t="n">
-        <v>0</v>
-      </c>
-      <c r="N80" t="n">
-        <v>3</v>
-      </c>
-      <c r="O80" t="n">
-        <v>2</v>
-      </c>
-      <c r="P80" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
-      <c r="R80" t="n">
-        <v>2</v>
-      </c>
       <c r="S80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -7055,32 +7055,32 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Grant Polk</t>
+          <t>Robert Miller III</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>LSU</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>TA&amp;M@LSU</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>6:26 - 1st Half</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
@@ -7089,28 +7089,28 @@
         <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q81" t="n">
         <v>1</v>
       </c>
       <c r="R81" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T81" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U81" t="n">
         <v>0</v>
@@ -7137,12 +7137,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Jake Wilkins</t>
+          <t>Sergej Macura</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -7156,49 +7156,49 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J82" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M82" t="n">
         <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P82" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="Q82" t="n">
         <v>1</v>
       </c>
       <c r="R82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
       </c>
       <c r="T82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -7219,56 +7219,56 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Patton Pinkins</t>
+          <t>T.O. Barrett</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I83" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J83" t="n">
         <v>1</v>
       </c>
       <c r="K83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M83" t="n">
         <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P83" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Q83" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R83" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -7277,10 +7277,10 @@
         <v>2</v>
       </c>
       <c r="U83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -7301,32 +7301,32 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Urban Klavzar</t>
+          <t>Dylan James</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>FLA</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>7:30 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I84" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
@@ -7338,25 +7338,25 @@
         <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P84" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Q84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R84" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U84" t="n">
         <v>0</v>
@@ -7383,35 +7383,35 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Isaiah Sealy</t>
+          <t>Kezza Giffa</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>ARK</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I85" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
@@ -7420,31 +7420,31 @@
         <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O85" t="n">
         <v>1</v>
       </c>
       <c r="P85" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
       </c>
       <c r="T85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
@@ -7465,35 +7465,35 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Jayden Leverett</t>
+          <t>Rashad King</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>LSU</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>TA&amp;M@LSU</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>6:26 - 1st Half</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I86" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L86" t="n">
         <v>0</v>
@@ -7502,25 +7502,25 @@
         <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R86" t="n">
         <v>2</v>
       </c>
       <c r="S86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U86" t="n">
         <v>0</v>
@@ -7547,17 +7547,17 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Jordan Butler</t>
+          <t>Troy Henderson</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -7566,16 +7566,16 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I87" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
@@ -7590,19 +7590,19 @@
         <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U87" t="n">
         <v>0</v>
@@ -7629,38 +7629,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Justin Bailey</t>
+          <t>Jasper Johnson</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>0:17 - 2nd Half</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
         <v>0</v>
@@ -7672,19 +7672,19 @@
         <v>1</v>
       </c>
       <c r="P88" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U88" t="n">
         <v>0</v>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Trent Burns</t>
+          <t>Zach Day</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -7745,7 +7745,7 @@
         <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N89" t="n">
         <v>0</v>
@@ -7754,7 +7754,7 @@
         <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Q89" t="n">
         <v>0</v>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Tyler Harris</t>
+          <t>Amaree Abram</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -7812,19 +7812,19 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K90" t="n">
         <v>0</v>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M90" t="n">
         <v>0</v>
@@ -7836,13 +7836,13 @@
         <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -7851,10 +7851,10 @@
         <v>0</v>
       </c>
       <c r="U90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
@@ -7875,67 +7875,1543 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
+          <t>Corey Chest</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>MISS</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>SC@MISS</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="H91" t="n">
+        <v>1</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="n">
+        <v>1</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>0</v>
+      </c>
+      <c r="R91" t="n">
+        <v>0</v>
+      </c>
+      <c r="S91" t="n">
+        <v>0</v>
+      </c>
+      <c r="T91" t="n">
+        <v>0</v>
+      </c>
+      <c r="U91" t="n">
+        <v>0</v>
+      </c>
+      <c r="V91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>EJ Walker</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>SC@MISS</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>1</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="n">
+        <v>5</v>
+      </c>
+      <c r="K92" t="n">
+        <v>1</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" t="n">
+        <v>3</v>
+      </c>
+      <c r="O92" t="n">
+        <v>2</v>
+      </c>
+      <c r="P92" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>0</v>
+      </c>
+      <c r="R92" t="n">
+        <v>2</v>
+      </c>
+      <c r="S92" t="n">
+        <v>0</v>
+      </c>
+      <c r="T92" t="n">
+        <v>2</v>
+      </c>
+      <c r="U92" t="n">
+        <v>0</v>
+      </c>
+      <c r="V92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Grant Polk</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>SC@MISS</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
+        <v>1</v>
+      </c>
+      <c r="I93" t="n">
+        <v>3</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" t="n">
+        <v>1</v>
+      </c>
+      <c r="P93" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>1</v>
+      </c>
+      <c r="R93" t="n">
+        <v>3</v>
+      </c>
+      <c r="S93" t="n">
+        <v>1</v>
+      </c>
+      <c r="T93" t="n">
+        <v>3</v>
+      </c>
+      <c r="U93" t="n">
+        <v>0</v>
+      </c>
+      <c r="V93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Jake Wilkins</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>UGA</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>UGA@MSST</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
+        <v>1</v>
+      </c>
+      <c r="I94" t="n">
+        <v>2</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0</v>
+      </c>
+      <c r="P94" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>1</v>
+      </c>
+      <c r="R94" t="n">
+        <v>2</v>
+      </c>
+      <c r="S94" t="n">
+        <v>0</v>
+      </c>
+      <c r="T94" t="n">
+        <v>1</v>
+      </c>
+      <c r="U94" t="n">
+        <v>0</v>
+      </c>
+      <c r="V94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Patton Pinkins</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>MISS</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>SC@MISS</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="H95" t="n">
+        <v>1</v>
+      </c>
+      <c r="I95" t="n">
+        <v>4</v>
+      </c>
+      <c r="J95" t="n">
+        <v>1</v>
+      </c>
+      <c r="K95" t="n">
+        <v>1</v>
+      </c>
+      <c r="L95" t="n">
+        <v>2</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" t="n">
+        <v>1</v>
+      </c>
+      <c r="O95" t="n">
+        <v>1</v>
+      </c>
+      <c r="P95" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>2</v>
+      </c>
+      <c r="R95" t="n">
+        <v>8</v>
+      </c>
+      <c r="S95" t="n">
+        <v>0</v>
+      </c>
+      <c r="T95" t="n">
+        <v>2</v>
+      </c>
+      <c r="U95" t="n">
+        <v>0</v>
+      </c>
+      <c r="V95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Urban Klavzar</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>FLA</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>FLA@UK</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>0:17 - 2nd Half</t>
+        </is>
+      </c>
+      <c r="H96" t="n">
+        <v>1</v>
+      </c>
+      <c r="I96" t="n">
+        <v>3</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" t="n">
+        <v>2</v>
+      </c>
+      <c r="P96" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>1</v>
+      </c>
+      <c r="R96" t="n">
+        <v>3</v>
+      </c>
+      <c r="S96" t="n">
+        <v>1</v>
+      </c>
+      <c r="T96" t="n">
+        <v>2</v>
+      </c>
+      <c r="U96" t="n">
+        <v>0</v>
+      </c>
+      <c r="V96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Ali Dibba</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>TA&amp;M</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>TA&amp;M@LSU</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>6:26 - 1st Half</t>
+        </is>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" t="n">
+        <v>2</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0</v>
+      </c>
+      <c r="P97" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>0</v>
+      </c>
+      <c r="R97" t="n">
+        <v>2</v>
+      </c>
+      <c r="S97" t="n">
+        <v>0</v>
+      </c>
+      <c r="T97" t="n">
+        <v>0</v>
+      </c>
+      <c r="U97" t="n">
+        <v>0</v>
+      </c>
+      <c r="V97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Federiko Federiko</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>TA&amp;M</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>TA&amp;M@LSU</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>6:26 - 1st Half</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>0</v>
+      </c>
+      <c r="R98" t="n">
+        <v>0</v>
+      </c>
+      <c r="S98" t="n">
+        <v>0</v>
+      </c>
+      <c r="T98" t="n">
+        <v>0</v>
+      </c>
+      <c r="U98" t="n">
+        <v>0</v>
+      </c>
+      <c r="V98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Isaiah Sealy</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>ARK</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>ARK@MIZ</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Final/OT</t>
+        </is>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" t="n">
+        <v>1</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" t="n">
+        <v>1</v>
+      </c>
+      <c r="O99" t="n">
+        <v>1</v>
+      </c>
+      <c r="P99" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>0</v>
+      </c>
+      <c r="R99" t="n">
+        <v>0</v>
+      </c>
+      <c r="S99" t="n">
+        <v>0</v>
+      </c>
+      <c r="T99" t="n">
+        <v>0</v>
+      </c>
+      <c r="U99" t="n">
+        <v>0</v>
+      </c>
+      <c r="V99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Jayden Leverett</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>VAN</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>VAN@TENN</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="n">
+        <v>2</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" t="n">
+        <v>2</v>
+      </c>
+      <c r="P100" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" t="n">
+        <v>2</v>
+      </c>
+      <c r="S100" t="n">
+        <v>0</v>
+      </c>
+      <c r="T100" t="n">
+        <v>0</v>
+      </c>
+      <c r="U100" t="n">
+        <v>0</v>
+      </c>
+      <c r="V100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Jordan Butler</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>SC@MISS</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>0</v>
+      </c>
+      <c r="R101" t="n">
+        <v>0</v>
+      </c>
+      <c r="S101" t="n">
+        <v>0</v>
+      </c>
+      <c r="T101" t="n">
+        <v>0</v>
+      </c>
+      <c r="U101" t="n">
+        <v>0</v>
+      </c>
+      <c r="V101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Josh Holloway</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>TA&amp;M</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>TA&amp;M@LSU</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>6:26 - 1st Half</t>
+        </is>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="n">
+        <v>3</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>1</v>
+      </c>
+      <c r="R102" t="n">
+        <v>4</v>
+      </c>
+      <c r="S102" t="n">
+        <v>1</v>
+      </c>
+      <c r="T102" t="n">
+        <v>3</v>
+      </c>
+      <c r="U102" t="n">
+        <v>0</v>
+      </c>
+      <c r="V102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Justin Bailey</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>UGA</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>UGA@MSST</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" t="n">
+        <v>1</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" t="n">
+        <v>1</v>
+      </c>
+      <c r="O103" t="n">
+        <v>1</v>
+      </c>
+      <c r="P103" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>0</v>
+      </c>
+      <c r="R103" t="n">
+        <v>0</v>
+      </c>
+      <c r="S103" t="n">
+        <v>0</v>
+      </c>
+      <c r="T103" t="n">
+        <v>0</v>
+      </c>
+      <c r="U103" t="n">
+        <v>0</v>
+      </c>
+      <c r="V103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Trent Burns</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>MIZ</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>ARK@MIZ</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Final/OT</t>
+        </is>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>0</v>
+      </c>
+      <c r="R104" t="n">
+        <v>0</v>
+      </c>
+      <c r="S104" t="n">
+        <v>0</v>
+      </c>
+      <c r="T104" t="n">
+        <v>0</v>
+      </c>
+      <c r="U104" t="n">
+        <v>0</v>
+      </c>
+      <c r="V104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Tyler Harris</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>VAN</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>VAN@TENN</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>0</v>
+      </c>
+      <c r="R105" t="n">
+        <v>0</v>
+      </c>
+      <c r="S105" t="n">
+        <v>0</v>
+      </c>
+      <c r="T105" t="n">
+        <v>0</v>
+      </c>
+      <c r="U105" t="n">
+        <v>0</v>
+      </c>
+      <c r="V105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Zach Clemence</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>TA&amp;M</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>TA&amp;M@LSU</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>6:26 - 1st Half</t>
+        </is>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" t="n">
+        <v>2</v>
+      </c>
+      <c r="J106" t="n">
+        <v>2</v>
+      </c>
+      <c r="K106" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
+      <c r="P106" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>1</v>
+      </c>
+      <c r="R106" t="n">
+        <v>5</v>
+      </c>
+      <c r="S106" t="n">
+        <v>0</v>
+      </c>
+      <c r="T106" t="n">
+        <v>2</v>
+      </c>
+      <c r="U106" t="n">
+        <v>0</v>
+      </c>
+      <c r="V106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Jacari Lane</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>TA&amp;M</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>TA&amp;M@LSU</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>6:26 - 1st Half</t>
+        </is>
+      </c>
+      <c r="H107" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
+      <c r="P107" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>0</v>
+      </c>
+      <c r="R107" t="n">
+        <v>1</v>
+      </c>
+      <c r="S107" t="n">
+        <v>0</v>
+      </c>
+      <c r="T107" t="n">
+        <v>0</v>
+      </c>
+      <c r="U107" t="n">
+        <v>0</v>
+      </c>
+      <c r="V107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
           <t>Max Smith</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="E108" t="inlineStr">
         <is>
           <t>MISS</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="F108" t="inlineStr">
         <is>
           <t>SC@MISS</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="G108" t="inlineStr">
         <is>
           <t>Final</t>
         </is>
       </c>
-      <c r="H91" t="n">
+      <c r="H108" t="n">
         <v>-1</v>
       </c>
-      <c r="I91" t="n">
-        <v>0</v>
-      </c>
-      <c r="J91" t="n">
-        <v>0</v>
-      </c>
-      <c r="K91" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" t="n">
-        <v>0</v>
-      </c>
-      <c r="M91" t="n">
-        <v>0</v>
-      </c>
-      <c r="N91" t="n">
-        <v>0</v>
-      </c>
-      <c r="O91" t="n">
-        <v>0</v>
-      </c>
-      <c r="P91" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
-      <c r="R91" t="n">
-        <v>1</v>
-      </c>
-      <c r="S91" t="n">
-        <v>0</v>
-      </c>
-      <c r="T91" t="n">
-        <v>1</v>
-      </c>
-      <c r="U91" t="n">
-        <v>0</v>
-      </c>
-      <c r="V91" t="n">
+      <c r="I108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0</v>
+      </c>
+      <c r="N108" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0</v>
+      </c>
+      <c r="P108" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>0</v>
+      </c>
+      <c r="R108" t="n">
+        <v>1</v>
+      </c>
+      <c r="S108" t="n">
+        <v>0</v>
+      </c>
+      <c r="T108" t="n">
+        <v>1</v>
+      </c>
+      <c r="U108" t="n">
+        <v>0</v>
+      </c>
+      <c r="V108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>PJ Carter</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>LSU</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>TA&amp;M@LSU</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>6:26 - 1st Half</t>
+        </is>
+      </c>
+      <c r="H109" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" t="n">
+        <v>0</v>
+      </c>
+      <c r="N109" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0</v>
+      </c>
+      <c r="P109" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>0</v>
+      </c>
+      <c r="R109" t="n">
+        <v>2</v>
+      </c>
+      <c r="S109" t="n">
+        <v>0</v>
+      </c>
+      <c r="T109" t="n">
+        <v>2</v>
+      </c>
+      <c r="U109" t="n">
+        <v>0</v>
+      </c>
+      <c r="V109" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7982,7 +9458,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C2" t="n">
         <v>3</v>
@@ -7991,63 +9467,63 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>The Backslashers</t>
+          <t>Three Dawg Nite</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bend Rimmers</t>
+          <t>The Backslashers</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Three Dawg Nite</t>
+          <t>Bend Rimmers</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>The Oddities</t>
+          <t>Hilton Heads</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Hilton Heads</t>
+          <t>The Oddities</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C7" t="n">
         <v>3</v>
@@ -8060,10 +9536,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Today_PoohPoints_SEC_ByOwner_2026-03-07.xlsx
+++ b/docs/Today_PoohPoints_SEC_ByOwner_2026-03-07.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V109"/>
+  <dimension ref="A1:V111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -429,7 +429,7 @@
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
     <col width="6" customWidth="1" min="8" max="8"/>
     <col width="5" customWidth="1" min="9" max="9"/>
     <col width="5" customWidth="1" min="10" max="10"/>
@@ -674,7 +674,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>6:26 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>6:26 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0:17 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1740,11 +1740,11 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0:17 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I16" t="n">
         <v>15</v>
@@ -1774,13 +1774,13 @@
         <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U16" t="n">
         <v>6</v>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0:17 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0:17 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0:17 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0:17 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -2642,14 +2642,14 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>6:26 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I27" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J27" t="n">
         <v>2</v>
@@ -2670,19 +2670,19 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="Q27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0:17 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0:17 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -3487,7 +3487,7 @@
         <v>4</v>
       </c>
       <c r="O37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P37" t="n">
         <v>27</v>
@@ -3544,17 +3544,17 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0:17 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I38" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J38" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K38" t="n">
         <v>5</v>
@@ -3587,10 +3587,10 @@
         <v>3</v>
       </c>
       <c r="U38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
@@ -3626,53 +3626,53 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>6:26 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I39" t="n">
+        <v>9</v>
+      </c>
+      <c r="J39" t="n">
         <v>6</v>
       </c>
-      <c r="J39" t="n">
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" t="n">
+        <v>2</v>
+      </c>
+      <c r="P39" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2</v>
+      </c>
+      <c r="R39" t="n">
+        <v>4</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
         <v>5</v>
       </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>1</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="n">
-        <v>1</v>
-      </c>
-      <c r="P39" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>1</v>
-      </c>
-      <c r="R39" t="n">
-        <v>3</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>4</v>
-      </c>
       <c r="V39" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0:17 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -3900,7 +3900,7 @@
         <v>2</v>
       </c>
       <c r="P42" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q42" t="n">
         <v>4</v>
@@ -4021,65 +4021,65 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Mouhamed Dioubate</t>
+          <t>Rylan Griffen</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>TA&amp;M</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>TA&amp;M@LSU</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0:17 - 2nd Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I44" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J44" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K44" t="n">
         <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P44" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Q44" t="n">
         <v>3</v>
       </c>
       <c r="R44" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="S44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V44" t="n">
         <v>6</v>
@@ -4103,68 +4103,68 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Rylan Griffen</t>
+          <t>Mouhamed Dioubate</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>TA&amp;M</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>TA&amp;M@LSU</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>6:26 - 1st Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I45" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J45" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K45" t="n">
         <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P45" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="Q45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R45" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="S45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V45" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46">
@@ -4446,17 +4446,17 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>6:26 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J49" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -4465,7 +4465,7 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N49" t="n">
         <v>1</v>
@@ -4474,13 +4474,13 @@
         <v>1</v>
       </c>
       <c r="P49" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R49" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -4489,10 +4489,10 @@
         <v>1</v>
       </c>
       <c r="U49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V49" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
@@ -4610,11 +4610,11 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>6:26 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I51" t="n">
         <v>6</v>
@@ -4623,7 +4623,7 @@
         <v>3</v>
       </c>
       <c r="K51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -4635,10 +4635,10 @@
         <v>2</v>
       </c>
       <c r="O51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P51" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q51" t="n">
         <v>3</v>
@@ -4774,7 +4774,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>6:26 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H53" t="n">
@@ -4802,7 +4802,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -5594,17 +5594,17 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>0:17 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I63" t="n">
         <v>7</v>
       </c>
       <c r="J63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K63" t="n">
         <v>2</v>
@@ -5622,7 +5622,7 @@
         <v>2</v>
       </c>
       <c r="P63" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q63" t="n">
         <v>3</v>
@@ -5676,11 +5676,11 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>6:26 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I64" t="n">
         <v>6</v>
@@ -5689,7 +5689,7 @@
         <v>1</v>
       </c>
       <c r="K64" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L64" t="n">
         <v>2</v>
@@ -5704,19 +5704,19 @@
         <v>1</v>
       </c>
       <c r="P64" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="Q64" t="n">
         <v>2</v>
       </c>
       <c r="R64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S64" t="n">
         <v>1</v>
       </c>
       <c r="T64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U64" t="n">
         <v>1</v>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>0:17 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H65" t="n">
@@ -5989,56 +5989,56 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Achor Achor</t>
+          <t>Robert Miller III</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>MSST</t>
+          <t>LSU</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>TA&amp;M@LSU</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I68" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J68" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N68" t="n">
         <v>1</v>
       </c>
       <c r="O68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P68" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="Q68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -6050,7 +6050,7 @@
         <v>0</v>
       </c>
       <c r="V68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -6071,17 +6071,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Chandler Bing</t>
+          <t>Achor Achor</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -6093,40 +6093,40 @@
         <v>8</v>
       </c>
       <c r="I69" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J69" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O69" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P69" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="Q69" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R69" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U69" t="n">
         <v>0</v>
@@ -6153,53 +6153,53 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Isaiah Brown</t>
+          <t>Chandler Bing</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>FLA</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>0:17 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H70" t="n">
         <v>8</v>
       </c>
       <c r="I70" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
         <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P70" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="Q70" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R70" t="n">
         <v>6</v>
@@ -6208,13 +6208,13 @@
         <v>1</v>
       </c>
       <c r="T70" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V70" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -6235,17 +6235,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Justin Abson</t>
+          <t>Isaiah Brown</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -6257,46 +6257,46 @@
         <v>8</v>
       </c>
       <c r="I71" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J71" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N71" t="n">
         <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P71" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T71" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U71" t="n">
         <v>2</v>
       </c>
       <c r="V71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
@@ -6317,17 +6317,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Travis Perry</t>
+          <t>Justin Abson</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -6336,43 +6336,43 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I72" t="n">
         <v>2</v>
       </c>
       <c r="J72" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K72" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
         <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Q72" t="n">
         <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
       </c>
       <c r="T72" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U72" t="n">
         <v>2</v>
@@ -6399,68 +6399,68 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>DeWayne Brown II</t>
+          <t>Pop Isaacs</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>TA&amp;M</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>TA&amp;M@LSU</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J73" t="n">
         <v>4</v>
       </c>
       <c r="K73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>1</v>
       </c>
       <c r="P73" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
       </c>
       <c r="T73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V73" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -6481,17 +6481,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Kareem Stagg</t>
+          <t>Travis Perry</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -6500,49 +6500,49 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I74" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J74" t="n">
         <v>3</v>
       </c>
       <c r="K74" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P74" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="Q74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T74" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -6563,62 +6563,62 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Pop Isaacs</t>
+          <t>DeWayne Brown II</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>TA&amp;M</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>TA&amp;M@LSU</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>6:26 - 1st Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H75" t="n">
         <v>5</v>
       </c>
       <c r="I75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O75" t="n">
         <v>1</v>
       </c>
       <c r="P75" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Q75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
       </c>
       <c r="T75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U75" t="n">
         <v>0</v>
@@ -6645,17 +6645,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Bishop Boswell</t>
+          <t>Kareem Stagg</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -6664,43 +6664,43 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I76" t="n">
+        <v>6</v>
+      </c>
+      <c r="J76" t="n">
+        <v>3</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
+        <v>1</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" t="n">
+        <v>2</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>2</v>
+      </c>
+      <c r="R76" t="n">
         <v>5</v>
       </c>
-      <c r="J76" t="n">
-        <v>0</v>
-      </c>
-      <c r="K76" t="n">
-        <v>4</v>
-      </c>
-      <c r="L76" t="n">
-        <v>2</v>
-      </c>
-      <c r="M76" t="n">
-        <v>0</v>
-      </c>
-      <c r="N76" t="n">
-        <v>2</v>
-      </c>
-      <c r="O76" t="n">
+      <c r="S76" t="n">
+        <v>2</v>
+      </c>
+      <c r="T76" t="n">
         <v>5</v>
-      </c>
-      <c r="P76" t="n">
-        <v>29</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>2</v>
-      </c>
-      <c r="R76" t="n">
-        <v>7</v>
-      </c>
-      <c r="S76" t="n">
-        <v>1</v>
-      </c>
-      <c r="T76" t="n">
-        <v>2</v>
       </c>
       <c r="U76" t="n">
         <v>0</v>
@@ -6727,62 +6727,62 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Eli Ellis</t>
+          <t>Ali Dibba</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>TA&amp;M</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>TA&amp;M@LSU</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H77" t="n">
         <v>4</v>
       </c>
       <c r="I77" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M77" t="n">
         <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R77" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
       </c>
       <c r="T77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U77" t="n">
         <v>0</v>
@@ -6809,17 +6809,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Elijah Strong</t>
+          <t>Bishop Boswell</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -6831,40 +6831,40 @@
         <v>4</v>
       </c>
       <c r="I78" t="n">
+        <v>5</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
+        <v>4</v>
+      </c>
+      <c r="L78" t="n">
+        <v>2</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" t="n">
+        <v>2</v>
+      </c>
+      <c r="O78" t="n">
+        <v>5</v>
+      </c>
+      <c r="P78" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>2</v>
+      </c>
+      <c r="R78" t="n">
         <v>7</v>
       </c>
-      <c r="J78" t="n">
-        <v>0</v>
-      </c>
-      <c r="K78" t="n">
-        <v>1</v>
-      </c>
-      <c r="L78" t="n">
-        <v>0</v>
-      </c>
-      <c r="M78" t="n">
-        <v>1</v>
-      </c>
-      <c r="N78" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" t="n">
-        <v>2</v>
-      </c>
-      <c r="P78" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>3</v>
-      </c>
-      <c r="R78" t="n">
-        <v>8</v>
-      </c>
       <c r="S78" t="n">
         <v>1</v>
       </c>
       <c r="T78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U78" t="n">
         <v>0</v>
@@ -6891,17 +6891,17 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Ethan Burg</t>
+          <t>Eli Ellis</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -6913,31 +6913,31 @@
         <v>4</v>
       </c>
       <c r="I79" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K79" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O79" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P79" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="Q79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
         <v>3</v>
@@ -6946,13 +6946,13 @@
         <v>0</v>
       </c>
       <c r="T79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U79" t="n">
         <v>0</v>
       </c>
       <c r="V79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -6973,17 +6973,17 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Jordan Ross</t>
+          <t>Elijah Strong</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -7001,40 +7001,40 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N80" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>2</v>
       </c>
       <c r="P80" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="Q80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R80" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S80" t="n">
         <v>1</v>
       </c>
       <c r="T80" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -7055,68 +7055,68 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Robert Miller III</t>
+          <t>Ethan Burg</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>LSU</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>TA&amp;M@LSU</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>6:26 - 1st Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H81" t="n">
         <v>4</v>
       </c>
       <c r="I81" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L81" t="n">
         <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P81" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="Q81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
       </c>
       <c r="T81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U81" t="n">
         <v>0</v>
       </c>
       <c r="V81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Sergej Macura</t>
+          <t>Jordan Ross</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>MSST</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -7159,43 +7159,43 @@
         <v>4</v>
       </c>
       <c r="I82" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J82" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
         <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P82" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="Q82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R82" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V82" t="n">
         <v>2</v>
@@ -7219,35 +7219,35 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>T.O. Barrett</t>
+          <t>Sergej Macura</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H83" t="n">
         <v>4</v>
       </c>
       <c r="I83" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J83" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K83" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L83" t="n">
         <v>1</v>
@@ -7259,25 +7259,25 @@
         <v>2</v>
       </c>
       <c r="O83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P83" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="Q83" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R83" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
       </c>
       <c r="T83" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V83" t="n">
         <v>2</v>
@@ -7301,68 +7301,68 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Dylan James</t>
+          <t>T.O. Barrett</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I84" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M84" t="n">
         <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P84" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="Q84" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R84" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
       </c>
       <c r="T84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -7383,17 +7383,17 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Kezza Giffa</t>
+          <t>Dylan James</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -7411,7 +7411,7 @@
         <v>2</v>
       </c>
       <c r="K85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
@@ -7420,16 +7420,16 @@
         <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="Q85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R85" t="n">
         <v>4</v>
@@ -7438,13 +7438,13 @@
         <v>0</v>
       </c>
       <c r="T85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -7465,32 +7465,32 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Rashad King</t>
+          <t>Kezza Giffa</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>LSU</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>TA&amp;M@LSU</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>6:26 - 1st Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H86" t="n">
         <v>3</v>
       </c>
       <c r="I86" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K86" t="n">
         <v>2</v>
@@ -7505,28 +7505,28 @@
         <v>2</v>
       </c>
       <c r="O86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P86" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="Q86" t="n">
         <v>1</v>
       </c>
       <c r="R86" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T86" t="n">
         <v>1</v>
       </c>
       <c r="U86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
@@ -7547,22 +7547,22 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Troy Henderson</t>
+          <t>Rashad King</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>LSU</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>TA&amp;M@LSU</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H87" t="n">
@@ -7572,10 +7572,10 @@
         <v>3</v>
       </c>
       <c r="J87" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K87" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
@@ -7584,25 +7584,25 @@
         <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="Q87" t="n">
         <v>1</v>
       </c>
       <c r="R87" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S87" t="n">
         <v>1</v>
       </c>
       <c r="T87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U87" t="n">
         <v>0</v>
@@ -7629,32 +7629,32 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Jasper Johnson</t>
+          <t>Troy Henderson</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>0:17 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I88" t="n">
         <v>3</v>
       </c>
       <c r="J88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K88" t="n">
         <v>1</v>
@@ -7666,25 +7666,25 @@
         <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Q88" t="n">
         <v>1</v>
       </c>
       <c r="R88" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S88" t="n">
         <v>1</v>
       </c>
       <c r="T88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U88" t="n">
         <v>0</v>
@@ -7711,17 +7711,17 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Zach Day</t>
+          <t>Jasper Johnson</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -7733,40 +7733,40 @@
         <v>2</v>
       </c>
       <c r="I89" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J89" t="n">
         <v>1</v>
       </c>
       <c r="K89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" t="n">
         <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P89" t="n">
         <v>10</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U89" t="n">
         <v>0</v>
@@ -7793,17 +7793,17 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Amaree Abram</t>
+          <t>Zach Day</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -7812,10 +7812,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J90" t="n">
         <v>1</v>
@@ -7824,10 +7824,10 @@
         <v>0</v>
       </c>
       <c r="L90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N90" t="n">
         <v>0</v>
@@ -7836,13 +7836,13 @@
         <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -7851,10 +7851,10 @@
         <v>0</v>
       </c>
       <c r="U90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V90" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -7875,17 +7875,17 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Corey Chest</t>
+          <t>Amaree Abram</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -7897,7 +7897,7 @@
         <v>1</v>
       </c>
       <c r="I91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J91" t="n">
         <v>1</v>
@@ -7906,7 +7906,7 @@
         <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M91" t="n">
         <v>0</v>
@@ -7918,13 +7918,13 @@
         <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -7933,10 +7933,10 @@
         <v>0</v>
       </c>
       <c r="U91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>EJ Walker</t>
+          <t>Corey Chest</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -7982,10 +7982,10 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L92" t="n">
         <v>0</v>
@@ -7994,25 +7994,25 @@
         <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
       </c>
       <c r="T92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U92" t="n">
         <v>0</v>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Grant Polk</t>
+          <t>EJ Walker</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -8061,13 +8061,13 @@
         <v>1</v>
       </c>
       <c r="I93" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" t="n">
         <v>0</v>
@@ -8076,25 +8076,25 @@
         <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P93" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="Q93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T93" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U93" t="n">
         <v>0</v>
@@ -8121,17 +8121,17 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Jake Wilkins</t>
+          <t>Grant Polk</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -8143,7 +8143,7 @@
         <v>1</v>
       </c>
       <c r="I94" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8161,22 +8161,22 @@
         <v>0</v>
       </c>
       <c r="O94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P94" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q94" t="n">
         <v>1</v>
       </c>
       <c r="R94" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T94" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U94" t="n">
         <v>0</v>
@@ -8203,17 +8203,17 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Patton Pinkins</t>
+          <t>Jake Wilkins</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -8225,40 +8225,40 @@
         <v>1</v>
       </c>
       <c r="I95" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
         <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P95" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="Q95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R95" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
       </c>
       <c r="T95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U95" t="n">
         <v>0</v>
@@ -8285,22 +8285,22 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Urban Klavzar</t>
+          <t>Josh Holloway</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>FLA</t>
+          <t>TA&amp;M</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>TA&amp;M@LSU</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>0:17 - 2nd Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H96" t="n">
@@ -8316,7 +8316,7 @@
         <v>0</v>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M96" t="n">
         <v>0</v>
@@ -8325,22 +8325,22 @@
         <v>0</v>
       </c>
       <c r="O96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P96" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Q96" t="n">
         <v>1</v>
       </c>
       <c r="R96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S96" t="n">
         <v>1</v>
       </c>
       <c r="T96" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U96" t="n">
         <v>0</v>
@@ -8367,35 +8367,35 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Ali Dibba</t>
+          <t>Patton Pinkins</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>TA&amp;M</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>TA&amp;M@LSU</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>6:26 - 1st Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I97" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L97" t="n">
         <v>2</v>
@@ -8404,25 +8404,25 @@
         <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P97" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R97" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
       </c>
       <c r="T97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U97" t="n">
         <v>0</v>
@@ -8449,29 +8449,29 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Federiko Federiko</t>
+          <t>Urban Klavzar</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>TA&amp;M</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>TA&amp;M@LSU</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>6:26 - 1st Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I98" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8489,22 +8489,22 @@
         <v>0</v>
       </c>
       <c r="O98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P98" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U98" t="n">
         <v>0</v>
@@ -8531,22 +8531,22 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Isaiah Sealy</t>
+          <t>Federiko Federiko</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>ARK</t>
+          <t>TA&amp;M</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>TA&amp;M@LSU</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H99" t="n">
@@ -8559,7 +8559,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L99" t="n">
         <v>0</v>
@@ -8568,13 +8568,13 @@
         <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
@@ -8613,22 +8613,22 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Jayden Leverett</t>
+          <t>Isaiah Sealy</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>ARK</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H100" t="n">
@@ -8638,10 +8638,10 @@
         <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L100" t="n">
         <v>0</v>
@@ -8650,19 +8650,19 @@
         <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P100" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -8695,17 +8695,17 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Jordan Butler</t>
+          <t>Jayden Leverett</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -8720,7 +8720,7 @@
         <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K101" t="n">
         <v>0</v>
@@ -8735,16 +8735,16 @@
         <v>0</v>
       </c>
       <c r="O101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P101" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q101" t="n">
         <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -8777,29 +8777,29 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Josh Holloway</t>
+          <t>Jordan Butler</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>TA&amp;M</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>TA&amp;M@LSU</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>6:26 - 1st Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H102" t="n">
         <v>0</v>
       </c>
       <c r="I102" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -8820,19 +8820,19 @@
         <v>0</v>
       </c>
       <c r="P102" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T102" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U102" t="n">
         <v>0</v>
@@ -9023,17 +9023,17 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Tyler Harris</t>
+          <t>Trent Noah</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -9105,32 +9105,32 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Zach Clemence</t>
+          <t>Tyler Harris</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>TA&amp;M</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>TA&amp;M@LSU</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>6:26 - 1st Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H106" t="n">
         <v>0</v>
       </c>
       <c r="I106" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J106" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K106" t="n">
         <v>0</v>
@@ -9148,19 +9148,19 @@
         <v>0</v>
       </c>
       <c r="P106" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Q106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
       </c>
       <c r="T106" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U106" t="n">
         <v>0</v>
@@ -9187,7 +9187,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Jacari Lane</t>
+          <t>Zach Clemence</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -9202,17 +9202,17 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>6:26 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H107" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I107" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J107" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K107" t="n">
         <v>0</v>
@@ -9230,19 +9230,19 @@
         <v>0</v>
       </c>
       <c r="P107" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R107" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
       </c>
       <c r="T107" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U107" t="n">
         <v>0</v>
@@ -9269,22 +9269,22 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Max Smith</t>
+          <t>Jacari Lane</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>TA&amp;M</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>TA&amp;M@LSU</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H108" t="n">
@@ -9312,7 +9312,7 @@
         <v>0</v>
       </c>
       <c r="P108" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q108" t="n">
         <v>0</v>
@@ -9324,7 +9324,7 @@
         <v>0</v>
       </c>
       <c r="T108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U108" t="n">
         <v>0</v>
@@ -9351,67 +9351,231 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
+          <t>Max Smith</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>MISS</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>SC@MISS</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Final</t>
+        </is>
+      </c>
+      <c r="H109" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" t="n">
+        <v>0</v>
+      </c>
+      <c r="N109" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0</v>
+      </c>
+      <c r="P109" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>0</v>
+      </c>
+      <c r="R109" t="n">
+        <v>1</v>
+      </c>
+      <c r="S109" t="n">
+        <v>0</v>
+      </c>
+      <c r="T109" t="n">
+        <v>1</v>
+      </c>
+      <c r="U109" t="n">
+        <v>0</v>
+      </c>
+      <c r="V109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Mazi Mosley</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>LSU</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>TA&amp;M@LSU</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Halftime</t>
+        </is>
+      </c>
+      <c r="H110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" t="n">
+        <v>0</v>
+      </c>
+      <c r="N110" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" t="n">
+        <v>0</v>
+      </c>
+      <c r="P110" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>0</v>
+      </c>
+      <c r="R110" t="n">
+        <v>1</v>
+      </c>
+      <c r="S110" t="n">
+        <v>0</v>
+      </c>
+      <c r="T110" t="n">
+        <v>1</v>
+      </c>
+      <c r="U110" t="n">
+        <v>0</v>
+      </c>
+      <c r="V110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
           <t>PJ Carter</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
+      <c r="E111" t="inlineStr">
         <is>
           <t>LSU</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
+      <c r="F111" t="inlineStr">
         <is>
           <t>TA&amp;M@LSU</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>6:26 - 1st Half</t>
-        </is>
-      </c>
-      <c r="H109" t="n">
-        <v>-2</v>
-      </c>
-      <c r="I109" t="n">
-        <v>0</v>
-      </c>
-      <c r="J109" t="n">
-        <v>0</v>
-      </c>
-      <c r="K109" t="n">
-        <v>0</v>
-      </c>
-      <c r="L109" t="n">
-        <v>0</v>
-      </c>
-      <c r="M109" t="n">
-        <v>0</v>
-      </c>
-      <c r="N109" t="n">
-        <v>0</v>
-      </c>
-      <c r="O109" t="n">
-        <v>0</v>
-      </c>
-      <c r="P109" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
-      <c r="R109" t="n">
-        <v>2</v>
-      </c>
-      <c r="S109" t="n">
-        <v>0</v>
-      </c>
-      <c r="T109" t="n">
-        <v>2</v>
-      </c>
-      <c r="U109" t="n">
-        <v>0</v>
-      </c>
-      <c r="V109" t="n">
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Halftime</t>
+        </is>
+      </c>
+      <c r="H111" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I111" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" t="n">
+        <v>0</v>
+      </c>
+      <c r="N111" t="n">
+        <v>0</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0</v>
+      </c>
+      <c r="P111" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>0</v>
+      </c>
+      <c r="R111" t="n">
+        <v>3</v>
+      </c>
+      <c r="S111" t="n">
+        <v>0</v>
+      </c>
+      <c r="T111" t="n">
+        <v>3</v>
+      </c>
+      <c r="U111" t="n">
+        <v>0</v>
+      </c>
+      <c r="V111" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9471,7 +9635,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C3" t="n">
         <v>5</v>
@@ -9506,11 +9670,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Hilton Heads</t>
+          <t>The Oddities</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C6" t="n">
         <v>3</v>
@@ -9519,7 +9683,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>The Oddities</t>
+          <t>Hilton Heads</t>
         </is>
       </c>
       <c r="B7" t="n">

--- a/docs/Today_PoohPoints_SEC_ByOwner_2026-03-07.xlsx
+++ b/docs/Today_PoohPoints_SEC_ByOwner_2026-03-07.xlsx
@@ -429,7 +429,7 @@
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="6" customWidth="1" min="8" max="8"/>
     <col width="5" customWidth="1" min="9" max="9"/>
     <col width="5" customWidth="1" min="10" max="10"/>
@@ -674,14 +674,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3:41 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -696,25 +696,25 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Q3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -756,7 +756,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2:02 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -1151,68 +1151,68 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Marcus Hill</t>
+          <t>Derrion Reid</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TA&amp;M</t>
+          <t>OU</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>TA&amp;M@LSU</t>
+          <t>OU@TEX</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Final/3OT</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H9" t="n">
         <v>5</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="V9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -1233,68 +1233,68 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Derrion Reid</t>
+          <t>Marcus Hill</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>OU</t>
+          <t>TA&amp;M</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>OU@TEX</t>
+          <t>TA&amp;M@LSU</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2:02 - 1st Half</t>
+          <t>Final/3OT</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2:02 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -1440,7 +1440,7 @@
         <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -1740,17 +1740,17 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>3:41 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1768,13 +1768,13 @@
         <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -2396,17 +2396,17 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2:02 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I24" t="n">
         <v>5</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -2642,14 +2642,14 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>3:41 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H27" t="n">
         <v>6</v>
       </c>
       <c r="I27" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
@@ -2670,25 +2670,25 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q27" t="n">
         <v>2</v>
       </c>
       <c r="R27" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>3:41 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -2752,7 +2752,7 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q28" t="n">
         <v>2</v>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>3:41 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2:02 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>3:41 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -3241,10 +3241,10 @@
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P34" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>3:41 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -4061,7 +4061,7 @@
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P44" t="n">
         <v>7</v>
@@ -4200,11 +4200,11 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2:02 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I46" t="n">
         <v>2</v>
@@ -4228,19 +4228,19 @@
         <v>2</v>
       </c>
       <c r="P46" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U46" t="n">
         <v>2</v>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>3:41 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H50" t="n">
@@ -4556,7 +4556,7 @@
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q50" t="n">
         <v>3</v>
@@ -4856,11 +4856,11 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2:02 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I54" t="n">
         <v>16</v>
@@ -4884,19 +4884,19 @@
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="Q54" t="n">
         <v>4</v>
       </c>
       <c r="R54" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="S54" t="n">
         <v>4</v>
       </c>
       <c r="T54" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U54" t="n">
         <v>4</v>
@@ -4938,11 +4938,11 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2:02 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I55" t="n">
         <v>12</v>
@@ -4966,13 +4966,13 @@
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Q55" t="n">
         <v>4</v>
       </c>
       <c r="R55" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S55" t="n">
         <v>1</v>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>3:41 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H56" t="n">
@@ -5048,7 +5048,7 @@
         <v>2</v>
       </c>
       <c r="P56" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q56" t="n">
         <v>1</v>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2:02 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H59" t="n">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2:02 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H61" t="n">
@@ -5840,17 +5840,17 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>3:41 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I66" t="n">
         <v>4</v>
       </c>
       <c r="J66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
@@ -5868,7 +5868,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q66" t="n">
         <v>2</v>
@@ -6168,17 +6168,17 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>3:41 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I70" t="n">
         <v>5</v>
       </c>
       <c r="J70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
@@ -6187,7 +6187,7 @@
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N70" t="n">
         <v>1</v>
@@ -6196,13 +6196,13 @@
         <v>1</v>
       </c>
       <c r="P70" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q70" t="n">
         <v>1</v>
       </c>
       <c r="R70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -6250,11 +6250,11 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>3:41 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I71" t="n">
         <v>7</v>
@@ -6263,10 +6263,10 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M71" t="n">
         <v>0</v>
@@ -6278,13 +6278,13 @@
         <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Q71" t="n">
         <v>3</v>
       </c>
       <c r="R71" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="S71" t="n">
         <v>1</v>
@@ -6399,68 +6399,68 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Tae Davis</t>
+          <t>Max Mackinnon</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>OU</t>
+          <t>LSU</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>OU@TEX</t>
+          <t>TA&amp;M@LSU</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2:02 - 1st Half</t>
+          <t>Final/3OT</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I73" t="n">
+        <v>20</v>
+      </c>
+      <c r="J73" t="n">
+        <v>4</v>
+      </c>
+      <c r="K73" t="n">
+        <v>3</v>
+      </c>
+      <c r="L73" t="n">
+        <v>2</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" t="n">
         <v>7</v>
       </c>
-      <c r="J73" t="n">
-        <v>5</v>
-      </c>
-      <c r="K73" t="n">
-        <v>1</v>
-      </c>
-      <c r="L73" t="n">
-        <v>1</v>
-      </c>
-      <c r="M73" t="n">
-        <v>0</v>
-      </c>
-      <c r="N73" t="n">
-        <v>2</v>
-      </c>
       <c r="O73" t="n">
         <v>2</v>
       </c>
       <c r="P73" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="Q73" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R73" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="S73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T73" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="U73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V73" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74">
@@ -6481,68 +6481,68 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Max Mackinnon</t>
+          <t>Shawn Jones Jr.</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>LSU</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>TA&amp;M@LSU</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Final/3OT</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H74" t="n">
         <v>7</v>
       </c>
       <c r="I74" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="J74" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K74" t="n">
         <v>3</v>
       </c>
       <c r="L74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O74" t="n">
         <v>2</v>
       </c>
       <c r="P74" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="Q74" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="R74" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="S74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T74" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="U74" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V74" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -6563,38 +6563,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Shawn Jones Jr.</t>
+          <t>Tae Davis</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>MSST</t>
+          <t>OU</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>OU@TEX</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H75" t="n">
         <v>7</v>
       </c>
       <c r="I75" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J75" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K75" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L75" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
@@ -6606,25 +6606,25 @@
         <v>2</v>
       </c>
       <c r="P75" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="Q75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R75" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
       </c>
       <c r="T75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U75" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V75" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76">
@@ -6645,32 +6645,32 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Rubén Dominguez</t>
+          <t>Elyjah Freeman</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>TA&amp;M</t>
+          <t>AUB</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>TA&amp;M@LSU</t>
+          <t>AUB@ALA</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Final/3OT</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
@@ -6679,34 +6679,34 @@
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P76" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="Q76" t="n">
         <v>1</v>
       </c>
       <c r="R76" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T76" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
@@ -6727,32 +6727,32 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Elyjah Freeman</t>
+          <t>Rubén Dominguez</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AUB</t>
+          <t>TA&amp;M</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>AUB@ALA</t>
+          <t>TA&amp;M@LSU</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>3:41 - 1st Half</t>
+          <t>Final/3OT</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I77" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
@@ -6761,28 +6761,28 @@
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>1</v>
       </c>
       <c r="P77" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R77" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T77" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U77" t="n">
         <v>0</v>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>3:41 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H99" t="n">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2:02 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H103" t="n">
@@ -8902,7 +8902,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q103" t="n">
         <v>1</v>
@@ -9105,68 +9105,68 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Bishop Boswell</t>
+          <t>Sebastian Williams-Adams</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>AUB</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>AUB@ALA</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H106" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I106" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J106" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K106" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L106" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
         <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P106" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="Q106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R106" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="S106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T106" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V106" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
@@ -9187,17 +9187,17 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Eli Ellis</t>
+          <t>Bishop Boswell</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -9209,37 +9209,37 @@
         <v>4</v>
       </c>
       <c r="I107" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J107" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K107" t="n">
+        <v>4</v>
+      </c>
+      <c r="L107" t="n">
+        <v>2</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" t="n">
+        <v>2</v>
+      </c>
+      <c r="O107" t="n">
         <v>5</v>
       </c>
-      <c r="L107" t="n">
-        <v>1</v>
-      </c>
-      <c r="M107" t="n">
-        <v>0</v>
-      </c>
-      <c r="N107" t="n">
-        <v>1</v>
-      </c>
-      <c r="O107" t="n">
-        <v>2</v>
-      </c>
       <c r="P107" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R107" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="S107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T107" t="n">
         <v>2</v>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Elijah Strong</t>
+          <t>Eli Ellis</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -9291,40 +9291,40 @@
         <v>4</v>
       </c>
       <c r="I108" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J108" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K108" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O108" t="n">
         <v>2</v>
       </c>
       <c r="P108" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="Q108" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="S108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U108" t="n">
         <v>0</v>
@@ -9351,17 +9351,17 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Ethan Burg</t>
+          <t>Elijah Strong</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -9373,46 +9373,46 @@
         <v>4</v>
       </c>
       <c r="I109" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
       </c>
       <c r="K109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L109" t="n">
         <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N109" t="n">
         <v>0</v>
       </c>
       <c r="O109" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P109" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q109" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R109" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="S109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U109" t="n">
         <v>0</v>
       </c>
       <c r="V109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -9433,22 +9433,22 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Filip Jovic</t>
+          <t>Ethan Burg</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AUB</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>AUB@ALA</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>3:41 - 1st Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H110" t="n">
@@ -9461,7 +9461,7 @@
         <v>0</v>
       </c>
       <c r="K110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L110" t="n">
         <v>0</v>
@@ -9473,28 +9473,28 @@
         <v>0</v>
       </c>
       <c r="O110" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P110" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="Q110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
       </c>
       <c r="T110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U110" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V110" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -9515,35 +9515,35 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Jordan Ross</t>
+          <t>Filip Jovic</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>AUB</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>AUB@ALA</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H111" t="n">
         <v>4</v>
       </c>
       <c r="I111" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L111" t="n">
         <v>0</v>
@@ -9552,25 +9552,25 @@
         <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P111" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="Q111" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R111" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U111" t="n">
         <v>2</v>
@@ -9597,12 +9597,12 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Sergej Macura</t>
+          <t>Jordan Ross</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>MSST</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -9619,43 +9619,43 @@
         <v>4</v>
       </c>
       <c r="I112" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J112" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K112" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
         <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P112" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="Q112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R112" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V112" t="n">
         <v>2</v>
@@ -9679,35 +9679,35 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>T.O. Barrett</t>
+          <t>Sergej Macura</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H113" t="n">
         <v>4</v>
       </c>
       <c r="I113" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J113" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K113" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L113" t="n">
         <v>1</v>
@@ -9719,25 +9719,25 @@
         <v>2</v>
       </c>
       <c r="O113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P113" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="Q113" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R113" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
       </c>
       <c r="T113" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V113" t="n">
         <v>2</v>
@@ -9761,68 +9761,68 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Dylan James</t>
+          <t>T.O. Barrett</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H114" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I114" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J114" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K114" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M114" t="n">
         <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O114" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P114" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="Q114" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R114" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
       </c>
       <c r="T114" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U114" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V114" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115">
@@ -9843,17 +9843,17 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Kezza Giffa</t>
+          <t>Dylan James</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -9871,7 +9871,7 @@
         <v>2</v>
       </c>
       <c r="K115" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L115" t="n">
         <v>0</v>
@@ -9880,16 +9880,16 @@
         <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P115" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="Q115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R115" t="n">
         <v>4</v>
@@ -9898,13 +9898,13 @@
         <v>0</v>
       </c>
       <c r="T115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U115" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V115" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -9925,35 +9925,35 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Sebastian Williams-Adams</t>
+          <t>Kezza Giffa</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AUB</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>AUB@ALA</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>3:41 - 1st Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H116" t="n">
         <v>3</v>
       </c>
       <c r="I116" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L116" t="n">
         <v>0</v>
@@ -9962,28 +9962,28 @@
         <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O116" t="n">
         <v>1</v>
       </c>
       <c r="P116" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="Q116" t="n">
         <v>1</v>
       </c>
       <c r="R116" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
       </c>
       <c r="T116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V116" t="n">
         <v>2</v>
@@ -10171,22 +10171,22 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Zach Day</t>
+          <t>Nic Codie</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>OU@TEX</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H119" t="n">
@@ -10196,7 +10196,7 @@
         <v>0</v>
       </c>
       <c r="J119" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K119" t="n">
         <v>0</v>
@@ -10205,22 +10205,22 @@
         <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
         <v>0</v>
       </c>
       <c r="O119" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P119" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q119" t="n">
         <v>0</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -10253,17 +10253,17 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Amaree Abram</t>
+          <t>Zach Day</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -10272,10 +10272,10 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J120" t="n">
         <v>1</v>
@@ -10284,10 +10284,10 @@
         <v>0</v>
       </c>
       <c r="L120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N120" t="n">
         <v>0</v>
@@ -10296,13 +10296,13 @@
         <v>0</v>
       </c>
       <c r="P120" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Q120" t="n">
         <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -10311,10 +10311,10 @@
         <v>0</v>
       </c>
       <c r="U120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V120" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -10335,17 +10335,17 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Corey Chest</t>
+          <t>Amaree Abram</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -10357,7 +10357,7 @@
         <v>1</v>
       </c>
       <c r="I121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J121" t="n">
         <v>1</v>
@@ -10366,7 +10366,7 @@
         <v>0</v>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M121" t="n">
         <v>0</v>
@@ -10378,13 +10378,13 @@
         <v>0</v>
       </c>
       <c r="P121" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q121" t="n">
         <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -10393,10 +10393,10 @@
         <v>0</v>
       </c>
       <c r="U121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V121" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="122">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>EJ Walker</t>
+          <t>Corey Chest</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -10442,10 +10442,10 @@
         <v>0</v>
       </c>
       <c r="J122" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L122" t="n">
         <v>0</v>
@@ -10454,25 +10454,25 @@
         <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P122" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="Q122" t="n">
         <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
       </c>
       <c r="T122" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U122" t="n">
         <v>0</v>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Grant Polk</t>
+          <t>EJ Walker</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -10521,13 +10521,13 @@
         <v>1</v>
       </c>
       <c r="I123" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J123" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L123" t="n">
         <v>0</v>
@@ -10536,25 +10536,25 @@
         <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P123" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="Q123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T123" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U123" t="n">
         <v>0</v>
@@ -10581,17 +10581,17 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Jake Wilkins</t>
+          <t>Grant Polk</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -10603,7 +10603,7 @@
         <v>1</v>
       </c>
       <c r="I124" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10621,22 +10621,22 @@
         <v>0</v>
       </c>
       <c r="O124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P124" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q124" t="n">
         <v>1</v>
       </c>
       <c r="R124" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T124" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U124" t="n">
         <v>0</v>
@@ -10663,62 +10663,62 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Josh Holloway</t>
+          <t>Jake Wilkins</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>TA&amp;M</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>TA&amp;M@LSU</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Final/3OT</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H125" t="n">
         <v>1</v>
       </c>
       <c r="I125" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
       </c>
       <c r="K125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
         <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P125" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="Q125" t="n">
         <v>1</v>
       </c>
       <c r="R125" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T125" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U125" t="n">
         <v>0</v>
@@ -10745,62 +10745,62 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Nic Codie</t>
+          <t>Josh Holloway</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>TA&amp;M</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>OU@TEX</t>
+          <t>TA&amp;M@LSU</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2:02 - 1st Half</t>
+          <t>Final/3OT</t>
         </is>
       </c>
       <c r="H126" t="n">
         <v>1</v>
       </c>
       <c r="I126" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J126" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M126" t="n">
         <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O126" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P126" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Q126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R126" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T126" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U126" t="n">
         <v>0</v>
@@ -10991,22 +10991,22 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Camden Heide</t>
+          <t>Isaiah Sealy</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>ARK</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>OU@TEX</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2:02 - 1st Half</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H129" t="n">
@@ -11016,10 +11016,10 @@
         <v>0</v>
       </c>
       <c r="J129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L129" t="n">
         <v>0</v>
@@ -11028,25 +11028,25 @@
         <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O129" t="n">
         <v>1</v>
       </c>
       <c r="P129" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="Q129" t="n">
         <v>0</v>
       </c>
       <c r="R129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
       </c>
       <c r="T129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U129" t="n">
         <v>0</v>
@@ -11073,22 +11073,22 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Isaiah Sealy</t>
+          <t>Jayden Leverett</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>ARK</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H130" t="n">
@@ -11098,10 +11098,10 @@
         <v>0</v>
       </c>
       <c r="J130" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L130" t="n">
         <v>0</v>
@@ -11110,19 +11110,19 @@
         <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P130" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q130" t="n">
         <v>0</v>
       </c>
       <c r="R130" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -11155,17 +11155,17 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Jayden Leverett</t>
+          <t>Jordan Butler</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -11180,7 +11180,7 @@
         <v>0</v>
       </c>
       <c r="J131" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K131" t="n">
         <v>0</v>
@@ -11195,16 +11195,16 @@
         <v>0</v>
       </c>
       <c r="O131" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P131" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q131" t="n">
         <v>0</v>
       </c>
       <c r="R131" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -11237,17 +11237,17 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Jordan Butler</t>
+          <t>Justin Bailey</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -11268,19 +11268,19 @@
         <v>0</v>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M132" t="n">
         <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P132" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q132" t="n">
         <v>0</v>
@@ -11319,22 +11319,22 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Justin Bailey</t>
+          <t>Kai Rogers</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>OU</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>OU@TEX</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H133" t="n">
@@ -11344,31 +11344,31 @@
         <v>0</v>
       </c>
       <c r="J133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K133" t="n">
         <v>0</v>
       </c>
       <c r="L133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
         <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P133" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q133" t="n">
         <v>0</v>
       </c>
       <c r="R133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -11662,7 +11662,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>3:41 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H137" t="n">
@@ -11729,22 +11729,22 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Federiko Federiko</t>
+          <t>Camden Heide</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>TA&amp;M</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>TA&amp;M@LSU</t>
+          <t>OU@TEX</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Final/3OT</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H138" t="n">
@@ -11754,7 +11754,7 @@
         <v>0</v>
       </c>
       <c r="J138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K138" t="n">
         <v>0</v>
@@ -11766,13 +11766,13 @@
         <v>0</v>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P138" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="Q138" t="n">
         <v>0</v>
@@ -11784,7 +11784,7 @@
         <v>0</v>
       </c>
       <c r="T138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U138" t="n">
         <v>0</v>
@@ -11811,7 +11811,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Jacari Lane</t>
+          <t>Federiko Federiko</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -11851,10 +11851,10 @@
         <v>0</v>
       </c>
       <c r="O139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P139" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q139" t="n">
         <v>0</v>
@@ -11893,22 +11893,22 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Kai Rogers</t>
+          <t>Jacari Lane</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>OU</t>
+          <t>TA&amp;M</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>OU@TEX</t>
+          <t>TA&amp;M@LSU</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2:02 - 1st Half</t>
+          <t>Final/3OT</t>
         </is>
       </c>
       <c r="H140" t="n">
@@ -11933,10 +11933,10 @@
         <v>0</v>
       </c>
       <c r="O140" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P140" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q140" t="n">
         <v>0</v>
@@ -12139,22 +12139,22 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Noah Williamson</t>
+          <t>Simeon Wilcher</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>AUB@ALA</t>
+          <t>OU@TEX</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>3:41 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H143" t="n">
@@ -12179,7 +12179,7 @@
         <v>0</v>
       </c>
       <c r="O143" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P143" t="n">
         <v>4</v>
@@ -12221,26 +12221,26 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Simeon Wilcher</t>
+          <t>Noah Williamson</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>ALA</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>OU@TEX</t>
+          <t>AUB@ALA</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2:02 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H144" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="I144" t="n">
         <v>0</v>
@@ -12258,10 +12258,10 @@
         <v>0</v>
       </c>
       <c r="N144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O144" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P144" t="n">
         <v>4</v>
@@ -12318,7 +12318,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2:02 - 1st Half</t>
+          <t>Halftime</t>
         </is>
       </c>
       <c r="H145" t="n">
@@ -12346,7 +12346,7 @@
         <v>0</v>
       </c>
       <c r="P145" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q145" t="n">
         <v>0</v>
@@ -12518,7 +12518,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C4" t="n">
         <v>5</v>
@@ -12531,7 +12531,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C5" t="n">
         <v>5</v>
@@ -12557,7 +12557,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C7" t="n">
         <v>4</v>

--- a/docs/Today_PoohPoints_SEC_ByOwner_2026-03-07.xlsx
+++ b/docs/Today_PoohPoints_SEC_ByOwner_2026-03-07.xlsx
@@ -429,7 +429,7 @@
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
     <col width="6" customWidth="1" min="8" max="8"/>
     <col width="5" customWidth="1" min="9" max="9"/>
     <col width="5" customWidth="1" min="10" max="10"/>
@@ -741,32 +741,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Matas Vokietaitis</t>
+          <t>Pablo Tamba</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>LSU</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>OU@TEX</t>
+          <t>TA&amp;M@LSU</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>Final/3OT</t>
         </is>
       </c>
       <c r="H4" t="n">
         <v>13</v>
       </c>
       <c r="I4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
@@ -775,22 +775,22 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4" t="n">
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P4" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -799,10 +799,10 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -823,32 +823,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Pablo Tamba</t>
+          <t>Matas Vokietaitis</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LSU</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>TA&amp;M@LSU</t>
+          <t>OU@TEX</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Final/3OT</t>
+          <t>17:41 - 2nd Half</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J5" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
@@ -857,22 +857,22 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="Q5" t="n">
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -881,10 +881,10 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -1166,11 +1166,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>17:41 - 2nd Half</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I9" t="n">
         <v>4</v>
@@ -1179,7 +1179,7 @@
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1194,7 +1194,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>17:41 - 2nd Half</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -1422,7 +1422,7 @@
         <v>2</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1440,19 +1440,19 @@
         <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U12" t="n">
         <v>2</v>
@@ -2299,32 +2299,32 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Micah Handlogten</t>
+          <t>Nijel Pack</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FLA</t>
+          <t>OU</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>OU@TEX</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>17:41 - 2nd Half</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2333,34 +2333,34 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R23" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -2381,33 +2381,33 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Nijel Pack</t>
+          <t>Micah Handlogten</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>OU</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>OU@TEX</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
         <v>5</v>
       </c>
-      <c r="J24" t="n">
-        <v>2</v>
-      </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
@@ -2415,34 +2415,34 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P24" t="n">
         <v>14</v>
       </c>
       <c r="Q24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>17:41 - 2nd Half</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>17:41 - 2nd Half</t>
         </is>
       </c>
       <c r="H46" t="n">
@@ -4677,68 +4677,68 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Malachi Moreno</t>
+          <t>Xzayvier Brown</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>OU</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>OU@TEX</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>17:41 - 2nd Half</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I52" t="n">
+        <v>16</v>
+      </c>
+      <c r="J52" t="n">
+        <v>2</v>
+      </c>
+      <c r="K52" t="n">
+        <v>1</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q52" t="n">
         <v>6</v>
       </c>
-      <c r="J52" t="n">
-        <v>6</v>
-      </c>
-      <c r="K52" t="n">
-        <v>4</v>
-      </c>
-      <c r="L52" t="n">
-        <v>1</v>
-      </c>
-      <c r="M52" t="n">
-        <v>2</v>
-      </c>
-      <c r="N52" t="n">
-        <v>4</v>
-      </c>
-      <c r="O52" t="n">
-        <v>5</v>
-      </c>
-      <c r="P52" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>3</v>
-      </c>
       <c r="R52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -4759,12 +4759,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Xaivian Lee</t>
+          <t>Malachi Moreno</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>FLA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -4781,46 +4781,46 @@
         <v>13</v>
       </c>
       <c r="I53" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J53" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K53" t="n">
+        <v>4</v>
+      </c>
+      <c r="L53" t="n">
+        <v>1</v>
+      </c>
+      <c r="M53" t="n">
+        <v>2</v>
+      </c>
+      <c r="N53" t="n">
+        <v>4</v>
+      </c>
+      <c r="O53" t="n">
         <v>5</v>
       </c>
-      <c r="L53" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="n">
-        <v>1</v>
-      </c>
-      <c r="O53" t="n">
-        <v>1</v>
-      </c>
       <c r="P53" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="Q53" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R53" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="S53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -4841,65 +4841,65 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Jordan Pope</t>
+          <t>Xaivian Lee</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>OU@TEX</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I54" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J54" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P54" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="Q54" t="n">
         <v>4</v>
       </c>
       <c r="R54" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="S54" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T54" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="U54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V54" t="n">
         <v>4</v>
@@ -4923,12 +4923,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Xzayvier Brown</t>
+          <t>Jordan Pope</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>OU</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -4938,23 +4938,23 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>17:41 - 2nd Half</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I55" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="J55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
@@ -4966,25 +4966,25 @@
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="Q55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R55" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="S55" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T55" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="U55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>17:41 - 2nd Half</t>
         </is>
       </c>
       <c r="H59" t="n">
@@ -5294,7 +5294,7 @@
         <v>2</v>
       </c>
       <c r="P59" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Q59" t="n">
         <v>2</v>
@@ -5430,11 +5430,11 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>17:41 - 2nd Half</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I61" t="n">
         <v>2</v>
@@ -5446,7 +5446,7 @@
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61" t="n">
         <v>0</v>
@@ -5458,7 +5458,7 @@
         <v>2</v>
       </c>
       <c r="P61" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>17:41 - 2nd Half</t>
         </is>
       </c>
       <c r="H75" t="n">
@@ -6588,10 +6588,10 @@
         <v>7</v>
       </c>
       <c r="J75" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L75" t="n">
         <v>1</v>
@@ -6606,7 +6606,7 @@
         <v>2</v>
       </c>
       <c r="P75" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Q75" t="n">
         <v>2</v>
@@ -6624,7 +6624,7 @@
         <v>3</v>
       </c>
       <c r="V75" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>17:41 - 2nd Half</t>
         </is>
       </c>
       <c r="H103" t="n">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>17:41 - 2nd Half</t>
         </is>
       </c>
       <c r="H119" t="n">
@@ -11334,7 +11334,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>17:41 - 2nd Half</t>
         </is>
       </c>
       <c r="H133" t="n">
@@ -11744,7 +11744,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>17:41 - 2nd Half</t>
         </is>
       </c>
       <c r="H138" t="n">
@@ -11769,10 +11769,10 @@
         <v>1</v>
       </c>
       <c r="O138" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P138" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q138" t="n">
         <v>0</v>
@@ -12154,7 +12154,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>17:41 - 2nd Half</t>
         </is>
       </c>
       <c r="H143" t="n">
@@ -12318,7 +12318,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>17:41 - 2nd Half</t>
         </is>
       </c>
       <c r="H145" t="n">
@@ -12492,7 +12492,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C2" t="n">
         <v>5</v>
@@ -12557,7 +12557,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C7" t="n">
         <v>4</v>

--- a/docs/Today_PoohPoints_SEC_ByOwner_2026-03-07.xlsx
+++ b/docs/Today_PoohPoints_SEC_ByOwner_2026-03-07.xlsx
@@ -674,20 +674,20 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>11:35 - 2nd Half</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
         <v>1</v>
@@ -699,28 +699,28 @@
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="Q3" t="n">
         <v>7</v>
       </c>
       <c r="R3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -741,32 +741,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Pablo Tamba</t>
+          <t>Matas Vokietaitis</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LSU</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>TA&amp;M@LSU</t>
+          <t>OU@TEX</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Final/3OT</t>
+          <t>9:14 - 2nd Half</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
@@ -778,16 +778,16 @@
         <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R4" t="n">
         <v>5</v>
@@ -799,10 +799,10 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -823,32 +823,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Matas Vokietaitis</t>
+          <t>Pablo Tamba</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>LSU</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>OU@TEX</t>
+          <t>TA&amp;M@LSU</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>17:41 - 2nd Half</t>
+          <t>Final/3OT</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
@@ -857,22 +857,22 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P5" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="Q5" t="n">
         <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -881,10 +881,10 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -1166,11 +1166,11 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>17:41 - 2nd Half</t>
+          <t>9:14 - 2nd Half</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I9" t="n">
         <v>4</v>
@@ -1188,13 +1188,13 @@
         <v>1</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
       </c>
       <c r="P9" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1412,14 +1412,14 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>17:41 - 2nd Half</t>
+          <t>9:14 - 2nd Half</t>
         </is>
       </c>
       <c r="H12" t="n">
         <v>-1</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
         <v>2</v>
@@ -1440,19 +1440,19 @@
         <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U12" t="n">
         <v>2</v>
@@ -1740,11 +1740,11 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>11:35 - 2nd Half</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I16" t="n">
         <v>6</v>
@@ -1768,13 +1768,13 @@
         <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q16" t="n">
         <v>3</v>
       </c>
       <c r="R16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -2314,17 +2314,17 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>17:41 - 2nd Half</t>
+          <t>9:14 - 2nd Half</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I23" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2342,25 +2342,25 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Q23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R23" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -2545,68 +2545,68 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Tyler Nickel</t>
+          <t>Aden Holloway</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>ALA</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>AUB@ALA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>11:35 - 2nd Half</t>
         </is>
       </c>
       <c r="H26" t="n">
+        <v>12</v>
+      </c>
+      <c r="I26" t="n">
+        <v>16</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1</v>
+      </c>
+      <c r="O26" t="n">
+        <v>2</v>
+      </c>
+      <c r="P26" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>4</v>
+      </c>
+      <c r="R26" t="n">
         <v>9</v>
       </c>
-      <c r="I26" t="n">
-        <v>7</v>
-      </c>
-      <c r="J26" t="n">
+      <c r="S26" t="n">
+        <v>2</v>
+      </c>
+      <c r="T26" t="n">
         <v>5</v>
       </c>
-      <c r="K26" t="n">
-        <v>1</v>
-      </c>
-      <c r="L26" t="n">
-        <v>2</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>5</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>29</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2</v>
-      </c>
-      <c r="R26" t="n">
-        <v>3</v>
-      </c>
-      <c r="S26" t="n">
-        <v>1</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2</v>
-      </c>
       <c r="U26" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V26" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
@@ -2627,68 +2627,68 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Aden Holloway</t>
+          <t>Tyler Nickel</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AUB@ALA</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I27" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="Q27" t="n">
         <v>2</v>
       </c>
       <c r="R27" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>11:35 - 2nd Half</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J28" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -2746,31 +2746,31 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="Q28" t="n">
         <v>2</v>
       </c>
       <c r="R28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>11:35 - 2nd Half</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -3134,17 +3134,17 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>17:41 - 2nd Half</t>
+          <t>9:14 - 2nd Half</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I33" t="n">
         <v>4</v>
       </c>
       <c r="J33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K33" t="n">
         <v>1</v>
@@ -3159,22 +3159,22 @@
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P33" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Q33" t="n">
         <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U33" t="n">
         <v>2</v>
@@ -3216,7 +3216,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>11:35 - 2nd Half</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -3226,7 +3226,7 @@
         <v>1</v>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -3244,19 +3244,19 @@
         <v>1</v>
       </c>
       <c r="P34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U34" t="n">
         <v>1</v>
@@ -3939,68 +3939,68 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Jaylen Carey</t>
+          <t>Jadon Jones</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>OU</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>OU@TEX</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>9:14 - 2nd Half</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O43" t="n">
         <v>3</v>
       </c>
       <c r="P43" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -4021,32 +4021,32 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Houston Mallette</t>
+          <t>Jaylen Carey</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>AUB@ALA</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -4061,10 +4061,10 @@
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P44" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -4103,35 +4103,35 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Nick Pringle</t>
+          <t>Houston Mallette</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>ARK</t>
+          <t>ALA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>AUB@ALA</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>11:35 - 2nd Half</t>
         </is>
       </c>
       <c r="H45" t="n">
         <v>4</v>
       </c>
       <c r="I45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -4143,22 +4143,22 @@
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P45" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="Q45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
@@ -4185,32 +4185,32 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Jadon Jones</t>
+          <t>Nick Pringle</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>OU</t>
+          <t>ARK</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>OU@TEX</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>17:41 - 2nd Half</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -4219,34 +4219,34 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P46" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -4528,41 +4528,41 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>11:35 - 2nd Half</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I50" t="n">
+        <v>8</v>
+      </c>
+      <c r="J50" t="n">
+        <v>4</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1</v>
+      </c>
+      <c r="L50" t="n">
+        <v>1</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
+        <v>1</v>
+      </c>
+      <c r="P50" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>4</v>
+      </c>
+      <c r="R50" t="n">
         <v>6</v>
-      </c>
-      <c r="J50" t="n">
-        <v>3</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" t="n">
-        <v>1</v>
-      </c>
-      <c r="M50" t="n">
-        <v>1</v>
-      </c>
-      <c r="N50" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>3</v>
-      </c>
-      <c r="R50" t="n">
-        <v>5</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -4692,7 +4692,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>17:41 - 2nd Half</t>
+          <t>9:14 - 2nd Half</t>
         </is>
       </c>
       <c r="H52" t="n">
@@ -4705,10 +4705,10 @@
         <v>2</v>
       </c>
       <c r="K52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
@@ -4720,13 +4720,13 @@
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="Q52" t="n">
         <v>6</v>
       </c>
       <c r="R52" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="S52" t="n">
         <v>1</v>
@@ -4759,68 +4759,68 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Malachi Moreno</t>
+          <t>Jordan Pope</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>OU@TEX</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>9:14 - 2nd Half</t>
         </is>
       </c>
       <c r="H53" t="n">
         <v>13</v>
       </c>
       <c r="I53" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="J53" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K53" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L53" t="n">
         <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O53" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
         <v>27</v>
       </c>
       <c r="Q53" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R53" t="n">
+        <v>15</v>
+      </c>
+      <c r="S53" t="n">
         <v>5</v>
       </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Xaivian Lee</t>
+          <t>Malachi Moreno</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>FLA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -4863,46 +4863,46 @@
         <v>13</v>
       </c>
       <c r="I54" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J54" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K54" t="n">
+        <v>4</v>
+      </c>
+      <c r="L54" t="n">
+        <v>1</v>
+      </c>
+      <c r="M54" t="n">
+        <v>2</v>
+      </c>
+      <c r="N54" t="n">
+        <v>4</v>
+      </c>
+      <c r="O54" t="n">
         <v>5</v>
       </c>
-      <c r="L54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" t="n">
-        <v>1</v>
-      </c>
-      <c r="O54" t="n">
-        <v>1</v>
-      </c>
       <c r="P54" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="Q54" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R54" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="S54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -4923,65 +4923,65 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Jordan Pope</t>
+          <t>Xaivian Lee</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>OU@TEX</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>17:41 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I55" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="J55" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P55" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="Q55" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R55" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T55" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="U55" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V55" t="n">
         <v>4</v>
@@ -5020,14 +5020,14 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>11:35 - 2nd Half</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I56" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J56" t="n">
         <v>4</v>
@@ -5045,28 +5045,28 @@
         <v>2</v>
       </c>
       <c r="O56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P56" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="Q56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R56" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -5266,20 +5266,20 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>17:41 - 2nd Half</t>
+          <t>9:14 - 2nd Half</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I59" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J59" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K59" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L59" t="n">
         <v>2</v>
@@ -5294,13 +5294,13 @@
         <v>2</v>
       </c>
       <c r="P59" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="Q59" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R59" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S59" t="n">
         <v>1</v>
@@ -5309,10 +5309,10 @@
         <v>2</v>
       </c>
       <c r="U59" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V59" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="60">
@@ -5430,14 +5430,14 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>17:41 - 2nd Half</t>
+          <t>9:14 - 2nd Half</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I61" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J61" t="n">
         <v>1</v>
@@ -5458,13 +5458,13 @@
         <v>2</v>
       </c>
       <c r="P61" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -5743,29 +5743,29 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Kobe Knox</t>
+          <t>Latrell Wrightsell</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ALA</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>AUB@ALA</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>11:35 - 2nd Half</t>
         </is>
       </c>
       <c r="H65" t="n">
+        <v>10</v>
+      </c>
+      <c r="I65" t="n">
         <v>6</v>
-      </c>
-      <c r="I65" t="n">
-        <v>12</v>
       </c>
       <c r="J65" t="n">
         <v>6</v>
@@ -5780,31 +5780,31 @@
         <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P65" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="Q65" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R65" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U65" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V65" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -5825,32 +5825,32 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Latrell Wrightsell</t>
+          <t>Kobe Knox</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>AUB@ALA</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H66" t="n">
         <v>6</v>
       </c>
       <c r="I66" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J66" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
@@ -5862,19 +5862,19 @@
         <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P66" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="Q66" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R66" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -5883,10 +5883,10 @@
         <v>2</v>
       </c>
       <c r="U66" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V66" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="67">
@@ -6168,53 +6168,53 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>11:35 - 2nd Half</t>
         </is>
       </c>
       <c r="H70" t="n">
+        <v>8</v>
+      </c>
+      <c r="I70" t="n">
+        <v>9</v>
+      </c>
+      <c r="J70" t="n">
+        <v>4</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>2</v>
+      </c>
+      <c r="N70" t="n">
+        <v>1</v>
+      </c>
+      <c r="O70" t="n">
+        <v>1</v>
+      </c>
+      <c r="P70" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>3</v>
+      </c>
+      <c r="R70" t="n">
         <v>5</v>
       </c>
-      <c r="I70" t="n">
-        <v>5</v>
-      </c>
-      <c r="J70" t="n">
-        <v>3</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" t="n">
-        <v>0</v>
-      </c>
-      <c r="M70" t="n">
-        <v>1</v>
-      </c>
-      <c r="N70" t="n">
-        <v>1</v>
-      </c>
-      <c r="O70" t="n">
-        <v>1</v>
-      </c>
-      <c r="P70" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>1</v>
-      </c>
-      <c r="R70" t="n">
-        <v>2</v>
-      </c>
       <c r="S70" t="n">
         <v>0</v>
       </c>
       <c r="T70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U70" t="n">
         <v>3</v>
       </c>
       <c r="V70" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71">
@@ -6250,47 +6250,47 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>11:35 - 2nd Half</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I71" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M71" t="n">
         <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P71" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="Q71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R71" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="S71" t="n">
         <v>1</v>
       </c>
       <c r="T71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U71" t="n">
         <v>0</v>
@@ -6399,68 +6399,68 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Max Mackinnon</t>
+          <t>Tae Davis</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>LSU</t>
+          <t>OU</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>TA&amp;M@LSU</t>
+          <t>OU@TEX</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Final/3OT</t>
+          <t>9:14 - 2nd Half</t>
         </is>
       </c>
       <c r="H73" t="n">
+        <v>9</v>
+      </c>
+      <c r="I73" t="n">
+        <v>10</v>
+      </c>
+      <c r="J73" t="n">
         <v>7</v>
       </c>
-      <c r="I73" t="n">
-        <v>20</v>
-      </c>
-      <c r="J73" t="n">
-        <v>4</v>
-      </c>
       <c r="K73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M73" t="n">
         <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O73" t="n">
         <v>2</v>
       </c>
       <c r="P73" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="Q73" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="R73" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="S73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T73" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="U73" t="n">
         <v>4</v>
       </c>
       <c r="V73" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="74">
@@ -6481,68 +6481,68 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Shawn Jones Jr.</t>
+          <t>Max Mackinnon</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>MSST</t>
+          <t>LSU</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>TA&amp;M@LSU</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/3OT</t>
         </is>
       </c>
       <c r="H74" t="n">
         <v>7</v>
       </c>
       <c r="I74" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="J74" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K74" t="n">
         <v>3</v>
       </c>
       <c r="L74" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O74" t="n">
         <v>2</v>
       </c>
       <c r="P74" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="Q74" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R74" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="S74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T74" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="U74" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V74" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75">
@@ -6563,38 +6563,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Tae Davis</t>
+          <t>Shawn Jones Jr.</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>OU</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>OU@TEX</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>17:41 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H75" t="n">
         <v>7</v>
       </c>
       <c r="I75" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J75" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L75" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
@@ -6606,25 +6606,25 @@
         <v>2</v>
       </c>
       <c r="P75" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="Q75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R75" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
       </c>
       <c r="T75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U75" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V75" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -6660,14 +6660,14 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>11:35 - 2nd Half</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I76" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J76" t="n">
         <v>1</v>
@@ -6688,19 +6688,19 @@
         <v>2</v>
       </c>
       <c r="P76" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="Q76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R76" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="S76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U76" t="n">
         <v>2</v>
@@ -7957,38 +7957,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Brandon Garrison</t>
+          <t>London Jemison</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>ALA</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>AUB@ALA</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>11:35 - 2nd Half</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I92" t="n">
         <v>6</v>
       </c>
       <c r="J92" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M92" t="n">
         <v>0</v>
@@ -7997,10 +7997,10 @@
         <v>1</v>
       </c>
       <c r="O92" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P92" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q92" t="n">
         <v>3</v>
@@ -8039,68 +8039,68 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>D.J. Wagner</t>
+          <t>Brandon Garrison</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>ARK</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H93" t="n">
         <v>9</v>
       </c>
       <c r="I93" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J93" t="n">
         <v>4</v>
       </c>
       <c r="K93" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" t="n">
+        <v>1</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" t="n">
+        <v>1</v>
+      </c>
+      <c r="O93" t="n">
         <v>5</v>
       </c>
-      <c r="L93" t="n">
-        <v>1</v>
-      </c>
-      <c r="M93" t="n">
-        <v>0</v>
-      </c>
-      <c r="N93" t="n">
-        <v>3</v>
-      </c>
-      <c r="O93" t="n">
-        <v>3</v>
-      </c>
       <c r="P93" t="n">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="Q93" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R93" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
       </c>
       <c r="T93" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V93" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -8121,68 +8121,68 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Eduardo Klafke</t>
+          <t>D.J. Wagner</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>ARK</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H94" t="n">
         <v>9</v>
       </c>
       <c r="I94" t="n">
+        <v>10</v>
+      </c>
+      <c r="J94" t="n">
+        <v>4</v>
+      </c>
+      <c r="K94" t="n">
         <v>5</v>
       </c>
-      <c r="J94" t="n">
-        <v>6</v>
-      </c>
-      <c r="K94" t="n">
-        <v>1</v>
-      </c>
       <c r="L94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M94" t="n">
         <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O94" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P94" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="Q94" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R94" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="S94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T94" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U94" t="n">
         <v>2</v>
       </c>
       <c r="V94" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="95">
@@ -8203,17 +8203,17 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Achor Achor</t>
+          <t>Eduardo Klafke</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>MSST</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -8222,19 +8222,19 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I95" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J95" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K95" t="n">
         <v>1</v>
       </c>
       <c r="L95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M95" t="n">
         <v>0</v>
@@ -8243,28 +8243,28 @@
         <v>1</v>
       </c>
       <c r="O95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P95" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="Q95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R95" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
@@ -8285,17 +8285,17 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Chandler Bing</t>
+          <t>Achor Achor</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -8307,40 +8307,40 @@
         <v>8</v>
       </c>
       <c r="I96" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J96" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M96" t="n">
         <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O96" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P96" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="Q96" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R96" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U96" t="n">
         <v>0</v>
@@ -8367,17 +8367,17 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Isaiah Brown</t>
+          <t>Chandler Bing</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>FLA</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -8389,31 +8389,31 @@
         <v>8</v>
       </c>
       <c r="I97" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
         <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P97" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="Q97" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R97" t="n">
         <v>6</v>
@@ -8422,13 +8422,13 @@
         <v>1</v>
       </c>
       <c r="T97" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V97" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -8449,17 +8449,17 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Justin Abson</t>
+          <t>Isaiah Brown</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -8471,46 +8471,46 @@
         <v>8</v>
       </c>
       <c r="I98" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J98" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N98" t="n">
         <v>0</v>
       </c>
       <c r="O98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P98" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T98" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U98" t="n">
         <v>2</v>
       </c>
       <c r="V98" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="99">
@@ -8531,38 +8531,38 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>London Jemison</t>
+          <t>Justin Abson</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>AUB@ALA</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H99" t="n">
         <v>8</v>
       </c>
       <c r="I99" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J99" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K99" t="n">
         <v>1</v>
       </c>
       <c r="L99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
         <v>0</v>
@@ -8574,13 +8574,13 @@
         <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Q99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -8589,10 +8589,10 @@
         <v>0</v>
       </c>
       <c r="U99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100">
@@ -8777,65 +8777,65 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Travis Perry</t>
+          <t>Sebastian Williams-Adams</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>AUB</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>AUB@ALA</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>11:35 - 2nd Half</t>
         </is>
       </c>
       <c r="H102" t="n">
         <v>6</v>
       </c>
       <c r="I102" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J102" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K102" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L102" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
         <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>1</v>
       </c>
       <c r="P102" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R102" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
       </c>
       <c r="T102" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V102" t="n">
         <v>2</v>
@@ -8859,26 +8859,26 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Chendall Weaver</t>
+          <t>Travis Perry</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>OU@TEX</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>17:41 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H103" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I103" t="n">
         <v>2</v>
@@ -8887,40 +8887,40 @@
         <v>3</v>
       </c>
       <c r="K103" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M103" t="n">
         <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O103" t="n">
         <v>1</v>
       </c>
       <c r="P103" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
       </c>
       <c r="T103" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U103" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V103" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -8941,56 +8941,56 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>DeWayne Brown II</t>
+          <t>Chendall Weaver</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>OU@TEX</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>9:14 - 2nd Half</t>
         </is>
       </c>
       <c r="H104" t="n">
         <v>5</v>
       </c>
       <c r="I104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J104" t="n">
         <v>4</v>
       </c>
       <c r="K104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L104" t="n">
         <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
         <v>1</v>
       </c>
       <c r="O104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P104" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -9023,17 +9023,17 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Kareem Stagg</t>
+          <t>DeWayne Brown II</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -9045,40 +9045,40 @@
         <v>5</v>
       </c>
       <c r="I105" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K105" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P105" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="Q105" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S105" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T105" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U105" t="n">
         <v>0</v>
@@ -9105,7 +9105,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Sebastian Williams-Adams</t>
+          <t>Filip Jovic</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -9120,17 +9120,17 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>11:35 - 2nd Half</t>
         </is>
       </c>
       <c r="H106" t="n">
         <v>5</v>
       </c>
       <c r="I106" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K106" t="n">
         <v>1</v>
@@ -9148,13 +9148,13 @@
         <v>1</v>
       </c>
       <c r="P106" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q106" t="n">
         <v>1</v>
       </c>
       <c r="R106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -9163,7 +9163,7 @@
         <v>0</v>
       </c>
       <c r="U106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V106" t="n">
         <v>2</v>
@@ -9187,17 +9187,17 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Bishop Boswell</t>
+          <t>Kareem Stagg</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -9206,43 +9206,43 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I107" t="n">
+        <v>6</v>
+      </c>
+      <c r="J107" t="n">
+        <v>3</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" t="n">
+        <v>1</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" t="n">
+        <v>2</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
+      <c r="P107" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>2</v>
+      </c>
+      <c r="R107" t="n">
         <v>5</v>
       </c>
-      <c r="J107" t="n">
-        <v>0</v>
-      </c>
-      <c r="K107" t="n">
-        <v>4</v>
-      </c>
-      <c r="L107" t="n">
-        <v>2</v>
-      </c>
-      <c r="M107" t="n">
-        <v>0</v>
-      </c>
-      <c r="N107" t="n">
-        <v>2</v>
-      </c>
-      <c r="O107" t="n">
+      <c r="S107" t="n">
+        <v>2</v>
+      </c>
+      <c r="T107" t="n">
         <v>5</v>
-      </c>
-      <c r="P107" t="n">
-        <v>29</v>
-      </c>
-      <c r="Q107" t="n">
-        <v>2</v>
-      </c>
-      <c r="R107" t="n">
-        <v>7</v>
-      </c>
-      <c r="S107" t="n">
-        <v>1</v>
-      </c>
-      <c r="T107" t="n">
-        <v>2</v>
       </c>
       <c r="U107" t="n">
         <v>0</v>
@@ -9269,17 +9269,17 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Eli Ellis</t>
+          <t>Bishop Boswell</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -9291,37 +9291,37 @@
         <v>4</v>
       </c>
       <c r="I108" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J108" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K108" t="n">
+        <v>4</v>
+      </c>
+      <c r="L108" t="n">
+        <v>2</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0</v>
+      </c>
+      <c r="N108" t="n">
+        <v>2</v>
+      </c>
+      <c r="O108" t="n">
         <v>5</v>
       </c>
-      <c r="L108" t="n">
-        <v>1</v>
-      </c>
-      <c r="M108" t="n">
-        <v>0</v>
-      </c>
-      <c r="N108" t="n">
-        <v>1</v>
-      </c>
-      <c r="O108" t="n">
-        <v>2</v>
-      </c>
       <c r="P108" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R108" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="S108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T108" t="n">
         <v>2</v>
@@ -9351,7 +9351,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Elijah Strong</t>
+          <t>Eli Ellis</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -9373,40 +9373,40 @@
         <v>4</v>
       </c>
       <c r="I109" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J109" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K109" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O109" t="n">
         <v>2</v>
       </c>
       <c r="P109" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="Q109" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="S109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T109" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U109" t="n">
         <v>0</v>
@@ -9433,17 +9433,17 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Ethan Burg</t>
+          <t>Elijah Strong</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -9455,46 +9455,46 @@
         <v>4</v>
       </c>
       <c r="I110" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
       </c>
       <c r="K110" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L110" t="n">
         <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N110" t="n">
         <v>0</v>
       </c>
       <c r="O110" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P110" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R110" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="S110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U110" t="n">
         <v>0</v>
       </c>
       <c r="V110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -9515,22 +9515,22 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Filip Jovic</t>
+          <t>Ethan Burg</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AUB</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>AUB@ALA</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H111" t="n">
@@ -9543,7 +9543,7 @@
         <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L111" t="n">
         <v>0</v>
@@ -9555,28 +9555,28 @@
         <v>0</v>
       </c>
       <c r="O111" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P111" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="Q111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
       </c>
       <c r="T111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U111" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V111" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
@@ -10089,35 +10089,35 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Jasper Johnson</t>
+          <t>Dayton Forsythe</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>OU</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>OU@TEX</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>9:14 - 2nd Half</t>
         </is>
       </c>
       <c r="H118" t="n">
         <v>2</v>
       </c>
       <c r="I118" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J118" t="n">
         <v>1</v>
       </c>
       <c r="K118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L118" t="n">
         <v>0</v>
@@ -10129,22 +10129,22 @@
         <v>1</v>
       </c>
       <c r="O118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P118" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Q118" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R118" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S118" t="n">
         <v>1</v>
       </c>
       <c r="T118" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U118" t="n">
         <v>0</v>
@@ -10171,35 +10171,35 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Nic Codie</t>
+          <t>Jasper Johnson</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>OU@TEX</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>17:41 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H119" t="n">
         <v>2</v>
       </c>
       <c r="I119" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J119" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L119" t="n">
         <v>0</v>
@@ -10208,25 +10208,25 @@
         <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P119" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R119" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T119" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U119" t="n">
         <v>0</v>
@@ -10827,62 +10827,62 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Patton Pinkins</t>
+          <t>Nic Codie</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>OU@TEX</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>9:14 - 2nd Half</t>
         </is>
       </c>
       <c r="H127" t="n">
         <v>1</v>
       </c>
       <c r="I127" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J127" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L127" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
         <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P127" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="Q127" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
       </c>
       <c r="T127" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U127" t="n">
         <v>0</v>
@@ -10909,17 +10909,17 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Urban Klavzar</t>
+          <t>Patton Pinkins</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>FLA</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -10931,37 +10931,37 @@
         <v>1</v>
       </c>
       <c r="I128" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M128" t="n">
         <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P128" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="Q128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R128" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="S128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T128" t="n">
         <v>2</v>
@@ -10991,35 +10991,35 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Isaiah Sealy</t>
+          <t>Urban Klavzar</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>ARK</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I129" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
       </c>
       <c r="K129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L129" t="n">
         <v>0</v>
@@ -11028,25 +11028,25 @@
         <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P129" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="Q129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R129" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T129" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U129" t="n">
         <v>0</v>
@@ -11073,22 +11073,22 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Jayden Leverett</t>
+          <t>Isaiah Sealy</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>ARK</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H130" t="n">
@@ -11098,10 +11098,10 @@
         <v>0</v>
       </c>
       <c r="J130" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L130" t="n">
         <v>0</v>
@@ -11110,19 +11110,19 @@
         <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O130" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P130" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q130" t="n">
         <v>0</v>
       </c>
       <c r="R130" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -11155,17 +11155,17 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Jordan Butler</t>
+          <t>Jayden Leverett</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -11180,7 +11180,7 @@
         <v>0</v>
       </c>
       <c r="J131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K131" t="n">
         <v>0</v>
@@ -11195,16 +11195,16 @@
         <v>0</v>
       </c>
       <c r="O131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P131" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q131" t="n">
         <v>0</v>
       </c>
       <c r="R131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -11237,17 +11237,17 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Justin Bailey</t>
+          <t>Jordan Butler</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -11268,19 +11268,19 @@
         <v>0</v>
       </c>
       <c r="L132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
         <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P132" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q132" t="n">
         <v>0</v>
@@ -11319,22 +11319,22 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Kai Rogers</t>
+          <t>Justin Bailey</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>OU</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>OU@TEX</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>17:41 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H133" t="n">
@@ -11344,31 +11344,31 @@
         <v>0</v>
       </c>
       <c r="J133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K133" t="n">
         <v>0</v>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M133" t="n">
         <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O133" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P133" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q133" t="n">
         <v>0</v>
       </c>
       <c r="R133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -11401,22 +11401,22 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Trent Burns</t>
+          <t>Kai Rogers</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>OU</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>OU@TEX</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>9:14 - 2nd Half</t>
         </is>
       </c>
       <c r="H134" t="n">
@@ -11426,7 +11426,7 @@
         <v>0</v>
       </c>
       <c r="J134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K134" t="n">
         <v>0</v>
@@ -11441,16 +11441,16 @@
         <v>0</v>
       </c>
       <c r="O134" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P134" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q134" t="n">
         <v>0</v>
       </c>
       <c r="R134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -11483,22 +11483,22 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Trent Noah</t>
+          <t>Noah Williamson</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>ALA</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>AUB@ALA</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>11:35 - 2nd Half</t>
         </is>
       </c>
       <c r="H135" t="n">
@@ -11508,7 +11508,7 @@
         <v>0</v>
       </c>
       <c r="J135" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K135" t="n">
         <v>0</v>
@@ -11520,25 +11520,25 @@
         <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P135" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Q135" t="n">
         <v>0</v>
       </c>
       <c r="R135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
       </c>
       <c r="T135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U135" t="n">
         <v>0</v>
@@ -11565,22 +11565,22 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Tyler Harris</t>
+          <t>Simeon Wilcher</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>OU@TEX</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>9:14 - 2nd Half</t>
         </is>
       </c>
       <c r="H136" t="n">
@@ -11593,7 +11593,7 @@
         <v>0</v>
       </c>
       <c r="K136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L136" t="n">
         <v>0</v>
@@ -11605,22 +11605,22 @@
         <v>0</v>
       </c>
       <c r="O136" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P136" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Q136" t="n">
         <v>0</v>
       </c>
       <c r="R136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
       </c>
       <c r="T136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U136" t="n">
         <v>0</v>
@@ -11647,26 +11647,26 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Blake Muschalek</t>
+          <t>Trent Burns</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AUB</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>AUB@ALA</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H137" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I137" t="n">
         <v>0</v>
@@ -11690,19 +11690,19 @@
         <v>0</v>
       </c>
       <c r="P137" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q137" t="n">
         <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
       </c>
       <c r="T137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U137" t="n">
         <v>0</v>
@@ -11729,32 +11729,32 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Camden Heide</t>
+          <t>Trent Noah</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>OU@TEX</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>17:41 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H138" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I138" t="n">
         <v>0</v>
       </c>
       <c r="J138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K138" t="n">
         <v>0</v>
@@ -11766,25 +11766,25 @@
         <v>0</v>
       </c>
       <c r="N138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O138" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P138" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="Q138" t="n">
         <v>0</v>
       </c>
       <c r="R138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
       </c>
       <c r="T138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U138" t="n">
         <v>0</v>
@@ -11811,26 +11811,26 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Federiko Federiko</t>
+          <t>Tyler Harris</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>TA&amp;M</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>TA&amp;M@LSU</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Final/3OT</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H139" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I139" t="n">
         <v>0</v>
@@ -11851,16 +11851,16 @@
         <v>0</v>
       </c>
       <c r="O139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P139" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q139" t="n">
         <v>0</v>
       </c>
       <c r="R139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -11893,22 +11893,22 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Jacari Lane</t>
+          <t>Blake Muschalek</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>TA&amp;M</t>
+          <t>AUB</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>TA&amp;M@LSU</t>
+          <t>AUB@ALA</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Final/3OT</t>
+          <t>11:35 - 2nd Half</t>
         </is>
       </c>
       <c r="H140" t="n">
@@ -11933,10 +11933,10 @@
         <v>0</v>
       </c>
       <c r="O140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P140" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q140" t="n">
         <v>0</v>
@@ -11948,7 +11948,7 @@
         <v>0</v>
       </c>
       <c r="T140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U140" t="n">
         <v>0</v>
@@ -11975,32 +11975,32 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Max Smith</t>
+          <t>Camden Heide</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>OU@TEX</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>9:14 - 2nd Half</t>
         </is>
       </c>
       <c r="H141" t="n">
         <v>-1</v>
       </c>
       <c r="I141" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K141" t="n">
         <v>0</v>
@@ -12012,25 +12012,25 @@
         <v>0</v>
       </c>
       <c r="N141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O141" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P141" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="Q141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R141" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
       </c>
       <c r="T141" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U141" t="n">
         <v>0</v>
@@ -12057,12 +12057,12 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Mazi Mosley</t>
+          <t>Federiko Federiko</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>LSU</t>
+          <t>TA&amp;M</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -12097,10 +12097,10 @@
         <v>0</v>
       </c>
       <c r="O142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P142" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q142" t="n">
         <v>0</v>
@@ -12112,7 +12112,7 @@
         <v>0</v>
       </c>
       <c r="T142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U142" t="n">
         <v>0</v>
@@ -12139,22 +12139,22 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Simeon Wilcher</t>
+          <t>Jacari Lane</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>TA&amp;M</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>OU@TEX</t>
+          <t>TA&amp;M@LSU</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>17:41 - 2nd Half</t>
+          <t>Final/3OT</t>
         </is>
       </c>
       <c r="H143" t="n">
@@ -12179,10 +12179,10 @@
         <v>0</v>
       </c>
       <c r="O143" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P143" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q143" t="n">
         <v>0</v>
@@ -12194,7 +12194,7 @@
         <v>0</v>
       </c>
       <c r="T143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U143" t="n">
         <v>0</v>
@@ -12221,26 +12221,26 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Noah Williamson</t>
+          <t>Max Smith</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>AUB@ALA</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Halftime</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H144" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="I144" t="n">
         <v>0</v>
@@ -12258,13 +12258,13 @@
         <v>0</v>
       </c>
       <c r="N144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P144" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q144" t="n">
         <v>0</v>
@@ -12303,26 +12303,26 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Dayton Forsythe</t>
+          <t>Mazi Mosley</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>OU</t>
+          <t>LSU</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>OU@TEX</t>
+          <t>TA&amp;M@LSU</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>17:41 - 2nd Half</t>
+          <t>Final/3OT</t>
         </is>
       </c>
       <c r="H145" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="I145" t="n">
         <v>0</v>
@@ -12340,25 +12340,25 @@
         <v>0</v>
       </c>
       <c r="N145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
       </c>
       <c r="P145" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Q145" t="n">
         <v>0</v>
       </c>
       <c r="R145" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
       </c>
       <c r="T145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U145" t="n">
         <v>0</v>
@@ -12492,7 +12492,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="C2" t="n">
         <v>5</v>
@@ -12514,11 +12514,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>The Backslashers</t>
+          <t>The Oddities</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C4" t="n">
         <v>5</v>
@@ -12527,11 +12527,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>The Oddities</t>
+          <t>The Backslashers</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C5" t="n">
         <v>5</v>
@@ -12544,7 +12544,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C6" t="n">
         <v>4</v>
@@ -12557,7 +12557,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C7" t="n">
         <v>4</v>
@@ -12570,7 +12570,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C8" t="n">
         <v>5</v>

--- a/docs/Today_PoohPoints_SEC_ByOwner_2026-03-07.xlsx
+++ b/docs/Today_PoohPoints_SEC_ByOwner_2026-03-07.xlsx
@@ -429,7 +429,7 @@
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
     <col width="6" customWidth="1" min="8" max="8"/>
     <col width="5" customWidth="1" min="9" max="9"/>
     <col width="5" customWidth="1" min="10" max="10"/>
@@ -674,14 +674,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>11:35 - 2nd Half</t>
+          <t>6:39 - 2nd Half</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -696,19 +696,19 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
@@ -756,17 +756,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>9:14 - 2nd Half</t>
+          <t>4:59 - 2nd Half</t>
         </is>
       </c>
       <c r="H4" t="n">
+        <v>18</v>
+      </c>
+      <c r="I4" t="n">
         <v>14</v>
       </c>
-      <c r="I4" t="n">
-        <v>12</v>
-      </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
@@ -784,13 +784,13 @@
         <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1166,14 +1166,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>9:14 - 2nd Half</t>
+          <t>4:59 - 2nd Half</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J9" t="n">
         <v>2</v>
@@ -1188,13 +1188,13 @@
         <v>1</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1209,10 +1209,10 @@
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="V9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -1315,68 +1315,68 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Jacob Crews</t>
+          <t>Tramon Mark</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>OU@TEX</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>4:59 - 2nd Half</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1397,68 +1397,68 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Tramon Mark</t>
+          <t>Jacob Crews</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>OU@TEX</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>9:14 - 2nd Half</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1740,11 +1740,11 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>11:35 - 2nd Half</t>
+          <t>6:39 - 2nd Half</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I16" t="n">
         <v>6</v>
@@ -1765,16 +1765,16 @@
         <v>2</v>
       </c>
       <c r="O16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="Q16" t="n">
         <v>3</v>
       </c>
       <c r="R16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -2135,68 +2135,68 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Denzel Aberdeen</t>
+          <t>Nijel Pack</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>OU</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>OU@TEX</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>4:59 - 2nd Half</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I21" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J21" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>7</v>
+      </c>
+      <c r="R21" t="n">
+        <v>11</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3</v>
+      </c>
+      <c r="T21" t="n">
         <v>5</v>
       </c>
-      <c r="K21" t="n">
-        <v>4</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>1</v>
-      </c>
-      <c r="O21" t="n">
-        <v>2</v>
-      </c>
-      <c r="P21" t="n">
-        <v>35</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>4</v>
-      </c>
-      <c r="R21" t="n">
-        <v>13</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1</v>
-      </c>
-      <c r="T21" t="n">
-        <v>6</v>
-      </c>
       <c r="U21" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="V21" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -2217,17 +2217,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Jayden Epps</t>
+          <t>Denzel Aberdeen</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>MSST</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2236,37 +2236,37 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I22" t="n">
+        <v>15</v>
+      </c>
+      <c r="J22" t="n">
+        <v>5</v>
+      </c>
+      <c r="K22" t="n">
+        <v>4</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2</v>
+      </c>
+      <c r="P22" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>4</v>
+      </c>
+      <c r="R22" t="n">
         <v>13</v>
-      </c>
-      <c r="J22" t="n">
-        <v>6</v>
-      </c>
-      <c r="K22" t="n">
-        <v>4</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1</v>
-      </c>
-      <c r="N22" t="n">
-        <v>4</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1</v>
-      </c>
-      <c r="P22" t="n">
-        <v>34</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>6</v>
-      </c>
-      <c r="R22" t="n">
-        <v>14</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2275,10 +2275,10 @@
         <v>6</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
@@ -2299,68 +2299,68 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Nijel Pack</t>
+          <t>Jayden Epps</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>OU</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>OU@TEX</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>9:14 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I23" t="n">
         <v>13</v>
       </c>
       <c r="J23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P23" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="Q23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R23" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2560,20 +2560,20 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>11:35 - 2nd Half</t>
+          <t>6:39 - 2nd Half</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I26" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
         <v>1</v>
@@ -2588,19 +2588,19 @@
         <v>2</v>
       </c>
       <c r="P26" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U26" t="n">
         <v>6</v>
@@ -2724,20 +2724,20 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>11:35 - 2nd Half</t>
+          <t>6:39 - 2nd Half</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I28" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J28" t="n">
         <v>6</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -2746,13 +2746,13 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P28" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Q28" t="n">
         <v>2</v>
@@ -2767,10 +2767,10 @@
         <v>4</v>
       </c>
       <c r="U28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>11:35 - 2nd Half</t>
+          <t>6:39 - 2nd Half</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -3080,7 +3080,7 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q32" t="n">
         <v>2</v>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>9:14 - 2nd Half</t>
+          <t>4:59 - 2nd Half</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>11:35 - 2nd Half</t>
+          <t>6:39 - 2nd Half</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -3244,7 +3244,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -3857,68 +3857,68 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Myles Stute</t>
+          <t>Jadon Jones</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>OU</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>OU@TEX</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>4:59 - 2nd Half</t>
         </is>
       </c>
       <c r="H42" t="n">
         <v>8</v>
       </c>
       <c r="I42" t="n">
+        <v>2</v>
+      </c>
+      <c r="J42" t="n">
         <v>6</v>
       </c>
-      <c r="J42" t="n">
-        <v>2</v>
-      </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P42" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="Q42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -3939,68 +3939,68 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Jadon Jones</t>
+          <t>Myles Stute</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>OU</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>OU@TEX</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>9:14 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J43" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P43" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>11:35 - 2nd Half</t>
+          <t>6:39 - 2nd Half</t>
         </is>
       </c>
       <c r="H45" t="n">
@@ -4143,10 +4143,10 @@
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P45" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -4528,41 +4528,41 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>11:35 - 2nd Half</t>
+          <t>6:39 - 2nd Half</t>
         </is>
       </c>
       <c r="H50" t="n">
         <v>13</v>
       </c>
       <c r="I50" t="n">
+        <v>10</v>
+      </c>
+      <c r="J50" t="n">
+        <v>4</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1</v>
+      </c>
+      <c r="L50" t="n">
+        <v>1</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1</v>
+      </c>
+      <c r="N50" t="n">
+        <v>1</v>
+      </c>
+      <c r="O50" t="n">
+        <v>1</v>
+      </c>
+      <c r="P50" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>5</v>
+      </c>
+      <c r="R50" t="n">
         <v>8</v>
-      </c>
-      <c r="J50" t="n">
-        <v>4</v>
-      </c>
-      <c r="K50" t="n">
-        <v>1</v>
-      </c>
-      <c r="L50" t="n">
-        <v>1</v>
-      </c>
-      <c r="M50" t="n">
-        <v>1</v>
-      </c>
-      <c r="N50" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" t="n">
-        <v>1</v>
-      </c>
-      <c r="P50" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>4</v>
-      </c>
-      <c r="R50" t="n">
-        <v>6</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -4692,14 +4692,14 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>9:14 - 2nd Half</t>
+          <t>4:59 - 2nd Half</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I52" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J52" t="n">
         <v>2</v>
@@ -4708,7 +4708,7 @@
         <v>2</v>
       </c>
       <c r="L52" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
@@ -4720,19 +4720,19 @@
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="Q52" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R52" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="S52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U52" t="n">
         <v>3</v>
@@ -4759,68 +4759,68 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Jordan Pope</t>
+          <t>Kevin Overton</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>AUB</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>OU@TEX</t>
+          <t>AUB@ALA</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>9:14 - 2nd Half</t>
+          <t>6:39 - 2nd Half</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I53" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K53" t="n">
         <v>1</v>
       </c>
       <c r="L53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P53" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q53" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R53" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T53" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="U53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -5005,38 +5005,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Kevin Overton</t>
+          <t>Jordan Pope</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AUB</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>AUB@ALA</t>
+          <t>OU@TEX</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>11:35 - 2nd Half</t>
+          <t>4:59 - 2nd Half</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I56" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="J56" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
@@ -5045,28 +5045,28 @@
         <v>2</v>
       </c>
       <c r="O56" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="Q56" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R56" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="S56" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T56" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="U56" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="V56" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
@@ -5266,14 +5266,14 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>9:14 - 2nd Half</t>
+          <t>4:59 - 2nd Half</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I59" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J59" t="n">
         <v>5</v>
@@ -5288,19 +5288,19 @@
         <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O59" t="n">
         <v>2</v>
       </c>
       <c r="P59" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="Q59" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R59" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S59" t="n">
         <v>1</v>
@@ -5312,7 +5312,7 @@
         <v>7</v>
       </c>
       <c r="V59" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60">
@@ -5430,11 +5430,11 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>9:14 - 2nd Half</t>
+          <t>4:59 - 2nd Half</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I61" t="n">
         <v>4</v>
@@ -5443,7 +5443,7 @@
         <v>1</v>
       </c>
       <c r="K61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" t="n">
         <v>1</v>
@@ -5455,10 +5455,10 @@
         <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P61" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Q61" t="n">
         <v>1</v>
@@ -5661,68 +5661,68 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Mouhamed Dioubate</t>
+          <t>Latrell Wrightsell</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>ALA</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>AUB@ALA</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>6:39 - 2nd Half</t>
         </is>
       </c>
       <c r="H64" t="n">
         <v>11</v>
       </c>
       <c r="I64" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J64" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L64" t="n">
         <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P64" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="Q64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R64" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="S64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T64" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U64" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V64" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -5743,68 +5743,68 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Latrell Wrightsell</t>
+          <t>Mouhamed Dioubate</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>AUB@ALA</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>11:35 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H65" t="n">
+        <v>11</v>
+      </c>
+      <c r="I65" t="n">
         <v>10</v>
-      </c>
-      <c r="I65" t="n">
-        <v>6</v>
       </c>
       <c r="J65" t="n">
         <v>6</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" t="n">
         <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O65" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P65" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Q65" t="n">
         <v>3</v>
       </c>
       <c r="R65" t="n">
+        <v>7</v>
+      </c>
+      <c r="S65" t="n">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>3</v>
+      </c>
+      <c r="V65" t="n">
         <v>6</v>
-      </c>
-      <c r="S65" t="n">
-        <v>0</v>
-      </c>
-      <c r="T65" t="n">
-        <v>3</v>
-      </c>
-      <c r="U65" t="n">
-        <v>0</v>
-      </c>
-      <c r="V65" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -6168,26 +6168,26 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>11:35 - 2nd Half</t>
+          <t>6:39 - 2nd Half</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I70" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J70" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N70" t="n">
         <v>1</v>
@@ -6196,7 +6196,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Q70" t="n">
         <v>3</v>
@@ -6211,10 +6211,10 @@
         <v>1</v>
       </c>
       <c r="U70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V70" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="71">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>11:35 - 2nd Half</t>
+          <t>6:39 - 2nd Half</t>
         </is>
       </c>
       <c r="H71" t="n">
@@ -6278,7 +6278,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="Q71" t="n">
         <v>4</v>
@@ -6317,65 +6317,65 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Jalen Washington</t>
+          <t>Elyjah Freeman</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>AUB</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>AUB@ALA</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>6:39 - 2nd Half</t>
         </is>
       </c>
       <c r="H72" t="n">
         <v>10</v>
       </c>
       <c r="I72" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J72" t="n">
+        <v>2</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="n">
+        <v>1</v>
+      </c>
+      <c r="M72" t="n">
+        <v>1</v>
+      </c>
+      <c r="N72" t="n">
+        <v>1</v>
+      </c>
+      <c r="O72" t="n">
+        <v>2</v>
+      </c>
+      <c r="P72" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>4</v>
+      </c>
+      <c r="R72" t="n">
         <v>8</v>
       </c>
-      <c r="K72" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" t="n">
-        <v>0</v>
-      </c>
-      <c r="M72" t="n">
-        <v>1</v>
-      </c>
-      <c r="N72" t="n">
-        <v>1</v>
-      </c>
-      <c r="O72" t="n">
-        <v>2</v>
-      </c>
-      <c r="P72" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>3</v>
-      </c>
-      <c r="R72" t="n">
-        <v>7</v>
-      </c>
       <c r="S72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T72" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V72" t="n">
         <v>2</v>
@@ -6399,44 +6399,44 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Tae Davis</t>
+          <t>Jalen Washington</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>OU</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>OU@TEX</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>9:14 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I73" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J73" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O73" t="n">
         <v>2</v>
@@ -6448,19 +6448,19 @@
         <v>3</v>
       </c>
       <c r="R73" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
       </c>
       <c r="T73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U73" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V73" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -6481,68 +6481,68 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Max Mackinnon</t>
+          <t>Tae Davis</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>LSU</t>
+          <t>OU</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>TA&amp;M@LSU</t>
+          <t>OU@TEX</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Final/3OT</t>
+          <t>4:59 - 2nd Half</t>
         </is>
       </c>
       <c r="H74" t="n">
+        <v>9</v>
+      </c>
+      <c r="I74" t="n">
+        <v>10</v>
+      </c>
+      <c r="J74" t="n">
         <v>7</v>
       </c>
-      <c r="I74" t="n">
-        <v>20</v>
-      </c>
-      <c r="J74" t="n">
-        <v>4</v>
-      </c>
       <c r="K74" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O74" t="n">
         <v>2</v>
       </c>
       <c r="P74" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="Q74" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="R74" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="S74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T74" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="U74" t="n">
         <v>4</v>
       </c>
       <c r="V74" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="75">
@@ -6563,68 +6563,68 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Shawn Jones Jr.</t>
+          <t>Max Mackinnon</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>MSST</t>
+          <t>LSU</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>TA&amp;M@LSU</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/3OT</t>
         </is>
       </c>
       <c r="H75" t="n">
         <v>7</v>
       </c>
       <c r="I75" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K75" t="n">
         <v>3</v>
       </c>
       <c r="L75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O75" t="n">
         <v>2</v>
       </c>
       <c r="P75" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="Q75" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R75" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="S75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T75" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="U75" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V75" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76">
@@ -6645,68 +6645,68 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Elyjah Freeman</t>
+          <t>Shawn Jones Jr.</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AUB</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>AUB@ALA</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>11:35 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I76" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O76" t="n">
         <v>2</v>
       </c>
       <c r="P76" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="Q76" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R76" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="S76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T76" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -7972,7 +7972,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>11:35 - 2nd Half</t>
+          <t>6:39 - 2nd Half</t>
         </is>
       </c>
       <c r="H92" t="n">
@@ -8613,35 +8613,35 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Zach Clemence</t>
+          <t>Sebastian Williams-Adams</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>TA&amp;M</t>
+          <t>AUB</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>TA&amp;M@LSU</t>
+          <t>AUB@ALA</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Final/3OT</t>
+          <t>6:39 - 2nd Half</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I100" t="n">
         <v>5</v>
       </c>
       <c r="J100" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="K100" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L100" t="n">
         <v>0</v>
@@ -8653,28 +8653,28 @@
         <v>0</v>
       </c>
       <c r="O100" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P100" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="Q100" t="n">
         <v>2</v>
       </c>
       <c r="R100" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
       </c>
       <c r="T100" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="U100" t="n">
         <v>1</v>
       </c>
       <c r="V100" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="101">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Rashad King</t>
+          <t>Zach Clemence</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>LSU</t>
+          <t>TA&amp;M</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -8714,49 +8714,49 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I101" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J101" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K101" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
         <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P101" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="Q101" t="n">
         <v>2</v>
       </c>
       <c r="R101" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="S101" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T101" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V101" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102">
@@ -8777,68 +8777,68 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Sebastian Williams-Adams</t>
+          <t>Rashad King</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AUB</t>
+          <t>LSU</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>AUB@ALA</t>
+          <t>TA&amp;M@LSU</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>11:35 - 2nd Half</t>
+          <t>Final/3OT</t>
         </is>
       </c>
       <c r="H102" t="n">
         <v>6</v>
       </c>
       <c r="I102" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J102" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K102" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M102" t="n">
         <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O102" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P102" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="Q102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R102" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S102" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T102" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V102" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>9:14 - 2nd Half</t>
+          <t>4:59 - 2nd Half</t>
         </is>
       </c>
       <c r="H104" t="n">
@@ -8984,7 +8984,7 @@
         <v>3</v>
       </c>
       <c r="P104" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q104" t="n">
         <v>1</v>
@@ -9120,7 +9120,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>11:35 - 2nd Half</t>
+          <t>6:39 - 2nd Half</t>
         </is>
       </c>
       <c r="H106" t="n">
@@ -9148,7 +9148,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q106" t="n">
         <v>1</v>
@@ -10104,7 +10104,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>9:14 - 2nd Half</t>
+          <t>4:59 - 2nd Half</t>
         </is>
       </c>
       <c r="H118" t="n">
@@ -10132,7 +10132,7 @@
         <v>0</v>
       </c>
       <c r="P118" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q118" t="n">
         <v>2</v>
@@ -10253,22 +10253,22 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Zach Day</t>
+          <t>Nic Codie</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>OU@TEX</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>4:59 - 2nd Half</t>
         </is>
       </c>
       <c r="H120" t="n">
@@ -10278,7 +10278,7 @@
         <v>0</v>
       </c>
       <c r="J120" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K120" t="n">
         <v>0</v>
@@ -10287,22 +10287,22 @@
         <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
         <v>0</v>
       </c>
       <c r="O120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P120" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="Q120" t="n">
         <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -10335,17 +10335,17 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Amaree Abram</t>
+          <t>Zach Day</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -10354,10 +10354,10 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J121" t="n">
         <v>1</v>
@@ -10366,10 +10366,10 @@
         <v>0</v>
       </c>
       <c r="L121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N121" t="n">
         <v>0</v>
@@ -10378,13 +10378,13 @@
         <v>0</v>
       </c>
       <c r="P121" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Q121" t="n">
         <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -10393,10 +10393,10 @@
         <v>0</v>
       </c>
       <c r="U121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V121" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -10417,17 +10417,17 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Corey Chest</t>
+          <t>Amaree Abram</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -10439,7 +10439,7 @@
         <v>1</v>
       </c>
       <c r="I122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J122" t="n">
         <v>1</v>
@@ -10448,7 +10448,7 @@
         <v>0</v>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M122" t="n">
         <v>0</v>
@@ -10460,13 +10460,13 @@
         <v>0</v>
       </c>
       <c r="P122" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q122" t="n">
         <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -10475,10 +10475,10 @@
         <v>0</v>
       </c>
       <c r="U122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V122" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="123">
@@ -10499,12 +10499,12 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>EJ Walker</t>
+          <t>Corey Chest</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -10524,10 +10524,10 @@
         <v>0</v>
       </c>
       <c r="J123" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L123" t="n">
         <v>0</v>
@@ -10536,25 +10536,25 @@
         <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P123" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="Q123" t="n">
         <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
       </c>
       <c r="T123" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U123" t="n">
         <v>0</v>
@@ -10581,7 +10581,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Grant Polk</t>
+          <t>EJ Walker</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -10603,13 +10603,13 @@
         <v>1</v>
       </c>
       <c r="I124" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J124" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L124" t="n">
         <v>0</v>
@@ -10618,25 +10618,25 @@
         <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O124" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P124" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="Q124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T124" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U124" t="n">
         <v>0</v>
@@ -10663,17 +10663,17 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Jake Wilkins</t>
+          <t>Grant Polk</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -10685,7 +10685,7 @@
         <v>1</v>
       </c>
       <c r="I125" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10703,22 +10703,22 @@
         <v>0</v>
       </c>
       <c r="O125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P125" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q125" t="n">
         <v>1</v>
       </c>
       <c r="R125" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T125" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U125" t="n">
         <v>0</v>
@@ -10745,62 +10745,62 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Josh Holloway</t>
+          <t>Jake Wilkins</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>TA&amp;M</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>TA&amp;M@LSU</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Final/3OT</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H126" t="n">
         <v>1</v>
       </c>
       <c r="I126" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
         <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P126" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="Q126" t="n">
         <v>1</v>
       </c>
       <c r="R126" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T126" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U126" t="n">
         <v>0</v>
@@ -10827,62 +10827,62 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Nic Codie</t>
+          <t>Josh Holloway</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>TA&amp;M</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>OU@TEX</t>
+          <t>TA&amp;M@LSU</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>9:14 - 2nd Half</t>
+          <t>Final/3OT</t>
         </is>
       </c>
       <c r="H127" t="n">
         <v>1</v>
       </c>
       <c r="I127" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J127" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M127" t="n">
         <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O127" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P127" t="n">
         <v>13</v>
       </c>
       <c r="Q127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R127" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T127" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U127" t="n">
         <v>0</v>
@@ -11073,22 +11073,22 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Isaiah Sealy</t>
+          <t>Blake Muschalek</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>ARK</t>
+          <t>AUB</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>AUB@ALA</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>6:39 - 2nd Half</t>
         </is>
       </c>
       <c r="H130" t="n">
@@ -11098,10 +11098,10 @@
         <v>0</v>
       </c>
       <c r="J130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L130" t="n">
         <v>0</v>
@@ -11110,10 +11110,10 @@
         <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P130" t="n">
         <v>5</v>
@@ -11122,13 +11122,13 @@
         <v>0</v>
       </c>
       <c r="R130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
       </c>
       <c r="T130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U130" t="n">
         <v>0</v>
@@ -11155,22 +11155,22 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Jayden Leverett</t>
+          <t>Isaiah Sealy</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>ARK</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H131" t="n">
@@ -11180,10 +11180,10 @@
         <v>0</v>
       </c>
       <c r="J131" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L131" t="n">
         <v>0</v>
@@ -11192,19 +11192,19 @@
         <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O131" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P131" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q131" t="n">
         <v>0</v>
       </c>
       <c r="R131" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -11237,17 +11237,17 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Jordan Butler</t>
+          <t>Jayden Leverett</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -11262,7 +11262,7 @@
         <v>0</v>
       </c>
       <c r="J132" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K132" t="n">
         <v>0</v>
@@ -11277,16 +11277,16 @@
         <v>0</v>
       </c>
       <c r="O132" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P132" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q132" t="n">
         <v>0</v>
       </c>
       <c r="R132" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -11319,17 +11319,17 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Justin Bailey</t>
+          <t>Jordan Butler</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -11350,19 +11350,19 @@
         <v>0</v>
       </c>
       <c r="L133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M133" t="n">
         <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P133" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q133" t="n">
         <v>0</v>
@@ -11401,22 +11401,22 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Kai Rogers</t>
+          <t>Justin Bailey</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>OU</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>OU@TEX</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>9:14 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H134" t="n">
@@ -11426,31 +11426,31 @@
         <v>0</v>
       </c>
       <c r="J134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K134" t="n">
         <v>0</v>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M134" t="n">
         <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O134" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P134" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q134" t="n">
         <v>0</v>
       </c>
       <c r="R134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -11483,22 +11483,22 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Noah Williamson</t>
+          <t>Kai Rogers</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>OU</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>AUB@ALA</t>
+          <t>OU@TEX</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>11:35 - 2nd Half</t>
+          <t>4:59 - 2nd Half</t>
         </is>
       </c>
       <c r="H135" t="n">
@@ -11508,7 +11508,7 @@
         <v>0</v>
       </c>
       <c r="J135" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K135" t="n">
         <v>0</v>
@@ -11520,13 +11520,13 @@
         <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P135" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q135" t="n">
         <v>0</v>
@@ -11538,7 +11538,7 @@
         <v>0</v>
       </c>
       <c r="T135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U135" t="n">
         <v>0</v>
@@ -11565,22 +11565,22 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Simeon Wilcher</t>
+          <t>Noah Williamson</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>ALA</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>OU@TEX</t>
+          <t>AUB@ALA</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>9:14 - 2nd Half</t>
+          <t>6:39 - 2nd Half</t>
         </is>
       </c>
       <c r="H136" t="n">
@@ -11590,10 +11590,10 @@
         <v>0</v>
       </c>
       <c r="J136" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L136" t="n">
         <v>0</v>
@@ -11602,13 +11602,13 @@
         <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O136" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P136" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q136" t="n">
         <v>0</v>
@@ -11647,22 +11647,22 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Trent Burns</t>
+          <t>Simeon Wilcher</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>OU@TEX</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>4:59 - 2nd Half</t>
         </is>
       </c>
       <c r="H137" t="n">
@@ -11675,7 +11675,7 @@
         <v>0</v>
       </c>
       <c r="K137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L137" t="n">
         <v>0</v>
@@ -11687,22 +11687,22 @@
         <v>0</v>
       </c>
       <c r="O137" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P137" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Q137" t="n">
         <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
       </c>
       <c r="T137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U137" t="n">
         <v>0</v>
@@ -11729,22 +11729,22 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Trent Noah</t>
+          <t>Trent Burns</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H138" t="n">
@@ -11772,7 +11772,7 @@
         <v>0</v>
       </c>
       <c r="P138" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q138" t="n">
         <v>0</v>
@@ -11811,17 +11811,17 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Tyler Harris</t>
+          <t>Trent Noah</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -11893,26 +11893,26 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Blake Muschalek</t>
+          <t>Tyler Harris</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AUB</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>AUB@ALA</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>11:35 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H140" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I140" t="n">
         <v>0</v>
@@ -11933,7 +11933,7 @@
         <v>0</v>
       </c>
       <c r="O140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P140" t="n">
         <v>2</v>
@@ -11942,13 +11942,13 @@
         <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
       </c>
       <c r="T140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U140" t="n">
         <v>0</v>
@@ -11990,7 +11990,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>9:14 - 2nd Half</t>
+          <t>4:59 - 2nd Half</t>
         </is>
       </c>
       <c r="H141" t="n">
@@ -12501,11 +12501,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Three Dawg Nite</t>
+          <t>The Oddities</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C3" t="n">
         <v>5</v>
@@ -12514,11 +12514,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>The Oddities</t>
+          <t>Three Dawg Nite</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C4" t="n">
         <v>5</v>
@@ -12531,7 +12531,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C5" t="n">
         <v>5</v>
@@ -12557,7 +12557,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C7" t="n">
         <v>4</v>
@@ -12570,7 +12570,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C8" t="n">
         <v>5</v>

--- a/docs/Today_PoohPoints_SEC_ByOwner_2026-03-07.xlsx
+++ b/docs/Today_PoohPoints_SEC_ByOwner_2026-03-07.xlsx
@@ -674,7 +674,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>6:39 - 2nd Half</t>
+          <t>6:21 - 2nd Half</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -702,7 +702,7 @@
         <v>2</v>
       </c>
       <c r="P3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q3" t="n">
         <v>8</v>
@@ -756,7 +756,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>4:59 - 2nd Half</t>
+          <t>3:33 - 2nd Half</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -784,7 +784,7 @@
         <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q4" t="n">
         <v>5</v>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4:59 - 2nd Half</t>
+          <t>3:33 - 2nd Half</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4:59 - 2nd Half</t>
+          <t>3:33 - 2nd Half</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1358,7 +1358,7 @@
         <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q11" t="n">
         <v>2</v>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>6:39 - 2nd Half</t>
+          <t>6:21 - 2nd Half</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>4:59 - 2nd Half</t>
+          <t>3:33 - 2nd Half</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>6:39 - 2nd Half</t>
+          <t>6:21 - 2nd Half</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -2588,7 +2588,7 @@
         <v>2</v>
       </c>
       <c r="P26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q26" t="n">
         <v>5</v>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>6:39 - 2nd Half</t>
+          <t>6:21 - 2nd Half</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>6:39 - 2nd Half</t>
+          <t>6:21 - 2nd Half</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>4:59 - 2nd Half</t>
+          <t>3:33 - 2nd Half</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>6:39 - 2nd Half</t>
+          <t>6:21 - 2nd Half</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>4:59 - 2nd Half</t>
+          <t>3:33 - 2nd Half</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -3900,7 +3900,7 @@
         <v>3</v>
       </c>
       <c r="P42" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>6:39 - 2nd Half</t>
+          <t>6:21 - 2nd Half</t>
         </is>
       </c>
       <c r="H45" t="n">
@@ -4431,68 +4431,68 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Duke Miles</t>
+          <t>Amari Allen</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>ALA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>AUB@ALA</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>6:21 - 2nd Half</t>
         </is>
       </c>
       <c r="H49" t="n">
         <v>14</v>
       </c>
       <c r="I49" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J49" t="n">
         <v>4</v>
       </c>
       <c r="K49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L49" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O49" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P49" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="Q49" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R49" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -4513,68 +4513,68 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Amari Allen</t>
+          <t>Duke Miles</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>AUB@ALA</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>6:39 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H50" t="n">
+        <v>14</v>
+      </c>
+      <c r="I50" t="n">
         <v>13</v>
       </c>
-      <c r="I50" t="n">
+      <c r="J50" t="n">
+        <v>4</v>
+      </c>
+      <c r="K50" t="n">
+        <v>2</v>
+      </c>
+      <c r="L50" t="n">
+        <v>4</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>2</v>
+      </c>
+      <c r="O50" t="n">
+        <v>5</v>
+      </c>
+      <c r="P50" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>3</v>
+      </c>
+      <c r="R50" t="n">
         <v>10</v>
       </c>
-      <c r="J50" t="n">
-        <v>4</v>
-      </c>
-      <c r="K50" t="n">
-        <v>1</v>
-      </c>
-      <c r="L50" t="n">
-        <v>1</v>
-      </c>
-      <c r="M50" t="n">
-        <v>1</v>
-      </c>
-      <c r="N50" t="n">
-        <v>1</v>
-      </c>
-      <c r="O50" t="n">
-        <v>1</v>
-      </c>
-      <c r="P50" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>5</v>
-      </c>
-      <c r="R50" t="n">
-        <v>8</v>
-      </c>
       <c r="S50" t="n">
         <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51">
@@ -4692,14 +4692,14 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>4:59 - 2nd Half</t>
+          <t>3:33 - 2nd Half</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I52" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J52" t="n">
         <v>2</v>
@@ -4720,19 +4720,19 @@
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Q52" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R52" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="S52" t="n">
         <v>2</v>
       </c>
       <c r="T52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U52" t="n">
         <v>3</v>
@@ -4774,17 +4774,17 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>6:39 - 2nd Half</t>
+          <t>6:21 - 2nd Half</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I53" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K53" t="n">
         <v>1</v>
@@ -4802,13 +4802,13 @@
         <v>3</v>
       </c>
       <c r="P53" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q53" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R53" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="S53" t="n">
         <v>3</v>
@@ -4841,68 +4841,68 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Malachi Moreno</t>
+          <t>Jordan Pope</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>OU@TEX</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>3:33 - 2nd Half</t>
         </is>
       </c>
       <c r="H54" t="n">
         <v>13</v>
       </c>
       <c r="I54" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="J54" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L54" t="n">
         <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q54" t="n">
         <v>5</v>
       </c>
-      <c r="P54" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>3</v>
-      </c>
       <c r="R54" t="n">
+        <v>16</v>
+      </c>
+      <c r="S54" t="n">
         <v>5</v>
       </c>
-      <c r="S54" t="n">
-        <v>0</v>
-      </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Xaivian Lee</t>
+          <t>Malachi Moreno</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>FLA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -4945,46 +4945,46 @@
         <v>13</v>
       </c>
       <c r="I55" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J55" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K55" t="n">
+        <v>4</v>
+      </c>
+      <c r="L55" t="n">
+        <v>1</v>
+      </c>
+      <c r="M55" t="n">
+        <v>2</v>
+      </c>
+      <c r="N55" t="n">
+        <v>4</v>
+      </c>
+      <c r="O55" t="n">
         <v>5</v>
       </c>
-      <c r="L55" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" t="n">
-        <v>1</v>
-      </c>
-      <c r="O55" t="n">
-        <v>1</v>
-      </c>
       <c r="P55" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="Q55" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R55" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="S55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V55" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -5005,65 +5005,65 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Jordan Pope</t>
+          <t>Xaivian Lee</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>OU@TEX</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>4:59 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I56" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="J56" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K56" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P56" t="n">
         <v>31</v>
       </c>
       <c r="Q56" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R56" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T56" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="U56" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V56" t="n">
         <v>4</v>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>4:59 - 2nd Half</t>
+          <t>3:33 - 2nd Half</t>
         </is>
       </c>
       <c r="H59" t="n">
@@ -5279,7 +5279,7 @@
         <v>5</v>
       </c>
       <c r="K59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L59" t="n">
         <v>2</v>
@@ -5294,13 +5294,13 @@
         <v>2</v>
       </c>
       <c r="P59" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="Q59" t="n">
         <v>5</v>
       </c>
       <c r="R59" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S59" t="n">
         <v>1</v>
@@ -5430,17 +5430,17 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>4:59 - 2nd Half</t>
+          <t>3:33 - 2nd Half</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I61" t="n">
         <v>4</v>
       </c>
       <c r="J61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K61" t="n">
         <v>1</v>
@@ -5449,7 +5449,7 @@
         <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N61" t="n">
         <v>0</v>
@@ -5458,7 +5458,7 @@
         <v>3</v>
       </c>
       <c r="P61" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q61" t="n">
         <v>1</v>
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>6:39 - 2nd Half</t>
+          <t>6:21 - 2nd Half</t>
         </is>
       </c>
       <c r="H64" t="n">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>6:39 - 2nd Half</t>
+          <t>6:21 - 2nd Half</t>
         </is>
       </c>
       <c r="H70" t="n">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>6:39 - 2nd Half</t>
+          <t>6:21 - 2nd Half</t>
         </is>
       </c>
       <c r="H71" t="n">
@@ -6275,7 +6275,7 @@
         <v>3</v>
       </c>
       <c r="O71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P71" t="n">
         <v>29</v>
@@ -6332,11 +6332,11 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>6:39 - 2nd Half</t>
+          <t>6:21 - 2nd Half</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I72" t="n">
         <v>11</v>
@@ -6345,7 +6345,7 @@
         <v>2</v>
       </c>
       <c r="K72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" t="n">
         <v>1</v>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>4:59 - 2nd Half</t>
+          <t>3:33 - 2nd Half</t>
         </is>
       </c>
       <c r="H74" t="n">
@@ -6524,7 +6524,7 @@
         <v>2</v>
       </c>
       <c r="P74" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Q74" t="n">
         <v>3</v>
@@ -7972,7 +7972,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>6:39 - 2nd Half</t>
+          <t>6:21 - 2nd Half</t>
         </is>
       </c>
       <c r="H92" t="n">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>6:39 - 2nd Half</t>
+          <t>6:21 - 2nd Half</t>
         </is>
       </c>
       <c r="H100" t="n">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>4:59 - 2nd Half</t>
+          <t>3:33 - 2nd Half</t>
         </is>
       </c>
       <c r="H104" t="n">
@@ -9120,7 +9120,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>6:39 - 2nd Half</t>
+          <t>6:21 - 2nd Half</t>
         </is>
       </c>
       <c r="H106" t="n">
@@ -9679,47 +9679,47 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Sergej Macura</t>
+          <t>Nic Codie</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>MSST</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>OU@TEX</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>3:33 - 2nd Half</t>
         </is>
       </c>
       <c r="H113" t="n">
         <v>4</v>
       </c>
       <c r="I113" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J113" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K113" t="n">
         <v>0</v>
       </c>
       <c r="L113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
         <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P113" t="n">
         <v>18</v>
@@ -9728,7 +9728,7 @@
         <v>1</v>
       </c>
       <c r="R113" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -9737,10 +9737,10 @@
         <v>0</v>
       </c>
       <c r="U113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V113" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -9761,35 +9761,35 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>T.O. Barrett</t>
+          <t>Sergej Macura</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H114" t="n">
         <v>4</v>
       </c>
       <c r="I114" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J114" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K114" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L114" t="n">
         <v>1</v>
@@ -9801,25 +9801,25 @@
         <v>2</v>
       </c>
       <c r="O114" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P114" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="Q114" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R114" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
       </c>
       <c r="T114" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U114" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V114" t="n">
         <v>2</v>
@@ -9843,68 +9843,68 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Dylan James</t>
+          <t>T.O. Barrett</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H115" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I115" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M115" t="n">
         <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P115" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="Q115" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R115" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
       </c>
       <c r="T115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116">
@@ -9925,17 +9925,17 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Kezza Giffa</t>
+          <t>Dylan James</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -9953,7 +9953,7 @@
         <v>2</v>
       </c>
       <c r="K116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L116" t="n">
         <v>0</v>
@@ -9962,16 +9962,16 @@
         <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P116" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="Q116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R116" t="n">
         <v>4</v>
@@ -9980,13 +9980,13 @@
         <v>0</v>
       </c>
       <c r="T116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -10007,17 +10007,17 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Troy Henderson</t>
+          <t>Kezza Giffa</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -10029,13 +10029,13 @@
         <v>3</v>
       </c>
       <c r="I117" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L117" t="n">
         <v>0</v>
@@ -10044,31 +10044,31 @@
         <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P117" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="Q117" t="n">
         <v>1</v>
       </c>
       <c r="R117" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T117" t="n">
         <v>1</v>
       </c>
       <c r="U117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118">
@@ -10089,35 +10089,35 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Dayton Forsythe</t>
+          <t>Troy Henderson</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>OU</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>OU@TEX</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>4:59 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H118" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I118" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L118" t="n">
         <v>0</v>
@@ -10126,19 +10126,19 @@
         <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
       </c>
       <c r="P118" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="Q118" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R118" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S118" t="n">
         <v>1</v>
@@ -10253,22 +10253,22 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Nic Codie</t>
+          <t>Zach Day</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>OU@TEX</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>4:59 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H120" t="n">
@@ -10278,7 +10278,7 @@
         <v>0</v>
       </c>
       <c r="J120" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K120" t="n">
         <v>0</v>
@@ -10287,22 +10287,22 @@
         <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N120" t="n">
         <v>0</v>
       </c>
       <c r="O120" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P120" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="Q120" t="n">
         <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -10335,17 +10335,17 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Zach Day</t>
+          <t>Amaree Abram</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -10354,10 +10354,10 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J121" t="n">
         <v>1</v>
@@ -10366,10 +10366,10 @@
         <v>0</v>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N121" t="n">
         <v>0</v>
@@ -10378,13 +10378,13 @@
         <v>0</v>
       </c>
       <c r="P121" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Q121" t="n">
         <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -10393,10 +10393,10 @@
         <v>0</v>
       </c>
       <c r="U121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V121" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="122">
@@ -10417,17 +10417,17 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Amaree Abram</t>
+          <t>Corey Chest</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -10439,7 +10439,7 @@
         <v>1</v>
       </c>
       <c r="I122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J122" t="n">
         <v>1</v>
@@ -10448,7 +10448,7 @@
         <v>0</v>
       </c>
       <c r="L122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
         <v>0</v>
@@ -10460,13 +10460,13 @@
         <v>0</v>
       </c>
       <c r="P122" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q122" t="n">
         <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -10475,10 +10475,10 @@
         <v>0</v>
       </c>
       <c r="U122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V122" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -10499,29 +10499,29 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Corey Chest</t>
+          <t>Dayton Forsythe</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>OU</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>OU@TEX</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>3:33 - 2nd Half</t>
         </is>
       </c>
       <c r="H123" t="n">
         <v>1</v>
       </c>
       <c r="I123" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J123" t="n">
         <v>1</v>
@@ -10536,25 +10536,25 @@
         <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
       </c>
       <c r="P123" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="Q123" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U123" t="n">
         <v>0</v>
@@ -11088,7 +11088,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>6:39 - 2nd Half</t>
+          <t>6:21 - 2nd Half</t>
         </is>
       </c>
       <c r="H130" t="n">
@@ -11498,7 +11498,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>4:59 - 2nd Half</t>
+          <t>3:33 - 2nd Half</t>
         </is>
       </c>
       <c r="H135" t="n">
@@ -11580,7 +11580,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>6:39 - 2nd Half</t>
+          <t>6:21 - 2nd Half</t>
         </is>
       </c>
       <c r="H136" t="n">
@@ -11662,7 +11662,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>4:59 - 2nd Half</t>
+          <t>3:33 - 2nd Half</t>
         </is>
       </c>
       <c r="H137" t="n">
@@ -11990,7 +11990,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>4:59 - 2nd Half</t>
+          <t>3:33 - 2nd Half</t>
         </is>
       </c>
       <c r="H141" t="n">
@@ -12492,7 +12492,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C2" t="n">
         <v>5</v>
@@ -12527,27 +12527,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>The Backslashers</t>
+          <t>Bend Rimmers</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bend Rimmers</t>
+          <t>The Backslashers</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>74</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">

--- a/docs/Today_PoohPoints_SEC_ByOwner_2026-03-07.xlsx
+++ b/docs/Today_PoohPoints_SEC_ByOwner_2026-03-07.xlsx
@@ -577,38 +577,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Billy Richmond III</t>
+          <t>Matas Vokietaitis</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ARK</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>OU@TEX</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>1:56 - 2nd Half</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J2" t="n">
         <v>6</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>1</v>
@@ -617,28 +617,28 @@
         <v>2</v>
       </c>
       <c r="O2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P2" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q2" t="n">
         <v>5</v>
       </c>
-      <c r="P2" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>4</v>
-      </c>
       <c r="R2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -659,62 +659,62 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Labaron Philon Jr.</t>
+          <t>Billy Richmond III</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>ARK</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AUB@ALA</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>6:21 - 2nd Half</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H3" t="n">
         <v>18</v>
       </c>
       <c r="I3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K3" t="n">
         <v>4</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
         <v>2</v>
       </c>
       <c r="O3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P3" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="Q3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
         <v>2</v>
@@ -741,68 +741,68 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Matas Vokietaitis</t>
+          <t>Labaron Philon Jr.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>ALA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>OU@TEX</t>
+          <t>AUB@ALA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3:33 - 2nd Half</t>
+          <t>2:47 - 2nd Half</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I4" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>2</v>
       </c>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="R4" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>3:33 - 2nd Half</t>
+          <t>1:56 - 2nd Half</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1330,14 +1330,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3:33 - 2nd Half</t>
+          <t>1:56 - 2nd Half</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J11" t="n">
         <v>2</v>
@@ -1355,16 +1355,16 @@
         <v>3</v>
       </c>
       <c r="O11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1740,35 +1740,35 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>6:21 - 2nd Half</t>
+          <t>2:47 - 2nd Half</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I16" t="n">
         <v>6</v>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O16" t="n">
         <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="Q16" t="n">
         <v>3</v>
@@ -2150,11 +2150,11 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>3:33 - 2nd Half</t>
+          <t>1:56 - 2nd Half</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I21" t="n">
         <v>19</v>
@@ -2178,7 +2178,7 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Q21" t="n">
         <v>7</v>
@@ -2196,7 +2196,7 @@
         <v>2</v>
       </c>
       <c r="V21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -2560,17 +2560,17 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>6:21 - 2nd Half</t>
+          <t>2:47 - 2nd Half</t>
         </is>
       </c>
       <c r="H26" t="n">
         <v>17</v>
       </c>
       <c r="I26" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K26" t="n">
         <v>1</v>
@@ -2588,19 +2588,19 @@
         <v>2</v>
       </c>
       <c r="P26" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="Q26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R26" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="S26" t="n">
         <v>3</v>
       </c>
       <c r="T26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U26" t="n">
         <v>6</v>
@@ -2627,68 +2627,68 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Tyler Nickel</t>
+          <t>Keyshawn Hall</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>AUB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>AUB@ALA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>2:47 - 2nd Half</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I27" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J27" t="n">
+        <v>6</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>4</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1</v>
+      </c>
+      <c r="P27" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>4</v>
+      </c>
+      <c r="R27" t="n">
+        <v>8</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2</v>
+      </c>
+      <c r="T27" t="n">
         <v>5</v>
       </c>
-      <c r="K27" t="n">
-        <v>1</v>
-      </c>
-      <c r="L27" t="n">
-        <v>2</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>5</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>29</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>2</v>
-      </c>
-      <c r="R27" t="n">
-        <v>3</v>
-      </c>
-      <c r="S27" t="n">
-        <v>1</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2</v>
-      </c>
       <c r="U27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -2709,68 +2709,68 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Keyshawn Hall</t>
+          <t>Tyler Nickel</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AUB</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AUB@ALA</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>6:21 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H28" t="n">
+        <v>9</v>
+      </c>
+      <c r="I28" t="n">
         <v>7</v>
       </c>
-      <c r="I28" t="n">
-        <v>8</v>
-      </c>
       <c r="J28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K28" t="n">
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="Q28" t="n">
         <v>2</v>
       </c>
       <c r="R28" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>6:21 - 2nd Half</t>
+          <t>2:47 - 2nd Half</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>3:33 - 2nd Half</t>
+          <t>1:56 - 2nd Half</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>6:21 - 2nd Half</t>
+          <t>2:47 - 2nd Half</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -3857,68 +3857,68 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Jadon Jones</t>
+          <t>Myles Stute</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>OU</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>OU@TEX</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>3:33 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H42" t="n">
         <v>8</v>
       </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J42" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P42" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -3939,68 +3939,68 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Myles Stute</t>
+          <t>Jadon Jones</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>OU</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>OU@TEX</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>1:56 - 2nd Half</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I43" t="n">
+        <v>2</v>
+      </c>
+      <c r="J43" t="n">
         <v>6</v>
       </c>
-      <c r="J43" t="n">
-        <v>2</v>
-      </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P43" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="Q43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
         <v>3</v>
       </c>
       <c r="S43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
         <v>3</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -4021,35 +4021,35 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Jaylen Carey</t>
+          <t>Houston Mallette</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>ALA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>AUB@ALA</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>2:47 - 2nd Half</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -4064,19 +4064,19 @@
         <v>3</v>
       </c>
       <c r="P44" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -4103,35 +4103,35 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Houston Mallette</t>
+          <t>Jaylen Carey</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>AUB@ALA</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>6:21 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -4146,19 +4146,19 @@
         <v>3</v>
       </c>
       <c r="P45" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
@@ -4349,68 +4349,68 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Somtochukwu Cyril</t>
+          <t>Amari Allen</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>ALA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>AUB@ALA</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>2:47 - 2nd Half</t>
         </is>
       </c>
       <c r="H48" t="n">
         <v>18</v>
       </c>
       <c r="I48" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J48" t="n">
         <v>5</v>
       </c>
       <c r="K48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P48" t="n">
         <v>24</v>
       </c>
       <c r="Q48" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="R48" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -4431,56 +4431,56 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Amari Allen</t>
+          <t>Somtochukwu Cyril</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>AUB@ALA</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>6:21 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I49" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P49" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q49" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R49" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -4489,10 +4489,10 @@
         <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>3:33 - 2nd Half</t>
+          <t>1:56 - 2nd Half</t>
         </is>
       </c>
       <c r="H52" t="n">
@@ -4720,7 +4720,7 @@
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="Q52" t="n">
         <v>8</v>
@@ -4774,7 +4774,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>6:21 - 2nd Half</t>
+          <t>2:47 - 2nd Half</t>
         </is>
       </c>
       <c r="H53" t="n">
@@ -4799,10 +4799,10 @@
         <v>2</v>
       </c>
       <c r="O53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P53" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="Q53" t="n">
         <v>7</v>
@@ -4856,14 +4856,14 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>3:33 - 2nd Half</t>
+          <t>1:56 - 2nd Half</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I54" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J54" t="n">
         <v>4</v>
@@ -4884,19 +4884,19 @@
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q54" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R54" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T54" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="U54" t="n">
         <v>4</v>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>3:33 - 2nd Half</t>
+          <t>1:56 - 2nd Half</t>
         </is>
       </c>
       <c r="H59" t="n">
@@ -5294,7 +5294,7 @@
         <v>2</v>
       </c>
       <c r="P59" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="Q59" t="n">
         <v>5</v>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>3:33 - 2nd Half</t>
+          <t>1:56 - 2nd Half</t>
         </is>
       </c>
       <c r="H61" t="n">
@@ -5455,10 +5455,10 @@
         <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P61" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="Q61" t="n">
         <v>1</v>
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>6:21 - 2nd Half</t>
+          <t>2:47 - 2nd Half</t>
         </is>
       </c>
       <c r="H64" t="n">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>6:21 - 2nd Half</t>
+          <t>2:47 - 2nd Half</t>
         </is>
       </c>
       <c r="H70" t="n">
@@ -6196,7 +6196,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="Q70" t="n">
         <v>3</v>
@@ -6250,26 +6250,26 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>6:21 - 2nd Half</t>
+          <t>2:47 - 2nd Half</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I71" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L71" t="n">
         <v>4</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N71" t="n">
         <v>3</v>
@@ -6278,13 +6278,13 @@
         <v>2</v>
       </c>
       <c r="P71" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Q71" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R71" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="S71" t="n">
         <v>1</v>
@@ -6332,11 +6332,11 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>6:21 - 2nd Half</t>
+          <t>2:47 - 2nd Half</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I72" t="n">
         <v>11</v>
@@ -6360,19 +6360,19 @@
         <v>2</v>
       </c>
       <c r="P72" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="Q72" t="n">
         <v>4</v>
       </c>
       <c r="R72" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S72" t="n">
         <v>1</v>
       </c>
       <c r="T72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U72" t="n">
         <v>2</v>
@@ -6496,17 +6496,17 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>3:33 - 2nd Half</t>
+          <t>1:56 - 2nd Half</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I74" t="n">
         <v>10</v>
       </c>
       <c r="J74" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K74" t="n">
         <v>2</v>
@@ -6524,7 +6524,7 @@
         <v>2</v>
       </c>
       <c r="P74" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q74" t="n">
         <v>3</v>
@@ -7972,7 +7972,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>6:21 - 2nd Half</t>
+          <t>2:47 - 2nd Half</t>
         </is>
       </c>
       <c r="H92" t="n">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>6:21 - 2nd Half</t>
+          <t>2:47 - 2nd Half</t>
         </is>
       </c>
       <c r="H100" t="n">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>3:33 - 2nd Half</t>
+          <t>1:56 - 2nd Half</t>
         </is>
       </c>
       <c r="H104" t="n">
@@ -9120,7 +9120,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>6:21 - 2nd Half</t>
+          <t>2:47 - 2nd Half</t>
         </is>
       </c>
       <c r="H106" t="n">
@@ -9269,62 +9269,62 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Bishop Boswell</t>
+          <t>Nic Codie</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>OU@TEX</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>1:56 - 2nd Half</t>
         </is>
       </c>
       <c r="H108" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I108" t="n">
+        <v>2</v>
+      </c>
+      <c r="J108" t="n">
         <v>5</v>
       </c>
-      <c r="J108" t="n">
-        <v>0</v>
-      </c>
       <c r="K108" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L108" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
         <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P108" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="Q108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R108" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="S108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T108" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U108" t="n">
         <v>0</v>
@@ -9351,17 +9351,17 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Eli Ellis</t>
+          <t>Bishop Boswell</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -9373,37 +9373,37 @@
         <v>4</v>
       </c>
       <c r="I109" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J109" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K109" t="n">
+        <v>4</v>
+      </c>
+      <c r="L109" t="n">
+        <v>2</v>
+      </c>
+      <c r="M109" t="n">
+        <v>0</v>
+      </c>
+      <c r="N109" t="n">
+        <v>2</v>
+      </c>
+      <c r="O109" t="n">
         <v>5</v>
       </c>
-      <c r="L109" t="n">
-        <v>1</v>
-      </c>
-      <c r="M109" t="n">
-        <v>0</v>
-      </c>
-      <c r="N109" t="n">
-        <v>1</v>
-      </c>
-      <c r="O109" t="n">
-        <v>2</v>
-      </c>
       <c r="P109" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R109" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="S109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T109" t="n">
         <v>2</v>
@@ -9433,7 +9433,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Elijah Strong</t>
+          <t>Eli Ellis</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -9455,40 +9455,40 @@
         <v>4</v>
       </c>
       <c r="I110" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J110" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K110" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O110" t="n">
         <v>2</v>
       </c>
       <c r="P110" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="Q110" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="S110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T110" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U110" t="n">
         <v>0</v>
@@ -9515,17 +9515,17 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Ethan Burg</t>
+          <t>Elijah Strong</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -9537,46 +9537,46 @@
         <v>4</v>
       </c>
       <c r="I111" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L111" t="n">
         <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N111" t="n">
         <v>0</v>
       </c>
       <c r="O111" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P111" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R111" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="S111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T111" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U111" t="n">
         <v>0</v>
       </c>
       <c r="V111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -9597,17 +9597,17 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Jordan Ross</t>
+          <t>Ethan Burg</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -9619,13 +9619,13 @@
         <v>4</v>
       </c>
       <c r="I112" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
       </c>
       <c r="K112" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L112" t="n">
         <v>0</v>
@@ -9634,31 +9634,31 @@
         <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P112" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="Q112" t="n">
         <v>2</v>
       </c>
       <c r="R112" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T112" t="n">
         <v>1</v>
       </c>
       <c r="U112" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V112" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
@@ -9679,35 +9679,35 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Nic Codie</t>
+          <t>Jordan Ross</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>OU@TEX</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>3:33 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H113" t="n">
         <v>4</v>
       </c>
       <c r="I113" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J113" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L113" t="n">
         <v>0</v>
@@ -9716,31 +9716,31 @@
         <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O113" t="n">
         <v>2</v>
       </c>
       <c r="P113" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="Q113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R113" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U113" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V113" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>3:33 - 2nd Half</t>
+          <t>1:56 - 2nd Half</t>
         </is>
       </c>
       <c r="H123" t="n">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>6:21 - 2nd Half</t>
+          <t>2:47 - 2nd Half</t>
         </is>
       </c>
       <c r="H130" t="n">
@@ -11498,7 +11498,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>3:33 - 2nd Half</t>
+          <t>1:56 - 2nd Half</t>
         </is>
       </c>
       <c r="H135" t="n">
@@ -11580,7 +11580,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>6:21 - 2nd Half</t>
+          <t>2:47 - 2nd Half</t>
         </is>
       </c>
       <c r="H136" t="n">
@@ -11662,7 +11662,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>3:33 - 2nd Half</t>
+          <t>1:56 - 2nd Half</t>
         </is>
       </c>
       <c r="H137" t="n">
@@ -11990,7 +11990,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>3:33 - 2nd Half</t>
+          <t>1:56 - 2nd Half</t>
         </is>
       </c>
       <c r="H141" t="n">
@@ -12505,7 +12505,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="C3" t="n">
         <v>5</v>
@@ -12531,7 +12531,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C5" t="n">
         <v>4</v>
@@ -12544,7 +12544,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C6" t="n">
         <v>5</v>
@@ -12553,27 +12553,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Boozers Losers</t>
+          <t>Hilton Heads</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Hilton Heads</t>
+          <t>Boozers Losers</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Today_PoohPoints_SEC_ByOwner_2026-03-07.xlsx
+++ b/docs/Today_PoohPoints_SEC_ByOwner_2026-03-07.xlsx
@@ -592,7 +592,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1:56 - 2nd Half</t>
+          <t>0:15 - 2nd Half</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -620,7 +620,7 @@
         <v>4</v>
       </c>
       <c r="P2" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Q2" t="n">
         <v>5</v>
@@ -756,14 +756,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2:47 - 2nd Half</t>
+          <t>1:53 - 2nd Half</t>
         </is>
       </c>
       <c r="H4" t="n">
         <v>16</v>
       </c>
       <c r="I4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -799,10 +799,10 @@
         <v>7</v>
       </c>
       <c r="U4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -1151,12 +1151,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Derrion Reid</t>
+          <t>Tramon Mark</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>OU</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1166,47 +1166,47 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1:56 - 2nd Half</t>
+          <t>0:15 - 2nd Half</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="J9" t="n">
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P9" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U9" t="n">
         <v>6</v>
@@ -1233,41 +1233,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Marcus Hill</t>
+          <t>Derrion Reid</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TA&amp;M</t>
+          <t>OU</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>TA&amp;M@LSU</t>
+          <t>OU@TEX</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Final/3OT</t>
+          <t>0:15 - 2nd Half</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
         <v>2</v>
@@ -1276,25 +1276,25 @@
         <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -1315,68 +1315,68 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Tramon Mark</t>
+          <t>Marcus Hill</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>TA&amp;M</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>OU@TEX</t>
+          <t>TA&amp;M@LSU</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1:56 - 2nd Half</t>
+          <t>Final/3OT</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I11" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2:47 - 2nd Half</t>
+          <t>1:53 - 2nd Half</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1:56 - 2nd Half</t>
+          <t>0:15 - 2nd Half</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -2175,7 +2175,7 @@
         <v>1</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P21" t="n">
         <v>26</v>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2:47 - 2nd Half</t>
+          <t>1:53 - 2nd Half</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2:47 - 2nd Half</t>
+          <t>1:53 - 2nd Half</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -2670,7 +2670,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q27" t="n">
         <v>4</v>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2:47 - 2nd Half</t>
+          <t>1:53 - 2nd Half</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1:56 - 2nd Half</t>
+          <t>0:15 - 2nd Half</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2:47 - 2nd Half</t>
+          <t>1:53 - 2nd Half</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -3244,7 +3244,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -3857,68 +3857,68 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Myles Stute</t>
+          <t>Jadon Jones</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>OU</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>OU@TEX</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>0:15 - 2nd Half</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I42" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J42" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O42" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P42" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="Q42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>3</v>
       </c>
       <c r="S42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
         <v>3</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -3939,68 +3939,68 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Jadon Jones</t>
+          <t>Myles Stute</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>OU</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>OU@TEX</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1:56 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J43" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P43" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R43" t="n">
         <v>3</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T43" t="n">
         <v>3</v>
       </c>
       <c r="U43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2:47 - 2nd Half</t>
+          <t>1:53 - 2nd Half</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -4061,10 +4061,10 @@
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P44" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2:47 - 2nd Half</t>
+          <t>1:53 - 2nd Half</t>
         </is>
       </c>
       <c r="H48" t="n">
@@ -4595,68 +4595,68 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Mike Nwoko</t>
+          <t>Xzayvier Brown</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>LSU</t>
+          <t>OU</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>TA&amp;M@LSU</t>
+          <t>OU@TEX</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Final/3OT</t>
+          <t>0:15 - 2nd Half</t>
         </is>
       </c>
       <c r="H51" t="n">
+        <v>22</v>
+      </c>
+      <c r="I51" t="n">
         <v>21</v>
       </c>
-      <c r="I51" t="n">
+      <c r="J51" t="n">
+        <v>2</v>
+      </c>
+      <c r="K51" t="n">
+        <v>3</v>
+      </c>
+      <c r="L51" t="n">
+        <v>4</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>8</v>
+      </c>
+      <c r="R51" t="n">
         <v>16</v>
       </c>
-      <c r="J51" t="n">
-        <v>13</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>1</v>
-      </c>
-      <c r="N51" t="n">
-        <v>3</v>
-      </c>
-      <c r="O51" t="n">
-        <v>5</v>
-      </c>
-      <c r="P51" t="n">
-        <v>31</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>2</v>
-      </c>
-      <c r="R51" t="n">
-        <v>6</v>
-      </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U51" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="V51" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -4677,68 +4677,68 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Xzayvier Brown</t>
+          <t>Mike Nwoko</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>OU</t>
+          <t>LSU</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>OU@TEX</t>
+          <t>TA&amp;M@LSU</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>1:56 - 2nd Half</t>
+          <t>Final/3OT</t>
         </is>
       </c>
       <c r="H52" t="n">
         <v>21</v>
       </c>
       <c r="I52" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="K52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P52" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q52" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="R52" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="S52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="V52" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="53">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2:47 - 2nd Half</t>
+          <t>1:53 - 2nd Half</t>
         </is>
       </c>
       <c r="H53" t="n">
@@ -4802,7 +4802,7 @@
         <v>4</v>
       </c>
       <c r="P53" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Q53" t="n">
         <v>7</v>
@@ -4856,11 +4856,11 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>1:56 - 2nd Half</t>
+          <t>0:15 - 2nd Half</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I54" t="n">
         <v>22</v>
@@ -4884,19 +4884,19 @@
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q54" t="n">
         <v>6</v>
       </c>
       <c r="R54" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="S54" t="n">
         <v>6</v>
       </c>
       <c r="T54" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="U54" t="n">
         <v>4</v>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>1:56 - 2nd Half</t>
+          <t>0:15 - 2nd Half</t>
         </is>
       </c>
       <c r="H59" t="n">
@@ -5294,7 +5294,7 @@
         <v>2</v>
       </c>
       <c r="P59" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q59" t="n">
         <v>5</v>
@@ -5430,14 +5430,14 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>1:56 - 2nd Half</t>
+          <t>0:15 - 2nd Half</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I61" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J61" t="n">
         <v>2</v>
@@ -5458,13 +5458,13 @@
         <v>4</v>
       </c>
       <c r="P61" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2:47 - 2nd Half</t>
+          <t>1:53 - 2nd Half</t>
         </is>
       </c>
       <c r="H64" t="n">
@@ -5704,7 +5704,7 @@
         <v>2</v>
       </c>
       <c r="P64" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q64" t="n">
         <v>4</v>
@@ -6071,68 +6071,68 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Mike Sharavjamts</t>
+          <t>Tahaad Pettiford</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>AUB</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>AUB@ALA</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>1:53 - 2nd Half</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I69" t="n">
+        <v>17</v>
+      </c>
+      <c r="J69" t="n">
+        <v>2</v>
+      </c>
+      <c r="K69" t="n">
+        <v>4</v>
+      </c>
+      <c r="L69" t="n">
+        <v>4</v>
+      </c>
+      <c r="M69" t="n">
+        <v>1</v>
+      </c>
+      <c r="N69" t="n">
+        <v>3</v>
+      </c>
+      <c r="O69" t="n">
+        <v>2</v>
+      </c>
+      <c r="P69" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q69" t="n">
         <v>7</v>
       </c>
-      <c r="J69" t="n">
-        <v>9</v>
-      </c>
-      <c r="K69" t="n">
-        <v>2</v>
-      </c>
-      <c r="L69" t="n">
-        <v>1</v>
-      </c>
-      <c r="M69" t="n">
-        <v>1</v>
-      </c>
-      <c r="N69" t="n">
-        <v>1</v>
-      </c>
-      <c r="O69" t="n">
-        <v>2</v>
-      </c>
-      <c r="P69" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>3</v>
-      </c>
       <c r="R69" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="S69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70">
@@ -6153,68 +6153,68 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Aiden Sherrell</t>
+          <t>Mike Sharavjamts</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>AUB@ALA</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2:47 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I70" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J70" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N70" t="n">
         <v>1</v>
       </c>
       <c r="O70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P70" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="Q70" t="n">
         <v>3</v>
       </c>
       <c r="R70" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
       </c>
       <c r="T70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U70" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V70" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
@@ -6235,12 +6235,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Tahaad Pettiford</t>
+          <t>Aiden Sherrell</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AUB</t>
+          <t>ALA</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -6250,53 +6250,53 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2:47 - 2nd Half</t>
+          <t>1:53 - 2nd Half</t>
         </is>
       </c>
       <c r="H71" t="n">
         <v>12</v>
       </c>
       <c r="I71" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J71" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K71" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L71" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N71" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P71" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="Q71" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R71" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="S71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T71" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U71" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V71" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="72">
@@ -6317,50 +6317,50 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Elyjah Freeman</t>
+          <t>Tae Davis</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AUB</t>
+          <t>OU</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>AUB@ALA</t>
+          <t>OU@TEX</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2:47 - 2nd Half</t>
+          <t>0:15 - 2nd Half</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I72" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J72" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L72" t="n">
         <v>1</v>
       </c>
       <c r="M72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P72" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="Q72" t="n">
         <v>4</v>
@@ -6369,16 +6369,16 @@
         <v>9</v>
       </c>
       <c r="S72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T72" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U72" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V72" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="73">
@@ -6399,38 +6399,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Jalen Washington</t>
+          <t>Elyjah Freeman</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>AUB</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>AUB@ALA</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>1:53 - 2nd Half</t>
         </is>
       </c>
       <c r="H73" t="n">
         <v>10</v>
       </c>
       <c r="I73" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J73" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M73" t="n">
         <v>1</v>
@@ -6442,22 +6442,22 @@
         <v>2</v>
       </c>
       <c r="P73" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="Q73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R73" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="S73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T73" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V73" t="n">
         <v>2</v>
@@ -6481,68 +6481,68 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Tae Davis</t>
+          <t>Jalen Washington</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>OU</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>OU@TEX</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>1:56 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H74" t="n">
         <v>10</v>
       </c>
       <c r="I74" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J74" t="n">
         <v>8</v>
       </c>
       <c r="K74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O74" t="n">
         <v>2</v>
       </c>
       <c r="P74" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Q74" t="n">
         <v>3</v>
       </c>
       <c r="R74" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
       </c>
       <c r="T74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U74" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V74" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -7972,17 +7972,17 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2:47 - 2nd Half</t>
+          <t>1:53 - 2nd Half</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I92" t="n">
         <v>6</v>
       </c>
       <c r="J92" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K92" t="n">
         <v>1</v>
@@ -8000,7 +8000,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q92" t="n">
         <v>3</v>
@@ -8628,7 +8628,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2:47 - 2nd Half</t>
+          <t>1:53 - 2nd Half</t>
         </is>
       </c>
       <c r="H100" t="n">
@@ -8656,7 +8656,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q100" t="n">
         <v>2</v>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>1:56 - 2nd Half</t>
+          <t>0:15 - 2nd Half</t>
         </is>
       </c>
       <c r="H104" t="n">
@@ -9120,7 +9120,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2:47 - 2nd Half</t>
+          <t>1:53 - 2nd Half</t>
         </is>
       </c>
       <c r="H106" t="n">
@@ -9284,7 +9284,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>1:56 - 2nd Half</t>
+          <t>0:15 - 2nd Half</t>
         </is>
       </c>
       <c r="H108" t="n">
@@ -9312,7 +9312,7 @@
         <v>2</v>
       </c>
       <c r="P108" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Q108" t="n">
         <v>1</v>
@@ -10253,32 +10253,32 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Zach Day</t>
+          <t>Noah Williamson</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>ALA</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>AUB@ALA</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>1:53 - 2nd Half</t>
         </is>
       </c>
       <c r="H120" t="n">
         <v>2</v>
       </c>
       <c r="I120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K120" t="n">
         <v>0</v>
@@ -10287,28 +10287,28 @@
         <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P120" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
       </c>
       <c r="T120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U120" t="n">
         <v>0</v>
@@ -10335,17 +10335,17 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Amaree Abram</t>
+          <t>Zach Day</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>TENN</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -10354,10 +10354,10 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J121" t="n">
         <v>1</v>
@@ -10366,10 +10366,10 @@
         <v>0</v>
       </c>
       <c r="L121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N121" t="n">
         <v>0</v>
@@ -10378,13 +10378,13 @@
         <v>0</v>
       </c>
       <c r="P121" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Q121" t="n">
         <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -10393,10 +10393,10 @@
         <v>0</v>
       </c>
       <c r="U121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V121" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -10417,17 +10417,17 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Corey Chest</t>
+          <t>Amaree Abram</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>TENN</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -10439,7 +10439,7 @@
         <v>1</v>
       </c>
       <c r="I122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J122" t="n">
         <v>1</v>
@@ -10448,7 +10448,7 @@
         <v>0</v>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M122" t="n">
         <v>0</v>
@@ -10460,13 +10460,13 @@
         <v>0</v>
       </c>
       <c r="P122" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q122" t="n">
         <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -10475,10 +10475,10 @@
         <v>0</v>
       </c>
       <c r="U122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V122" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="123">
@@ -10499,29 +10499,29 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Dayton Forsythe</t>
+          <t>Corey Chest</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>OU</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>OU@TEX</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>1:56 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H123" t="n">
         <v>1</v>
       </c>
       <c r="I123" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J123" t="n">
         <v>1</v>
@@ -10536,25 +10536,25 @@
         <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
       </c>
       <c r="P123" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="Q123" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U123" t="n">
         <v>0</v>
@@ -11088,7 +11088,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2:47 - 2nd Half</t>
+          <t>1:53 - 2nd Half</t>
         </is>
       </c>
       <c r="H130" t="n">
@@ -11155,35 +11155,35 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Isaiah Sealy</t>
+          <t>Dayton Forsythe</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>ARK</t>
+          <t>OU</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>OU@TEX</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>0:15 - 2nd Half</t>
         </is>
       </c>
       <c r="H131" t="n">
         <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L131" t="n">
         <v>0</v>
@@ -11192,25 +11192,25 @@
         <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P131" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="Q131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R131" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U131" t="n">
         <v>0</v>
@@ -11237,22 +11237,22 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Jayden Leverett</t>
+          <t>Isaiah Sealy</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>ARK</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H132" t="n">
@@ -11262,10 +11262,10 @@
         <v>0</v>
       </c>
       <c r="J132" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L132" t="n">
         <v>0</v>
@@ -11274,19 +11274,19 @@
         <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O132" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P132" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q132" t="n">
         <v>0</v>
       </c>
       <c r="R132" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -11319,17 +11319,17 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Jordan Butler</t>
+          <t>Jayden Leverett</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -11344,7 +11344,7 @@
         <v>0</v>
       </c>
       <c r="J133" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K133" t="n">
         <v>0</v>
@@ -11359,16 +11359,16 @@
         <v>0</v>
       </c>
       <c r="O133" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P133" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q133" t="n">
         <v>0</v>
       </c>
       <c r="R133" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -11401,17 +11401,17 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Justin Bailey</t>
+          <t>Jordan Butler</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -11432,19 +11432,19 @@
         <v>0</v>
       </c>
       <c r="L134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M134" t="n">
         <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P134" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q134" t="n">
         <v>0</v>
@@ -11483,22 +11483,22 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Kai Rogers</t>
+          <t>Justin Bailey</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>OU</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>OU@TEX</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>1:56 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H135" t="n">
@@ -11508,31 +11508,31 @@
         <v>0</v>
       </c>
       <c r="J135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K135" t="n">
         <v>0</v>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M135" t="n">
         <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O135" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P135" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q135" t="n">
         <v>0</v>
       </c>
       <c r="R135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -11565,22 +11565,22 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Noah Williamson</t>
+          <t>Kai Rogers</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>OU</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>AUB@ALA</t>
+          <t>OU@TEX</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2:47 - 2nd Half</t>
+          <t>0:15 - 2nd Half</t>
         </is>
       </c>
       <c r="H136" t="n">
@@ -11590,7 +11590,7 @@
         <v>0</v>
       </c>
       <c r="J136" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K136" t="n">
         <v>0</v>
@@ -11602,13 +11602,13 @@
         <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O136" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P136" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q136" t="n">
         <v>0</v>
@@ -11620,7 +11620,7 @@
         <v>0</v>
       </c>
       <c r="T136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U136" t="n">
         <v>0</v>
@@ -11662,7 +11662,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>1:56 - 2nd Half</t>
+          <t>0:15 - 2nd Half</t>
         </is>
       </c>
       <c r="H137" t="n">
@@ -11990,7 +11990,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>1:56 - 2nd Half</t>
+          <t>0:15 - 2nd Half</t>
         </is>
       </c>
       <c r="H141" t="n">
@@ -12492,7 +12492,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C2" t="n">
         <v>5</v>
@@ -12505,7 +12505,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C3" t="n">
         <v>5</v>

--- a/docs/Today_PoohPoints_SEC_ByOwner_2026-03-07.xlsx
+++ b/docs/Today_PoohPoints_SEC_ByOwner_2026-03-07.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V146"/>
+  <dimension ref="A1:V147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -592,7 +592,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0:15 - 2nd Half</t>
+          <t>End of 2nd Half</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -756,7 +756,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1:53 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -1166,14 +1166,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0:15 - 2nd Half</t>
+          <t>End of 2nd Half</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J9" t="n">
         <v>2</v>
@@ -1209,10 +1209,10 @@
         <v>4</v>
       </c>
       <c r="U9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0:15 - 2nd Half</t>
+          <t>End of 2nd Half</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1740,18 +1740,18 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1:53 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H16" t="n">
+        <v>11</v>
+      </c>
+      <c r="I16" t="n">
         <v>8</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>6</v>
       </c>
-      <c r="J16" t="n">
-        <v>5</v>
-      </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
@@ -1765,10 +1765,10 @@
         <v>3</v>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P16" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q16" t="n">
         <v>3</v>
@@ -1783,10 +1783,10 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0:15 - 2nd Half</t>
+          <t>End of 2nd Half</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1:53 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1:53 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -2670,7 +2670,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="Q27" t="n">
         <v>4</v>
@@ -3052,14 +3052,14 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1:53 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H32" t="n">
         <v>7</v>
       </c>
       <c r="I32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J32" t="n">
         <v>1</v>
@@ -3080,7 +3080,7 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q32" t="n">
         <v>2</v>
@@ -3095,10 +3095,10 @@
         <v>2</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0:15 - 2nd Half</t>
+          <t>End of 2nd Half</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -3216,11 +3216,11 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1:53 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I34" t="n">
         <v>1</v>
@@ -3229,7 +3229,7 @@
         <v>2</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -3244,7 +3244,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -3872,7 +3872,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0:15 - 2nd Half</t>
+          <t>End of 2nd Half</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -4036,20 +4036,20 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1:53 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -4064,13 +4064,13 @@
         <v>4</v>
       </c>
       <c r="P44" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1:53 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H48" t="n">
@@ -4595,68 +4595,68 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Xzayvier Brown</t>
+          <t>Kevin Overton</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>OU</t>
+          <t>AUB</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>OU@TEX</t>
+          <t>AUB@ALA</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>0:15 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H51" t="n">
         <v>22</v>
       </c>
       <c r="I51" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L51" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P51" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q51" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R51" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S51" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T51" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -4759,68 +4759,68 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Kevin Overton</t>
+          <t>Xzayvier Brown</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AUB</t>
+          <t>OU</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>AUB@ALA</t>
+          <t>OU@TEX</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>1:53 - 2nd Half</t>
+          <t>End of 2nd Half</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I53" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P53" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="Q53" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R53" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="S53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T53" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="U53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -4856,17 +4856,17 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>0:15 - 2nd Half</t>
+          <t>End of 2nd Half</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I54" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J54" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K54" t="n">
         <v>2</v>
@@ -4884,25 +4884,25 @@
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q54" t="n">
         <v>6</v>
       </c>
       <c r="R54" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="S54" t="n">
         <v>6</v>
       </c>
       <c r="T54" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U54" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="V54" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>0:15 - 2nd Half</t>
+          <t>End of 2nd Half</t>
         </is>
       </c>
       <c r="H59" t="n">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>0:15 - 2nd Half</t>
+          <t>End of 2nd Half</t>
         </is>
       </c>
       <c r="H61" t="n">
@@ -5458,7 +5458,7 @@
         <v>4</v>
       </c>
       <c r="P61" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q61" t="n">
         <v>2</v>
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>1:53 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H64" t="n">
@@ -5704,7 +5704,7 @@
         <v>2</v>
       </c>
       <c r="P64" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q64" t="n">
         <v>4</v>
@@ -6086,14 +6086,14 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>1:53 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I69" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J69" t="n">
         <v>2</v>
@@ -6114,7 +6114,7 @@
         <v>2</v>
       </c>
       <c r="P69" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="Q69" t="n">
         <v>7</v>
@@ -6129,10 +6129,10 @@
         <v>3</v>
       </c>
       <c r="U69" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V69" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>1:53 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H71" t="n">
@@ -6332,14 +6332,14 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>0:15 - 2nd Half</t>
+          <t>End of 2nd Half</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I72" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J72" t="n">
         <v>8</v>
@@ -6375,10 +6375,10 @@
         <v>1</v>
       </c>
       <c r="U72" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="V72" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="73">
@@ -6414,11 +6414,11 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>1:53 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I73" t="n">
         <v>11</v>
@@ -6427,7 +6427,7 @@
         <v>2</v>
       </c>
       <c r="K73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L73" t="n">
         <v>1</v>
@@ -6439,10 +6439,10 @@
         <v>1</v>
       </c>
       <c r="O73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P73" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q73" t="n">
         <v>4</v>
@@ -7465,17 +7465,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Ja'Borri McGhee</t>
+          <t>London Jemison</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>MSST</t>
+          <t>ALA</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>AUB@ALA</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -7484,19 +7484,19 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I86" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J86" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
@@ -7505,28 +7505,28 @@
         <v>1</v>
       </c>
       <c r="O86" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P86" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="Q86" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="R86" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="S86" t="n">
         <v>1</v>
       </c>
       <c r="T86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V86" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
@@ -7547,65 +7547,65 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Ali Dibba</t>
+          <t>Ja'Borri McGhee</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>TA&amp;M</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>TA&amp;M@LSU</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Final/3OT</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H87" t="n">
+        <v>15</v>
+      </c>
+      <c r="I87" t="n">
+        <v>20</v>
+      </c>
+      <c r="J87" t="n">
+        <v>1</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="n">
+        <v>1</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="n">
+        <v>1</v>
+      </c>
+      <c r="O87" t="n">
+        <v>4</v>
+      </c>
+      <c r="P87" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>8</v>
+      </c>
+      <c r="R87" t="n">
         <v>13</v>
       </c>
-      <c r="I87" t="n">
-        <v>12</v>
-      </c>
-      <c r="J87" t="n">
-        <v>1</v>
-      </c>
-      <c r="K87" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" t="n">
-        <v>5</v>
-      </c>
-      <c r="M87" t="n">
-        <v>0</v>
-      </c>
-      <c r="N87" t="n">
-        <v>0</v>
-      </c>
-      <c r="O87" t="n">
-        <v>1</v>
-      </c>
-      <c r="P87" t="n">
-        <v>37</v>
-      </c>
-      <c r="Q87" t="n">
-        <v>5</v>
-      </c>
-      <c r="R87" t="n">
-        <v>8</v>
-      </c>
       <c r="S87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U87" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V87" t="n">
         <v>4</v>
@@ -7629,68 +7629,68 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Jamarion Davis-Fleming</t>
+          <t>Ali Dibba</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>MSST</t>
+          <t>TA&amp;M</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>TA&amp;M@LSU</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/3OT</t>
         </is>
       </c>
       <c r="H88" t="n">
         <v>13</v>
       </c>
       <c r="I88" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J88" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
         <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P88" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="Q88" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R88" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
       </c>
       <c r="T88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U88" t="n">
         <v>2</v>
       </c>
       <c r="V88" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="89">
@@ -7711,17 +7711,17 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Nordin Kapic</t>
+          <t>Jamarion Davis-Fleming</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>MSST</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -7733,13 +7733,13 @@
         <v>13</v>
       </c>
       <c r="I89" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J89" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L89" t="n">
         <v>0</v>
@@ -7748,25 +7748,25 @@
         <v>1</v>
       </c>
       <c r="N89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P89" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Q89" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R89" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="S89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T89" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U89" t="n">
         <v>2</v>
@@ -7793,68 +7793,68 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Trent Pierce</t>
+          <t>Nordin Kapic</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H90" t="n">
+        <v>13</v>
+      </c>
+      <c r="I90" t="n">
         <v>12</v>
       </c>
-      <c r="I90" t="n">
-        <v>13</v>
-      </c>
       <c r="J90" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O90" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P90" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="Q90" t="n">
+        <v>4</v>
+      </c>
+      <c r="R90" t="n">
+        <v>7</v>
+      </c>
+      <c r="S90" t="n">
+        <v>2</v>
+      </c>
+      <c r="T90" t="n">
         <v>5</v>
       </c>
-      <c r="R90" t="n">
-        <v>11</v>
-      </c>
-      <c r="S90" t="n">
-        <v>3</v>
-      </c>
-      <c r="T90" t="n">
-        <v>7</v>
-      </c>
       <c r="U90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
@@ -7875,68 +7875,68 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Andrija Jelavic</t>
+          <t>Trent Pierce</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H91" t="n">
+        <v>12</v>
+      </c>
+      <c r="I91" t="n">
+        <v>13</v>
+      </c>
+      <c r="J91" t="n">
+        <v>6</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="n">
+        <v>1</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="n">
+        <v>1</v>
+      </c>
+      <c r="O91" t="n">
+        <v>3</v>
+      </c>
+      <c r="P91" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>5</v>
+      </c>
+      <c r="R91" t="n">
         <v>11</v>
       </c>
-      <c r="I91" t="n">
+      <c r="S91" t="n">
+        <v>3</v>
+      </c>
+      <c r="T91" t="n">
         <v>7</v>
       </c>
-      <c r="J91" t="n">
-        <v>4</v>
-      </c>
-      <c r="K91" t="n">
-        <v>2</v>
-      </c>
-      <c r="L91" t="n">
-        <v>1</v>
-      </c>
-      <c r="M91" t="n">
-        <v>1</v>
-      </c>
-      <c r="N91" t="n">
-        <v>0</v>
-      </c>
-      <c r="O91" t="n">
-        <v>2</v>
-      </c>
-      <c r="P91" t="n">
-        <v>21</v>
-      </c>
-      <c r="Q91" t="n">
-        <v>3</v>
-      </c>
-      <c r="R91" t="n">
-        <v>7</v>
-      </c>
-      <c r="S91" t="n">
-        <v>1</v>
-      </c>
-      <c r="T91" t="n">
-        <v>3</v>
-      </c>
       <c r="U91" t="n">
         <v>0</v>
       </c>
       <c r="V91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -7957,62 +7957,62 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>London Jemison</t>
+          <t>Andrija Jelavic</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>ALA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>AUB@ALA</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>1:53 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H92" t="n">
         <v>11</v>
       </c>
       <c r="I92" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J92" t="n">
         <v>4</v>
       </c>
       <c r="K92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P92" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="Q92" t="n">
         <v>3</v>
       </c>
       <c r="R92" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T92" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U92" t="n">
         <v>0</v>
@@ -8628,7 +8628,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>1:53 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H100" t="n">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>0:15 - 2nd Half</t>
+          <t>End of 2nd Half</t>
         </is>
       </c>
       <c r="H104" t="n">
@@ -9120,7 +9120,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>1:53 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H106" t="n">
@@ -9284,7 +9284,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>0:15 - 2nd Half</t>
+          <t>End of 2nd Half</t>
         </is>
       </c>
       <c r="H108" t="n">
@@ -9309,7 +9309,7 @@
         <v>0</v>
       </c>
       <c r="O108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P108" t="n">
         <v>21</v>
@@ -10268,7 +10268,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>1:53 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H120" t="n">
@@ -10293,10 +10293,10 @@
         <v>1</v>
       </c>
       <c r="O120" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P120" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q120" t="n">
         <v>1</v>
@@ -11088,7 +11088,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>1:53 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H130" t="n">
@@ -11170,7 +11170,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>0:15 - 2nd Half</t>
+          <t>End of 2nd Half</t>
         </is>
       </c>
       <c r="H131" t="n">
@@ -11580,7 +11580,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>0:15 - 2nd Half</t>
+          <t>End of 2nd Half</t>
         </is>
       </c>
       <c r="H136" t="n">
@@ -11647,22 +11647,22 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Simeon Wilcher</t>
+          <t>Preston Murphy Jr.</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>ALA</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>OU@TEX</t>
+          <t>AUB@ALA</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>0:15 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H137" t="n">
@@ -11675,7 +11675,7 @@
         <v>0</v>
       </c>
       <c r="K137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L137" t="n">
         <v>0</v>
@@ -11687,22 +11687,22 @@
         <v>0</v>
       </c>
       <c r="O137" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P137" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Q137" t="n">
         <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
       </c>
       <c r="T137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U137" t="n">
         <v>0</v>
@@ -11729,22 +11729,22 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Trent Burns</t>
+          <t>Simeon Wilcher</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>MIZ</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>ARK@MIZ</t>
+          <t>OU@TEX</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Final/OT</t>
+          <t>End of 2nd Half</t>
         </is>
       </c>
       <c r="H138" t="n">
@@ -11757,7 +11757,7 @@
         <v>0</v>
       </c>
       <c r="K138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L138" t="n">
         <v>0</v>
@@ -11769,22 +11769,22 @@
         <v>0</v>
       </c>
       <c r="O138" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P138" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Q138" t="n">
         <v>0</v>
       </c>
       <c r="R138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
       </c>
       <c r="T138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U138" t="n">
         <v>0</v>
@@ -11811,22 +11811,22 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Trent Noah</t>
+          <t>Trent Burns</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>MIZ</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>ARK@MIZ</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H139" t="n">
@@ -11854,7 +11854,7 @@
         <v>0</v>
       </c>
       <c r="P139" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q139" t="n">
         <v>0</v>
@@ -11893,17 +11893,17 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Tyler Harris</t>
+          <t>Trent Noah</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -11975,32 +11975,32 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Camden Heide</t>
+          <t>Tyler Harris</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>OU@TEX</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>0:15 - 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H141" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K141" t="n">
         <v>0</v>
@@ -12012,25 +12012,25 @@
         <v>0</v>
       </c>
       <c r="N141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O141" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P141" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="Q141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
       </c>
       <c r="T141" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U141" t="n">
         <v>0</v>
@@ -12057,32 +12057,32 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Federiko Federiko</t>
+          <t>Camden Heide</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>TA&amp;M</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>TA&amp;M@LSU</t>
+          <t>OU@TEX</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Final/3OT</t>
+          <t>End of 2nd Half</t>
         </is>
       </c>
       <c r="H142" t="n">
         <v>-1</v>
       </c>
       <c r="I142" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K142" t="n">
         <v>0</v>
@@ -12094,25 +12094,25 @@
         <v>0</v>
       </c>
       <c r="N142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O142" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P142" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="Q142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R142" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
       </c>
       <c r="T142" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U142" t="n">
         <v>0</v>
@@ -12139,7 +12139,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Jacari Lane</t>
+          <t>Federiko Federiko</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -12179,10 +12179,10 @@
         <v>0</v>
       </c>
       <c r="O143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P143" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q143" t="n">
         <v>0</v>
@@ -12221,22 +12221,22 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Max Smith</t>
+          <t>Jacari Lane</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>TA&amp;M</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>TA&amp;M@LSU</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>Final/3OT</t>
         </is>
       </c>
       <c r="H144" t="n">
@@ -12264,7 +12264,7 @@
         <v>0</v>
       </c>
       <c r="P144" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q144" t="n">
         <v>0</v>
@@ -12276,7 +12276,7 @@
         <v>0</v>
       </c>
       <c r="T144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U144" t="n">
         <v>0</v>
@@ -12303,22 +12303,22 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Mazi Mosley</t>
+          <t>Max Smith</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>LSU</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>TA&amp;M@LSU</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Final/3OT</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H145" t="n">
@@ -12346,7 +12346,7 @@
         <v>0</v>
       </c>
       <c r="P145" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q145" t="n">
         <v>0</v>
@@ -12385,67 +12385,149 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
+          <t>Mazi Mosley</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>LSU</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>TA&amp;M@LSU</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Final/3OT</t>
+        </is>
+      </c>
+      <c r="H146" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I146" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" t="n">
+        <v>0</v>
+      </c>
+      <c r="K146" t="n">
+        <v>0</v>
+      </c>
+      <c r="L146" t="n">
+        <v>0</v>
+      </c>
+      <c r="M146" t="n">
+        <v>0</v>
+      </c>
+      <c r="N146" t="n">
+        <v>0</v>
+      </c>
+      <c r="O146" t="n">
+        <v>0</v>
+      </c>
+      <c r="P146" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>0</v>
+      </c>
+      <c r="R146" t="n">
+        <v>1</v>
+      </c>
+      <c r="S146" t="n">
+        <v>0</v>
+      </c>
+      <c r="T146" t="n">
+        <v>1</v>
+      </c>
+      <c r="U146" t="n">
+        <v>0</v>
+      </c>
+      <c r="V146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Undrafted</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
           <t>PJ Carter</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr">
+      <c r="E147" t="inlineStr">
         <is>
           <t>LSU</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr">
+      <c r="F147" t="inlineStr">
         <is>
           <t>TA&amp;M@LSU</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr">
+      <c r="G147" t="inlineStr">
         <is>
           <t>Final/3OT</t>
         </is>
       </c>
-      <c r="H146" t="n">
+      <c r="H147" t="n">
         <v>-3</v>
       </c>
-      <c r="I146" t="n">
-        <v>0</v>
-      </c>
-      <c r="J146" t="n">
-        <v>0</v>
-      </c>
-      <c r="K146" t="n">
-        <v>0</v>
-      </c>
-      <c r="L146" t="n">
-        <v>0</v>
-      </c>
-      <c r="M146" t="n">
-        <v>0</v>
-      </c>
-      <c r="N146" t="n">
-        <v>0</v>
-      </c>
-      <c r="O146" t="n">
-        <v>0</v>
-      </c>
-      <c r="P146" t="n">
+      <c r="I147" t="n">
+        <v>0</v>
+      </c>
+      <c r="J147" t="n">
+        <v>0</v>
+      </c>
+      <c r="K147" t="n">
+        <v>0</v>
+      </c>
+      <c r="L147" t="n">
+        <v>0</v>
+      </c>
+      <c r="M147" t="n">
+        <v>0</v>
+      </c>
+      <c r="N147" t="n">
+        <v>0</v>
+      </c>
+      <c r="O147" t="n">
+        <v>0</v>
+      </c>
+      <c r="P147" t="n">
         <v>7</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
-      <c r="R146" t="n">
-        <v>3</v>
-      </c>
-      <c r="S146" t="n">
-        <v>0</v>
-      </c>
-      <c r="T146" t="n">
-        <v>3</v>
-      </c>
-      <c r="U146" t="n">
-        <v>0</v>
-      </c>
-      <c r="V146" t="n">
+      <c r="Q147" t="n">
+        <v>0</v>
+      </c>
+      <c r="R147" t="n">
+        <v>3</v>
+      </c>
+      <c r="S147" t="n">
+        <v>0</v>
+      </c>
+      <c r="T147" t="n">
+        <v>3</v>
+      </c>
+      <c r="U147" t="n">
+        <v>0</v>
+      </c>
+      <c r="V147" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12505,7 +12587,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C3" t="n">
         <v>5</v>
@@ -12514,11 +12596,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Three Dawg Nite</t>
+          <t>The Backslashers</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C4" t="n">
         <v>5</v>
@@ -12527,27 +12609,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bend Rimmers</t>
+          <t>Three Dawg Nite</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>79</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>The Backslashers</t>
+          <t>Bend Rimmers</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">

--- a/docs/Today_PoohPoints_SEC_ByOwner_2026-03-07.xlsx
+++ b/docs/Today_PoohPoints_SEC_ByOwner_2026-03-07.xlsx
@@ -429,7 +429,7 @@
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="6" customWidth="1" min="8" max="8"/>
     <col width="5" customWidth="1" min="9" max="9"/>
     <col width="5" customWidth="1" min="10" max="10"/>
@@ -592,7 +592,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>End of 2nd Half</t>
+          <t>3:19 - OT</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -620,7 +620,7 @@
         <v>4</v>
       </c>
       <c r="P2" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Q2" t="n">
         <v>5</v>
@@ -1151,12 +1151,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Tramon Mark</t>
+          <t>Derrion Reid</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>OU</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1166,53 +1166,53 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>End of 2nd Half</t>
+          <t>3:19 - OT</t>
         </is>
       </c>
       <c r="H9" t="n">
         <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J9" t="n">
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Derrion Reid</t>
+          <t>Tramon Mark</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>OU</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1248,53 +1248,53 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>End of 2nd Half</t>
+          <t>3:19 - OT</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I10" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="J10" t="n">
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>End of 2nd Half</t>
+          <t>3:19 - OT</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -2163,7 +2163,7 @@
         <v>3</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2172,13 +2172,13 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O21" t="n">
         <v>1</v>
       </c>
       <c r="P21" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Q21" t="n">
         <v>7</v>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>End of 2nd Half</t>
+          <t>3:19 - OT</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>End of 2nd Half</t>
+          <t>3:19 - OT</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -4774,11 +4774,11 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>End of 2nd Half</t>
+          <t>3:19 - OT</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I53" t="n">
         <v>21</v>
@@ -4802,13 +4802,13 @@
         <v>1</v>
       </c>
       <c r="P53" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q53" t="n">
         <v>8</v>
       </c>
       <c r="R53" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="S53" t="n">
         <v>2</v>
@@ -4856,14 +4856,14 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>End of 2nd Half</t>
+          <t>3:19 - OT</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I54" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J54" t="n">
         <v>5</v>
@@ -4884,13 +4884,13 @@
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q54" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R54" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S54" t="n">
         <v>6</v>
@@ -5266,35 +5266,35 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>End of 2nd Half</t>
+          <t>3:19 - OT</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I59" t="n">
         <v>18</v>
       </c>
       <c r="J59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K59" t="n">
         <v>6</v>
       </c>
       <c r="L59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O59" t="n">
         <v>2</v>
       </c>
       <c r="P59" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Q59" t="n">
         <v>5</v>
@@ -5333,56 +5333,56 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Rueben Chinyelu</t>
+          <t>Mohamed Wague</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>FLA</t>
+          <t>OU</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>FLA@UK</t>
+          <t>OU@TEX</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>3:19 - OT</t>
         </is>
       </c>
       <c r="H60" t="n">
         <v>13</v>
       </c>
       <c r="I60" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J60" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M60" t="n">
         <v>1</v>
       </c>
       <c r="N60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P60" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="Q60" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R60" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -5391,10 +5391,10 @@
         <v>0</v>
       </c>
       <c r="U60" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="V60" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -5415,56 +5415,56 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Mohamed Wague</t>
+          <t>Rueben Chinyelu</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>OU</t>
+          <t>FLA</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>OU@TEX</t>
+          <t>FLA@UK</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>End of 2nd Half</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I61" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="J61" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
         <v>1</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O61" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P61" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="Q61" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R61" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -5473,10 +5473,10 @@
         <v>0</v>
       </c>
       <c r="U61" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="V61" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="62">
@@ -6332,7 +6332,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>End of 2nd Half</t>
+          <t>3:19 - OT</t>
         </is>
       </c>
       <c r="H72" t="n">
@@ -6360,7 +6360,7 @@
         <v>3</v>
       </c>
       <c r="P72" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="Q72" t="n">
         <v>4</v>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>End of 2nd Half</t>
+          <t>3:19 - OT</t>
         </is>
       </c>
       <c r="H104" t="n">
@@ -9284,7 +9284,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>End of 2nd Half</t>
+          <t>3:19 - OT</t>
         </is>
       </c>
       <c r="H108" t="n">
@@ -9312,7 +9312,7 @@
         <v>3</v>
       </c>
       <c r="P108" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Q108" t="n">
         <v>1</v>
@@ -11170,7 +11170,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>End of 2nd Half</t>
+          <t>3:19 - OT</t>
         </is>
       </c>
       <c r="H131" t="n">
@@ -11580,7 +11580,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>End of 2nd Half</t>
+          <t>3:19 - OT</t>
         </is>
       </c>
       <c r="H136" t="n">
@@ -11744,7 +11744,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>End of 2nd Half</t>
+          <t>3:19 - OT</t>
         </is>
       </c>
       <c r="H138" t="n">
@@ -12072,7 +12072,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>End of 2nd Half</t>
+          <t>3:19 - OT</t>
         </is>
       </c>
       <c r="H142" t="n">
@@ -12574,7 +12574,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C2" t="n">
         <v>5</v>

--- a/docs/Today_PoohPoints_SEC_ByOwner_2026-03-07.xlsx
+++ b/docs/Today_PoohPoints_SEC_ByOwner_2026-03-07.xlsx
@@ -592,7 +592,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>3:19 - OT</t>
+          <t>End of OT</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -620,7 +620,7 @@
         <v>4</v>
       </c>
       <c r="P2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Q2" t="n">
         <v>5</v>
@@ -905,68 +905,68 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>James Scott</t>
+          <t>Derrion Reid</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MISS</t>
+          <t>OU</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SC@MISS</t>
+          <t>OU@TEX</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>End of OT</t>
         </is>
       </c>
       <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="n">
         <v>11</v>
       </c>
-      <c r="I6" t="n">
-        <v>7</v>
-      </c>
       <c r="J6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O6" t="n">
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -987,17 +987,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Jeremiah Wilkinson</t>
+          <t>James Scott</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>MISS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>SC@MISS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1009,46 +1009,46 @@
         <v>11</v>
       </c>
       <c r="I7" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -1069,17 +1069,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Devin McGlockton</t>
+          <t>Jeremiah Wilkinson</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>VAN</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>VAN@TENN</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1088,49 +1088,49 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I8" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="U8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -1151,32 +1151,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Derrion Reid</t>
+          <t>Devin McGlockton</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>OU</t>
+          <t>VAN</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>OU@TEX</t>
+          <t>VAN@TENN</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>3:19 - OT</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I9" t="n">
         <v>8</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K9" t="n">
         <v>1</v>
@@ -1191,16 +1191,16 @@
         <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P9" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1209,10 +1209,10 @@
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="V9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -1248,14 +1248,14 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3:19 - OT</t>
+          <t>End of OT</t>
         </is>
       </c>
       <c r="H10" t="n">
         <v>7</v>
       </c>
       <c r="I10" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J10" t="n">
         <v>2</v>
@@ -1276,25 +1276,25 @@
         <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U10" t="n">
         <v>7</v>
       </c>
       <c r="V10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -2150,17 +2150,17 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>3:19 - OT</t>
+          <t>End of OT</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I21" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K21" t="n">
         <v>2</v>
@@ -2178,25 +2178,25 @@
         <v>1</v>
       </c>
       <c r="P21" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="Q21" t="n">
         <v>7</v>
       </c>
       <c r="R21" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U21" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V21" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>3:19 - OT</t>
+          <t>End of OT</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>3:19 - OT</t>
+          <t>End of OT</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -3897,10 +3897,10 @@
         <v>1</v>
       </c>
       <c r="O42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P42" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -4774,11 +4774,11 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>3:19 - OT</t>
+          <t>End of OT</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I53" t="n">
         <v>21</v>
@@ -4787,7 +4787,7 @@
         <v>2</v>
       </c>
       <c r="K53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L53" t="n">
         <v>4</v>
@@ -4802,7 +4802,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="Q53" t="n">
         <v>8</v>
@@ -4856,17 +4856,17 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>3:19 - OT</t>
+          <t>End of OT</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I54" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J54" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K54" t="n">
         <v>2</v>
@@ -4881,22 +4881,22 @@
         <v>2</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P54" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="Q54" t="n">
+        <v>8</v>
+      </c>
+      <c r="R54" t="n">
+        <v>25</v>
+      </c>
+      <c r="S54" t="n">
         <v>7</v>
       </c>
-      <c r="R54" t="n">
-        <v>21</v>
-      </c>
-      <c r="S54" t="n">
-        <v>6</v>
-      </c>
       <c r="T54" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="U54" t="n">
         <v>7</v>
@@ -5169,68 +5169,68 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Blue Cain</t>
+          <t>Dailyn Swain</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>UGA@MSST</t>
+          <t>OU@TEX</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Final</t>
+          <t>End of OT</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I58" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K58" t="n">
+        <v>8</v>
+      </c>
+      <c r="L58" t="n">
+        <v>3</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>3</v>
+      </c>
+      <c r="O58" t="n">
+        <v>2</v>
+      </c>
+      <c r="P58" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q58" t="n">
         <v>5</v>
       </c>
-      <c r="L58" t="n">
-        <v>2</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" t="n">
-        <v>1</v>
-      </c>
-      <c r="O58" t="n">
-        <v>3</v>
-      </c>
-      <c r="P58" t="n">
-        <v>29</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>4</v>
-      </c>
       <c r="R58" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U58" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="V58" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59">
@@ -5251,68 +5251,68 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Dailyn Swain</t>
+          <t>Blue Cain</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>OU@TEX</t>
+          <t>UGA@MSST</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>3:19 - OT</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="H59" t="n">
         <v>25</v>
       </c>
       <c r="I59" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J59" t="n">
         <v>6</v>
       </c>
       <c r="K59" t="n">
+        <v>5</v>
+      </c>
+      <c r="L59" t="n">
+        <v>2</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>1</v>
+      </c>
+      <c r="O59" t="n">
+        <v>3</v>
+      </c>
+      <c r="P59" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>4</v>
+      </c>
+      <c r="R59" t="n">
         <v>6</v>
       </c>
-      <c r="L59" t="n">
-        <v>3</v>
-      </c>
-      <c r="M59" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" t="n">
-        <v>3</v>
-      </c>
-      <c r="O59" t="n">
-        <v>2</v>
-      </c>
-      <c r="P59" t="n">
-        <v>38</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>5</v>
-      </c>
-      <c r="R59" t="n">
-        <v>8</v>
-      </c>
       <c r="S59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U59" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="V59" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60">
@@ -5348,17 +5348,17 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>3:19 - OT</t>
+          <t>End of OT</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I60" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J60" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K60" t="n">
         <v>1</v>
@@ -5376,13 +5376,13 @@
         <v>4</v>
       </c>
       <c r="P60" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="Q60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -6332,7 +6332,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>3:19 - OT</t>
+          <t>End of OT</t>
         </is>
       </c>
       <c r="H72" t="n">
@@ -6342,7 +6342,7 @@
         <v>14</v>
       </c>
       <c r="J72" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K72" t="n">
         <v>2</v>
@@ -6354,13 +6354,13 @@
         <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O72" t="n">
         <v>3</v>
       </c>
       <c r="P72" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="Q72" t="n">
         <v>4</v>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>3:19 - OT</t>
+          <t>End of OT</t>
         </is>
       </c>
       <c r="H104" t="n">
@@ -8981,10 +8981,10 @@
         <v>1</v>
       </c>
       <c r="O104" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P104" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Q104" t="n">
         <v>1</v>
@@ -9284,7 +9284,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>3:19 - OT</t>
+          <t>End of OT</t>
         </is>
       </c>
       <c r="H108" t="n">
@@ -9312,7 +9312,7 @@
         <v>3</v>
       </c>
       <c r="P108" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q108" t="n">
         <v>1</v>
@@ -11170,7 +11170,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>3:19 - OT</t>
+          <t>End of OT</t>
         </is>
       </c>
       <c r="H131" t="n">
@@ -11580,7 +11580,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>3:19 - OT</t>
+          <t>End of OT</t>
         </is>
       </c>
       <c r="H136" t="n">
@@ -11744,7 +11744,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>3:19 - OT</t>
+          <t>End of OT</t>
         </is>
       </c>
       <c r="H138" t="n">
@@ -12072,7 +12072,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>3:19 - OT</t>
+          <t>End of OT</t>
         </is>
       </c>
       <c r="H142" t="n">
@@ -12574,7 +12574,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C2" t="n">
         <v>5</v>

--- a/docs/Today_PoohPoints_SEC_ByOwner_2026-03-07.xlsx
+++ b/docs/Today_PoohPoints_SEC_ByOwner_2026-03-07.xlsx
@@ -592,7 +592,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>End of OT</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -920,7 +920,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>End of OT</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>End of OT</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>End of OT</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>End of OT</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>End of OT</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>End of OT</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H53" t="n">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>End of OT</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H54" t="n">
@@ -5184,7 +5184,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>End of OT</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H58" t="n">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>End of OT</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H60" t="n">
@@ -6332,7 +6332,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>End of OT</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H72" t="n">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>End of OT</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H104" t="n">
@@ -9284,7 +9284,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>End of OT</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H108" t="n">
@@ -11170,7 +11170,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>End of OT</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H131" t="n">
@@ -11580,7 +11580,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>End of OT</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H136" t="n">
@@ -11744,7 +11744,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>End of OT</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H138" t="n">
@@ -12072,7 +12072,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>End of OT</t>
+          <t>Final/OT</t>
         </is>
       </c>
       <c r="H142" t="n">
